--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1069,20 +1069,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUSH4)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to KRUSN ~2026-09-14T20:30:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="n"/>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1135,22 +1135,20 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
+          <t>VNSGN -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v/>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-16T16:00:00</t>
+          <t>In transit, ETA 2026-09-18T10:00:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
@@ -1515,20 +1513,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUS05)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to KRINC ~2026-09-17T21:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -2101,20 +2101,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH04)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to THBKK ~2026-09-17T00:00:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2131,7 +2133,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>46281.70833333334</v>
+        <v>46283.95833333334</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2142,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2610N</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -688,11 +688,11 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-28T13:00:00</t>
+          <t>In transit, ETA 2026-09-28T15:00:00</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>46304.83333333334</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>46304.3125</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to IDJKT ~2026-09-24T09:30:00</t>
+          <t>Alongside, departs to IDJKT ~2026-09-24T09:00:00</t>
         </is>
       </c>
       <c r="I5" s="3" t="n"/>
@@ -1119,20 +1119,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to THLCH ~2026-09-25T01:00:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="n"/>
@@ -1196,7 +1198,7 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46305.08333333334</v>
+        <v>46305.375</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1209,7 +1211,7 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46305</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1245,22 +1247,20 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>THBKK (BKK02)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
+          <t>THBKK -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v/>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-23T13:00:00</t>
+          <t>In transit, ETA 2026-09-23T17:00:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-25T00:30:00</t>
+          <t>In transit, ETA 2026-09-25T03:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>46307.375</v>
+        <v>46307.45833333334</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>46306.85416666666</v>
+        <v>46306.9375</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>46300.33333333334</v>
+        <v>46300.54166666666</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46299.625</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1811,20 +1811,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v/>
+          <t>CNSHA (SHAW1)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to THLCH ~2026-09-25T11:00:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -1877,22 +1879,20 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH04)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>THLCH -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v/>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-09-23T14:00:00</t>
+          <t>In transit, ETA 2026-09-25T03:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
@@ -2147,20 +2147,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v/>
+          <t>CNSHA (SHAW1)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to IDJKT ~2026-09-27T12:00:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
@@ -2291,7 +2293,7 @@
         <v/>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46314.0625</v>
+        <v>46314.72916666666</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2588,7 +2590,7 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>46287.58333333334</v>
+        <v>46287.625</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>46288.70833333334</v>
@@ -2635,7 +2637,7 @@
         <v>46290.25</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46290.66666666666</v>
+        <v>46290.625</v>
       </c>
     </row>
     <row r="4">
@@ -2670,13 +2672,13 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>46294.95833333334</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>46295.02083333334</v>
+        <v>46294.97916666666</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>46295.5</v>
+        <v>46295.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -2711,13 +2713,13 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
+        <v>46295.54166666666</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>46295.58333333334</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>46295.625</v>
-      </c>
       <c r="I5" s="3" t="n">
-        <v>46296</v>
+        <v>46295.95833333334</v>
       </c>
     </row>
     <row r="6">
@@ -2752,13 +2754,13 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
+        <v>46297.5</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>46297.54166666666</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>46297.58333333334</v>
-      </c>
       <c r="I6" s="3" t="n">
-        <v>46298.08333333334</v>
+        <v>46298.04166666666</v>
       </c>
     </row>
     <row r="7">
@@ -4269,13 +4271,13 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>46287.5</v>
+        <v>46287.6875</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>46287.66666666666</v>
+        <v>46287.85416666666</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46288.33333333334</v>
+        <v>46288.375</v>
       </c>
     </row>
     <row r="44">
@@ -4310,13 +4312,13 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>46293.54166666666</v>
+        <v>46293.625</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>46293.58333333334</v>
+        <v>46293.66666666666</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46294.25</v>
+        <v>46294.33333333334</v>
       </c>
     </row>
     <row r="45">
@@ -4351,13 +4353,13 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>46294.41666666666</v>
+        <v>46294.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>46294.47916666666</v>
+        <v>46294.5625</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>46294.72916666666</v>
+        <v>46294.8125</v>
       </c>
     </row>
     <row r="46">
@@ -4392,13 +4394,13 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>46295.625</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>46295.6875</v>
+        <v>46295.77083333334</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>46296.10416666666</v>
+        <v>46296.1875</v>
       </c>
     </row>
     <row r="47">
@@ -4433,13 +4435,13 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>46296.375</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46296.39583333334</v>
+        <v>46296.47916666666</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>46297</v>
+        <v>46297.08333333334</v>
       </c>
     </row>
     <row r="48">
@@ -4474,13 +4476,13 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>46301.91666666666</v>
+        <v>46302</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>46302.08333333334</v>
+        <v>46302.16666666666</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>46302.66666666666</v>
+        <v>46302.75</v>
       </c>
     </row>
     <row r="49">
@@ -4515,13 +4517,13 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>46304.3125</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>46304.35416666666</v>
+        <v>46304.4375</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46304.79166666666</v>
       </c>
     </row>
     <row r="50">
@@ -4556,13 +4558,13 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>46304.83333333334</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>46304.91666666666</v>
+        <v>46305</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>46305.91666666666</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="51">
@@ -4597,13 +4599,13 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>46306.125</v>
+        <v>46306.20833333334</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>46306.16666666666</v>
+        <v>46306.25</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>46306.66666666666</v>
+        <v>46306.75</v>
       </c>
     </row>
     <row r="52">
@@ -4638,13 +4640,13 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>46308.47916666666</v>
+        <v>46308.5625</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>46308.64583333334</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>46309.33333333334</v>
+        <v>46309.41666666666</v>
       </c>
     </row>
     <row r="53">
@@ -4679,13 +4681,13 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>46314.54166666666</v>
+        <v>46314.625</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>46314.58333333334</v>
+        <v>46314.66666666666</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>46315.25</v>
+        <v>46315.33333333334</v>
       </c>
     </row>
     <row r="54">
@@ -4720,13 +4722,13 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>46315.41666666666</v>
+        <v>46315.5</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>46315.47916666666</v>
+        <v>46315.5625</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>46315.72916666666</v>
+        <v>46315.8125</v>
       </c>
     </row>
     <row r="55">
@@ -4761,13 +4763,13 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>46316.625</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>46316.6875</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>46317.10416666666</v>
+        <v>46317.1875</v>
       </c>
     </row>
     <row r="56">
@@ -4802,13 +4804,13 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>46317.375</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>46317.39583333334</v>
+        <v>46317.47916666666</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>46318</v>
+        <v>46318.08333333334</v>
       </c>
     </row>
     <row r="57">
@@ -4843,13 +4845,13 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>46322.91666666666</v>
+        <v>46323</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>46323.08333333334</v>
+        <v>46323.16666666666</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>46323.66666666666</v>
+        <v>46323.75</v>
       </c>
     </row>
     <row r="58">
@@ -4884,13 +4886,13 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>46325.3125</v>
+        <v>46325.39583333334</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>46325.35416666666</v>
+        <v>46325.4375</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>46325.70833333334</v>
+        <v>46325.79166666666</v>
       </c>
     </row>
     <row r="59">
@@ -4925,13 +4927,13 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>46325.83333333334</v>
+        <v>46325.91666666666</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>46325.91666666666</v>
+        <v>46326</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>46326.91666666666</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="60">
@@ -4966,13 +4968,13 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>46327.125</v>
+        <v>46327.20833333334</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>46327.16666666666</v>
+        <v>46327.25</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>46327.66666666666</v>
+        <v>46327.75</v>
       </c>
     </row>
     <row r="61">
@@ -5007,13 +5009,13 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>46329.47916666666</v>
+        <v>46329.5625</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>46329.64583333334</v>
+        <v>46329.72916666666</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>46330.33333333334</v>
+        <v>46330.41666666666</v>
       </c>
     </row>
     <row r="62">
@@ -5048,13 +5050,13 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>46335.54166666666</v>
+        <v>46335.625</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>46335.58333333334</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>46336.25</v>
+        <v>46336.33333333334</v>
       </c>
     </row>
     <row r="63">
@@ -5089,13 +5091,13 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>46336.41666666666</v>
+        <v>46336.5</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>46336.47916666666</v>
+        <v>46336.5625</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>46336.72916666666</v>
+        <v>46336.8125</v>
       </c>
     </row>
     <row r="64">
@@ -5130,13 +5132,13 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>46337.625</v>
+        <v>46337.70833333334</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>46337.6875</v>
+        <v>46337.77083333334</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>46338.10416666666</v>
+        <v>46338.1875</v>
       </c>
     </row>
     <row r="65">
@@ -5171,13 +5173,13 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>46338.375</v>
+        <v>46338.45833333334</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>46338.39583333334</v>
+        <v>46338.47916666666</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>46339</v>
+        <v>46339.08333333334</v>
       </c>
     </row>
     <row r="66">
@@ -5212,13 +5214,13 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>46343.91666666666</v>
+        <v>46344</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>46344.08333333334</v>
+        <v>46344.16666666666</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>46344.66666666666</v>
+        <v>46344.75</v>
       </c>
     </row>
     <row r="67">
@@ -5253,13 +5255,13 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>46346.3125</v>
+        <v>46346.39583333334</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>46346.35416666666</v>
+        <v>46346.4375</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>46346.70833333334</v>
+        <v>46346.79166666666</v>
       </c>
     </row>
     <row r="68">
@@ -5294,13 +5296,13 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>46346.83333333334</v>
+        <v>46346.91666666666</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>46346.91666666666</v>
+        <v>46347</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>46347.91666666666</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="69">
@@ -5335,13 +5337,13 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>46348.125</v>
+        <v>46348.20833333334</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>46348.16666666666</v>
+        <v>46348.25</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>46348.66666666666</v>
+        <v>46348.75</v>
       </c>
     </row>
     <row r="70">
@@ -5379,10 +5381,10 @@
         <v>46286.41666666666</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>46288.4375</v>
+        <v>46288.45833333334</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>46289.39583333334</v>
+        <v>46289.375</v>
       </c>
     </row>
     <row r="71">
@@ -5581,13 +5583,13 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>46311.75</v>
+        <v>46311.375</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>46311.79166666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>46313.29166666666</v>
+        <v>46312.91666666666</v>
       </c>
     </row>
     <row r="76">
@@ -5622,13 +5624,13 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>46313.70833333334</v>
+        <v>46313.33333333334</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>46313.77083333334</v>
+        <v>46313.39583333334</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>46314.20833333334</v>
+        <v>46313.75</v>
       </c>
     </row>
     <row r="77">
@@ -5663,13 +5665,13 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>46315.20833333334</v>
+        <v>46314.75</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>46315.41666666666</v>
+        <v>46315</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>46316.41666666666</v>
+        <v>46315.83333333334</v>
       </c>
     </row>
     <row r="78">
@@ -5704,13 +5706,13 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>46324.04166666666</v>
+        <v>46322.45833333334</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>46324.125</v>
+        <v>46322.54166666666</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>46325.75</v>
+        <v>46324.29166666666</v>
       </c>
     </row>
     <row r="79">
@@ -5745,13 +5747,13 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>46326.75</v>
+        <v>46325.29166666666</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>46326.83333333334</v>
+        <v>46325.375</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>46327.75</v>
+        <v>46326.20833333334</v>
       </c>
     </row>
     <row r="80">
@@ -5786,13 +5788,13 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>46330.79166666666</v>
+        <v>46329.5</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>46330.95833333334</v>
+        <v>46329.66666666666</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>46331.79166666666</v>
+        <v>46330.41666666666</v>
       </c>
     </row>
     <row r="81">
@@ -5827,13 +5829,13 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>46337.25</v>
+        <v>46335.41666666666</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>46337.41666666666</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>46338.41666666666</v>
+        <v>46336.5</v>
       </c>
     </row>
     <row r="82">
@@ -6691,10 +6693,10 @@
         <v>46289.83333333334</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>46291</v>
+        <v>46289.95833333334</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>46292.66666666666</v>
+        <v>46292.52083333334</v>
       </c>
     </row>
     <row r="103">
@@ -6729,13 +6731,13 @@
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>46295.14583333334</v>
+        <v>46295</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>46295.3125</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>46296.14583333334</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="104">
@@ -6770,13 +6772,13 @@
         </is>
       </c>
       <c r="G104" s="3" t="n">
-        <v>46298.6875</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>46298.75</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>46299.25</v>
+        <v>46299.10416666666</v>
       </c>
     </row>
     <row r="105">
@@ -6811,13 +6813,13 @@
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>46299.47916666666</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>46299.52083333334</v>
+        <v>46299.375</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>46300.02083333334</v>
+        <v>46299.875</v>
       </c>
     </row>
     <row r="106">
@@ -6852,13 +6854,13 @@
         </is>
       </c>
       <c r="G106" s="3" t="n">
-        <v>46303.3125</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>46303.35416666666</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>46304.02083333334</v>
+        <v>46303.875</v>
       </c>
     </row>
     <row r="107">
@@ -6893,13 +6895,13 @@
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>46305.10416666666</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>46305.14583333334</v>
+        <v>46305</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>46305.72916666666</v>
+        <v>46305.58333333334</v>
       </c>
     </row>
     <row r="108">
@@ -6934,13 +6936,13 @@
         </is>
       </c>
       <c r="G108" s="3" t="n">
-        <v>46305.72986111111</v>
+        <v>46305.58402777778</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>46305.73055555556</v>
+        <v>46305.58472222222</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>46305.73125</v>
+        <v>46305.58541666667</v>
       </c>
     </row>
     <row r="109">
@@ -11526,13 +11528,13 @@
         </is>
       </c>
       <c r="G220" s="3" t="n">
-        <v>46290.29166666666</v>
+        <v>46290.39583333334</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>46290.35416666666</v>
+        <v>46290.45833333334</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>46290.85416666666</v>
+        <v>46290.95833333334</v>
       </c>
     </row>
     <row r="221">
@@ -11567,13 +11569,13 @@
         </is>
       </c>
       <c r="G221" s="3" t="n">
-        <v>46291.70833333334</v>
+        <v>46292</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>46291.75</v>
+        <v>46292.04166666666</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>46292.375</v>
+        <v>46292.66666666666</v>
       </c>
     </row>
     <row r="222">
@@ -11608,13 +11610,13 @@
         </is>
       </c>
       <c r="G222" s="3" t="n">
-        <v>46294.70833333334</v>
+        <v>46295</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>46294.75</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>46295.75</v>
+        <v>46296.04166666666</v>
       </c>
     </row>
     <row r="223">
@@ -11649,13 +11651,13 @@
         </is>
       </c>
       <c r="G223" s="3" t="n">
-        <v>46296.04166666666</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>46296.10416666666</v>
+        <v>46296.39583333334</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46296.72916666666</v>
       </c>
     </row>
     <row r="224">
@@ -11690,13 +11692,13 @@
         </is>
       </c>
       <c r="G224" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.625</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>46299.39583333334</v>
+        <v>46299.6875</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>46299.89583333334</v>
+        <v>46300.1875</v>
       </c>
     </row>
     <row r="225">
@@ -11731,13 +11733,13 @@
         </is>
       </c>
       <c r="G225" s="3" t="n">
-        <v>46302.25</v>
+        <v>46302.54166666666</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>46302.41666666666</v>
+        <v>46302.70833333334</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>46303.04166666666</v>
+        <v>46303.33333333334</v>
       </c>
     </row>
     <row r="226">
@@ -11772,13 +11774,13 @@
         </is>
       </c>
       <c r="G226" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46305</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>46304.75</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>46304.95833333334</v>
+        <v>46305.25</v>
       </c>
     </row>
     <row r="227">
@@ -11813,13 +11815,13 @@
         </is>
       </c>
       <c r="G227" s="3" t="n">
-        <v>46305.08333333334</v>
+        <v>46305.375</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.5</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>46306.66666666666</v>
+        <v>46306.95833333334</v>
       </c>
     </row>
     <row r="228">
@@ -11854,13 +11856,13 @@
         </is>
       </c>
       <c r="G228" s="3" t="n">
-        <v>46306.875</v>
+        <v>46307.16666666666</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>46306.91666666666</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>46307.25</v>
+        <v>46307.54166666666</v>
       </c>
     </row>
     <row r="229">
@@ -11895,13 +11897,13 @@
         </is>
       </c>
       <c r="G229" s="3" t="n">
-        <v>46311.33333333334</v>
+        <v>46311.625</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>46311.375</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>46311.83333333334</v>
+        <v>46312.125</v>
       </c>
     </row>
     <row r="230">
@@ -11936,13 +11938,13 @@
         </is>
       </c>
       <c r="G230" s="3" t="n">
-        <v>46312.91666666666</v>
+        <v>46313.20833333334</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.25</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>46313.54166666666</v>
+        <v>46313.83333333334</v>
       </c>
     </row>
     <row r="231">
@@ -15667,13 +15669,13 @@
         </is>
       </c>
       <c r="G321" s="3" t="n">
-        <v>46287.66666666666</v>
+        <v>46287.60416666666</v>
       </c>
       <c r="H321" s="3" t="n">
-        <v>46287.70833333334</v>
+        <v>46288.33333333334</v>
       </c>
       <c r="I321" s="3" t="n">
-        <v>46288.20833333334</v>
+        <v>46288.66666666666</v>
       </c>
     </row>
     <row r="322">
@@ -15708,13 +15710,13 @@
         </is>
       </c>
       <c r="G322" s="3" t="n">
-        <v>46290.02083333334</v>
+        <v>46290.125</v>
       </c>
       <c r="H322" s="3" t="n">
-        <v>46290.1875</v>
+        <v>46290.29166666666</v>
       </c>
       <c r="I322" s="3" t="n">
-        <v>46290.875</v>
+        <v>46290.95833333334</v>
       </c>
     </row>
     <row r="323">
@@ -15749,13 +15751,13 @@
         </is>
       </c>
       <c r="G323" s="3" t="n">
-        <v>46296.08333333334</v>
+        <v>46296.16666666666</v>
       </c>
       <c r="H323" s="3" t="n">
-        <v>46296.125</v>
+        <v>46296.20833333334</v>
       </c>
       <c r="I323" s="3" t="n">
-        <v>46296.79166666666</v>
+        <v>46296.875</v>
       </c>
     </row>
     <row r="324">
@@ -15790,13 +15792,13 @@
         </is>
       </c>
       <c r="G324" s="3" t="n">
-        <v>46296.95833333334</v>
+        <v>46297.04166666666</v>
       </c>
       <c r="H324" s="3" t="n">
-        <v>46297.02083333334</v>
+        <v>46297.10416666666</v>
       </c>
       <c r="I324" s="3" t="n">
-        <v>46297.27083333334</v>
+        <v>46297.35416666666</v>
       </c>
     </row>
     <row r="325">
@@ -15831,13 +15833,13 @@
         </is>
       </c>
       <c r="G325" s="3" t="n">
-        <v>46298.16666666666</v>
+        <v>46298.25</v>
       </c>
       <c r="H325" s="3" t="n">
-        <v>46298.22916666666</v>
+        <v>46298.3125</v>
       </c>
       <c r="I325" s="3" t="n">
-        <v>46298.64583333334</v>
+        <v>46298.72916666666</v>
       </c>
     </row>
     <row r="326">
@@ -15872,13 +15874,13 @@
         </is>
       </c>
       <c r="G326" s="3" t="n">
-        <v>46298.91666666666</v>
+        <v>46299</v>
       </c>
       <c r="H326" s="3" t="n">
-        <v>46298.9375</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="I326" s="3" t="n">
-        <v>46299.54166666666</v>
+        <v>46299.625</v>
       </c>
     </row>
     <row r="327">
@@ -15913,13 +15915,13 @@
         </is>
       </c>
       <c r="G327" s="3" t="n">
-        <v>46304.45833333334</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="H327" s="3" t="n">
-        <v>46304.625</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="I327" s="3" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.29166666666</v>
       </c>
     </row>
     <row r="328">
@@ -15954,13 +15956,13 @@
         </is>
       </c>
       <c r="G328" s="3" t="n">
-        <v>46306.85416666666</v>
+        <v>46306.9375</v>
       </c>
       <c r="H328" s="3" t="n">
-        <v>46306.89583333334</v>
+        <v>46306.97916666666</v>
       </c>
       <c r="I328" s="3" t="n">
-        <v>46307.25</v>
+        <v>46307.33333333334</v>
       </c>
     </row>
     <row r="329">
@@ -15995,13 +15997,13 @@
         </is>
       </c>
       <c r="G329" s="3" t="n">
-        <v>46307.375</v>
+        <v>46307.45833333334</v>
       </c>
       <c r="H329" s="3" t="n">
-        <v>46307.45833333334</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="I329" s="3" t="n">
-        <v>46308.45833333334</v>
+        <v>46308.54166666666</v>
       </c>
     </row>
     <row r="330">
@@ -16036,13 +16038,13 @@
         </is>
       </c>
       <c r="G330" s="3" t="n">
-        <v>46308.66666666666</v>
+        <v>46308.75</v>
       </c>
       <c r="H330" s="3" t="n">
-        <v>46308.70833333334</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="I330" s="3" t="n">
-        <v>46309.20833333334</v>
+        <v>46309.29166666666</v>
       </c>
     </row>
     <row r="331">
@@ -16077,13 +16079,13 @@
         </is>
       </c>
       <c r="G331" s="3" t="n">
-        <v>46311.02083333334</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="H331" s="3" t="n">
-        <v>46311.1875</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="I331" s="3" t="n">
-        <v>46311.875</v>
+        <v>46311.95833333334</v>
       </c>
     </row>
     <row r="332">
@@ -16118,13 +16120,13 @@
         </is>
       </c>
       <c r="G332" s="3" t="n">
-        <v>46317.08333333334</v>
+        <v>46317.16666666666</v>
       </c>
       <c r="H332" s="3" t="n">
-        <v>46317.125</v>
+        <v>46317.20833333334</v>
       </c>
       <c r="I332" s="3" t="n">
-        <v>46317.79166666666</v>
+        <v>46317.875</v>
       </c>
     </row>
     <row r="333">
@@ -16159,13 +16161,13 @@
         </is>
       </c>
       <c r="G333" s="3" t="n">
-        <v>46317.95833333334</v>
+        <v>46318.04166666666</v>
       </c>
       <c r="H333" s="3" t="n">
-        <v>46318.02083333334</v>
+        <v>46318.10416666666</v>
       </c>
       <c r="I333" s="3" t="n">
-        <v>46318.27083333334</v>
+        <v>46318.35416666666</v>
       </c>
     </row>
     <row r="334">
@@ -16200,13 +16202,13 @@
         </is>
       </c>
       <c r="G334" s="3" t="n">
-        <v>46319.16666666666</v>
+        <v>46319.25</v>
       </c>
       <c r="H334" s="3" t="n">
-        <v>46319.22916666666</v>
+        <v>46319.3125</v>
       </c>
       <c r="I334" s="3" t="n">
-        <v>46319.64583333334</v>
+        <v>46319.72916666666</v>
       </c>
     </row>
     <row r="335">
@@ -16241,13 +16243,13 @@
         </is>
       </c>
       <c r="G335" s="3" t="n">
-        <v>46319.91666666666</v>
+        <v>46320</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>46319.9375</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="I335" s="3" t="n">
-        <v>46320.54166666666</v>
+        <v>46320.625</v>
       </c>
     </row>
     <row r="336">
@@ -16282,13 +16284,13 @@
         </is>
       </c>
       <c r="G336" s="3" t="n">
-        <v>46325.45833333334</v>
+        <v>46325.54166666666</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>46325.625</v>
+        <v>46325.70833333334</v>
       </c>
       <c r="I336" s="3" t="n">
-        <v>46326.20833333334</v>
+        <v>46326.29166666666</v>
       </c>
     </row>
     <row r="337">
@@ -16323,13 +16325,13 @@
         </is>
       </c>
       <c r="G337" s="3" t="n">
-        <v>46327.85416666666</v>
+        <v>46327.9375</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>46327.89583333334</v>
+        <v>46327.97916666666</v>
       </c>
       <c r="I337" s="3" t="n">
-        <v>46328.25</v>
+        <v>46328.33333333334</v>
       </c>
     </row>
     <row r="338">
@@ -16364,13 +16366,13 @@
         </is>
       </c>
       <c r="G338" s="3" t="n">
-        <v>46328.375</v>
+        <v>46328.45833333334</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>46328.45833333334</v>
+        <v>46328.54166666666</v>
       </c>
       <c r="I338" s="3" t="n">
-        <v>46329.45833333334</v>
+        <v>46329.54166666666</v>
       </c>
     </row>
     <row r="339">
@@ -16405,13 +16407,13 @@
         </is>
       </c>
       <c r="G339" s="3" t="n">
-        <v>46329.66666666666</v>
+        <v>46329.75</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>46329.70833333334</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="I339" s="3" t="n">
-        <v>46330.20833333334</v>
+        <v>46330.29166666666</v>
       </c>
     </row>
     <row r="340">
@@ -16446,13 +16448,13 @@
         </is>
       </c>
       <c r="G340" s="3" t="n">
-        <v>46332.02083333334</v>
+        <v>46332.10416666666</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>46332.1875</v>
+        <v>46332.27083333334</v>
       </c>
       <c r="I340" s="3" t="n">
-        <v>46332.875</v>
+        <v>46332.95833333334</v>
       </c>
     </row>
     <row r="341">
@@ -17600,7 +17602,7 @@
         <v>46289.25</v>
       </c>
       <c r="I368" s="3" t="n">
-        <v>46290.25</v>
+        <v>46291.66666666666</v>
       </c>
     </row>
     <row r="369">
@@ -17635,13 +17637,13 @@
         </is>
       </c>
       <c r="G369" s="3" t="n">
-        <v>46290.375</v>
+        <v>46291.77083333334</v>
       </c>
       <c r="H369" s="3" t="n">
-        <v>46290.41666666666</v>
+        <v>46291.8125</v>
       </c>
       <c r="I369" s="3" t="n">
-        <v>46291.91666666666</v>
+        <v>46291.97916666666</v>
       </c>
     </row>
     <row r="370">
@@ -17676,13 +17678,13 @@
         </is>
       </c>
       <c r="G370" s="3" t="n">
-        <v>46294.75</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>46294.79166666666</v>
+        <v>46295</v>
       </c>
       <c r="I370" s="3" t="n">
-        <v>46295.16666666666</v>
+        <v>46295.375</v>
       </c>
     </row>
     <row r="371">
@@ -17717,13 +17719,13 @@
         </is>
       </c>
       <c r="G371" s="3" t="n">
-        <v>46297.125</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>46297.29166666666</v>
+        <v>46297.5</v>
       </c>
       <c r="I371" s="3" t="n">
-        <v>46297.83333333334</v>
+        <v>46298.04166666666</v>
       </c>
     </row>
     <row r="372">
@@ -17758,13 +17760,13 @@
         </is>
       </c>
       <c r="G372" s="3" t="n">
-        <v>46299.625</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>46299.66666666666</v>
+        <v>46299.875</v>
       </c>
       <c r="I372" s="3" t="n">
-        <v>46299.91666666666</v>
+        <v>46300.125</v>
       </c>
     </row>
     <row r="373">
@@ -17799,13 +17801,13 @@
         </is>
       </c>
       <c r="G373" s="3" t="n">
-        <v>46300.33333333334</v>
+        <v>46300.54166666666</v>
       </c>
       <c r="H373" s="3" t="n">
-        <v>46300.45833333334</v>
+        <v>46300.66666666666</v>
       </c>
       <c r="I373" s="3" t="n">
-        <v>46301.58333333334</v>
+        <v>46301.79166666666</v>
       </c>
     </row>
     <row r="374">
@@ -17840,13 +17842,13 @@
         </is>
       </c>
       <c r="G374" s="3" t="n">
-        <v>46301.91666666666</v>
+        <v>46302.125</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>46301.95833333334</v>
+        <v>46302.16666666666</v>
       </c>
       <c r="I374" s="3" t="n">
-        <v>46302.29166666666</v>
+        <v>46302.5</v>
       </c>
     </row>
     <row r="375">
@@ -17881,13 +17883,13 @@
         </is>
       </c>
       <c r="G375" s="3" t="n">
-        <v>46306.16666666666</v>
+        <v>46306.375</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>46306.20833333334</v>
+        <v>46306.41666666666</v>
       </c>
       <c r="I375" s="3" t="n">
-        <v>46306.625</v>
+        <v>46306.83333333334</v>
       </c>
     </row>
     <row r="376">
@@ -17922,13 +17924,13 @@
         </is>
       </c>
       <c r="G376" s="3" t="n">
-        <v>46306.875</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>46306.875</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="I376" s="3" t="n">
-        <v>46307.25</v>
+        <v>46307.45833333334</v>
       </c>
     </row>
     <row r="377">
@@ -17963,13 +17965,13 @@
         </is>
       </c>
       <c r="G377" s="3" t="n">
-        <v>46308.78541666667</v>
+        <v>46308.99375</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>46308.78541666667</v>
+        <v>46308.99375</v>
       </c>
       <c r="I377" s="3" t="n">
-        <v>46309.03541666667</v>
+        <v>46309.24375</v>
       </c>
     </row>
     <row r="378">
@@ -25100,10 +25102,10 @@
         <v>46288.54166666666</v>
       </c>
       <c r="H551" s="3" t="n">
-        <v>46290.75</v>
+        <v>46291.5</v>
       </c>
       <c r="I551" s="3" t="n">
-        <v>46291.75</v>
+        <v>46292.5</v>
       </c>
     </row>
     <row r="552">
@@ -25138,13 +25140,13 @@
         </is>
       </c>
       <c r="G552" s="3" t="n">
-        <v>46298.75</v>
+        <v>46299.5</v>
       </c>
       <c r="H552" s="3" t="n">
-        <v>46298.79166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="I552" s="3" t="n">
-        <v>46300.66666666666</v>
+        <v>46301.41666666666</v>
       </c>
     </row>
     <row r="553">
@@ -25179,13 +25181,13 @@
         </is>
       </c>
       <c r="G553" s="3" t="n">
-        <v>46301.66666666666</v>
+        <v>46302.41666666666</v>
       </c>
       <c r="H553" s="3" t="n">
-        <v>46301.75</v>
+        <v>46302.5</v>
       </c>
       <c r="I553" s="3" t="n">
-        <v>46302.75</v>
+        <v>46303.5</v>
       </c>
     </row>
     <row r="554">
@@ -25220,13 +25222,13 @@
         </is>
       </c>
       <c r="G554" s="3" t="n">
-        <v>46306</v>
+        <v>46306.75</v>
       </c>
       <c r="H554" s="3" t="n">
-        <v>46306.16666666666</v>
+        <v>46306.91666666666</v>
       </c>
       <c r="I554" s="3" t="n">
-        <v>46307</v>
+        <v>46307.75</v>
       </c>
     </row>
     <row r="555">
@@ -25261,13 +25263,13 @@
         </is>
       </c>
       <c r="G555" s="3" t="n">
-        <v>46311.58333333334</v>
+        <v>46312.33333333334</v>
       </c>
       <c r="H555" s="3" t="n">
-        <v>46312.75</v>
+        <v>46313.5</v>
       </c>
       <c r="I555" s="3" t="n">
-        <v>46313.75</v>
+        <v>46314.5</v>
       </c>
     </row>
     <row r="556">
@@ -25302,13 +25304,13 @@
         </is>
       </c>
       <c r="G556" s="3" t="n">
-        <v>46315.16666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="H556" s="3" t="n">
-        <v>46315.20833333334</v>
+        <v>46315.95833333334</v>
       </c>
       <c r="I556" s="3" t="n">
-        <v>46316.83333333334</v>
+        <v>46317.58333333334</v>
       </c>
     </row>
     <row r="557">
@@ -25343,13 +25345,13 @@
         </is>
       </c>
       <c r="G557" s="3" t="n">
-        <v>46317.125</v>
+        <v>46317.875</v>
       </c>
       <c r="H557" s="3" t="n">
-        <v>46317.1875</v>
+        <v>46317.9375</v>
       </c>
       <c r="I557" s="3" t="n">
-        <v>46317.66666666666</v>
+        <v>46318.41666666666</v>
       </c>
     </row>
     <row r="558">
@@ -25384,13 +25386,13 @@
         </is>
       </c>
       <c r="G558" s="3" t="n">
-        <v>46318.66666666666</v>
+        <v>46319.41666666666</v>
       </c>
       <c r="H558" s="3" t="n">
-        <v>46319.83333333334</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="I558" s="3" t="n">
-        <v>46320.83333333334</v>
+        <v>46321.58333333334</v>
       </c>
     </row>
     <row r="559">
@@ -25425,13 +25427,13 @@
         </is>
       </c>
       <c r="G559" s="3" t="n">
-        <v>46327.83333333334</v>
+        <v>46328.58333333334</v>
       </c>
       <c r="H559" s="3" t="n">
-        <v>46327.91666666666</v>
+        <v>46328.66666666666</v>
       </c>
       <c r="I559" s="3" t="n">
-        <v>46329.75</v>
+        <v>46330.5</v>
       </c>
     </row>
     <row r="560">
@@ -25466,13 +25468,13 @@
         </is>
       </c>
       <c r="G560" s="3" t="n">
-        <v>46330.75</v>
+        <v>46331.5</v>
       </c>
       <c r="H560" s="3" t="n">
-        <v>46330.83333333334</v>
+        <v>46331.58333333334</v>
       </c>
       <c r="I560" s="3" t="n">
-        <v>46331.91666666666</v>
+        <v>46332.66666666666</v>
       </c>
     </row>
     <row r="561">
@@ -25507,13 +25509,13 @@
         </is>
       </c>
       <c r="G561" s="3" t="n">
-        <v>46335.41666666666</v>
+        <v>46336.16666666666</v>
       </c>
       <c r="H561" s="3" t="n">
-        <v>46335.5</v>
+        <v>46336.25</v>
       </c>
       <c r="I561" s="3" t="n">
-        <v>46336.33333333334</v>
+        <v>46337.08333333334</v>
       </c>
     </row>
     <row r="562">
@@ -25548,13 +25550,13 @@
         </is>
       </c>
       <c r="G562" s="3" t="n">
-        <v>46341.25</v>
+        <v>46342</v>
       </c>
       <c r="H562" s="3" t="n">
-        <v>46342.25</v>
+        <v>46343</v>
       </c>
       <c r="I562" s="3" t="n">
-        <v>46343.25</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="563">
@@ -26819,13 +26821,13 @@
         </is>
       </c>
       <c r="G593" s="3" t="n">
-        <v>46290.625</v>
+        <v>46290.75</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>46290.66666666666</v>
+        <v>46291.33333333334</v>
       </c>
       <c r="I593" s="3" t="n">
-        <v>46292.33333333334</v>
+        <v>46293.02083333334</v>
       </c>
     </row>
     <row r="594">
@@ -26860,13 +26862,13 @@
         </is>
       </c>
       <c r="G594" s="3" t="n">
-        <v>46294.75</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="H594" s="3" t="n">
-        <v>46294.91666666666</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="I594" s="3" t="n">
-        <v>46295.58333333334</v>
+        <v>46296.25</v>
       </c>
     </row>
     <row r="595">
@@ -26901,13 +26903,13 @@
         </is>
       </c>
       <c r="G595" s="3" t="n">
-        <v>46297.91666666666</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="H595" s="3" t="n">
-        <v>46297.97916666666</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="I595" s="3" t="n">
-        <v>46298.47916666666</v>
+        <v>46299.14583333334</v>
       </c>
     </row>
     <row r="596">
@@ -26942,13 +26944,13 @@
         </is>
       </c>
       <c r="G596" s="3" t="n">
-        <v>46298.60416666666</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="H596" s="3" t="n">
-        <v>46298.72916666666</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="I596" s="3" t="n">
-        <v>46299.1875</v>
+        <v>46299.85416666666</v>
       </c>
     </row>
     <row r="597">
@@ -26983,13 +26985,13 @@
         </is>
       </c>
       <c r="G597" s="3" t="n">
-        <v>46302.27083333334</v>
+        <v>46302.9375</v>
       </c>
       <c r="H597" s="3" t="n">
-        <v>46302.3125</v>
+        <v>46302.97916666666</v>
       </c>
       <c r="I597" s="3" t="n">
-        <v>46302.97916666666</v>
+        <v>46303.64583333334</v>
       </c>
     </row>
     <row r="598">
@@ -27024,13 +27026,13 @@
         </is>
       </c>
       <c r="G598" s="3" t="n">
-        <v>46304.0625</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="H598" s="3" t="n">
-        <v>46304.10416666666</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="I598" s="3" t="n">
-        <v>46304.6875</v>
+        <v>46305.35416666666</v>
       </c>
     </row>
     <row r="599">
@@ -27065,13 +27067,13 @@
         </is>
       </c>
       <c r="G599" s="3" t="n">
-        <v>46304.875</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="H599" s="3" t="n">
-        <v>46304.9375</v>
+        <v>46305.60416666666</v>
       </c>
       <c r="I599" s="3" t="n">
-        <v>46305.27083333334</v>
+        <v>46305.9375</v>
       </c>
     </row>
     <row r="600">
@@ -27106,13 +27108,13 @@
         </is>
       </c>
       <c r="G600" s="3" t="n">
-        <v>46306.5625</v>
+        <v>46307.22916666666</v>
       </c>
       <c r="H600" s="3" t="n">
-        <v>46306.72916666666</v>
+        <v>46307.39583333334</v>
       </c>
       <c r="I600" s="3" t="n">
-        <v>46307.22916666666</v>
+        <v>46307.89583333334</v>
       </c>
     </row>
     <row r="601">
@@ -27147,13 +27149,13 @@
         </is>
       </c>
       <c r="G601" s="3" t="n">
-        <v>46311.39583333334</v>
+        <v>46312.0625</v>
       </c>
       <c r="H601" s="3" t="n">
-        <v>46311.5625</v>
+        <v>46312.22916666666</v>
       </c>
       <c r="I601" s="3" t="n">
-        <v>46312.39583333334</v>
+        <v>46313.0625</v>
       </c>
     </row>
     <row r="602">
@@ -27188,13 +27190,13 @@
         </is>
       </c>
       <c r="G602" s="3" t="n">
-        <v>46314.0625</v>
+        <v>46314.72916666666</v>
       </c>
       <c r="H602" s="3" t="n">
-        <v>46314.10416666666</v>
+        <v>46314.77083333334</v>
       </c>
       <c r="I602" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46315.60416666666</v>
       </c>
     </row>
     <row r="603">
@@ -27229,13 +27231,13 @@
         </is>
       </c>
       <c r="G603" s="3" t="n">
-        <v>46318.10416666666</v>
+        <v>46318.77083333334</v>
       </c>
       <c r="H603" s="3" t="n">
-        <v>46318.1875</v>
+        <v>46318.85416666666</v>
       </c>
       <c r="I603" s="3" t="n">
-        <v>46319.85416666666</v>
+        <v>46320.52083333334</v>
       </c>
     </row>
     <row r="604">
@@ -27270,13 +27272,13 @@
         </is>
       </c>
       <c r="G604" s="3" t="n">
-        <v>46322.3125</v>
+        <v>46322.97916666666</v>
       </c>
       <c r="H604" s="3" t="n">
-        <v>46322.47916666666</v>
+        <v>46323.14583333334</v>
       </c>
       <c r="I604" s="3" t="n">
-        <v>46323.3125</v>
+        <v>46323.97916666666</v>
       </c>
     </row>
     <row r="605">
@@ -27311,13 +27313,13 @@
         </is>
       </c>
       <c r="G605" s="3" t="n">
-        <v>46325.85416666666</v>
+        <v>46326.52083333334</v>
       </c>
       <c r="H605" s="3" t="n">
-        <v>46325.91666666666</v>
+        <v>46326.58333333334</v>
       </c>
       <c r="I605" s="3" t="n">
-        <v>46326.41666666666</v>
+        <v>46327.08333333334</v>
       </c>
     </row>
     <row r="606">
@@ -27352,13 +27354,13 @@
         </is>
       </c>
       <c r="G606" s="3" t="n">
-        <v>46326.64583333334</v>
+        <v>46327.3125</v>
       </c>
       <c r="H606" s="3" t="n">
-        <v>46326.6875</v>
+        <v>46327.35416666666</v>
       </c>
       <c r="I606" s="3" t="n">
-        <v>46327.1875</v>
+        <v>46327.85416666666</v>
       </c>
     </row>
     <row r="607">
@@ -27393,13 +27395,13 @@
         </is>
       </c>
       <c r="G607" s="3" t="n">
-        <v>46330.27083333334</v>
+        <v>46330.9375</v>
       </c>
       <c r="H607" s="3" t="n">
-        <v>46330.3125</v>
+        <v>46330.97916666666</v>
       </c>
       <c r="I607" s="3" t="n">
-        <v>46330.97916666666</v>
+        <v>46331.64583333334</v>
       </c>
     </row>
     <row r="608">
@@ -27434,13 +27436,13 @@
         </is>
       </c>
       <c r="G608" s="3" t="n">
-        <v>46332.0625</v>
+        <v>46332.72916666666</v>
       </c>
       <c r="H608" s="3" t="n">
-        <v>46332.10416666666</v>
+        <v>46332.77083333334</v>
       </c>
       <c r="I608" s="3" t="n">
-        <v>46332.6875</v>
+        <v>46333.35416666666</v>
       </c>
     </row>
     <row r="609">
@@ -27475,13 +27477,13 @@
         </is>
       </c>
       <c r="G609" s="3" t="n">
-        <v>46332.875</v>
+        <v>46333.54166666666</v>
       </c>
       <c r="H609" s="3" t="n">
-        <v>46332.9375</v>
+        <v>46333.60416666666</v>
       </c>
       <c r="I609" s="3" t="n">
-        <v>46333.27083333334</v>
+        <v>46333.9375</v>
       </c>
     </row>
     <row r="610">
@@ -27516,13 +27518,13 @@
         </is>
       </c>
       <c r="G610" s="3" t="n">
-        <v>46334.5625</v>
+        <v>46335.22916666666</v>
       </c>
       <c r="H610" s="3" t="n">
-        <v>46334.72916666666</v>
+        <v>46335.39583333334</v>
       </c>
       <c r="I610" s="3" t="n">
-        <v>46335.22916666666</v>
+        <v>46335.89583333334</v>
       </c>
     </row>
     <row r="611">
@@ -27557,13 +27559,13 @@
         </is>
       </c>
       <c r="G611" s="3" t="n">
-        <v>46339.39583333334</v>
+        <v>46340.0625</v>
       </c>
       <c r="H611" s="3" t="n">
-        <v>46339.5625</v>
+        <v>46340.22916666666</v>
       </c>
       <c r="I611" s="3" t="n">
-        <v>46340.39583333334</v>
+        <v>46341.0625</v>
       </c>
     </row>
     <row r="612">
@@ -27598,13 +27600,13 @@
         </is>
       </c>
       <c r="G612" s="3" t="n">
-        <v>46342.0625</v>
+        <v>46342.72916666666</v>
       </c>
       <c r="H612" s="3" t="n">
-        <v>46342.10416666666</v>
+        <v>46342.77083333334</v>
       </c>
       <c r="I612" s="3" t="n">
-        <v>46342.9375</v>
+        <v>46343.60416666666</v>
       </c>
     </row>
     <row r="613">
@@ -27639,13 +27641,13 @@
         </is>
       </c>
       <c r="G613" s="3" t="n">
-        <v>46346.10416666666</v>
+        <v>46346.77083333334</v>
       </c>
       <c r="H613" s="3" t="n">
-        <v>46346.1875</v>
+        <v>46346.85416666666</v>
       </c>
       <c r="I613" s="3" t="n">
-        <v>46347.85416666666</v>
+        <v>46348.52083333334</v>
       </c>
     </row>
     <row r="614">
@@ -27724,10 +27726,10 @@
         <v>46296.75</v>
       </c>
       <c r="H615" s="3" t="n">
-        <v>46298.08333333334</v>
+        <v>46297.91666666666</v>
       </c>
       <c r="I615" s="3" t="n">
-        <v>46299.08333333334</v>
+        <v>46298.91666666666</v>
       </c>
     </row>
     <row r="616">
@@ -27762,13 +27764,13 @@
         </is>
       </c>
       <c r="G616" s="3" t="n">
-        <v>46300.5</v>
+        <v>46300.41666666666</v>
       </c>
       <c r="H616" s="3" t="n">
-        <v>46300.54166666666</v>
+        <v>46300.45833333334</v>
       </c>
       <c r="I616" s="3" t="n">
-        <v>46301.75</v>
+        <v>46301.66666666666</v>
       </c>
     </row>
     <row r="617">
@@ -27803,13 +27805,13 @@
         </is>
       </c>
       <c r="G617" s="3" t="n">
-        <v>46301.85416666666</v>
+        <v>46301.77083333334</v>
       </c>
       <c r="H617" s="3" t="n">
-        <v>46302.89583333334</v>
+        <v>46302.8125</v>
       </c>
       <c r="I617" s="3" t="n">
-        <v>46303.58333333334</v>
+        <v>46303.5</v>
       </c>
     </row>
     <row r="618">
@@ -27844,13 +27846,13 @@
         </is>
       </c>
       <c r="G618" s="3" t="n">
-        <v>46303.91666666666</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="H618" s="3" t="n">
-        <v>46303.97916666666</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="I618" s="3" t="n">
-        <v>46304.5</v>
+        <v>46304.41666666666</v>
       </c>
     </row>
     <row r="619">
@@ -29340,10 +29342,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -29381,7 +29383,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (9-23-1130-SKED.xls)</t>
+          <t>New ETA (9-23-1630-SKED.xls)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -29398,32 +29400,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46289.91666666666</v>
+        <v>46287.58333333334</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46290.125</v>
+        <v>46287.625</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -29434,115 +29436,115 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46295.875</v>
+        <v>46294.95833333334</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46296.08333333334</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46297.125</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46297.33333333334</v>
+        <v>46295.54166666666</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46297.875</v>
+        <v>46297.54166666666</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46298.125</v>
+        <v>46297.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -29552,22 +29554,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>0151N</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46303.29166666666</v>
+        <v>46287.5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46303.5</v>
+        <v>46287.6875</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -29578,464 +29580,464 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46306.04166666666</v>
+        <v>46293.54166666666</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46305.95833333334</v>
+        <v>46293.625</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46307.41666666666</v>
+        <v>46294.41666666666</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46306.33333333334</v>
+        <v>46294.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-26</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46309.375</v>
+        <v>46295.625</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46308.16666666666</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-29</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46311.41666666666</v>
+        <v>46296.375</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46310.25</v>
+        <v>46296.45833333334</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-28</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46318</v>
+        <v>46301.91666666666</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46316.33333333334</v>
+        <v>46302</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-40</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46319.29166666666</v>
+        <v>46304.3125</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46317.58333333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-41</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46320.04166666666</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46318.375</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-40</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46325.45833333334</v>
+        <v>46306.125</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46323.75</v>
+        <v>46306.20833333334</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-41</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46328.20833333334</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46326.5</v>
+        <v>46308.5625</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-41</v>
+        <v>2</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46329.58333333334</v>
+        <v>46314.54166666666</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46326.875</v>
+        <v>46314.625</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-65</v>
+        <v>2</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46331.54166666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46328.70833333334</v>
+        <v>46315.5</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-68</v>
+        <v>2</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46333.54166666666</v>
+        <v>46316.625</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46330.75</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-67</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46289.66666666666</v>
+        <v>46317.375</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46290.10416666666</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -30046,12 +30048,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -30061,17 +30063,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46290.04166666666</v>
+        <v>46322.91666666666</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>46290.47916666666</v>
+        <v>46323</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -30082,7 +30084,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -30092,22 +30094,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46291.83333333334</v>
+        <v>46325.3125</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>46292.27083333334</v>
+        <v>46325.39583333334</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -30118,32 +30120,32 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46296.22916666666</v>
+        <v>46325.83333333334</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46296.66666666666</v>
+        <v>46325.91666666666</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -30154,32 +30156,32 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46297.8125</v>
+        <v>46327.125</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>46298.25</v>
+        <v>46327.20833333334</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -30190,32 +30192,32 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46300.3125</v>
+        <v>46329.47916666666</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46300.75</v>
+        <v>46329.5625</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -30226,32 +30228,32 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46301.39583333334</v>
+        <v>46335.54166666666</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>46301.83333333334</v>
+        <v>46335.625</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -30262,32 +30264,32 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46304.64583333334</v>
+        <v>46336.41666666666</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>46305.08333333334</v>
+        <v>46336.5</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -30298,32 +30300,32 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46307.35416666666</v>
+        <v>46337.625</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>46307.79166666666</v>
+        <v>46337.70833333334</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -30334,32 +30336,32 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46309.72916666666</v>
+        <v>46338.375</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>46310.16666666666</v>
+        <v>46338.45833333334</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -30370,12 +30372,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -30385,17 +30387,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46310.1875</v>
+        <v>46343.91666666666</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46310.625</v>
+        <v>46344</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -30406,7 +30408,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -30416,22 +30418,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46312.14583333334</v>
+        <v>46346.3125</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46312.58333333334</v>
+        <v>46346.39583333334</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -30442,32 +30444,32 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0154N</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46316.5625</v>
+        <v>46346.83333333334</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46317</v>
+        <v>46346.91666666666</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -30478,36 +30480,3204 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0154N</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46348.125</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>46348.20833333334</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>HAPPY LUCKY</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2641S</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46311.75</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>46311.375</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>HAPPY LUCKY</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2641S</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46313.70833333334</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>46313.33333333334</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>HAPPY LUCKY</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2641S</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46315.20833333334</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46314.75</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HAPPY LUCKY</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>IDSUB</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2641N</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46324.04166666666</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46322.45833333334</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>-38</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HAPPY LUCKY</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>IDSUB</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2641N</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46326.75</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46325.29166666666</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>HAPPY LUCKY</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2641N</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46330.79166666666</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46329.5</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HAPPY LUCKY</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2641N</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46337.25</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46335.41666666666</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>-44</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46295.14583333334</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46298.6875</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46298.54166666666</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46299.47916666666</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>46303.3125</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>46303.16666666666</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46305.10416666666</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>46304.95833333334</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>46305.72986111111</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>46305.58402777778</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
           <t>CNXMN</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>46290.29166666666</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>46290.39583333334</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>46291.70833333334</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>46294.70833333334</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>46296.04166666666</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>46296.33333333334</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>46299.625</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>46302.25</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>46304.70833333334</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2612N</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E53" s="3" t="n">
+        <v>46305.08333333334</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>46305.375</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>46306.875</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>46311.33333333334</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>46311.625</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>KMTC TAIPEIS</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>46312.91666666666</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>46313.20833333334</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>46287.66666666666</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>46287.60416666666</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>46290.02083333334</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>46290.125</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>46296.08333333334</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>46296.16666666666</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>46296.95833333334</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>46297.04166666666</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>46298.16666666666</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>46298.25</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>46298.91666666666</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>46304.45833333334</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>46304.54166666666</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>46306.85416666666</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>46306.9375</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>46307.375</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>46307.45833333334</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>46308.66666666666</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>46308.75</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>46311.02083333334</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>46311.10416666666</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>46317.08333333334</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>46317.16666666666</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>46317.95833333334</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>46318.04166666666</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>46319.16666666666</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>46319.25</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>46319.91666666666</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>46325.45833333334</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>46325.54166666666</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>46327.85416666666</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>46327.9375</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>46328.375</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>46328.45833333334</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>46329.66666666666</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>46329.75</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>PEGASUS PROTO</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>46332.02083333334</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>46332.10416666666</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>46290.375</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>46291.77083333334</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>46294.75</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>46294.95833333334</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>46297.125</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>46297.33333333334</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>46299.625</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>46302.125</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>46306.375</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46306.875</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>46308.78541666667</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>46308.99375</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>IDSUB</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>46298.75</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>46299.5</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>IDSUB</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>46306.75</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>46311.58333333334</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>46312.33333333334</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>46315.16666666666</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>46315.91666666666</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>46317.125</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>46317.875</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>46318.66666666666</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>46319.41666666666</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>IDSUB</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>46327.83333333334</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>46328.58333333334</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>IDSUB</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>46330.75</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>46331.5</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46335.41666666666</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>46336.16666666666</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SHANGHAI VOYAGER</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>46341.25</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>46290.625</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>46290.75</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>46294.75</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>46295.41666666666</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>46297.91666666666</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>46298.58333333334</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>46298.60416666666</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>46299.27083333334</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>46302.9375</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>46304.0625</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>46304.72916666666</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>46304.875</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>46305.54166666666</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>46306.5625</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>46307.22916666666</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>46311.39583333334</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>46312.0625</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>46314.0625</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>46314.72916666666</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
         <v>46318.10416666666</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>46318.54166666666</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="F107" s="3" t="n">
+        <v>46318.77083333334</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>46322.3125</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>46322.97916666666</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>46325.85416666666</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>46326.52083333334</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>46326.64583333334</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>46327.3125</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>46330.27083333334</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>46330.9375</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>46332.0625</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>46332.72916666666</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>46332.875</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>46333.54166666666</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>46334.5625</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>46335.22916666666</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>46339.39583333334</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>46340.0625</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>46342.0625</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>46342.72916666666</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>46346.10416666666</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>46346.77083333334</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>SURABAYA VOYAGER</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>46300.5</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>SURABAYA VOYAGER</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>SURABAYA VOYAGER</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>46303.91666666666</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>46303.83333333334</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -903,22 +903,20 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>KRKAN (KAN06)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
+          <t>KRKAN -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v/>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-09-23T18:00:00</t>
+          <t>In transit, ETA 2026-09-28T23:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1099,20 +1097,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>CNSHA -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-23T13:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-09-25T01:00:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="n"/>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>THBKK (BKK02)</t>
+          <t>THLCH (LCH05)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-23T13:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-09-24T07:00:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>46288.70833333334</v>
+        <v>46306.58333333334</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2616S</t>
         </is>
       </c>
     </row>
@@ -1461,22 +1461,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH04)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>THLCH -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v/>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-09-23T16:00:00</t>
+          <t>In transit, ETA 2026-09-25T03:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
@@ -1655,20 +1653,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-23T19:30:00</t>
+          <t>Alongside, departs to KRINC ~2026-09-24T09:00:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -1771,20 +1771,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CNTAO -&gt; CNSHA</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v/>
+          <t>CNSHA (SHAW1)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-23T12:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-09-25T11:00:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -1835,22 +1837,20 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH04)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>THLCH -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v/>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-09-23T14:00:00</t>
+          <t>In transit, ETA 2026-09-25T03:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
@@ -2097,20 +2097,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>KRKAN -&gt; CNSHA</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v/>
+          <t>CNSHA (SHAW1)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-23T13:00:00</t>
+          <t>Alongside, departs to IDJKT ~2026-09-27T12:00:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="n"/>
@@ -32384,10 +32386,10 @@
         <v>46289.04166666666</v>
       </c>
       <c r="H731" s="3" t="n">
-        <v>46289.125</v>
+        <v>46291.33333333334</v>
       </c>
       <c r="I731" s="3" t="n">
-        <v>46292.125</v>
+        <v>46292.79166666666</v>
       </c>
     </row>
     <row r="732">
@@ -32463,13 +32465,13 @@
         </is>
       </c>
       <c r="G733" s="3" t="n">
-        <v>46293.95833333334</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="H733" s="3" t="n">
-        <v>46294</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="I733" s="3" t="n">
-        <v>46296</v>
+        <v>46297.33333333334</v>
       </c>
     </row>
     <row r="734">
@@ -32504,13 +32506,13 @@
         </is>
       </c>
       <c r="G734" s="3" t="n">
-        <v>46298</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="H734" s="3" t="n">
-        <v>46298.04166666666</v>
+        <v>46299.375</v>
       </c>
       <c r="I734" s="3" t="n">
-        <v>46299.04166666666</v>
+        <v>46300.375</v>
       </c>
     </row>
     <row r="735">
@@ -49187,14 +49189,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -49228,7 +49230,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260923-1158-SKED.xlsx)</t>
+          <t>New ETA (auto-20260924-0047-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -49239,6 +49241,114 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KMTC JAKARTA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46258.75</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46258.54166666666</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE CAPELLA</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>RUVVO</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>9001S</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46293.95833333334</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46295.29166666666</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE CAPELLA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9001S</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1589,20 +1589,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>TWKEL -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUSH4)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-24T05:00:00</t>
+          <t>Alongside, departs to KRUSN ~2026-09-26T16:00:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1719,20 +1721,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>KRINC -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUS05)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-24T01:00:00</t>
+          <t>Alongside, departs to RUVVO ~2026-09-27T01:00:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="n"/>
@@ -49189,10 +49193,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -49230,7 +49234,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260924-0047-SKED.xlsx)</t>
+          <t>New ETA (auto-20260924-0537-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -49277,78 +49281,6 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE CAPELLA</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>RUVVO</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>9001S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46293.95833333334</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46295.29166666666</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE CAPELLA</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9001S</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46299.33333333334</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1043,22 +1043,20 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>THBKK (BKK01)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>THBKK -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v/>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-24T12:00:00</t>
+          <t>In transit, ETA 2026-09-24T17:00:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1587,20 +1585,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>KRINC -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-24T15:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-09-25T14:00:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1965,22 +1965,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>THBKK (BKK04)</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
+          <t>THBKK -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v/>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-24T14:00:00</t>
+          <t>In transit, ETA 2026-09-24T19:00:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
@@ -49639,7 +49637,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -49668,7 +49666,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (prev)</t>
+          <t>Old ETA (9-24-1300-SKED.xls)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -863,20 +863,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; IDJKT</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v/>
+          <t>IDJKT (JKT01)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-24T20:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-09-27T12:30:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -1043,20 +1045,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>THBKK -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH04)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-24T17:00:00</t>
+          <t>Alongside, departs to HKHKG ~2026-09-25T03:00:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1073,7 +1077,7 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>46289.70833333334</v>
+        <v>46307.91666666666</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1082,7 +1086,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611S</t>
         </is>
       </c>
     </row>
@@ -1965,20 +1969,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>THBKK -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH01)</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-24T19:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-09-25T06:00:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
@@ -1995,7 +2001,7 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46289.79166666666</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2004,7 +2010,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610S</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2050,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to IDJKT ~2026-09-26T21:00:00</t>
+          <t>Alongside, departs to IDJKT ~2026-09-27T21:00:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="n"/>
@@ -2055,7 +2061,7 @@
         <v/>
       </c>
       <c r="L26" s="3" t="n">
-        <v>46305.22916666666</v>
+        <v>46306.22916666666</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -2155,20 +2161,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; HKHKG</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v/>
+          <t>HKHKG (HKG03)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-24T20:00:00</t>
+          <t>Alongside, departs to CNXMN ~2026-09-25T10:00:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
@@ -2416,7 +2424,7 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>46314.125</v>
+        <v>46312.64583333334</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2429,7 +2437,7 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46313.5</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -38395,10 +38403,10 @@
         <v>46287.79166666666</v>
       </c>
       <c r="H876" s="3" t="n">
-        <v>46290.95833333334</v>
+        <v>46291.95833333334</v>
       </c>
       <c r="I876" s="3" t="n">
-        <v>46291.875</v>
+        <v>46292.875</v>
       </c>
     </row>
     <row r="877">
@@ -38433,13 +38441,13 @@
         </is>
       </c>
       <c r="G877" s="3" t="n">
-        <v>46298.875</v>
+        <v>46299.875</v>
       </c>
       <c r="H877" s="3" t="n">
-        <v>46298.95833333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="I877" s="3" t="n">
-        <v>46299.79166666666</v>
+        <v>46300.79166666666</v>
       </c>
     </row>
     <row r="878">
@@ -38474,13 +38482,13 @@
         </is>
       </c>
       <c r="G878" s="3" t="n">
-        <v>46300.52083333334</v>
+        <v>46301.52083333334</v>
       </c>
       <c r="H878" s="3" t="n">
-        <v>46300.60416666666</v>
+        <v>46301.60416666666</v>
       </c>
       <c r="I878" s="3" t="n">
-        <v>46301.5</v>
+        <v>46302.5</v>
       </c>
     </row>
     <row r="879">
@@ -38515,13 +38523,13 @@
         </is>
       </c>
       <c r="G879" s="3" t="n">
-        <v>46305.22916666666</v>
+        <v>46306.22916666666</v>
       </c>
       <c r="H879" s="3" t="n">
-        <v>46305.27083333334</v>
+        <v>46306.27083333334</v>
       </c>
       <c r="I879" s="3" t="n">
-        <v>46305.9375</v>
+        <v>46306.9375</v>
       </c>
     </row>
     <row r="880">
@@ -38556,13 +38564,13 @@
         </is>
       </c>
       <c r="G880" s="3" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="H880" s="3" t="n">
-        <v>46312.20833333334</v>
+        <v>46313.20833333334</v>
       </c>
       <c r="I880" s="3" t="n">
-        <v>46312.875</v>
+        <v>46313.875</v>
       </c>
     </row>
     <row r="881">
@@ -38597,13 +38605,13 @@
         </is>
       </c>
       <c r="G881" s="3" t="n">
-        <v>46314.27083333334</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="H881" s="3" t="n">
-        <v>46314.3125</v>
+        <v>46315.3125</v>
       </c>
       <c r="I881" s="3" t="n">
-        <v>46315.3125</v>
+        <v>46316.3125</v>
       </c>
     </row>
     <row r="882">
@@ -38638,13 +38646,13 @@
         </is>
       </c>
       <c r="G882" s="3" t="n">
-        <v>46315.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="H882" s="3" t="n">
-        <v>46315.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="I882" s="3" t="n">
-        <v>46316.27083333334</v>
+        <v>46317.27083333334</v>
       </c>
     </row>
     <row r="883">
@@ -38679,13 +38687,13 @@
         </is>
       </c>
       <c r="G883" s="3" t="n">
-        <v>46317.77083333334</v>
+        <v>46318.77083333334</v>
       </c>
       <c r="H883" s="3" t="n">
-        <v>46317.97916666666</v>
+        <v>46318.97916666666</v>
       </c>
       <c r="I883" s="3" t="n">
-        <v>46318.64583333334</v>
+        <v>46319.64583333334</v>
       </c>
     </row>
     <row r="884">
@@ -38720,13 +38728,13 @@
         </is>
       </c>
       <c r="G884" s="3" t="n">
-        <v>46325.64583333334</v>
+        <v>46326.64583333334</v>
       </c>
       <c r="H884" s="3" t="n">
-        <v>46325.72916666666</v>
+        <v>46326.72916666666</v>
       </c>
       <c r="I884" s="3" t="n">
-        <v>46326.5625</v>
+        <v>46327.5625</v>
       </c>
     </row>
     <row r="885">
@@ -38761,13 +38769,13 @@
         </is>
       </c>
       <c r="G885" s="3" t="n">
-        <v>46327.64583333334</v>
+        <v>46328.64583333334</v>
       </c>
       <c r="H885" s="3" t="n">
-        <v>46327.72916666666</v>
+        <v>46328.72916666666</v>
       </c>
       <c r="I885" s="3" t="n">
-        <v>46328.22916666666</v>
+        <v>46329.22916666666</v>
       </c>
     </row>
     <row r="886">
@@ -38802,13 +38810,13 @@
         </is>
       </c>
       <c r="G886" s="3" t="n">
-        <v>46332.22916666666</v>
+        <v>46333.22916666666</v>
       </c>
       <c r="H886" s="3" t="n">
-        <v>46332.27083333334</v>
+        <v>46333.27083333334</v>
       </c>
       <c r="I886" s="3" t="n">
-        <v>46332.9375</v>
+        <v>46333.9375</v>
       </c>
     </row>
     <row r="887">
@@ -38843,13 +38851,13 @@
         </is>
       </c>
       <c r="G887" s="3" t="n">
-        <v>46339.35416666666</v>
+        <v>46340.35416666666</v>
       </c>
       <c r="H887" s="3" t="n">
-        <v>46339.5625</v>
+        <v>46340.5625</v>
       </c>
       <c r="I887" s="3" t="n">
-        <v>46340.22916666666</v>
+        <v>46341.22916666666</v>
       </c>
     </row>
     <row r="888">
@@ -38884,13 +38892,13 @@
         </is>
       </c>
       <c r="G888" s="3" t="n">
-        <v>46341.6875</v>
+        <v>46342.6875</v>
       </c>
       <c r="H888" s="3" t="n">
-        <v>46341.72916666666</v>
+        <v>46342.72916666666</v>
       </c>
       <c r="I888" s="3" t="n">
-        <v>46342.72916666666</v>
+        <v>46343.72916666666</v>
       </c>
     </row>
     <row r="889">
@@ -38925,13 +38933,13 @@
         </is>
       </c>
       <c r="G889" s="3" t="n">
-        <v>46343.35416666666</v>
+        <v>46344.35416666666</v>
       </c>
       <c r="H889" s="3" t="n">
-        <v>46343.39583333334</v>
+        <v>46344.39583333334</v>
       </c>
       <c r="I889" s="3" t="n">
-        <v>46344.02083333334</v>
+        <v>46345.02083333334</v>
       </c>
     </row>
     <row r="890">
@@ -38966,13 +38974,13 @@
         </is>
       </c>
       <c r="G890" s="3" t="n">
-        <v>46345.52083333334</v>
+        <v>46346.52083333334</v>
       </c>
       <c r="H890" s="3" t="n">
-        <v>46345.72916666666</v>
+        <v>46346.72916666666</v>
       </c>
       <c r="I890" s="3" t="n">
-        <v>46346.39583333334</v>
+        <v>46347.39583333334</v>
       </c>
     </row>
     <row r="891">
@@ -39007,13 +39015,13 @@
         </is>
       </c>
       <c r="G891" s="3" t="n">
-        <v>46353.39583333334</v>
+        <v>46354.39583333334</v>
       </c>
       <c r="H891" s="3" t="n">
-        <v>46353.47916666666</v>
+        <v>46354.47916666666</v>
       </c>
       <c r="I891" s="3" t="n">
-        <v>46354.3125</v>
+        <v>46355.3125</v>
       </c>
     </row>
     <row r="892">
@@ -39048,13 +39056,13 @@
         </is>
       </c>
       <c r="G892" s="3" t="n">
-        <v>46355.39583333334</v>
+        <v>46356.39583333334</v>
       </c>
       <c r="H892" s="3" t="n">
-        <v>46355.47916666666</v>
+        <v>46356.47916666666</v>
       </c>
       <c r="I892" s="3" t="n">
-        <v>46355.97916666666</v>
+        <v>46356.97916666666</v>
       </c>
     </row>
     <row r="893">
@@ -39089,13 +39097,13 @@
         </is>
       </c>
       <c r="G893" s="3" t="n">
-        <v>46359.97916666666</v>
+        <v>46360.97916666666</v>
       </c>
       <c r="H893" s="3" t="n">
-        <v>46360.02083333334</v>
+        <v>46361.02083333334</v>
       </c>
       <c r="I893" s="3" t="n">
-        <v>46360.6875</v>
+        <v>46361.6875</v>
       </c>
     </row>
     <row r="894">
@@ -39128,13 +39136,13 @@
         <v/>
       </c>
       <c r="G894" s="3" t="n">
-        <v>46367.10416666666</v>
+        <v>46368.10416666666</v>
       </c>
       <c r="H894" s="3" t="n">
-        <v>46367.3125</v>
+        <v>46368.3125</v>
       </c>
       <c r="I894" s="3" t="n">
-        <v>46367.97916666666</v>
+        <v>46368.97916666666</v>
       </c>
     </row>
     <row r="895">
@@ -47072,13 +47080,13 @@
         </is>
       </c>
       <c r="G1088" s="3" t="n">
-        <v>46303.25</v>
+        <v>46301.10416666666</v>
       </c>
       <c r="H1088" s="3" t="n">
-        <v>46303.33333333334</v>
+        <v>46301.1875</v>
       </c>
       <c r="I1088" s="3" t="n">
-        <v>46304.16666666666</v>
+        <v>46302.02083333334</v>
       </c>
     </row>
     <row r="1089">
@@ -47113,13 +47121,13 @@
         </is>
       </c>
       <c r="G1089" s="3" t="n">
-        <v>46305.16666666666</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="H1089" s="3" t="n">
-        <v>46305.20833333334</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="I1089" s="3" t="n">
-        <v>46305.70833333334</v>
+        <v>46303.60416666666</v>
       </c>
     </row>
     <row r="1090">
@@ -47154,13 +47162,13 @@
         </is>
       </c>
       <c r="G1090" s="3" t="n">
-        <v>46306.79166666666</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="H1090" s="3" t="n">
-        <v>46306.95833333334</v>
+        <v>46304.9375</v>
       </c>
       <c r="I1090" s="3" t="n">
-        <v>46307.75</v>
+        <v>46305.6875</v>
       </c>
     </row>
     <row r="1091">
@@ -47195,13 +47203,13 @@
         </is>
       </c>
       <c r="G1091" s="3" t="n">
-        <v>46313.5</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="H1091" s="3" t="n">
-        <v>46313.54166666666</v>
+        <v>46312.0625</v>
       </c>
       <c r="I1091" s="3" t="n">
-        <v>46313.83333333334</v>
+        <v>46312.35416666666</v>
       </c>
     </row>
     <row r="1092">
@@ -47236,13 +47244,13 @@
         </is>
       </c>
       <c r="G1092" s="3" t="n">
-        <v>46314.125</v>
+        <v>46312.64583333334</v>
       </c>
       <c r="H1092" s="3" t="n">
-        <v>46314.125</v>
+        <v>46312.64583333334</v>
       </c>
       <c r="I1092" s="3" t="n">
-        <v>46315.5</v>
+        <v>46314.02083333334</v>
       </c>
     </row>
     <row r="1093">
@@ -47277,13 +47285,13 @@
         </is>
       </c>
       <c r="G1093" s="3" t="n">
-        <v>46315.75</v>
+        <v>46314.27083333334</v>
       </c>
       <c r="H1093" s="3" t="n">
-        <v>46315.79166666666</v>
+        <v>46314.3125</v>
       </c>
       <c r="I1093" s="3" t="n">
-        <v>46316.25</v>
+        <v>46314.77083333334</v>
       </c>
     </row>
     <row r="1094">
@@ -47318,13 +47326,13 @@
         </is>
       </c>
       <c r="G1094" s="3" t="n">
-        <v>46320.08333333334</v>
+        <v>46318.60416666666</v>
       </c>
       <c r="H1094" s="3" t="n">
-        <v>46320.08333333334</v>
+        <v>46318.60416666666</v>
       </c>
       <c r="I1094" s="3" t="n">
-        <v>46320.54166666666</v>
+        <v>46319.0625</v>
       </c>
     </row>
     <row r="1095">
@@ -47359,13 +47367,13 @@
         </is>
       </c>
       <c r="G1095" s="3" t="n">
-        <v>46321.54166666666</v>
+        <v>46320.0625</v>
       </c>
       <c r="H1095" s="3" t="n">
-        <v>46321.54166666666</v>
+        <v>46320.0625</v>
       </c>
       <c r="I1095" s="3" t="n">
-        <v>46322.04166666666</v>
+        <v>46320.5625</v>
       </c>
     </row>
     <row r="1096">
@@ -47400,13 +47408,13 @@
         </is>
       </c>
       <c r="G1096" s="3" t="n">
-        <v>46325.66666666666</v>
+        <v>46323.52083333334</v>
       </c>
       <c r="H1096" s="3" t="n">
-        <v>46325.70833333334</v>
+        <v>46323.5625</v>
       </c>
       <c r="I1096" s="3" t="n">
-        <v>46326.33333333334</v>
+        <v>46324.1875</v>
       </c>
     </row>
     <row r="1097">
@@ -47441,13 +47449,13 @@
         </is>
       </c>
       <c r="G1097" s="3" t="n">
-        <v>46327.33333333334</v>
+        <v>46325.1875</v>
       </c>
       <c r="H1097" s="3" t="n">
-        <v>46327.375</v>
+        <v>46325.22916666666</v>
       </c>
       <c r="I1097" s="3" t="n">
-        <v>46327.875</v>
+        <v>46325.72916666666</v>
       </c>
     </row>
     <row r="1098">
@@ -47482,13 +47490,13 @@
         </is>
       </c>
       <c r="G1098" s="3" t="n">
-        <v>46328.95833333334</v>
+        <v>46326.8125</v>
       </c>
       <c r="H1098" s="3" t="n">
-        <v>46329.125</v>
+        <v>46326.97916666666</v>
       </c>
       <c r="I1098" s="3" t="n">
-        <v>46329.91666666666</v>
+        <v>46327.77083333334</v>
       </c>
     </row>
     <row r="1099">
@@ -47523,13 +47531,13 @@
         </is>
       </c>
       <c r="G1099" s="3" t="n">
-        <v>46335.66666666666</v>
+        <v>46333.52083333334</v>
       </c>
       <c r="H1099" s="3" t="n">
-        <v>46335.70833333334</v>
+        <v>46333.5625</v>
       </c>
       <c r="I1099" s="3" t="n">
-        <v>46336</v>
+        <v>46333.85416666666</v>
       </c>
     </row>
     <row r="1100">
@@ -47564,13 +47572,13 @@
         </is>
       </c>
       <c r="G1100" s="3" t="n">
-        <v>46336.29166666666</v>
+        <v>46334.14583333334</v>
       </c>
       <c r="H1100" s="3" t="n">
-        <v>46336.29166666666</v>
+        <v>46334.14583333334</v>
       </c>
       <c r="I1100" s="3" t="n">
-        <v>46337.66666666666</v>
+        <v>46335.52083333334</v>
       </c>
     </row>
     <row r="1101">
@@ -47605,13 +47613,13 @@
         </is>
       </c>
       <c r="G1101" s="3" t="n">
-        <v>46337.91666666666</v>
+        <v>46335.77083333334</v>
       </c>
       <c r="H1101" s="3" t="n">
-        <v>46337.95833333334</v>
+        <v>46335.8125</v>
       </c>
       <c r="I1101" s="3" t="n">
-        <v>46338.41666666666</v>
+        <v>46336.27083333334</v>
       </c>
     </row>
     <row r="1102">
@@ -47646,13 +47654,13 @@
         </is>
       </c>
       <c r="G1102" s="3" t="n">
-        <v>46342.25</v>
+        <v>46340.10416666666</v>
       </c>
       <c r="H1102" s="3" t="n">
-        <v>46342.25</v>
+        <v>46340.10416666666</v>
       </c>
       <c r="I1102" s="3" t="n">
-        <v>46342.70833333334</v>
+        <v>46340.5625</v>
       </c>
     </row>
     <row r="1103">
@@ -47687,13 +47695,13 @@
         </is>
       </c>
       <c r="G1103" s="3" t="n">
-        <v>46343.70833333334</v>
+        <v>46341.5625</v>
       </c>
       <c r="H1103" s="3" t="n">
-        <v>46343.70833333334</v>
+        <v>46341.5625</v>
       </c>
       <c r="I1103" s="3" t="n">
-        <v>46344.20833333334</v>
+        <v>46342.0625</v>
       </c>
     </row>
     <row r="1104">
@@ -47728,13 +47736,13 @@
         </is>
       </c>
       <c r="G1104" s="3" t="n">
-        <v>46346.66666666666</v>
+        <v>46344.52083333334</v>
       </c>
       <c r="H1104" s="3" t="n">
-        <v>46346.70833333334</v>
+        <v>46344.5625</v>
       </c>
       <c r="I1104" s="3" t="n">
-        <v>46347.33333333334</v>
+        <v>46345.1875</v>
       </c>
     </row>
     <row r="1105">
@@ -47769,13 +47777,13 @@
         </is>
       </c>
       <c r="G1105" s="3" t="n">
-        <v>46348.33333333334</v>
+        <v>46346.1875</v>
       </c>
       <c r="H1105" s="3" t="n">
-        <v>46348.375</v>
+        <v>46346.22916666666</v>
       </c>
       <c r="I1105" s="3" t="n">
-        <v>46348.875</v>
+        <v>46346.72916666666</v>
       </c>
     </row>
     <row r="1106">
@@ -47810,13 +47818,13 @@
         </is>
       </c>
       <c r="G1106" s="3" t="n">
-        <v>46349.95833333334</v>
+        <v>46347.8125</v>
       </c>
       <c r="H1106" s="3" t="n">
-        <v>46350.125</v>
+        <v>46347.97916666666</v>
       </c>
       <c r="I1106" s="3" t="n">
-        <v>46350.91666666666</v>
+        <v>46348.77083333334</v>
       </c>
     </row>
     <row r="1107">
@@ -47851,13 +47859,13 @@
         </is>
       </c>
       <c r="G1107" s="3" t="n">
-        <v>46356.66666666666</v>
+        <v>46354.52083333334</v>
       </c>
       <c r="H1107" s="3" t="n">
-        <v>46356.70833333334</v>
+        <v>46354.5625</v>
       </c>
       <c r="I1107" s="3" t="n">
-        <v>46357</v>
+        <v>46354.85416666666</v>
       </c>
     </row>
     <row r="1108">
@@ -47892,13 +47900,13 @@
         </is>
       </c>
       <c r="G1108" s="3" t="n">
-        <v>46357.29166666666</v>
+        <v>46355.14583333334</v>
       </c>
       <c r="H1108" s="3" t="n">
-        <v>46357.29166666666</v>
+        <v>46355.14583333334</v>
       </c>
       <c r="I1108" s="3" t="n">
-        <v>46358.66666666666</v>
+        <v>46356.52083333334</v>
       </c>
     </row>
     <row r="1109">
@@ -47933,13 +47941,13 @@
         </is>
       </c>
       <c r="G1109" s="3" t="n">
-        <v>46358.91666666666</v>
+        <v>46356.77083333334</v>
       </c>
       <c r="H1109" s="3" t="n">
-        <v>46358.95833333334</v>
+        <v>46356.8125</v>
       </c>
       <c r="I1109" s="3" t="n">
-        <v>46359.41666666666</v>
+        <v>46357.27083333334</v>
       </c>
     </row>
     <row r="1110">
@@ -47974,13 +47982,13 @@
         </is>
       </c>
       <c r="G1110" s="3" t="n">
-        <v>46363.25</v>
+        <v>46361.10416666666</v>
       </c>
       <c r="H1110" s="3" t="n">
-        <v>46363.25</v>
+        <v>46361.10416666666</v>
       </c>
       <c r="I1110" s="3" t="n">
-        <v>46363.70833333334</v>
+        <v>46361.5625</v>
       </c>
     </row>
     <row r="1111">
@@ -48013,13 +48021,13 @@
         <v/>
       </c>
       <c r="G1111" s="3" t="n">
-        <v>46364.70833333334</v>
+        <v>46362.5625</v>
       </c>
       <c r="H1111" s="3" t="n">
-        <v>46364.70833333334</v>
+        <v>46362.5625</v>
       </c>
       <c r="I1111" s="3" t="n">
-        <v>46365.20833333334</v>
+        <v>46363.0625</v>
       </c>
     </row>
     <row r="1112">
@@ -49630,14 +49638,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -49666,12 +49674,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (9-24-1300-SKED.xls)</t>
+          <t>Old ETA (prev)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260924-0915-SKED.xlsx)</t>
+          <t>New ETA (auto-20260924-1353-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -49682,6 +49690,1550 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KMTC JAKARTA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46258.75</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46258.54166666666</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46298.875</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46299.875</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46305.22916666666</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46314.27083333334</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46315.27083333334</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46315.60416666666</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>46316.60416666666</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46317.77083333334</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>46318.77083333334</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46325.64583333334</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46326.64583333334</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46327.64583333334</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>46328.64583333334</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46332.22916666666</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>46333.22916666666</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46339.35416666666</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>46340.35416666666</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>46341.6875</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>46342.6875</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46343.35416666666</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>46344.35416666666</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>46345.52083333334</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>46346.52083333334</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>46353.39583333334</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46354.39583333334</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46355.39583333334</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>46356.39583333334</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46359.97916666666</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>46360.97916666666</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46367.10416666666</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>46368.10416666666</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2618S</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46303.25</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2618S</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46305.16666666666</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>46303.02083333334</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2618S</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>46306.79166666666</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46304.77083333334</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>-48.5</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2618S</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46313.5</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>46312.02083333334</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>46314.125</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>46312.64583333334</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46315.75</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>46314.27083333334</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46320.08333333334</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>46318.60416666666</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46321.54166666666</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>46320.0625</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>46325.66666666666</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>46323.52083333334</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46327.33333333334</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>46325.1875</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>46328.95833333334</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>46326.8125</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46335.66666666666</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>46333.52083333334</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2619N</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46336.29166666666</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>46334.14583333334</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2619N</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46337.91666666666</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>46335.77083333334</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2619N</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46342.25</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46340.10416666666</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2619N</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46343.70833333334</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46341.5625</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2620S</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46346.66666666666</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46344.52083333334</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2620S</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46348.33333333334</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46346.1875</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2620S</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46349.95833333334</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46347.8125</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2620S</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46356.66666666666</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46354.52083333334</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2620N</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46357.29166666666</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46355.14583333334</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2620N</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46358.91666666666</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46356.77083333334</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2620N</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>46363.25</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>46361.10416666666</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2620N</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46364.70833333334</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>46362.5625</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>-51.5</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>THBKK (BKK01)</t>
+          <t>THLCH (LCH04)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-24T23:50:00</t>
+          <t>Alongside, departs to HKHKG ~2026-09-25T15:00:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>46290.20833333334</v>
+        <v>46311.125</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2615S</t>
         </is>
       </c>
     </row>
@@ -1045,22 +1045,20 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH04)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>THLCH -&gt; HKHKG</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v/>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to HKHKG ~2026-09-25T03:00:00</t>
+          <t>In transit, ETA 2026-09-28T23:00:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1111,22 +1109,20 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
+          <t>VNSGN -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v/>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-25T01:00:00</t>
+          <t>In transit, ETA 2026-09-26T14:00:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="n"/>
@@ -1171,20 +1167,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; HKHKG</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v/>
+          <t>HKHKG (HKG03)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-25T09:30:00</t>
+          <t>Alongside, departs to CNXMN ~2026-09-25T23:00:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1461,20 +1459,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>KRPUS -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-24T22:00:00</t>
+          <t>Alongside, departs to KRINC ~2026-09-25T20:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
@@ -1525,20 +1525,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-25T03:00:00</t>
+          <t>Alongside, departs to KRINC ~2026-09-25T23:00:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -1905,20 +1907,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-25T03:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-09-25T19:00:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -1969,26 +1973,24 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH01)</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
+          <t>THLCH -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v/>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-09-25T06:00:00</t>
+          <t>In transit, ETA 2026-09-26T21:00:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>46312.45833333334</v>
+        <v>46312.58333333334</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2001,7 +2003,7 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46311.83333333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2290,7 +2292,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>VNSGN -&gt; THLCH</t>
+          <t>THLCH -&gt; THBKK</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
@@ -2298,7 +2300,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-25T02:30:00</t>
+          <t>In transit, ETA 2026-09-25T11:30:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
@@ -2315,7 +2317,7 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46290.10416666666</v>
+        <v>46292.27083333334</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2324,7 +2326,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2611N</t>
         </is>
       </c>
     </row>
@@ -22558,10 +22560,10 @@
         <v>46290.45833333334</v>
       </c>
       <c r="H489" s="3" t="n">
-        <v>46292.25</v>
+        <v>46293.5</v>
       </c>
       <c r="I489" s="3" t="n">
-        <v>46293.83333333334</v>
+        <v>46295.29166666666</v>
       </c>
     </row>
     <row r="490">
@@ -22678,13 +22680,13 @@
         </is>
       </c>
       <c r="G492" s="3" t="n">
-        <v>46294.125</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="H492" s="3" t="n">
-        <v>46294.1875</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="I492" s="3" t="n">
-        <v>46294.66666666666</v>
+        <v>46296.125</v>
       </c>
     </row>
     <row r="493">
@@ -22719,13 +22721,13 @@
         </is>
       </c>
       <c r="G493" s="3" t="n">
-        <v>46296.14583333334</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>46297.22916666666</v>
+        <v>46298.6875</v>
       </c>
       <c r="I493" s="3" t="n">
-        <v>46297.72916666666</v>
+        <v>46299.1875</v>
       </c>
     </row>
     <row r="494">
@@ -22760,13 +22762,13 @@
         </is>
       </c>
       <c r="G494" s="3" t="n">
-        <v>46300.6875</v>
+        <v>46302.14583333334</v>
       </c>
       <c r="H494" s="3" t="n">
-        <v>46300.8125</v>
+        <v>46302.27083333334</v>
       </c>
       <c r="I494" s="3" t="n">
-        <v>46301.22916666666</v>
+        <v>46302.6875</v>
       </c>
     </row>
     <row r="495">
@@ -22801,13 +22803,13 @@
         </is>
       </c>
       <c r="G495" s="3" t="n">
-        <v>46313.47916666666</v>
+        <v>46314.9375</v>
       </c>
       <c r="H495" s="3" t="n">
-        <v>46314.5625</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="I495" s="3" t="n">
-        <v>46315.22916666666</v>
+        <v>46316.6875</v>
       </c>
     </row>
     <row r="496">
@@ -22842,13 +22844,13 @@
         </is>
       </c>
       <c r="G496" s="3" t="n">
-        <v>46316.47916666666</v>
+        <v>46317.9375</v>
       </c>
       <c r="H496" s="3" t="n">
-        <v>46316.5625</v>
+        <v>46318.02083333334</v>
       </c>
       <c r="I496" s="3" t="n">
-        <v>46317.0625</v>
+        <v>46318.52083333334</v>
       </c>
     </row>
     <row r="497">
@@ -22883,13 +22885,13 @@
         </is>
       </c>
       <c r="G497" s="3" t="n">
-        <v>46317.97916666666</v>
+        <v>46319.4375</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>46318.0625</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="I497" s="3" t="n">
-        <v>46318.64583333334</v>
+        <v>46320.10416666666</v>
       </c>
     </row>
     <row r="498">
@@ -22924,13 +22926,13 @@
         </is>
       </c>
       <c r="G498" s="3" t="n">
-        <v>46327.52083333334</v>
+        <v>46328.97916666666</v>
       </c>
       <c r="H498" s="3" t="n">
-        <v>46328.5625</v>
+        <v>46330.02083333334</v>
       </c>
       <c r="I498" s="3" t="n">
-        <v>46329.14583333334</v>
+        <v>46330.60416666666</v>
       </c>
     </row>
     <row r="499">
@@ -22963,13 +22965,13 @@
         <v/>
       </c>
       <c r="G499" s="3" t="n">
-        <v>46337.9375</v>
+        <v>46339.39583333334</v>
       </c>
       <c r="H499" s="3" t="n">
-        <v>46337.97916666666</v>
+        <v>46339.4375</v>
       </c>
       <c r="I499" s="3" t="n">
-        <v>46338.72916666666</v>
+        <v>46340.1875</v>
       </c>
     </row>
     <row r="500">
@@ -36885,13 +36887,13 @@
         </is>
       </c>
       <c r="G839" s="3" t="n">
-        <v>46289.79166666666</v>
+        <v>46289.91666666666</v>
       </c>
       <c r="H839" s="3" t="n">
-        <v>46289.83333333334</v>
+        <v>46289.95416666667</v>
       </c>
       <c r="I839" s="3" t="n">
-        <v>46290.25</v>
+        <v>46290.375</v>
       </c>
     </row>
     <row r="840">
@@ -36926,13 +36928,13 @@
         </is>
       </c>
       <c r="G840" s="3" t="n">
-        <v>46291.75</v>
+        <v>46291.875</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>46291.91666666666</v>
+        <v>46292.04166666666</v>
       </c>
       <c r="I840" s="3" t="n">
-        <v>46292.41666666666</v>
+        <v>46292.54166666666</v>
       </c>
     </row>
     <row r="841">
@@ -36967,13 +36969,13 @@
         </is>
       </c>
       <c r="G841" s="3" t="n">
-        <v>46297.4375</v>
+        <v>46297.5625</v>
       </c>
       <c r="H841" s="3" t="n">
-        <v>46297.5</v>
+        <v>46297.625</v>
       </c>
       <c r="I841" s="3" t="n">
-        <v>46297.75</v>
+        <v>46297.875</v>
       </c>
     </row>
     <row r="842">
@@ -37008,13 +37010,13 @@
         </is>
       </c>
       <c r="G842" s="3" t="n">
-        <v>46298.6875</v>
+        <v>46298.8125</v>
       </c>
       <c r="H842" s="3" t="n">
-        <v>46298.75</v>
+        <v>46298.875</v>
       </c>
       <c r="I842" s="3" t="n">
-        <v>46299.16666666666</v>
+        <v>46299.29166666666</v>
       </c>
     </row>
     <row r="843">
@@ -37049,13 +37051,13 @@
         </is>
       </c>
       <c r="G843" s="3" t="n">
-        <v>46299.5</v>
+        <v>46299.625</v>
       </c>
       <c r="H843" s="3" t="n">
-        <v>46299.54166666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="I843" s="3" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.29166666666</v>
       </c>
     </row>
     <row r="844">
@@ -37090,13 +37092,13 @@
         </is>
       </c>
       <c r="G844" s="3" t="n">
-        <v>46301.25</v>
+        <v>46301.375</v>
       </c>
       <c r="H844" s="3" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="I844" s="3" t="n">
-        <v>46304.41666666666</v>
+        <v>46304.54166666666</v>
       </c>
     </row>
     <row r="845">
@@ -37131,13 +37133,13 @@
         </is>
       </c>
       <c r="G845" s="3" t="n">
-        <v>46308.625</v>
+        <v>46308.75</v>
       </c>
       <c r="H845" s="3" t="n">
-        <v>46309.75</v>
+        <v>46309.875</v>
       </c>
       <c r="I845" s="3" t="n">
-        <v>46310.25</v>
+        <v>46310.375</v>
       </c>
     </row>
     <row r="846">
@@ -37172,13 +37174,13 @@
         </is>
       </c>
       <c r="G846" s="3" t="n">
-        <v>46311.83333333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>46311.875</v>
+        <v>46312</v>
       </c>
       <c r="I846" s="3" t="n">
-        <v>46312.29166666666</v>
+        <v>46312.41666666666</v>
       </c>
     </row>
     <row r="847">
@@ -37213,13 +37215,13 @@
         </is>
       </c>
       <c r="G847" s="3" t="n">
-        <v>46312.45833333334</v>
+        <v>46312.58333333334</v>
       </c>
       <c r="H847" s="3" t="n">
-        <v>46312.58333333334</v>
+        <v>46312.70833333334</v>
       </c>
       <c r="I847" s="3" t="n">
-        <v>46313.58333333334</v>
+        <v>46313.70833333334</v>
       </c>
     </row>
     <row r="848">
@@ -37254,13 +37256,13 @@
         </is>
       </c>
       <c r="G848" s="3" t="n">
-        <v>46313.83333333334</v>
+        <v>46313.95833333334</v>
       </c>
       <c r="H848" s="3" t="n">
-        <v>46313.875</v>
+        <v>46314</v>
       </c>
       <c r="I848" s="3" t="n">
-        <v>46314.29166666666</v>
+        <v>46314.41666666666</v>
       </c>
     </row>
     <row r="849">
@@ -37295,13 +37297,13 @@
         </is>
       </c>
       <c r="G849" s="3" t="n">
-        <v>46315.79166666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="H849" s="3" t="n">
-        <v>46316.91666666666</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="I849" s="3" t="n">
-        <v>46317.41666666666</v>
+        <v>46317.54166666666</v>
       </c>
     </row>
     <row r="850">
@@ -37336,13 +37338,13 @@
         </is>
       </c>
       <c r="G850" s="3" t="n">
-        <v>46323.39583333334</v>
+        <v>46323.52083333334</v>
       </c>
       <c r="H850" s="3" t="n">
-        <v>46323.45833333334</v>
+        <v>46323.58333333334</v>
       </c>
       <c r="I850" s="3" t="n">
-        <v>46323.70833333334</v>
+        <v>46323.83333333334</v>
       </c>
     </row>
     <row r="851">
@@ -37377,13 +37379,13 @@
         </is>
       </c>
       <c r="G851" s="3" t="n">
-        <v>46324.64583333334</v>
+        <v>46324.77083333334</v>
       </c>
       <c r="H851" s="3" t="n">
-        <v>46324.70833333334</v>
+        <v>46324.83333333334</v>
       </c>
       <c r="I851" s="3" t="n">
-        <v>46325.125</v>
+        <v>46325.25</v>
       </c>
     </row>
     <row r="852">
@@ -37418,13 +37420,13 @@
         </is>
       </c>
       <c r="G852" s="3" t="n">
-        <v>46325.45833333334</v>
+        <v>46325.58333333334</v>
       </c>
       <c r="H852" s="3" t="n">
-        <v>46325.5</v>
+        <v>46325.625</v>
       </c>
       <c r="I852" s="3" t="n">
-        <v>46326.125</v>
+        <v>46326.25</v>
       </c>
     </row>
     <row r="853">
@@ -37459,13 +37461,13 @@
         </is>
       </c>
       <c r="G853" s="3" t="n">
-        <v>46327.20833333334</v>
+        <v>46327.33333333334</v>
       </c>
       <c r="H853" s="3" t="n">
-        <v>46327.375</v>
+        <v>46327.5</v>
       </c>
       <c r="I853" s="3" t="n">
-        <v>46328.375</v>
+        <v>46328.5</v>
       </c>
     </row>
     <row r="854">
@@ -37500,13 +37502,13 @@
         </is>
       </c>
       <c r="G854" s="3" t="n">
-        <v>46332.58333333334</v>
+        <v>46332.70833333334</v>
       </c>
       <c r="H854" s="3" t="n">
-        <v>46332.70833333334</v>
+        <v>46332.83333333334</v>
       </c>
       <c r="I854" s="3" t="n">
-        <v>46333.20833333334</v>
+        <v>46333.33333333334</v>
       </c>
     </row>
     <row r="855">
@@ -37541,13 +37543,13 @@
         </is>
       </c>
       <c r="G855" s="3" t="n">
-        <v>46334.79166666666</v>
+        <v>46334.91666666666</v>
       </c>
       <c r="H855" s="3" t="n">
-        <v>46334.83333333334</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="I855" s="3" t="n">
-        <v>46335.25</v>
+        <v>46335.375</v>
       </c>
     </row>
     <row r="856">
@@ -37582,13 +37584,13 @@
         </is>
       </c>
       <c r="G856" s="3" t="n">
-        <v>46335.41666666666</v>
+        <v>46335.54166666666</v>
       </c>
       <c r="H856" s="3" t="n">
-        <v>46335.54166666666</v>
+        <v>46335.66666666666</v>
       </c>
       <c r="I856" s="3" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.66666666666</v>
       </c>
     </row>
     <row r="857">
@@ -37623,13 +37625,13 @@
         </is>
       </c>
       <c r="G857" s="3" t="n">
-        <v>46336.79166666666</v>
+        <v>46336.91666666666</v>
       </c>
       <c r="H857" s="3" t="n">
-        <v>46336.83333333334</v>
+        <v>46336.95833333334</v>
       </c>
       <c r="I857" s="3" t="n">
-        <v>46337.25</v>
+        <v>46337.375</v>
       </c>
     </row>
     <row r="858">
@@ -37664,13 +37666,13 @@
         </is>
       </c>
       <c r="G858" s="3" t="n">
-        <v>46338.75</v>
+        <v>46338.875</v>
       </c>
       <c r="H858" s="3" t="n">
-        <v>46338.875</v>
+        <v>46339</v>
       </c>
       <c r="I858" s="3" t="n">
-        <v>46339.375</v>
+        <v>46339.5</v>
       </c>
     </row>
     <row r="859">
@@ -37705,13 +37707,13 @@
         </is>
       </c>
       <c r="G859" s="3" t="n">
-        <v>46344.39583333334</v>
+        <v>46344.52083333334</v>
       </c>
       <c r="H859" s="3" t="n">
-        <v>46344.45833333334</v>
+        <v>46344.58333333334</v>
       </c>
       <c r="I859" s="3" t="n">
-        <v>46344.70833333334</v>
+        <v>46344.83333333334</v>
       </c>
     </row>
     <row r="860">
@@ -37746,13 +37748,13 @@
         </is>
       </c>
       <c r="G860" s="3" t="n">
-        <v>46345.64583333334</v>
+        <v>46345.77083333334</v>
       </c>
       <c r="H860" s="3" t="n">
-        <v>46345.70833333334</v>
+        <v>46345.83333333334</v>
       </c>
       <c r="I860" s="3" t="n">
-        <v>46346.125</v>
+        <v>46346.25</v>
       </c>
     </row>
     <row r="861">
@@ -37787,13 +37789,13 @@
         </is>
       </c>
       <c r="G861" s="3" t="n">
-        <v>46346.45833333334</v>
+        <v>46346.58333333334</v>
       </c>
       <c r="H861" s="3" t="n">
-        <v>46346.5</v>
+        <v>46346.625</v>
       </c>
       <c r="I861" s="3" t="n">
-        <v>46347.125</v>
+        <v>46347.25</v>
       </c>
     </row>
     <row r="862">
@@ -37828,13 +37830,13 @@
         </is>
       </c>
       <c r="G862" s="3" t="n">
-        <v>46348.20833333334</v>
+        <v>46348.33333333334</v>
       </c>
       <c r="H862" s="3" t="n">
-        <v>46348.375</v>
+        <v>46348.5</v>
       </c>
       <c r="I862" s="3" t="n">
-        <v>46349.375</v>
+        <v>46349.5</v>
       </c>
     </row>
     <row r="863">
@@ -37869,13 +37871,13 @@
         </is>
       </c>
       <c r="G863" s="3" t="n">
-        <v>46353.58333333334</v>
+        <v>46353.70833333334</v>
       </c>
       <c r="H863" s="3" t="n">
-        <v>46353.70833333334</v>
+        <v>46353.83333333334</v>
       </c>
       <c r="I863" s="3" t="n">
-        <v>46354.20833333334</v>
+        <v>46354.33333333334</v>
       </c>
     </row>
     <row r="864">
@@ -37910,13 +37912,13 @@
         </is>
       </c>
       <c r="G864" s="3" t="n">
-        <v>46355.79166666666</v>
+        <v>46355.91666666666</v>
       </c>
       <c r="H864" s="3" t="n">
-        <v>46355.83333333334</v>
+        <v>46355.95833333334</v>
       </c>
       <c r="I864" s="3" t="n">
-        <v>46356.25</v>
+        <v>46356.375</v>
       </c>
     </row>
     <row r="865">
@@ -37951,13 +37953,13 @@
         </is>
       </c>
       <c r="G865" s="3" t="n">
-        <v>46356.41666666666</v>
+        <v>46356.54166666666</v>
       </c>
       <c r="H865" s="3" t="n">
-        <v>46356.54166666666</v>
+        <v>46356.66666666666</v>
       </c>
       <c r="I865" s="3" t="n">
-        <v>46357.54166666666</v>
+        <v>46357.66666666666</v>
       </c>
     </row>
     <row r="866">
@@ -37992,13 +37994,13 @@
         </is>
       </c>
       <c r="G866" s="3" t="n">
-        <v>46357.79166666666</v>
+        <v>46357.91666666666</v>
       </c>
       <c r="H866" s="3" t="n">
-        <v>46357.83333333334</v>
+        <v>46357.95833333334</v>
       </c>
       <c r="I866" s="3" t="n">
-        <v>46358.25</v>
+        <v>46358.375</v>
       </c>
     </row>
     <row r="867">
@@ -38031,13 +38033,13 @@
         <v/>
       </c>
       <c r="G867" s="3" t="n">
-        <v>46359.75</v>
+        <v>46359.875</v>
       </c>
       <c r="H867" s="3" t="n">
-        <v>46359.875</v>
+        <v>46360</v>
       </c>
       <c r="I867" s="3" t="n">
-        <v>46360.375</v>
+        <v>46360.5</v>
       </c>
     </row>
     <row r="868">
@@ -49638,10 +49640,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -49679,7 +49681,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260924-1353-SKED.xlsx)</t>
+          <t>New ETA (auto-20260925-0237-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -49732,32 +49734,32 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46298.875</v>
+        <v>46294.125</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46299.875</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -49768,32 +49770,32 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46300.52083333334</v>
+        <v>46296.14583333334</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46301.52083333334</v>
+        <v>46297.60416666666</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -49804,32 +49806,32 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>INNSA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46305.22916666666</v>
+        <v>46300.6875</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46306.22916666666</v>
+        <v>46302.14583333334</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -49840,32 +49842,32 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>INNSA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>INMUN</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46312</v>
+        <v>46313.47916666666</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46313</v>
+        <v>46314.9375</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -49876,32 +49878,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>INMUN</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>PKKHI</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46314.27083333334</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46315.27083333334</v>
+        <v>46317.9375</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -49912,32 +49914,32 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>PKKHI</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>MYPKL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46315.60416666666</v>
+        <v>46317.97916666666</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46316.60416666666</v>
+        <v>46319.4375</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -49948,32 +49950,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>MYPKL</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46317.77083333334</v>
+        <v>46327.52083333334</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46318.77083333334</v>
+        <v>46328.97916666666</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -49984,32 +49986,30 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v/>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46325.64583333334</v>
+        <v>46337.9375</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46326.64583333334</v>
+        <v>46339.39583333334</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -50020,32 +50020,32 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46327.64583333334</v>
+        <v>46289.79166666666</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46328.64583333334</v>
+        <v>46289.91666666666</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -50056,32 +50056,32 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46332.22916666666</v>
+        <v>46291.75</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46333.22916666666</v>
+        <v>46291.875</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -50092,32 +50092,32 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46339.35416666666</v>
+        <v>46297.4375</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46340.35416666666</v>
+        <v>46297.5625</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -50128,32 +50128,32 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46341.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46342.6875</v>
+        <v>46298.8125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -50164,12 +50164,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -50179,17 +50179,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46343.35416666666</v>
+        <v>46299.5</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46344.35416666666</v>
+        <v>46299.625</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -50210,22 +50210,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46345.52083333334</v>
+        <v>46301.25</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46346.52083333334</v>
+        <v>46301.375</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -50236,32 +50236,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46353.39583333334</v>
+        <v>46308.625</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46354.39583333334</v>
+        <v>46308.75</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -50272,32 +50272,32 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46355.39583333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46356.39583333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -50308,32 +50308,32 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46359.97916666666</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46360.97916666666</v>
+        <v>46312.58333333334</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -50344,30 +50344,32 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE RIGEL</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v/>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46367.10416666666</v>
+        <v>46313.83333333334</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>46368.10416666666</v>
+        <v>46313.95833333334</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -50378,862 +50380,682 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46303.25</v>
+        <v>46315.79166666666</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>46301.10416666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46305.16666666666</v>
+        <v>46323.39583333334</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46303.02083333334</v>
+        <v>46323.52083333334</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46306.79166666666</v>
+        <v>46324.64583333334</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>46304.77083333334</v>
+        <v>46324.77083333334</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-48.5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46313.5</v>
+        <v>46325.45833333334</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46312.02083333334</v>
+        <v>46325.58333333334</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-35.5</v>
+        <v>3</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46314.125</v>
+        <v>46327.20833333334</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>46312.64583333334</v>
+        <v>46327.33333333334</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-35.5</v>
+        <v>3</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46315.75</v>
+        <v>46332.58333333334</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>46314.27083333334</v>
+        <v>46332.70833333334</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-35.5</v>
+        <v>3</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46320.08333333334</v>
+        <v>46334.79166666666</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>46318.60416666666</v>
+        <v>46334.91666666666</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-35.5</v>
+        <v>3</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46321.54166666666</v>
+        <v>46335.41666666666</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>46320.0625</v>
+        <v>46335.54166666666</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-35.5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46325.66666666666</v>
+        <v>46336.79166666666</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46323.52083333334</v>
+        <v>46336.91666666666</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46327.33333333334</v>
+        <v>46338.75</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46325.1875</v>
+        <v>46338.875</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46328.95833333334</v>
+        <v>46344.39583333334</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46326.8125</v>
+        <v>46344.52083333334</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46335.66666666666</v>
+        <v>46345.64583333334</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>46333.52083333334</v>
+        <v>46345.77083333334</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46336.29166666666</v>
+        <v>46346.45833333334</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>46334.14583333334</v>
+        <v>46346.58333333334</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46337.91666666666</v>
+        <v>46348.20833333334</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>46335.77083333334</v>
+        <v>46348.33333333334</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46342.25</v>
+        <v>46353.58333333334</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>46340.10416666666</v>
+        <v>46353.70833333334</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>46343.70833333334</v>
+        <v>46355.79166666666</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>46341.5625</v>
+        <v>46355.91666666666</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46346.66666666666</v>
+        <v>46356.41666666666</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>46344.52083333334</v>
+        <v>46356.54166666666</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>46348.33333333334</v>
+        <v>46357.79166666666</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>46346.1875</v>
+        <v>46357.91666666666</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>SAWASDEE MIMOSA</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v/>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>46349.95833333334</v>
+        <v>46359.75</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>46347.8125</v>
+        <v>46359.875</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-51.5</v>
+        <v>3</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TS XIAMEN</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2620S</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46356.66666666666</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>46354.52083333334</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>-51.5</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TS XIAMEN</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2620N</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46357.29166666666</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>46355.14583333334</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>-51.5</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TS XIAMEN</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2620N</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>46358.91666666666</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>46356.77083333334</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>-51.5</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TS XIAMEN</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2620N</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>46363.25</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>46361.10416666666</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>-51.5</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TS XIAMEN</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2620N</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>46364.70833333334</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>46362.5625</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>-51.5</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1255,20 +1255,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to KRINC ~2026-09-26T13:00:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -1321,20 +1323,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v/>
+          <t>KRINC (INC08)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to KRPUS ~2026-09-26T12:00:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
@@ -1491,22 +1495,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
+          <t>VNSGN -&gt; KRINC</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v/>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRINC ~2026-09-25T20:00:00</t>
+          <t>In transit, ETA 2026-10-01T06:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
@@ -1949,22 +1951,20 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>VNSGN -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v/>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-09-25T19:00:00</t>
+          <t>In transit, ETA 2026-10-01T02:00:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -2403,20 +2403,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v/>
+          <t>IDJKT (JKT02)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to VNSGN ~2026-09-28T00:30:00</t>
         </is>
       </c>
       <c r="I31" s="3" t="n"/>
@@ -34390,7 +34392,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -34419,7 +34421,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (prev)</t>
+          <t>Old ETA (auto-20260925-1011-SKED.xlsx)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28959,7 +28959,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -28988,7 +28988,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (prev)</t>
+          <t>Old ETA (9-25-1700-SKED.xls)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1317,22 +1317,20 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>KRINC (INC08)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
+          <t>KRINC -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v/>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-09-26T12:00:00</t>
+          <t>In transit, ETA 2026-09-27T11:30:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1107,20 +1107,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>VNSGN -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH04)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-26T14:00:00</t>
+          <t>Alongside, departs to IDJKT ~2026-09-27T11:00:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="n"/>
@@ -1131,7 +1133,7 @@
         <v/>
       </c>
       <c r="L11" s="3" t="n">
-        <v>46291.58333333334</v>
+        <v>46321.97916666666</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1142,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2608S</t>
         </is>
       </c>
     </row>
@@ -1781,24 +1783,26 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CNSHA -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v/>
+          <t>CNSHA (SHAW1)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-01T05:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-09-28T12:00:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>46296.83333333334</v>
+        <v>46299.875</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -1811,7 +1815,7 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46296.20833333334</v>
+        <v>46299.25</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1922,11 +1926,11 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-26T21:00:00</t>
+          <t>In transit, ETA 2026-09-26T23:00:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>46312.58333333334</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -1939,7 +1943,7 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>46311.95833333334</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1988,7 +1992,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to IDJKT ~2026-09-27T21:00:00</t>
+          <t>Alongside, departs to IDJKT ~2026-09-27T08:00:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
@@ -1999,7 +2003,7 @@
         <v/>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46306.22916666666</v>
+        <v>46305.6875</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2048,11 +2052,11 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-09-27T07:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-09-28T10:00:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46300.45833333334</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2065,7 +2069,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>46298.70833333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -2099,22 +2103,20 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>CNXMN (XMN01)</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>CNXMN -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v/>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-09-26T20:00:00</t>
+          <t>In transit, ETA 2026-09-29T05:00:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
@@ -2426,7 +2428,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-27T01:00:00</t>
+          <t>In transit, ETA 2026-09-27T00:00:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
@@ -32775,10 +32777,10 @@
         <v>46288.5</v>
       </c>
       <c r="H740" s="3" t="n">
-        <v>46289.66666666666</v>
+        <v>46293.22916666666</v>
       </c>
       <c r="I740" s="3" t="n">
-        <v>46290.45833333334</v>
+        <v>46293.5</v>
       </c>
     </row>
     <row r="741">
@@ -32813,13 +32815,13 @@
         </is>
       </c>
       <c r="G741" s="3" t="n">
-        <v>46296.20833333334</v>
+        <v>46299.25</v>
       </c>
       <c r="H741" s="3" t="n">
-        <v>46296.25</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="I741" s="3" t="n">
-        <v>46296.54166666666</v>
+        <v>46299.58333333334</v>
       </c>
     </row>
     <row r="742">
@@ -32854,13 +32856,13 @@
         </is>
       </c>
       <c r="G742" s="3" t="n">
-        <v>46296.83333333334</v>
+        <v>46299.875</v>
       </c>
       <c r="H742" s="3" t="n">
-        <v>46296.83333333334</v>
+        <v>46299.875</v>
       </c>
       <c r="I742" s="3" t="n">
-        <v>46298.20833333334</v>
+        <v>46301.25</v>
       </c>
     </row>
     <row r="743">
@@ -32895,13 +32897,13 @@
         </is>
       </c>
       <c r="G743" s="3" t="n">
-        <v>46298.45833333334</v>
+        <v>46301.5</v>
       </c>
       <c r="H743" s="3" t="n">
-        <v>46298.5</v>
+        <v>46301.54166666666</v>
       </c>
       <c r="I743" s="3" t="n">
-        <v>46298.95833333334</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="744">
@@ -32936,13 +32938,13 @@
         </is>
       </c>
       <c r="G744" s="3" t="n">
-        <v>46302.79166666666</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="H744" s="3" t="n">
-        <v>46302.79166666666</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="I744" s="3" t="n">
-        <v>46303.25</v>
+        <v>46306.29166666666</v>
       </c>
     </row>
     <row r="745">
@@ -32977,13 +32979,13 @@
         </is>
       </c>
       <c r="G745" s="3" t="n">
-        <v>46304.25</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="H745" s="3" t="n">
-        <v>46304.25</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="I745" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46307.75</v>
       </c>
     </row>
     <row r="746">
@@ -33018,13 +33020,13 @@
         </is>
       </c>
       <c r="G746" s="3" t="n">
-        <v>46307.1875</v>
+        <v>46310.22916666666</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>46307.22916666666</v>
+        <v>46310.27083333334</v>
       </c>
       <c r="I746" s="3" t="n">
-        <v>46307.85416666666</v>
+        <v>46310.89583333334</v>
       </c>
     </row>
     <row r="747">
@@ -33059,13 +33061,13 @@
         </is>
       </c>
       <c r="G747" s="3" t="n">
-        <v>46308.85416666666</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="H747" s="3" t="n">
-        <v>46308.89583333334</v>
+        <v>46311.9375</v>
       </c>
       <c r="I747" s="3" t="n">
-        <v>46309.39583333334</v>
+        <v>46312.4375</v>
       </c>
     </row>
     <row r="748">
@@ -33100,13 +33102,13 @@
         </is>
       </c>
       <c r="G748" s="3" t="n">
-        <v>46310.47916666666</v>
+        <v>46313.52083333334</v>
       </c>
       <c r="H748" s="3" t="n">
-        <v>46310.64583333334</v>
+        <v>46313.6875</v>
       </c>
       <c r="I748" s="3" t="n">
-        <v>46311.4375</v>
+        <v>46314.47916666666</v>
       </c>
     </row>
     <row r="749">
@@ -33141,13 +33143,13 @@
         </is>
       </c>
       <c r="G749" s="3" t="n">
-        <v>46317.1875</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="H749" s="3" t="n">
-        <v>46317.22916666666</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="I749" s="3" t="n">
-        <v>46317.52083333334</v>
+        <v>46320.5625</v>
       </c>
     </row>
     <row r="750">
@@ -33182,13 +33184,13 @@
         </is>
       </c>
       <c r="G750" s="3" t="n">
-        <v>46317.8125</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="H750" s="3" t="n">
-        <v>46317.8125</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="I750" s="3" t="n">
-        <v>46319.1875</v>
+        <v>46322.22916666666</v>
       </c>
     </row>
     <row r="751">
@@ -33223,13 +33225,13 @@
         </is>
       </c>
       <c r="G751" s="3" t="n">
-        <v>46319.4375</v>
+        <v>46322.47916666666</v>
       </c>
       <c r="H751" s="3" t="n">
-        <v>46319.47916666666</v>
+        <v>46322.52083333334</v>
       </c>
       <c r="I751" s="3" t="n">
-        <v>46319.9375</v>
+        <v>46322.97916666666</v>
       </c>
     </row>
     <row r="752">
@@ -33264,13 +33266,13 @@
         </is>
       </c>
       <c r="G752" s="3" t="n">
-        <v>46323.77083333334</v>
+        <v>46326.8125</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>46323.77083333334</v>
+        <v>46326.8125</v>
       </c>
       <c r="I752" s="3" t="n">
-        <v>46324.22916666666</v>
+        <v>46327.27083333334</v>
       </c>
     </row>
     <row r="753">
@@ -33305,13 +33307,13 @@
         </is>
       </c>
       <c r="G753" s="3" t="n">
-        <v>46325.22916666666</v>
+        <v>46328.27083333334</v>
       </c>
       <c r="H753" s="3" t="n">
-        <v>46325.22916666666</v>
+        <v>46328.27083333334</v>
       </c>
       <c r="I753" s="3" t="n">
-        <v>46325.72916666666</v>
+        <v>46328.77083333334</v>
       </c>
     </row>
     <row r="754">
@@ -33346,13 +33348,13 @@
         </is>
       </c>
       <c r="G754" s="3" t="n">
-        <v>46328.1875</v>
+        <v>46331.22916666666</v>
       </c>
       <c r="H754" s="3" t="n">
-        <v>46328.22916666666</v>
+        <v>46331.27083333334</v>
       </c>
       <c r="I754" s="3" t="n">
-        <v>46328.85416666666</v>
+        <v>46331.89583333334</v>
       </c>
     </row>
     <row r="755">
@@ -33387,13 +33389,13 @@
         </is>
       </c>
       <c r="G755" s="3" t="n">
-        <v>46329.85416666666</v>
+        <v>46332.89583333334</v>
       </c>
       <c r="H755" s="3" t="n">
-        <v>46329.89583333334</v>
+        <v>46332.9375</v>
       </c>
       <c r="I755" s="3" t="n">
-        <v>46330.39583333334</v>
+        <v>46333.4375</v>
       </c>
     </row>
     <row r="756">
@@ -33428,13 +33430,13 @@
         </is>
       </c>
       <c r="G756" s="3" t="n">
-        <v>46331.47916666666</v>
+        <v>46334.52083333334</v>
       </c>
       <c r="H756" s="3" t="n">
-        <v>46331.64583333334</v>
+        <v>46334.6875</v>
       </c>
       <c r="I756" s="3" t="n">
-        <v>46332.4375</v>
+        <v>46335.47916666666</v>
       </c>
     </row>
     <row r="757">
@@ -33469,13 +33471,13 @@
         </is>
       </c>
       <c r="G757" s="3" t="n">
-        <v>46338.1875</v>
+        <v>46341.22916666666</v>
       </c>
       <c r="H757" s="3" t="n">
-        <v>46338.22916666666</v>
+        <v>46341.27083333334</v>
       </c>
       <c r="I757" s="3" t="n">
-        <v>46338.52083333334</v>
+        <v>46341.5625</v>
       </c>
     </row>
     <row r="758">
@@ -33510,13 +33512,13 @@
         </is>
       </c>
       <c r="G758" s="3" t="n">
-        <v>46338.8125</v>
+        <v>46341.85416666666</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>46338.8125</v>
+        <v>46341.85416666666</v>
       </c>
       <c r="I758" s="3" t="n">
-        <v>46340.1875</v>
+        <v>46343.22916666666</v>
       </c>
     </row>
     <row r="759">
@@ -33551,13 +33553,13 @@
         </is>
       </c>
       <c r="G759" s="3" t="n">
-        <v>46340.4375</v>
+        <v>46343.47916666666</v>
       </c>
       <c r="H759" s="3" t="n">
-        <v>46340.47916666666</v>
+        <v>46343.52083333334</v>
       </c>
       <c r="I759" s="3" t="n">
-        <v>46340.9375</v>
+        <v>46343.97916666666</v>
       </c>
     </row>
     <row r="760">
@@ -33592,13 +33594,13 @@
         </is>
       </c>
       <c r="G760" s="3" t="n">
-        <v>46344.77083333334</v>
+        <v>46347.8125</v>
       </c>
       <c r="H760" s="3" t="n">
-        <v>46344.77083333334</v>
+        <v>46347.8125</v>
       </c>
       <c r="I760" s="3" t="n">
-        <v>46345.22916666666</v>
+        <v>46348.27083333334</v>
       </c>
     </row>
     <row r="761">
@@ -33633,13 +33635,13 @@
         </is>
       </c>
       <c r="G761" s="3" t="n">
-        <v>46346.22916666666</v>
+        <v>46349.27083333334</v>
       </c>
       <c r="H761" s="3" t="n">
-        <v>46346.22916666666</v>
+        <v>46349.27083333334</v>
       </c>
       <c r="I761" s="3" t="n">
-        <v>46346.72916666666</v>
+        <v>46349.77083333334</v>
       </c>
     </row>
     <row r="762">
@@ -33674,13 +33676,13 @@
         </is>
       </c>
       <c r="G762" s="3" t="n">
-        <v>46349.1875</v>
+        <v>46352.22916666666</v>
       </c>
       <c r="H762" s="3" t="n">
-        <v>46349.22916666666</v>
+        <v>46352.27083333334</v>
       </c>
       <c r="I762" s="3" t="n">
-        <v>46349.85416666666</v>
+        <v>46352.89583333334</v>
       </c>
     </row>
     <row r="763">
@@ -33715,13 +33717,13 @@
         </is>
       </c>
       <c r="G763" s="3" t="n">
-        <v>46350.85416666666</v>
+        <v>46353.89583333334</v>
       </c>
       <c r="H763" s="3" t="n">
-        <v>46350.89583333334</v>
+        <v>46353.9375</v>
       </c>
       <c r="I763" s="3" t="n">
-        <v>46351.39583333334</v>
+        <v>46354.4375</v>
       </c>
     </row>
     <row r="764">
@@ -33756,13 +33758,13 @@
         </is>
       </c>
       <c r="G764" s="3" t="n">
-        <v>46352.47916666666</v>
+        <v>46355.52083333334</v>
       </c>
       <c r="H764" s="3" t="n">
-        <v>46352.64583333334</v>
+        <v>46355.6875</v>
       </c>
       <c r="I764" s="3" t="n">
-        <v>46353.4375</v>
+        <v>46356.47916666666</v>
       </c>
     </row>
     <row r="765">
@@ -33797,13 +33799,13 @@
         </is>
       </c>
       <c r="G765" s="3" t="n">
-        <v>46359.1875</v>
+        <v>46362.22916666666</v>
       </c>
       <c r="H765" s="3" t="n">
-        <v>46359.22916666666</v>
+        <v>46362.27083333334</v>
       </c>
       <c r="I765" s="3" t="n">
-        <v>46359.52083333334</v>
+        <v>46362.5625</v>
       </c>
     </row>
     <row r="766">
@@ -33838,13 +33840,13 @@
         </is>
       </c>
       <c r="G766" s="3" t="n">
-        <v>46359.8125</v>
+        <v>46362.85416666666</v>
       </c>
       <c r="H766" s="3" t="n">
-        <v>46359.8125</v>
+        <v>46362.85416666666</v>
       </c>
       <c r="I766" s="3" t="n">
-        <v>46361.1875</v>
+        <v>46364.22916666666</v>
       </c>
     </row>
     <row r="767">
@@ -33879,13 +33881,13 @@
         </is>
       </c>
       <c r="G767" s="3" t="n">
-        <v>46361.4375</v>
+        <v>46364.47916666666</v>
       </c>
       <c r="H767" s="3" t="n">
-        <v>46361.47916666666</v>
+        <v>46364.52083333334</v>
       </c>
       <c r="I767" s="3" t="n">
-        <v>46361.9375</v>
+        <v>46364.97916666666</v>
       </c>
     </row>
     <row r="768">
@@ -33920,13 +33922,13 @@
         </is>
       </c>
       <c r="G768" s="3" t="n">
-        <v>46365.77083333334</v>
+        <v>46368.8125</v>
       </c>
       <c r="H768" s="3" t="n">
-        <v>46365.77083333334</v>
+        <v>46368.8125</v>
       </c>
       <c r="I768" s="3" t="n">
-        <v>46366.22916666666</v>
+        <v>46369.27083333334</v>
       </c>
     </row>
     <row r="769">
@@ -33959,13 +33961,13 @@
         <v/>
       </c>
       <c r="G769" s="3" t="n">
-        <v>46367.22916666666</v>
+        <v>46370.27083333334</v>
       </c>
       <c r="H769" s="3" t="n">
-        <v>46367.22916666666</v>
+        <v>46370.27083333334</v>
       </c>
       <c r="I769" s="3" t="n">
-        <v>46367.72916666666</v>
+        <v>46370.77083333334</v>
       </c>
     </row>
     <row r="770">
@@ -35931,7 +35933,7 @@
         <v>46289.95416666667</v>
       </c>
       <c r="I817" s="3" t="n">
-        <v>46290.375</v>
+        <v>46290.45416666667</v>
       </c>
     </row>
     <row r="818">
@@ -35966,13 +35968,13 @@
         </is>
       </c>
       <c r="G818" s="3" t="n">
-        <v>46291.875</v>
+        <v>46291.95833333334</v>
       </c>
       <c r="H818" s="3" t="n">
-        <v>46292.04166666666</v>
+        <v>46293</v>
       </c>
       <c r="I818" s="3" t="n">
-        <v>46292.54166666666</v>
+        <v>46293.5</v>
       </c>
     </row>
     <row r="819">
@@ -36007,13 +36009,13 @@
         </is>
       </c>
       <c r="G819" s="3" t="n">
-        <v>46297.5625</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="H819" s="3" t="n">
-        <v>46297.625</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="I819" s="3" t="n">
-        <v>46297.875</v>
+        <v>46298.83333333334</v>
       </c>
     </row>
     <row r="820">
@@ -36048,13 +36050,13 @@
         </is>
       </c>
       <c r="G820" s="3" t="n">
-        <v>46298.8125</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>46298.875</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="I820" s="3" t="n">
-        <v>46299.29166666666</v>
+        <v>46300.25</v>
       </c>
     </row>
     <row r="821">
@@ -36089,13 +36091,13 @@
         </is>
       </c>
       <c r="G821" s="3" t="n">
-        <v>46299.625</v>
+        <v>46300.58333333334</v>
       </c>
       <c r="H821" s="3" t="n">
-        <v>46299.66666666666</v>
+        <v>46300.625</v>
       </c>
       <c r="I821" s="3" t="n">
-        <v>46300.29166666666</v>
+        <v>46301.25</v>
       </c>
     </row>
     <row r="822">
@@ -36130,13 +36132,13 @@
         </is>
       </c>
       <c r="G822" s="3" t="n">
-        <v>46301.375</v>
+        <v>46302.33333333334</v>
       </c>
       <c r="H822" s="3" t="n">
-        <v>46303.54166666666</v>
+        <v>46304.5</v>
       </c>
       <c r="I822" s="3" t="n">
-        <v>46304.54166666666</v>
+        <v>46305.5</v>
       </c>
     </row>
     <row r="823">
@@ -36171,13 +36173,13 @@
         </is>
       </c>
       <c r="G823" s="3" t="n">
-        <v>46308.75</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="H823" s="3" t="n">
-        <v>46309.875</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="I823" s="3" t="n">
-        <v>46310.375</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="824">
@@ -36212,13 +36214,13 @@
         </is>
       </c>
       <c r="G824" s="3" t="n">
-        <v>46311.95833333334</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="H824" s="3" t="n">
-        <v>46312</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="I824" s="3" t="n">
-        <v>46312.41666666666</v>
+        <v>46313.375</v>
       </c>
     </row>
     <row r="825">
@@ -36253,13 +36255,13 @@
         </is>
       </c>
       <c r="G825" s="3" t="n">
-        <v>46312.58333333334</v>
+        <v>46313.54166666666</v>
       </c>
       <c r="H825" s="3" t="n">
-        <v>46312.70833333334</v>
+        <v>46313.66666666666</v>
       </c>
       <c r="I825" s="3" t="n">
-        <v>46313.70833333334</v>
+        <v>46314.66666666666</v>
       </c>
     </row>
     <row r="826">
@@ -36294,13 +36296,13 @@
         </is>
       </c>
       <c r="G826" s="3" t="n">
-        <v>46313.95833333334</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="H826" s="3" t="n">
-        <v>46314</v>
+        <v>46314.95833333334</v>
       </c>
       <c r="I826" s="3" t="n">
-        <v>46314.41666666666</v>
+        <v>46315.375</v>
       </c>
     </row>
     <row r="827">
@@ -36335,13 +36337,13 @@
         </is>
       </c>
       <c r="G827" s="3" t="n">
-        <v>46315.91666666666</v>
+        <v>46316.875</v>
       </c>
       <c r="H827" s="3" t="n">
-        <v>46317.04166666666</v>
+        <v>46318</v>
       </c>
       <c r="I827" s="3" t="n">
-        <v>46317.54166666666</v>
+        <v>46318.5</v>
       </c>
     </row>
     <row r="828">
@@ -36376,13 +36378,13 @@
         </is>
       </c>
       <c r="G828" s="3" t="n">
-        <v>46323.52083333334</v>
+        <v>46324.47916666666</v>
       </c>
       <c r="H828" s="3" t="n">
-        <v>46323.58333333334</v>
+        <v>46324.54166666666</v>
       </c>
       <c r="I828" s="3" t="n">
-        <v>46323.83333333334</v>
+        <v>46324.79166666666</v>
       </c>
     </row>
     <row r="829">
@@ -36417,13 +36419,13 @@
         </is>
       </c>
       <c r="G829" s="3" t="n">
-        <v>46324.77083333334</v>
+        <v>46325.72916666666</v>
       </c>
       <c r="H829" s="3" t="n">
-        <v>46324.83333333334</v>
+        <v>46325.79166666666</v>
       </c>
       <c r="I829" s="3" t="n">
-        <v>46325.25</v>
+        <v>46326.20833333334</v>
       </c>
     </row>
     <row r="830">
@@ -36458,13 +36460,13 @@
         </is>
       </c>
       <c r="G830" s="3" t="n">
-        <v>46325.58333333334</v>
+        <v>46326.54166666666</v>
       </c>
       <c r="H830" s="3" t="n">
-        <v>46325.625</v>
+        <v>46326.58333333334</v>
       </c>
       <c r="I830" s="3" t="n">
-        <v>46326.25</v>
+        <v>46327.20833333334</v>
       </c>
     </row>
     <row r="831">
@@ -36499,13 +36501,13 @@
         </is>
       </c>
       <c r="G831" s="3" t="n">
-        <v>46327.33333333334</v>
+        <v>46328.29166666666</v>
       </c>
       <c r="H831" s="3" t="n">
-        <v>46327.5</v>
+        <v>46328.45833333334</v>
       </c>
       <c r="I831" s="3" t="n">
-        <v>46328.5</v>
+        <v>46329.45833333334</v>
       </c>
     </row>
     <row r="832">
@@ -36540,13 +36542,13 @@
         </is>
       </c>
       <c r="G832" s="3" t="n">
-        <v>46332.70833333334</v>
+        <v>46333.66666666666</v>
       </c>
       <c r="H832" s="3" t="n">
-        <v>46332.83333333334</v>
+        <v>46333.79166666666</v>
       </c>
       <c r="I832" s="3" t="n">
-        <v>46333.33333333334</v>
+        <v>46334.29166666666</v>
       </c>
     </row>
     <row r="833">
@@ -36581,13 +36583,13 @@
         </is>
       </c>
       <c r="G833" s="3" t="n">
-        <v>46334.91666666666</v>
+        <v>46335.875</v>
       </c>
       <c r="H833" s="3" t="n">
-        <v>46334.95833333334</v>
+        <v>46335.91666666666</v>
       </c>
       <c r="I833" s="3" t="n">
-        <v>46335.375</v>
+        <v>46336.33333333334</v>
       </c>
     </row>
     <row r="834">
@@ -36622,13 +36624,13 @@
         </is>
       </c>
       <c r="G834" s="3" t="n">
-        <v>46335.54166666666</v>
+        <v>46336.5</v>
       </c>
       <c r="H834" s="3" t="n">
-        <v>46335.66666666666</v>
+        <v>46336.625</v>
       </c>
       <c r="I834" s="3" t="n">
-        <v>46336.66666666666</v>
+        <v>46337.625</v>
       </c>
     </row>
     <row r="835">
@@ -36663,13 +36665,13 @@
         </is>
       </c>
       <c r="G835" s="3" t="n">
-        <v>46336.91666666666</v>
+        <v>46337.875</v>
       </c>
       <c r="H835" s="3" t="n">
-        <v>46336.95833333334</v>
+        <v>46337.91666666666</v>
       </c>
       <c r="I835" s="3" t="n">
-        <v>46337.375</v>
+        <v>46338.33333333334</v>
       </c>
     </row>
     <row r="836">
@@ -36704,13 +36706,13 @@
         </is>
       </c>
       <c r="G836" s="3" t="n">
-        <v>46338.875</v>
+        <v>46339.83333333334</v>
       </c>
       <c r="H836" s="3" t="n">
-        <v>46339</v>
+        <v>46339.95833333334</v>
       </c>
       <c r="I836" s="3" t="n">
-        <v>46339.5</v>
+        <v>46340.45833333334</v>
       </c>
     </row>
     <row r="837">
@@ -36745,13 +36747,13 @@
         </is>
       </c>
       <c r="G837" s="3" t="n">
-        <v>46344.52083333334</v>
+        <v>46345.47916666666</v>
       </c>
       <c r="H837" s="3" t="n">
-        <v>46344.58333333334</v>
+        <v>46345.54166666666</v>
       </c>
       <c r="I837" s="3" t="n">
-        <v>46344.83333333334</v>
+        <v>46345.79166666666</v>
       </c>
     </row>
     <row r="838">
@@ -36786,13 +36788,13 @@
         </is>
       </c>
       <c r="G838" s="3" t="n">
-        <v>46345.77083333334</v>
+        <v>46346.72916666666</v>
       </c>
       <c r="H838" s="3" t="n">
-        <v>46345.83333333334</v>
+        <v>46346.79166666666</v>
       </c>
       <c r="I838" s="3" t="n">
-        <v>46346.25</v>
+        <v>46347.20833333334</v>
       </c>
     </row>
     <row r="839">
@@ -36827,13 +36829,13 @@
         </is>
       </c>
       <c r="G839" s="3" t="n">
-        <v>46346.58333333334</v>
+        <v>46347.54166666666</v>
       </c>
       <c r="H839" s="3" t="n">
-        <v>46346.625</v>
+        <v>46347.58333333334</v>
       </c>
       <c r="I839" s="3" t="n">
-        <v>46347.25</v>
+        <v>46348.20833333334</v>
       </c>
     </row>
     <row r="840">
@@ -36868,13 +36870,13 @@
         </is>
       </c>
       <c r="G840" s="3" t="n">
-        <v>46348.33333333334</v>
+        <v>46349.29166666666</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>46348.5</v>
+        <v>46349.45833333334</v>
       </c>
       <c r="I840" s="3" t="n">
-        <v>46349.5</v>
+        <v>46350.45833333334</v>
       </c>
     </row>
     <row r="841">
@@ -36909,13 +36911,13 @@
         </is>
       </c>
       <c r="G841" s="3" t="n">
-        <v>46353.70833333334</v>
+        <v>46354.66666666666</v>
       </c>
       <c r="H841" s="3" t="n">
-        <v>46353.83333333334</v>
+        <v>46354.79166666666</v>
       </c>
       <c r="I841" s="3" t="n">
-        <v>46354.33333333334</v>
+        <v>46355.29166666666</v>
       </c>
     </row>
     <row r="842">
@@ -36950,13 +36952,13 @@
         </is>
       </c>
       <c r="G842" s="3" t="n">
-        <v>46355.91666666666</v>
+        <v>46356.875</v>
       </c>
       <c r="H842" s="3" t="n">
-        <v>46355.95833333334</v>
+        <v>46356.91666666666</v>
       </c>
       <c r="I842" s="3" t="n">
-        <v>46356.375</v>
+        <v>46357.33333333334</v>
       </c>
     </row>
     <row r="843">
@@ -36991,13 +36993,13 @@
         </is>
       </c>
       <c r="G843" s="3" t="n">
-        <v>46356.54166666666</v>
+        <v>46357.5</v>
       </c>
       <c r="H843" s="3" t="n">
-        <v>46356.66666666666</v>
+        <v>46357.625</v>
       </c>
       <c r="I843" s="3" t="n">
-        <v>46357.66666666666</v>
+        <v>46358.625</v>
       </c>
     </row>
     <row r="844">
@@ -37032,13 +37034,13 @@
         </is>
       </c>
       <c r="G844" s="3" t="n">
-        <v>46357.91666666666</v>
+        <v>46358.875</v>
       </c>
       <c r="H844" s="3" t="n">
-        <v>46357.95833333334</v>
+        <v>46358.91666666666</v>
       </c>
       <c r="I844" s="3" t="n">
-        <v>46358.375</v>
+        <v>46359.33333333334</v>
       </c>
     </row>
     <row r="845">
@@ -37071,13 +37073,13 @@
         <v/>
       </c>
       <c r="G845" s="3" t="n">
-        <v>46359.875</v>
+        <v>46360.83333333334</v>
       </c>
       <c r="H845" s="3" t="n">
-        <v>46360</v>
+        <v>46360.95833333334</v>
       </c>
       <c r="I845" s="3" t="n">
-        <v>46360.5</v>
+        <v>46361.45833333334</v>
       </c>
     </row>
     <row r="846">
@@ -37443,10 +37445,10 @@
         <v>46287.79166666666</v>
       </c>
       <c r="H854" s="3" t="n">
-        <v>46291.95833333334</v>
+        <v>46291.50416666667</v>
       </c>
       <c r="I854" s="3" t="n">
-        <v>46292.875</v>
+        <v>46292.33333333334</v>
       </c>
     </row>
     <row r="855">
@@ -37481,13 +37483,13 @@
         </is>
       </c>
       <c r="G855" s="3" t="n">
-        <v>46299.875</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="H855" s="3" t="n">
-        <v>46299.95833333334</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="I855" s="3" t="n">
-        <v>46300.79166666666</v>
+        <v>46300.25</v>
       </c>
     </row>
     <row r="856">
@@ -37522,13 +37524,13 @@
         </is>
       </c>
       <c r="G856" s="3" t="n">
-        <v>46301.52083333334</v>
+        <v>46300.97916666666</v>
       </c>
       <c r="H856" s="3" t="n">
-        <v>46301.60416666666</v>
+        <v>46301.0625</v>
       </c>
       <c r="I856" s="3" t="n">
-        <v>46302.5</v>
+        <v>46301.95833333334</v>
       </c>
     </row>
     <row r="857">
@@ -37563,13 +37565,13 @@
         </is>
       </c>
       <c r="G857" s="3" t="n">
-        <v>46306.22916666666</v>
+        <v>46305.6875</v>
       </c>
       <c r="H857" s="3" t="n">
-        <v>46306.27083333334</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="I857" s="3" t="n">
-        <v>46306.9375</v>
+        <v>46306.39583333334</v>
       </c>
     </row>
     <row r="858">
@@ -37604,13 +37606,13 @@
         </is>
       </c>
       <c r="G858" s="3" t="n">
-        <v>46313</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="H858" s="3" t="n">
-        <v>46313.20833333334</v>
+        <v>46312.66666666666</v>
       </c>
       <c r="I858" s="3" t="n">
-        <v>46313.875</v>
+        <v>46313.33333333334</v>
       </c>
     </row>
     <row r="859">
@@ -37645,13 +37647,13 @@
         </is>
       </c>
       <c r="G859" s="3" t="n">
-        <v>46315.27083333334</v>
+        <v>46314.72916666666</v>
       </c>
       <c r="H859" s="3" t="n">
-        <v>46315.3125</v>
+        <v>46314.77083333334</v>
       </c>
       <c r="I859" s="3" t="n">
-        <v>46316.3125</v>
+        <v>46315.77083333334</v>
       </c>
     </row>
     <row r="860">
@@ -37686,13 +37688,13 @@
         </is>
       </c>
       <c r="G860" s="3" t="n">
-        <v>46316.60416666666</v>
+        <v>46316.0625</v>
       </c>
       <c r="H860" s="3" t="n">
-        <v>46316.64583333334</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="I860" s="3" t="n">
-        <v>46317.27083333334</v>
+        <v>46316.72916666666</v>
       </c>
     </row>
     <row r="861">
@@ -37727,13 +37729,13 @@
         </is>
       </c>
       <c r="G861" s="3" t="n">
-        <v>46318.77083333334</v>
+        <v>46318.22916666666</v>
       </c>
       <c r="H861" s="3" t="n">
-        <v>46318.97916666666</v>
+        <v>46318.4375</v>
       </c>
       <c r="I861" s="3" t="n">
-        <v>46319.64583333334</v>
+        <v>46319.10416666666</v>
       </c>
     </row>
     <row r="862">
@@ -37768,13 +37770,13 @@
         </is>
       </c>
       <c r="G862" s="3" t="n">
-        <v>46326.64583333334</v>
+        <v>46326.10416666666</v>
       </c>
       <c r="H862" s="3" t="n">
-        <v>46326.72916666666</v>
+        <v>46326.1875</v>
       </c>
       <c r="I862" s="3" t="n">
-        <v>46327.5625</v>
+        <v>46327.02083333334</v>
       </c>
     </row>
     <row r="863">
@@ -37809,13 +37811,13 @@
         </is>
       </c>
       <c r="G863" s="3" t="n">
-        <v>46328.64583333334</v>
+        <v>46328.10416666666</v>
       </c>
       <c r="H863" s="3" t="n">
-        <v>46328.72916666666</v>
+        <v>46328.1875</v>
       </c>
       <c r="I863" s="3" t="n">
-        <v>46329.22916666666</v>
+        <v>46328.6875</v>
       </c>
     </row>
     <row r="864">
@@ -37850,13 +37852,13 @@
         </is>
       </c>
       <c r="G864" s="3" t="n">
-        <v>46333.22916666666</v>
+        <v>46332.6875</v>
       </c>
       <c r="H864" s="3" t="n">
-        <v>46333.27083333334</v>
+        <v>46332.72916666666</v>
       </c>
       <c r="I864" s="3" t="n">
-        <v>46333.9375</v>
+        <v>46333.39583333334</v>
       </c>
     </row>
     <row r="865">
@@ -37891,13 +37893,13 @@
         </is>
       </c>
       <c r="G865" s="3" t="n">
-        <v>46340.35416666666</v>
+        <v>46339.8125</v>
       </c>
       <c r="H865" s="3" t="n">
-        <v>46340.5625</v>
+        <v>46340.02083333334</v>
       </c>
       <c r="I865" s="3" t="n">
-        <v>46341.22916666666</v>
+        <v>46340.6875</v>
       </c>
     </row>
     <row r="866">
@@ -37932,13 +37934,13 @@
         </is>
       </c>
       <c r="G866" s="3" t="n">
-        <v>46342.6875</v>
+        <v>46342.14583333334</v>
       </c>
       <c r="H866" s="3" t="n">
-        <v>46342.72916666666</v>
+        <v>46342.1875</v>
       </c>
       <c r="I866" s="3" t="n">
-        <v>46343.72916666666</v>
+        <v>46343.1875</v>
       </c>
     </row>
     <row r="867">
@@ -37973,13 +37975,13 @@
         </is>
       </c>
       <c r="G867" s="3" t="n">
-        <v>46344.35416666666</v>
+        <v>46343.8125</v>
       </c>
       <c r="H867" s="3" t="n">
-        <v>46344.39583333334</v>
+        <v>46343.85416666666</v>
       </c>
       <c r="I867" s="3" t="n">
-        <v>46345.02083333334</v>
+        <v>46344.47916666666</v>
       </c>
     </row>
     <row r="868">
@@ -38014,13 +38016,13 @@
         </is>
       </c>
       <c r="G868" s="3" t="n">
-        <v>46346.52083333334</v>
+        <v>46345.97916666666</v>
       </c>
       <c r="H868" s="3" t="n">
-        <v>46346.72916666666</v>
+        <v>46346.1875</v>
       </c>
       <c r="I868" s="3" t="n">
-        <v>46347.39583333334</v>
+        <v>46346.85416666666</v>
       </c>
     </row>
     <row r="869">
@@ -38055,13 +38057,13 @@
         </is>
       </c>
       <c r="G869" s="3" t="n">
-        <v>46354.39583333334</v>
+        <v>46353.85416666666</v>
       </c>
       <c r="H869" s="3" t="n">
-        <v>46354.47916666666</v>
+        <v>46353.9375</v>
       </c>
       <c r="I869" s="3" t="n">
-        <v>46355.3125</v>
+        <v>46354.77083333334</v>
       </c>
     </row>
     <row r="870">
@@ -38096,13 +38098,13 @@
         </is>
       </c>
       <c r="G870" s="3" t="n">
-        <v>46356.39583333334</v>
+        <v>46355.85416666666</v>
       </c>
       <c r="H870" s="3" t="n">
-        <v>46356.47916666666</v>
+        <v>46355.9375</v>
       </c>
       <c r="I870" s="3" t="n">
-        <v>46356.97916666666</v>
+        <v>46356.4375</v>
       </c>
     </row>
     <row r="871">
@@ -38137,13 +38139,13 @@
         </is>
       </c>
       <c r="G871" s="3" t="n">
-        <v>46360.97916666666</v>
+        <v>46360.4375</v>
       </c>
       <c r="H871" s="3" t="n">
-        <v>46361.02083333334</v>
+        <v>46360.47916666666</v>
       </c>
       <c r="I871" s="3" t="n">
-        <v>46361.6875</v>
+        <v>46361.14583333334</v>
       </c>
     </row>
     <row r="872">
@@ -38176,13 +38178,13 @@
         <v/>
       </c>
       <c r="G872" s="3" t="n">
-        <v>46368.10416666666</v>
+        <v>46367.5625</v>
       </c>
       <c r="H872" s="3" t="n">
-        <v>46368.3125</v>
+        <v>46367.77083333334</v>
       </c>
       <c r="I872" s="3" t="n">
-        <v>46368.97916666666</v>
+        <v>46368.4375</v>
       </c>
     </row>
     <row r="873">
@@ -38712,10 +38714,10 @@
         <v>46287.125</v>
       </c>
       <c r="H885" s="3" t="n">
-        <v>46291.29166666666</v>
+        <v>46292.41666666666</v>
       </c>
       <c r="I885" s="3" t="n">
-        <v>46292.29166666666</v>
+        <v>46293.41666666666</v>
       </c>
     </row>
     <row r="886">
@@ -38750,13 +38752,13 @@
         </is>
       </c>
       <c r="G886" s="3" t="n">
-        <v>46296.5</v>
+        <v>46297.625</v>
       </c>
       <c r="H886" s="3" t="n">
-        <v>46296.625</v>
+        <v>46297.75</v>
       </c>
       <c r="I886" s="3" t="n">
-        <v>46297.125</v>
+        <v>46298.25</v>
       </c>
     </row>
     <row r="887">
@@ -38791,13 +38793,13 @@
         </is>
       </c>
       <c r="G887" s="3" t="n">
-        <v>46298.70833333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="H887" s="3" t="n">
-        <v>46298.75</v>
+        <v>46299.875</v>
       </c>
       <c r="I887" s="3" t="n">
-        <v>46299.16666666666</v>
+        <v>46300.29166666666</v>
       </c>
     </row>
     <row r="888">
@@ -38832,13 +38834,13 @@
         </is>
       </c>
       <c r="G888" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46300.45833333334</v>
       </c>
       <c r="H888" s="3" t="n">
-        <v>46299.45833333334</v>
+        <v>46300.58333333334</v>
       </c>
       <c r="I888" s="3" t="n">
-        <v>46300.45833333334</v>
+        <v>46301.58333333334</v>
       </c>
     </row>
     <row r="889">
@@ -38873,13 +38875,13 @@
         </is>
       </c>
       <c r="G889" s="3" t="n">
-        <v>46300.70833333334</v>
+        <v>46301.83333333334</v>
       </c>
       <c r="H889" s="3" t="n">
-        <v>46300.75</v>
+        <v>46301.875</v>
       </c>
       <c r="I889" s="3" t="n">
-        <v>46301.16666666666</v>
+        <v>46302.29166666666</v>
       </c>
     </row>
     <row r="890">
@@ -38914,13 +38916,13 @@
         </is>
       </c>
       <c r="G890" s="3" t="n">
-        <v>46302.66666666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="H890" s="3" t="n">
-        <v>46302.83333333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="I890" s="3" t="n">
-        <v>46303.33333333334</v>
+        <v>46304.45833333334</v>
       </c>
     </row>
     <row r="891">
@@ -38955,13 +38957,13 @@
         </is>
       </c>
       <c r="G891" s="3" t="n">
-        <v>46308.35416666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="H891" s="3" t="n">
-        <v>46308.41666666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="I891" s="3" t="n">
-        <v>46308.66666666666</v>
+        <v>46309.79166666666</v>
       </c>
     </row>
     <row r="892">
@@ -38996,13 +38998,13 @@
         </is>
       </c>
       <c r="G892" s="3" t="n">
-        <v>46309.60416666666</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="H892" s="3" t="n">
-        <v>46309.66666666666</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="I892" s="3" t="n">
-        <v>46310.08333333334</v>
+        <v>46311.20833333334</v>
       </c>
     </row>
     <row r="893">
@@ -39037,13 +39039,13 @@
         </is>
       </c>
       <c r="G893" s="3" t="n">
-        <v>46310.41666666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="H893" s="3" t="n">
-        <v>46310.45833333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="I893" s="3" t="n">
-        <v>46311.08333333334</v>
+        <v>46312.20833333334</v>
       </c>
     </row>
     <row r="894">
@@ -39078,13 +39080,13 @@
         </is>
       </c>
       <c r="G894" s="3" t="n">
-        <v>46312.16666666666</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="H894" s="3" t="n">
-        <v>46312.33333333334</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="I894" s="3" t="n">
-        <v>46313.33333333334</v>
+        <v>46314.45833333334</v>
       </c>
     </row>
     <row r="895">
@@ -39119,13 +39121,13 @@
         </is>
       </c>
       <c r="G895" s="3" t="n">
-        <v>46317.54166666666</v>
+        <v>46318.66666666666</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>46317.66666666666</v>
+        <v>46318.79166666666</v>
       </c>
       <c r="I895" s="3" t="n">
-        <v>46318.16666666666</v>
+        <v>46319.29166666666</v>
       </c>
     </row>
     <row r="896">
@@ -39160,13 +39162,13 @@
         </is>
       </c>
       <c r="G896" s="3" t="n">
-        <v>46319.75</v>
+        <v>46320.875</v>
       </c>
       <c r="H896" s="3" t="n">
-        <v>46319.79166666666</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="I896" s="3" t="n">
-        <v>46320.20833333334</v>
+        <v>46321.33333333334</v>
       </c>
     </row>
     <row r="897">
@@ -39201,13 +39203,13 @@
         </is>
       </c>
       <c r="G897" s="3" t="n">
-        <v>46320.375</v>
+        <v>46321.5</v>
       </c>
       <c r="H897" s="3" t="n">
-        <v>46320.5</v>
+        <v>46321.625</v>
       </c>
       <c r="I897" s="3" t="n">
-        <v>46321.5</v>
+        <v>46322.625</v>
       </c>
     </row>
     <row r="898">
@@ -39242,13 +39244,13 @@
         </is>
       </c>
       <c r="G898" s="3" t="n">
-        <v>46321.75</v>
+        <v>46322.875</v>
       </c>
       <c r="H898" s="3" t="n">
-        <v>46321.79166666666</v>
+        <v>46322.91666666666</v>
       </c>
       <c r="I898" s="3" t="n">
-        <v>46322.20833333334</v>
+        <v>46323.33333333334</v>
       </c>
     </row>
     <row r="899">
@@ -39283,13 +39285,13 @@
         </is>
       </c>
       <c r="G899" s="3" t="n">
-        <v>46323.70833333334</v>
+        <v>46324.83333333334</v>
       </c>
       <c r="H899" s="3" t="n">
-        <v>46323.83333333334</v>
+        <v>46324.95833333334</v>
       </c>
       <c r="I899" s="3" t="n">
-        <v>46324.33333333334</v>
+        <v>46325.45833333334</v>
       </c>
     </row>
     <row r="900">
@@ -39324,13 +39326,13 @@
         </is>
       </c>
       <c r="G900" s="3" t="n">
-        <v>46330.89583333334</v>
+        <v>46332.02083333334</v>
       </c>
       <c r="H900" s="3" t="n">
-        <v>46330.95833333334</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="I900" s="3" t="n">
-        <v>46331.20833333334</v>
+        <v>46332.33333333334</v>
       </c>
     </row>
     <row r="901">
@@ -39365,13 +39367,13 @@
         </is>
       </c>
       <c r="G901" s="3" t="n">
-        <v>46332.14583333334</v>
+        <v>46333.27083333334</v>
       </c>
       <c r="H901" s="3" t="n">
-        <v>46332.20833333334</v>
+        <v>46333.33333333334</v>
       </c>
       <c r="I901" s="3" t="n">
-        <v>46332.625</v>
+        <v>46333.75</v>
       </c>
     </row>
     <row r="902">
@@ -39406,13 +39408,13 @@
         </is>
       </c>
       <c r="G902" s="3" t="n">
-        <v>46332.95833333334</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="H902" s="3" t="n">
-        <v>46333</v>
+        <v>46334.125</v>
       </c>
       <c r="I902" s="3" t="n">
-        <v>46333.625</v>
+        <v>46334.75</v>
       </c>
     </row>
     <row r="903">
@@ -39447,13 +39449,13 @@
         </is>
       </c>
       <c r="G903" s="3" t="n">
-        <v>46334.70555555556</v>
+        <v>46335.83055555556</v>
       </c>
       <c r="H903" s="3" t="n">
-        <v>46334.87222222222</v>
+        <v>46335.99722222222</v>
       </c>
       <c r="I903" s="3" t="n">
-        <v>46335.87222222222</v>
+        <v>46336.99722222222</v>
       </c>
     </row>
     <row r="904">
@@ -39488,13 +39490,13 @@
         </is>
       </c>
       <c r="G904" s="3" t="n">
-        <v>46340.08055555556</v>
+        <v>46341.20555555556</v>
       </c>
       <c r="H904" s="3" t="n">
-        <v>46340.20555555556</v>
+        <v>46341.33055555556</v>
       </c>
       <c r="I904" s="3" t="n">
-        <v>46340.70555555556</v>
+        <v>46341.83055555556</v>
       </c>
     </row>
     <row r="905">
@@ -39529,13 +39531,13 @@
         </is>
       </c>
       <c r="G905" s="3" t="n">
-        <v>46342.28888888889</v>
+        <v>46343.41388888889</v>
       </c>
       <c r="H905" s="3" t="n">
-        <v>46342.33055555556</v>
+        <v>46343.45555555556</v>
       </c>
       <c r="I905" s="3" t="n">
-        <v>46342.74722222222</v>
+        <v>46343.87222222222</v>
       </c>
     </row>
     <row r="906">
@@ -39570,13 +39572,13 @@
         </is>
       </c>
       <c r="G906" s="3" t="n">
-        <v>46342.91388888889</v>
+        <v>46344.03888888889</v>
       </c>
       <c r="H906" s="3" t="n">
-        <v>46343.03888888889</v>
+        <v>46344.16388888889</v>
       </c>
       <c r="I906" s="3" t="n">
-        <v>46344.03888888889</v>
+        <v>46345.16388888889</v>
       </c>
     </row>
     <row r="907">
@@ -39611,13 +39613,13 @@
         </is>
       </c>
       <c r="G907" s="3" t="n">
-        <v>46344.28888888889</v>
+        <v>46345.41388888889</v>
       </c>
       <c r="H907" s="3" t="n">
-        <v>46344.33055555556</v>
+        <v>46345.45555555556</v>
       </c>
       <c r="I907" s="3" t="n">
-        <v>46344.74722222222</v>
+        <v>46345.87222222222</v>
       </c>
     </row>
     <row r="908">
@@ -39652,13 +39654,13 @@
         </is>
       </c>
       <c r="G908" s="3" t="n">
-        <v>46346.24722222222</v>
+        <v>46347.37222222222</v>
       </c>
       <c r="H908" s="3" t="n">
-        <v>46346.37222222222</v>
+        <v>46347.49722222222</v>
       </c>
       <c r="I908" s="3" t="n">
-        <v>46346.87222222222</v>
+        <v>46347.99722222222</v>
       </c>
     </row>
     <row r="909">
@@ -39693,13 +39695,13 @@
         </is>
       </c>
       <c r="G909" s="3" t="n">
-        <v>46351.89305555556</v>
+        <v>46353.01805555556</v>
       </c>
       <c r="H909" s="3" t="n">
-        <v>46351.95555555556</v>
+        <v>46353.08055555556</v>
       </c>
       <c r="I909" s="3" t="n">
-        <v>46352.20555555556</v>
+        <v>46353.33055555556</v>
       </c>
     </row>
     <row r="910">
@@ -39734,13 +39736,13 @@
         </is>
       </c>
       <c r="G910" s="3" t="n">
-        <v>46353.14305555556</v>
+        <v>46354.26805555556</v>
       </c>
       <c r="H910" s="3" t="n">
-        <v>46353.20555555556</v>
+        <v>46354.33055555556</v>
       </c>
       <c r="I910" s="3" t="n">
-        <v>46353.62222222222</v>
+        <v>46354.74722222222</v>
       </c>
     </row>
     <row r="911">
@@ -39775,13 +39777,13 @@
         </is>
       </c>
       <c r="G911" s="3" t="n">
-        <v>46353.95555555556</v>
+        <v>46355.08055555556</v>
       </c>
       <c r="H911" s="3" t="n">
-        <v>46353.99722222222</v>
+        <v>46355.12222222222</v>
       </c>
       <c r="I911" s="3" t="n">
-        <v>46354.62222222222</v>
+        <v>46355.74722222222</v>
       </c>
     </row>
     <row r="912">
@@ -39816,13 +39818,13 @@
         </is>
       </c>
       <c r="G912" s="3" t="n">
-        <v>46355.70277777778</v>
+        <v>46356.82777777778</v>
       </c>
       <c r="H912" s="3" t="n">
-        <v>46355.86944444444</v>
+        <v>46356.99444444444</v>
       </c>
       <c r="I912" s="3" t="n">
-        <v>46356.86944444444</v>
+        <v>46357.99444444444</v>
       </c>
     </row>
     <row r="913">
@@ -39857,13 +39859,13 @@
         </is>
       </c>
       <c r="G913" s="3" t="n">
-        <v>46361.07777777778</v>
+        <v>46362.20277777778</v>
       </c>
       <c r="H913" s="3" t="n">
-        <v>46361.20277777778</v>
+        <v>46362.32777777778</v>
       </c>
       <c r="I913" s="3" t="n">
-        <v>46361.70277777778</v>
+        <v>46362.82777777778</v>
       </c>
     </row>
     <row r="914">
@@ -39898,13 +39900,13 @@
         </is>
       </c>
       <c r="G914" s="3" t="n">
-        <v>46363.28611111111</v>
+        <v>46364.41111111111</v>
       </c>
       <c r="H914" s="3" t="n">
-        <v>46363.32777777778</v>
+        <v>46364.45277777778</v>
       </c>
       <c r="I914" s="3" t="n">
-        <v>46363.74444444444</v>
+        <v>46364.86944444444</v>
       </c>
     </row>
     <row r="915">
@@ -39939,13 +39941,13 @@
         </is>
       </c>
       <c r="G915" s="3" t="n">
-        <v>46363.91111111111</v>
+        <v>46365.03611111111</v>
       </c>
       <c r="H915" s="3" t="n">
-        <v>46364.03611111111</v>
+        <v>46365.16111111111</v>
       </c>
       <c r="I915" s="3" t="n">
-        <v>46365.03611111111</v>
+        <v>46366.16111111111</v>
       </c>
     </row>
     <row r="916">
@@ -39980,13 +39982,13 @@
         </is>
       </c>
       <c r="G916" s="3" t="n">
-        <v>46365.28611111111</v>
+        <v>46366.41111111111</v>
       </c>
       <c r="H916" s="3" t="n">
-        <v>46365.32777777778</v>
+        <v>46366.45277777778</v>
       </c>
       <c r="I916" s="3" t="n">
-        <v>46365.74444444444</v>
+        <v>46366.86944444444</v>
       </c>
     </row>
     <row r="917">
@@ -40019,13 +40021,13 @@
         <v/>
       </c>
       <c r="G917" s="3" t="n">
-        <v>46367.24444444444</v>
+        <v>46368.36944444444</v>
       </c>
       <c r="H917" s="3" t="n">
-        <v>46367.36944444444</v>
+        <v>46368.49444444444</v>
       </c>
       <c r="I917" s="3" t="n">
-        <v>46367.86944444444</v>
+        <v>46368.99444444444</v>
       </c>
     </row>
     <row r="918">
@@ -47354,7 +47356,7 @@
         <v>46289.95833333334</v>
       </c>
       <c r="I1096" s="3" t="n">
-        <v>46290.85416666666</v>
+        <v>46290.8375</v>
       </c>
     </row>
     <row r="1097">
@@ -47389,13 +47391,13 @@
         </is>
       </c>
       <c r="G1097" s="3" t="n">
-        <v>46292.04166666666</v>
+        <v>46292</v>
       </c>
       <c r="H1097" s="3" t="n">
-        <v>46292.10416666666</v>
+        <v>46292.0625</v>
       </c>
       <c r="I1097" s="3" t="n">
-        <v>46292.5</v>
+        <v>46292.375</v>
       </c>
     </row>
     <row r="1098">
@@ -47430,13 +47432,13 @@
         </is>
       </c>
       <c r="G1098" s="3" t="n">
-        <v>46292.79166666666</v>
+        <v>46292.66666666666</v>
       </c>
       <c r="H1098" s="3" t="n">
-        <v>46292.83333333334</v>
+        <v>46292.875</v>
       </c>
       <c r="I1098" s="3" t="n">
-        <v>46293.70833333334</v>
+        <v>46294.16666666666</v>
       </c>
     </row>
     <row r="1099">
@@ -48678,14 +48680,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -48719,7 +48721,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260926-0609-SKED.xlsx)</t>
+          <t>New ETA (auto-20260926-1344-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -48730,6 +48732,3958 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KMTC JAKARTA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46258.75</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46258.54166666666</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46296.20833333334</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46299.25</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46296.83333333334</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46299.875</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46298.45833333334</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>46301.5</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46305.83333333334</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46304.25</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46307.1875</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>46310.22916666666</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46308.85416666666</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>46311.89583333334</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46310.47916666666</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46313.52083333334</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46317.1875</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>46320.22916666666</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46317.8125</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>46320.85416666666</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46319.4375</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>46322.47916666666</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>46323.77083333334</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>46326.8125</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46325.22916666666</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>46328.27083333334</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>46328.1875</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>46331.22916666666</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>46329.85416666666</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46332.89583333334</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46331.47916666666</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>46334.52083333334</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46338.1875</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>46341.22916666666</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46338.8125</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>46341.85416666666</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46340.4375</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>46343.47916666666</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46344.77083333334</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>46347.8125</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>46346.22916666666</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46349.27083333334</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46349.1875</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>46352.22916666666</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>46350.85416666666</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>46353.89583333334</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46352.47916666666</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>46355.52083333334</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46359.1875</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>46362.22916666666</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46359.8125</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>46362.85416666666</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>46361.4375</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>46364.47916666666</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46365.77083333334</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>46368.8125</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>46367.22916666666</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>46370.27083333334</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46291.875</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>46291.95833333334</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>46298.52083333334</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46298.8125</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>46299.77083333334</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46299.625</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46301.375</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46308.75</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46309.70833333334</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46311.95833333334</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46312.91666666666</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46312.58333333334</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46313.54166666666</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46313.95833333334</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46314.91666666666</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46315.91666666666</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46316.875</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46323.52083333334</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46324.47916666666</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>46324.77083333334</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>46325.72916666666</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46325.58333333334</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>46326.54166666666</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>46327.33333333334</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>46328.29166666666</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>46332.70833333334</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>46333.66666666666</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>46334.91666666666</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>46335.875</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>46335.54166666666</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>46336.5</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>46336.91666666666</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>46337.875</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>46338.875</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>46339.83333333334</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>46344.52083333334</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>46345.47916666666</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>46345.77083333334</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>46346.72916666666</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>46346.58333333334</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>46347.54166666666</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>46348.33333333334</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>46349.29166666666</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>46353.70833333334</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>46354.66666666666</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>46355.91666666666</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>46356.875</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>46356.54166666666</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>46357.5</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>46357.91666666666</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>46358.875</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>46359.875</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>46360.83333333334</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>46299.875</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>46305.6875</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>46312.45833333334</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>46315.27083333334</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>46314.72916666666</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>46316.60416666666</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>46316.0625</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>46318.77083333334</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>46318.22916666666</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>46326.64583333334</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>46326.10416666666</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>46328.64583333334</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>46328.10416666666</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>46333.22916666666</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>46332.6875</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>46340.35416666666</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>46339.8125</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>46342.6875</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>46342.14583333334</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>46344.35416666666</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>46343.8125</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>46346.52083333334</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>46345.97916666666</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>46354.39583333334</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>46353.85416666666</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>46356.39583333334</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>46355.85416666666</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>46360.97916666666</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>46360.4375</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE RIGEL</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>46368.10416666666</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>46367.5625</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>46296.5</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>46297.625</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>46298.70833333334</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>46303.79166666666</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>46308.35416666666</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>46309.47916666666</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46309.60416666666</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>46310.72916666666</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>46310.41666666666</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>46311.54166666666</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>46312.16666666666</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>46313.29166666666</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46317.54166666666</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>46318.66666666666</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46319.75</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>46320.875</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>46320.375</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>46321.5</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>46321.75</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>46322.875</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>46323.70833333334</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>46324.83333333334</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>46330.89583333334</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>46332.02083333334</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>46332.14583333334</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>46333.27083333334</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>46332.95833333334</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>46334.08333333334</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46334.70555555556</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>46335.83055555556</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>46340.08055555556</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>46341.20555555556</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>46342.28888888889</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>46343.41388888889</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>46342.91388888889</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>46344.03888888889</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>46344.28888888889</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>46345.41388888889</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>46346.24722222222</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>46347.37222222222</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>46351.89305555556</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>46353.01805555556</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>46353.14305555556</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>46354.26805555556</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>46353.95555555556</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>46355.08055555556</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>46355.70277777778</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>46356.82777777778</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>46361.07777777778</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>46362.20277777778</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>46363.28611111111</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>46364.41111111111</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>46363.91111111111</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>46365.03611111111</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>46365.28611111111</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>46366.41111111111</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>46367.24444444444</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>46368.36944444444</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>YEOSU VOYAGER</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>46292.04166666666</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>YEOSU VOYAGER</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>46292.79166666666</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>46292.66666666666</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -679,20 +679,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>IDSRG -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH06)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-26T22:00:00</t>
+          <t>Alongside, departs to CNSHA ~2026-09-27T17:00:00</t>
         </is>
       </c>
       <c r="I4" s="3" t="n"/>
@@ -703,7 +705,7 @@
         <v/>
       </c>
       <c r="L4" s="3" t="n">
-        <v>46291.91666666666</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -712,7 +714,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
     </row>
@@ -801,22 +803,20 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>CNTAO (TAO06)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2608E</t>
-        </is>
+          <t>CNTAO -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v/>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-09-27T11:00:00</t>
+          <t>In transit, ETA 2026-09-28T21:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -861,22 +861,20 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>IDJKT (JKT01)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
+          <t>IDJKT -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v/>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-09-27T12:30:00</t>
+          <t>In transit, ETA 2026-09-30T00:00:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -979,24 +977,26 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>CNSHA -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v/>
+          <t>THBKK (BKK04)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-27T00:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-09-29T05:00:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>46292.45833333334</v>
+        <v>46314.04166666666</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1005,20 +1005,20 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>46294.41666666666</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>LCH05</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>2610N</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>LCH10</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
         </is>
       </c>
     </row>
@@ -1107,22 +1107,20 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH04)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
+          <t>THLCH -&gt; IDJKT</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v/>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to IDJKT ~2026-09-27T11:00:00</t>
+          <t>In transit, ETA 2026-09-30T09:30:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="n"/>
@@ -1167,20 +1165,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>HKHKG -&gt; CNXMN</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v/>
+          <t>CNXMN (XMN01)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-27T00:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-09-27T16:00:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1295,20 +1295,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>KRINC -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUSH4)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-27T11:30:00</t>
+          <t>Alongside, departs to KRUSN ~2026-09-28T02:30:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
@@ -1368,7 +1370,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-09-30T09:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-01T02:00:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="n"/>
@@ -1523,22 +1525,20 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>VNSGN -&gt; KRINC</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v/>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRINC ~2026-09-27T03:30:00</t>
+          <t>In transit, ETA 2026-10-02T10:00:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -1589,20 +1589,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>VNSGN -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH01)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-27T05:00:00</t>
+          <t>Alongside, departs to THBKK ~2026-09-27T16:00:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1619,7 +1621,7 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46292.20833333334</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1628,7 +1630,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2608N</t>
         </is>
       </c>
     </row>
@@ -1653,26 +1655,24 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUSH4)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
+          <t>KRUSN -&gt; HKHKG</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v/>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRUSN ~2026-09-27T00:00:00</t>
+          <t>In transit, ETA 2026-09-30T11:30:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46301.1875</v>
+        <v>46301.0625</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.35416666666</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1913,20 +1913,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-26T23:00:00</t>
+          <t>Alongside, departs to KRPTK ~2026-09-28T12:00:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -1977,22 +1979,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>CNSHA (SHAW1)</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
+          <t>CNSHA -&gt; IDJKT</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v/>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to IDJKT ~2026-09-27T08:00:00</t>
+          <t>In transit, ETA 2026-10-04T08:00:00</t>
         </is>
       </c>
       <c r="I25" s="3" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>THBKK (BKK01)</t>
+          <t>THLCH (LCH04)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-27T01:30:00</t>
+          <t>Alongside, departs to HKHKG ~2026-09-27T15:30:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46292.27083333334</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>CNSHA -&gt; KRKAN</t>
+          <t>KRKAN -&gt; KRPUS</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-27T00:00:00</t>
+          <t>In transit, ETA 2026-09-27T16:00:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
@@ -22500,10 +22500,10 @@
         <v>46290.45833333334</v>
       </c>
       <c r="H489" s="3" t="n">
-        <v>46293.58333333334</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="I489" s="3" t="n">
-        <v>46295.375</v>
+        <v>46296.08333333334</v>
       </c>
     </row>
     <row r="490">
@@ -22620,13 +22620,13 @@
         </is>
       </c>
       <c r="G492" s="3" t="n">
-        <v>46295.66666666666</v>
+        <v>46296.375</v>
       </c>
       <c r="H492" s="3" t="n">
-        <v>46295.72916666666</v>
+        <v>46296.4375</v>
       </c>
       <c r="I492" s="3" t="n">
-        <v>46296.20833333334</v>
+        <v>46296.91666666666</v>
       </c>
     </row>
     <row r="493">
@@ -22661,13 +22661,13 @@
         </is>
       </c>
       <c r="G493" s="3" t="n">
-        <v>46297.6875</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>46298.77083333334</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="I493" s="3" t="n">
-        <v>46299.27083333334</v>
+        <v>46299.97916666666</v>
       </c>
     </row>
     <row r="494">
@@ -22702,13 +22702,13 @@
         </is>
       </c>
       <c r="G494" s="3" t="n">
-        <v>46302.22916666666</v>
+        <v>46302.9375</v>
       </c>
       <c r="H494" s="3" t="n">
-        <v>46302.35416666666</v>
+        <v>46303.0625</v>
       </c>
       <c r="I494" s="3" t="n">
-        <v>46302.77083333334</v>
+        <v>46303.47916666666</v>
       </c>
     </row>
     <row r="495">
@@ -22743,13 +22743,13 @@
         </is>
       </c>
       <c r="G495" s="3" t="n">
-        <v>46315.02083333334</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="H495" s="3" t="n">
-        <v>46316.10416666666</v>
+        <v>46316.8125</v>
       </c>
       <c r="I495" s="3" t="n">
-        <v>46316.77083333334</v>
+        <v>46317.47916666666</v>
       </c>
     </row>
     <row r="496">
@@ -22784,13 +22784,13 @@
         </is>
       </c>
       <c r="G496" s="3" t="n">
-        <v>46318.02083333334</v>
+        <v>46318.72916666666</v>
       </c>
       <c r="H496" s="3" t="n">
-        <v>46318.10416666666</v>
+        <v>46318.8125</v>
       </c>
       <c r="I496" s="3" t="n">
-        <v>46318.60416666666</v>
+        <v>46319.3125</v>
       </c>
     </row>
     <row r="497">
@@ -22825,13 +22825,13 @@
         </is>
       </c>
       <c r="G497" s="3" t="n">
-        <v>46319.52083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>46319.60416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="I497" s="3" t="n">
-        <v>46320.1875</v>
+        <v>46320.89583333334</v>
       </c>
     </row>
     <row r="498">
@@ -22866,13 +22866,13 @@
         </is>
       </c>
       <c r="G498" s="3" t="n">
-        <v>46329.0625</v>
+        <v>46329.77083333334</v>
       </c>
       <c r="H498" s="3" t="n">
-        <v>46330.10416666666</v>
+        <v>46330.8125</v>
       </c>
       <c r="I498" s="3" t="n">
-        <v>46330.6875</v>
+        <v>46331.39583333334</v>
       </c>
     </row>
     <row r="499">
@@ -22905,13 +22905,13 @@
         <v/>
       </c>
       <c r="G499" s="3" t="n">
-        <v>46339.47916666666</v>
+        <v>46340.1875</v>
       </c>
       <c r="H499" s="3" t="n">
-        <v>46339.52083333334</v>
+        <v>46340.22916666666</v>
       </c>
       <c r="I499" s="3" t="n">
-        <v>46340.27083333334</v>
+        <v>46340.97916666666</v>
       </c>
     </row>
     <row r="500">
@@ -28930,7 +28930,7 @@
         <v>46292.14583333334</v>
       </c>
       <c r="I646" s="3" t="n">
-        <v>46292.625</v>
+        <v>46292.5</v>
       </c>
     </row>
     <row r="647">
@@ -28965,13 +28965,13 @@
         </is>
       </c>
       <c r="G647" s="3" t="n">
-        <v>46295.60416666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="H647" s="3" t="n">
-        <v>46295.64583333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="I647" s="3" t="n">
-        <v>46296.02083333334</v>
+        <v>46295.89583333334</v>
       </c>
     </row>
     <row r="648">
@@ -29006,13 +29006,13 @@
         </is>
       </c>
       <c r="G648" s="3" t="n">
-        <v>46297.97916666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="H648" s="3" t="n">
-        <v>46298.14583333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="I648" s="3" t="n">
-        <v>46298.6875</v>
+        <v>46298.5625</v>
       </c>
     </row>
     <row r="649">
@@ -29047,13 +29047,13 @@
         </is>
       </c>
       <c r="G649" s="3" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.35416666666</v>
       </c>
       <c r="H649" s="3" t="n">
-        <v>46300.52083333334</v>
+        <v>46300.39583333334</v>
       </c>
       <c r="I649" s="3" t="n">
-        <v>46300.77083333334</v>
+        <v>46300.64583333334</v>
       </c>
     </row>
     <row r="650">
@@ -29088,13 +29088,13 @@
         </is>
       </c>
       <c r="G650" s="3" t="n">
+        <v>46301.0625</v>
+      </c>
+      <c r="H650" s="3" t="n">
         <v>46301.1875</v>
       </c>
-      <c r="H650" s="3" t="n">
-        <v>46301.3125</v>
-      </c>
       <c r="I650" s="3" t="n">
-        <v>46302.4375</v>
+        <v>46302.3125</v>
       </c>
     </row>
     <row r="651">
@@ -29129,13 +29129,13 @@
         </is>
       </c>
       <c r="G651" s="3" t="n">
-        <v>46302.77083333334</v>
+        <v>46302.64583333334</v>
       </c>
       <c r="H651" s="3" t="n">
-        <v>46302.8125</v>
+        <v>46302.6875</v>
       </c>
       <c r="I651" s="3" t="n">
-        <v>46303.14583333334</v>
+        <v>46303.02083333334</v>
       </c>
     </row>
     <row r="652">
@@ -29170,13 +29170,13 @@
         </is>
       </c>
       <c r="G652" s="3" t="n">
-        <v>46307.02083333334</v>
+        <v>46306.89583333334</v>
       </c>
       <c r="H652" s="3" t="n">
-        <v>46307.0625</v>
+        <v>46306.9375</v>
       </c>
       <c r="I652" s="3" t="n">
-        <v>46307.47916666666</v>
+        <v>46307.35416666666</v>
       </c>
     </row>
     <row r="653">
@@ -29211,13 +29211,13 @@
         </is>
       </c>
       <c r="G653" s="3" t="n">
-        <v>46307.72916666666</v>
+        <v>46307.60416666666</v>
       </c>
       <c r="H653" s="3" t="n">
-        <v>46307.72916666666</v>
+        <v>46307.60416666666</v>
       </c>
       <c r="I653" s="3" t="n">
-        <v>46308.10416666666</v>
+        <v>46307.97916666666</v>
       </c>
     </row>
     <row r="654">
@@ -29293,13 +29293,13 @@
         </is>
       </c>
       <c r="G655" s="3" t="n">
-        <v>46309.63958333333</v>
+        <v>46309.51458333333</v>
       </c>
       <c r="H655" s="3" t="n">
-        <v>46309.63958333333</v>
+        <v>46309.51458333333</v>
       </c>
       <c r="I655" s="3" t="n">
-        <v>46309.88958333333</v>
+        <v>46309.76458333333</v>
       </c>
     </row>
     <row r="656">
@@ -48680,10 +48680,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -48721,7 +48721,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260926-1344-SKED.xlsx)</t>
+          <t>New ETA (auto-20260927-0636-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -48774,32 +48774,32 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46296.20833333334</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46299.25</v>
+        <v>46296.375</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -48810,32 +48810,32 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46296.83333333334</v>
+        <v>46297.6875</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46299.875</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -48846,32 +48846,32 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>INNSA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46298.45833333334</v>
+        <v>46302.22916666666</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46301.5</v>
+        <v>46302.9375</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -48882,32 +48882,32 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>INNSA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>INMUN</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46302.79166666666</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46305.83333333334</v>
+        <v>46315.72916666666</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -48918,32 +48918,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>INMUN</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>PKKHI</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46304.25</v>
+        <v>46318.02083333334</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46307.29166666666</v>
+        <v>46318.72916666666</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -48954,32 +48954,32 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>PKKHI</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>MYPKL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46307.1875</v>
+        <v>46319.52083333334</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46310.22916666666</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -48990,32 +48990,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>MYPKL</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46308.85416666666</v>
+        <v>46329.0625</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46311.89583333334</v>
+        <v>46329.77083333334</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -49026,32 +49026,30 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v/>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46310.47916666666</v>
+        <v>46339.47916666666</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46313.52083333334</v>
+        <v>46340.1875</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -49062,48 +49060,48 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>SAWASDEE ATLANTIC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46317.1875</v>
+        <v>46295.60416666666</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46320.22916666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>73</v>
+        <v>-3</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>SAWASDEE ATLANTIC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -49113,28 +49111,28 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46317.8125</v>
+        <v>46297.97916666666</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46320.85416666666</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>73</v>
+        <v>-3</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>SAWASDEE ATLANTIC</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -49144,3544 +49142,204 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46319.4375</v>
+        <v>46300.47916666666</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46322.47916666666</v>
+        <v>46300.35416666666</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>73</v>
+        <v>-3</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>SAWASDEE ATLANTIC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46323.77083333334</v>
+        <v>46301.1875</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46326.8125</v>
+        <v>46301.0625</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>73</v>
+        <v>-3</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>SAWASDEE ATLANTIC</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46325.22916666666</v>
+        <v>46302.77083333334</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46328.27083333334</v>
+        <v>46302.64583333334</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>73</v>
+        <v>-3</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>SAWASDEE ATLANTIC</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46328.1875</v>
+        <v>46307.02083333334</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46331.22916666666</v>
+        <v>46306.89583333334</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>73</v>
+        <v>-3</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>SAWASDEE ATLANTIC</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46329.85416666666</v>
+        <v>46307.72916666666</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46332.89583333334</v>
+        <v>46307.60416666666</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>73</v>
+        <v>-3</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE DENEB</t>
+          <t>SAWASDEE ATLANTIC</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46331.47916666666</v>
+        <v>46309.63958333333</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46334.52083333334</v>
+        <v>46309.51458333333</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>73</v>
+        <v>-3</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>46338.1875</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>46341.22916666666</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>46338.8125</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>46341.85416666666</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>46340.4375</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>46343.47916666666</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>46344.77083333334</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>46347.8125</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>46346.22916666666</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>46349.27083333334</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46349.1875</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>46352.22916666666</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>46350.85416666666</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>46353.89583333334</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>46352.47916666666</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>46355.52083333334</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>46359.1875</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>46362.22916666666</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>46359.8125</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>46362.85416666666</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>46361.4375</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>46364.47916666666</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>46365.77083333334</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>46368.8125</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE DENEB</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>46367.22916666666</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>46370.27083333334</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>46291.875</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>46291.95833333334</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>46297.5625</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>46298.52083333334</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>46298.8125</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>46299.77083333334</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>46299.625</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>46300.58333333334</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>46301.375</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>46302.33333333334</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>46308.75</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>46309.70833333334</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>46311.95833333334</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>46312.91666666666</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>46312.58333333334</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>46313.54166666666</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46313.95833333334</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>46314.91666666666</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46315.91666666666</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>46316.875</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>46323.52083333334</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>46324.47916666666</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>46324.77083333334</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>46325.72916666666</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>46325.58333333334</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>46326.54166666666</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>46327.33333333334</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>46328.29166666666</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>46332.70833333334</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>46333.66666666666</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>46334.91666666666</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>46335.875</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>46335.54166666666</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>46336.5</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>46336.91666666666</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>46337.875</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>46338.875</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>46339.83333333334</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>46344.52083333334</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>46345.47916666666</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>46345.77083333334</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>46346.72916666666</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>46346.58333333334</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>46347.54166666666</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>46348.33333333334</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>46349.29166666666</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>46353.70833333334</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>46354.66666666666</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>46355.91666666666</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>46356.875</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>46356.54166666666</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>46357.5</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>46357.91666666666</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>46358.875</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>46359.875</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>46360.83333333334</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>46299.875</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>46299.33333333334</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>46301.52083333334</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>46300.97916666666</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>46306.22916666666</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>46305.6875</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>46312.45833333334</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>46315.27083333334</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>46314.72916666666</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>46316.60416666666</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>46316.0625</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>46318.77083333334</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>46318.22916666666</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>46326.64583333334</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>46326.10416666666</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>46328.64583333334</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>46328.10416666666</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>46333.22916666666</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>46332.6875</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>46340.35416666666</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>46339.8125</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>46342.6875</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>46342.14583333334</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>46344.35416666666</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>46343.8125</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>46346.52083333334</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>46345.97916666666</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>46354.39583333334</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>46353.85416666666</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>46356.39583333334</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>46355.85416666666</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>46360.97916666666</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>46360.4375</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>46368.10416666666</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>46367.5625</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>46296.5</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>46297.625</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>46298.70833333334</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>46299.83333333334</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>46299.33333333334</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>46300.45833333334</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>46300.70833333334</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>46301.83333333334</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>46302.66666666666</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>46303.79166666666</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>46308.35416666666</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>46309.47916666666</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>46309.60416666666</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>46310.72916666666</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>46310.41666666666</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>46311.54166666666</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>46312.16666666666</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>46313.29166666666</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>46317.54166666666</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>46318.66666666666</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>46319.75</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>46320.875</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>46320.375</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>46321.5</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>46321.75</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>46322.875</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>46323.70833333334</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>46324.83333333334</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>46330.89583333334</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>46332.02083333334</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>46332.14583333334</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>46333.27083333334</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>46332.95833333334</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>46334.08333333334</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>46334.70555555556</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>46335.83055555556</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>46340.08055555556</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>46341.20555555556</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>46342.28888888889</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>46343.41388888889</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>46342.91388888889</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>46344.03888888889</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>46344.28888888889</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>46345.41388888889</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>46346.24722222222</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>46347.37222222222</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>46351.89305555556</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>46353.01805555556</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>46353.14305555556</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>46354.26805555556</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>46353.95555555556</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>46355.08055555556</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>46355.70277777778</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>46356.82777777778</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>46361.07777777778</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>46362.20277777778</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>46363.28611111111</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>46364.41111111111</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>46363.91111111111</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>46365.03611111111</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>46365.28611111111</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>46366.41111111111</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>46367.24444444444</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>46368.36944444444</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>46292.04166666666</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>46292.79166666666</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>46292.66666666666</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Early</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -679,22 +679,20 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH06)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>THLCH -&gt; CNSHA</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v/>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNSHA ~2026-09-27T17:00:00</t>
+          <t>In transit, ETA 2026-10-03T18:30:00</t>
         </is>
       </c>
       <c r="I4" s="3" t="n"/>
@@ -803,20 +801,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>CNTAO -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v/>
+          <t>CNTAO (TAO06)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2608E</t>
+        </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-28T21:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-09-28T21:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T00:00:00</t>
+          <t>In transit, ETA 2026-09-29T18:00:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -1165,22 +1165,20 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>CNXMN (XMN01)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>CNXMN -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v/>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-09-27T16:00:00</t>
+          <t>In transit, ETA 2026-09-30T00:00:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1594,21 +1592,21 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH01)</t>
+          <t>THBKK (BKK02)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THBKK ~2026-09-27T16:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-09-28T15:00:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>46292.79166666666</v>
+        <v>46313.5</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1617,11 +1615,11 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2608N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46294.16666666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1668,11 +1666,11 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T11:30:00</t>
+          <t>In transit, ETA 2026-09-30T21:00:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46301.0625</v>
+        <v>46301.45833333334</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1685,7 +1683,7 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46300.35416666666</v>
+        <v>46300.75</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1802,7 +1800,7 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>46299.875</v>
+        <v>46300</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -1815,7 +1813,7 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46299.25</v>
+        <v>46299.375</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -2225,22 +2223,20 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH04)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>THLCH -&gt; HKHKG</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v/>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to HKHKG ~2026-09-27T15:30:00</t>
+          <t>In transit, ETA 2026-10-01T16:00:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
@@ -2415,20 +2411,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>KRKAN -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUS05)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-27T16:00:00</t>
+          <t>Alongside, departs to KRUSN ~2026-09-29T04:00:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
@@ -8455,10 +8453,10 @@
         <v>46288.375</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>46291.75</v>
+        <v>46293.20833333334</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>46292.45833333334</v>
+        <v>46293.875</v>
       </c>
     </row>
     <row r="147">
@@ -8469,12 +8467,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>2608E</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -8496,10 +8494,10 @@
         <v>46293.875</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>46293.91666666666</v>
+        <v>46294.75</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>46294.625</v>
+        <v>46295.45833333334</v>
       </c>
     </row>
     <row r="148">
@@ -8510,12 +8508,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2608E</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -8534,13 +8532,13 @@
         </is>
       </c>
       <c r="G148" s="3" t="n">
-        <v>46293.875</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>46294.75</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>46295.45833333334</v>
+        <v>46296.04166666666</v>
       </c>
     </row>
     <row r="149">
@@ -9645,7 +9643,7 @@
         <v>46289.875</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>46292.52083333334</v>
+        <v>46292.27916666667</v>
       </c>
     </row>
     <row r="176">
@@ -9680,13 +9678,13 @@
         </is>
       </c>
       <c r="G176" s="3" t="n">
-        <v>46295</v>
+        <v>46294.75</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>46295.16666666666</v>
+        <v>46294.91666666666</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>46296</v>
+        <v>46295.75</v>
       </c>
     </row>
     <row r="177">
@@ -9721,13 +9719,13 @@
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>46298.54166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="H177" s="3" t="n">
-        <v>46298.60416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>46299.10416666666</v>
+        <v>46298.85416666666</v>
       </c>
     </row>
     <row r="178">
@@ -9762,13 +9760,13 @@
         </is>
       </c>
       <c r="G178" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>46299.375</v>
+        <v>46299.125</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>46299.875</v>
+        <v>46299.625</v>
       </c>
     </row>
     <row r="179">
@@ -9803,13 +9801,13 @@
         </is>
       </c>
       <c r="G179" s="3" t="n">
-        <v>46303.16666666666</v>
+        <v>46302.91666666666</v>
       </c>
       <c r="H179" s="3" t="n">
-        <v>46303.20833333334</v>
+        <v>46302.95833333334</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>46303.875</v>
+        <v>46303.625</v>
       </c>
     </row>
     <row r="180">
@@ -9844,13 +9842,13 @@
         </is>
       </c>
       <c r="G180" s="3" t="n">
-        <v>46304.95833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="H180" s="3" t="n">
-        <v>46305</v>
+        <v>46304.75</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>46305.58333333334</v>
+        <v>46305.33333333334</v>
       </c>
     </row>
     <row r="181">
@@ -27456,7 +27454,7 @@
         <v>46292.25</v>
       </c>
       <c r="I610" s="3" t="n">
-        <v>46292.66666666666</v>
+        <v>46292.58333333334</v>
       </c>
     </row>
     <row r="611">
@@ -27491,13 +27489,13 @@
         </is>
       </c>
       <c r="G611" s="3" t="n">
-        <v>46292.79166666666</v>
+        <v>46292.66666666666</v>
       </c>
       <c r="H611" s="3" t="n">
-        <v>46292.91666666666</v>
+        <v>46292.75</v>
       </c>
       <c r="I611" s="3" t="n">
-        <v>46294</v>
+        <v>46293.625</v>
       </c>
     </row>
     <row r="612">
@@ -27532,13 +27530,13 @@
         </is>
       </c>
       <c r="G612" s="3" t="n">
-        <v>46294.16666666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="H612" s="3" t="n">
-        <v>46294.20833333334</v>
+        <v>46293.83333333334</v>
       </c>
       <c r="I612" s="3" t="n">
-        <v>46294.875</v>
+        <v>46294.5</v>
       </c>
     </row>
     <row r="613">
@@ -27573,13 +27571,13 @@
         </is>
       </c>
       <c r="G613" s="3" t="n">
-        <v>46296.33333333334</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="H613" s="3" t="n">
-        <v>46296.5</v>
+        <v>46296.125</v>
       </c>
       <c r="I613" s="3" t="n">
-        <v>46297.375</v>
+        <v>46297.33333333334</v>
       </c>
     </row>
     <row r="614">
@@ -27614,13 +27612,13 @@
         </is>
       </c>
       <c r="G614" s="3" t="n">
-        <v>46302.66666666666</v>
+        <v>46302.83333333334</v>
       </c>
       <c r="H614" s="3" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.875</v>
       </c>
       <c r="I614" s="3" t="n">
-        <v>46303.29166666666</v>
+        <v>46303.875</v>
       </c>
     </row>
     <row r="615">
@@ -27655,13 +27653,13 @@
         </is>
       </c>
       <c r="G615" s="3" t="n">
+        <v>46304.875</v>
+      </c>
+      <c r="H615" s="3" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="H615" s="3" t="n">
-        <v>46304.95833333334</v>
-      </c>
       <c r="I615" s="3" t="n">
-        <v>46305.5</v>
+        <v>46305.91666666666</v>
       </c>
     </row>
     <row r="616">
@@ -28889,7 +28887,7 @@
         <v>46289.29166666666</v>
       </c>
       <c r="I645" s="3" t="n">
-        <v>46292</v>
+        <v>46292.08333333334</v>
       </c>
     </row>
     <row r="646">
@@ -28924,13 +28922,13 @@
         </is>
       </c>
       <c r="G646" s="3" t="n">
-        <v>46292.10416666666</v>
+        <v>46292.16666666666</v>
       </c>
       <c r="H646" s="3" t="n">
-        <v>46292.14583333334</v>
+        <v>46292.22916666666</v>
       </c>
       <c r="I646" s="3" t="n">
-        <v>46292.5</v>
+        <v>46292.62916666667</v>
       </c>
     </row>
     <row r="647">
@@ -28965,13 +28963,13 @@
         </is>
       </c>
       <c r="G647" s="3" t="n">
-        <v>46295.47916666666</v>
+        <v>46295.875</v>
       </c>
       <c r="H647" s="3" t="n">
-        <v>46295.52083333334</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="I647" s="3" t="n">
-        <v>46295.89583333334</v>
+        <v>46296.29166666666</v>
       </c>
     </row>
     <row r="648">
@@ -29006,13 +29004,13 @@
         </is>
       </c>
       <c r="G648" s="3" t="n">
-        <v>46297.85416666666</v>
+        <v>46298.25</v>
       </c>
       <c r="H648" s="3" t="n">
-        <v>46298.02083333334</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="I648" s="3" t="n">
-        <v>46298.5625</v>
+        <v>46298.95833333334</v>
       </c>
     </row>
     <row r="649">
@@ -29047,13 +29045,13 @@
         </is>
       </c>
       <c r="G649" s="3" t="n">
-        <v>46300.35416666666</v>
+        <v>46300.75</v>
       </c>
       <c r="H649" s="3" t="n">
-        <v>46300.39583333334</v>
+        <v>46300.79166666666</v>
       </c>
       <c r="I649" s="3" t="n">
-        <v>46300.64583333334</v>
+        <v>46301.04166666666</v>
       </c>
     </row>
     <row r="650">
@@ -29088,13 +29086,13 @@
         </is>
       </c>
       <c r="G650" s="3" t="n">
-        <v>46301.0625</v>
+        <v>46301.45833333334</v>
       </c>
       <c r="H650" s="3" t="n">
-        <v>46301.1875</v>
+        <v>46301.58333333334</v>
       </c>
       <c r="I650" s="3" t="n">
-        <v>46302.3125</v>
+        <v>46302.70833333334</v>
       </c>
     </row>
     <row r="651">
@@ -29129,13 +29127,13 @@
         </is>
       </c>
       <c r="G651" s="3" t="n">
-        <v>46302.64583333334</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="H651" s="3" t="n">
-        <v>46302.6875</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="I651" s="3" t="n">
-        <v>46303.02083333334</v>
+        <v>46303.41666666666</v>
       </c>
     </row>
     <row r="652">
@@ -29170,13 +29168,13 @@
         </is>
       </c>
       <c r="G652" s="3" t="n">
-        <v>46306.89583333334</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="H652" s="3" t="n">
-        <v>46306.9375</v>
+        <v>46307.33333333334</v>
       </c>
       <c r="I652" s="3" t="n">
-        <v>46307.35416666666</v>
+        <v>46307.75</v>
       </c>
     </row>
     <row r="653">
@@ -29207,17 +29205,17 @@
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="G653" s="3" t="n">
-        <v>46307.60416666666</v>
+        <v>46308</v>
       </c>
       <c r="H653" s="3" t="n">
-        <v>46307.60416666666</v>
+        <v>46308</v>
       </c>
       <c r="I653" s="3" t="n">
-        <v>46307.97916666666</v>
+        <v>46308.375</v>
       </c>
     </row>
     <row r="654">
@@ -29233,32 +29231,32 @@
       </c>
       <c r="C654" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D654" s="2" t="inlineStr">
         <is>
-          <t>PUSH4</t>
+          <t>KEL02</t>
         </is>
       </c>
       <c r="E654" s="2" t="inlineStr">
         <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="F654" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
       <c r="G654" s="3" t="n">
-        <v>46309.28541666667</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="H654" s="3" t="n">
-        <v>46309.32708333333</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="I654" s="3" t="n">
-        <v>46310.03541666667</v>
+        <v>46309.95833333334</v>
       </c>
     </row>
     <row r="655">
@@ -29274,17 +29272,17 @@
       </c>
       <c r="C655" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="D655" s="2" t="inlineStr">
         <is>
-          <t>KEL02</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="E655" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="F655" s="2" t="inlineStr">
@@ -29293,13 +29291,13 @@
         </is>
       </c>
       <c r="G655" s="3" t="n">
-        <v>46309.51458333333</v>
+        <v>46312</v>
       </c>
       <c r="H655" s="3" t="n">
-        <v>46309.51458333333</v>
+        <v>46312.04166666666</v>
       </c>
       <c r="I655" s="3" t="n">
-        <v>46309.76458333333</v>
+        <v>46312.75</v>
       </c>
     </row>
     <row r="656">
@@ -29334,13 +29332,13 @@
         </is>
       </c>
       <c r="G656" s="3" t="n">
-        <v>46310.24305555555</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="H656" s="3" t="n">
-        <v>46310.28472222222</v>
+        <v>46313</v>
       </c>
       <c r="I656" s="3" t="n">
-        <v>46310.61805555555</v>
+        <v>46313.33333333334</v>
       </c>
     </row>
     <row r="657">
@@ -29375,13 +29373,13 @@
         </is>
       </c>
       <c r="G657" s="3" t="n">
-        <v>46314.05833333333</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="H657" s="3" t="n">
-        <v>46314.1</v>
+        <v>46316.625</v>
       </c>
       <c r="I657" s="3" t="n">
-        <v>46314.475</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="658">
@@ -29416,13 +29414,13 @@
         </is>
       </c>
       <c r="G658" s="3" t="n">
-        <v>46316.93333333333</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="H658" s="3" t="n">
-        <v>46317.1</v>
+        <v>46319.625</v>
       </c>
       <c r="I658" s="3" t="n">
-        <v>46317.64166666667</v>
+        <v>46320.16666666666</v>
       </c>
     </row>
     <row r="659">
@@ -29457,13 +29455,13 @@
         </is>
       </c>
       <c r="G659" s="3" t="n">
-        <v>46319.43333333333</v>
+        <v>46321.95833333334</v>
       </c>
       <c r="H659" s="3" t="n">
-        <v>46319.475</v>
+        <v>46322</v>
       </c>
       <c r="I659" s="3" t="n">
-        <v>46319.725</v>
+        <v>46322.25</v>
       </c>
     </row>
     <row r="660">
@@ -29498,13 +29496,13 @@
         </is>
       </c>
       <c r="G660" s="3" t="n">
-        <v>46320.14166666667</v>
+        <v>46322.66666666666</v>
       </c>
       <c r="H660" s="3" t="n">
-        <v>46320.26666666667</v>
+        <v>46322.79166666666</v>
       </c>
       <c r="I660" s="3" t="n">
-        <v>46321.39166666667</v>
+        <v>46323.91666666666</v>
       </c>
     </row>
     <row r="661">
@@ -29539,13 +29537,13 @@
         </is>
       </c>
       <c r="G661" s="3" t="n">
-        <v>46321.725</v>
+        <v>46324.25</v>
       </c>
       <c r="H661" s="3" t="n">
-        <v>46321.76666666667</v>
+        <v>46324.29166666666</v>
       </c>
       <c r="I661" s="3" t="n">
-        <v>46322.1</v>
+        <v>46324.625</v>
       </c>
     </row>
     <row r="662">
@@ -29580,13 +29578,13 @@
         </is>
       </c>
       <c r="G662" s="3" t="n">
-        <v>46325.975</v>
+        <v>46328.5</v>
       </c>
       <c r="H662" s="3" t="n">
-        <v>46326.01666666667</v>
+        <v>46328.54166666666</v>
       </c>
       <c r="I662" s="3" t="n">
-        <v>46326.43333333333</v>
+        <v>46328.95833333334</v>
       </c>
     </row>
     <row r="663">
@@ -29621,13 +29619,13 @@
         </is>
       </c>
       <c r="G663" s="3" t="n">
-        <v>46326.68333333333</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="H663" s="3" t="n">
-        <v>46326.68333333333</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="I663" s="3" t="n">
-        <v>46327.05833333333</v>
+        <v>46329.58333333334</v>
       </c>
     </row>
     <row r="664">
@@ -29662,13 +29660,13 @@
         </is>
       </c>
       <c r="G664" s="3" t="n">
-        <v>46328.30833333333</v>
+        <v>46330.83333333334</v>
       </c>
       <c r="H664" s="3" t="n">
-        <v>46328.30833333333</v>
+        <v>46330.83333333334</v>
       </c>
       <c r="I664" s="3" t="n">
-        <v>46328.55833333333</v>
+        <v>46331.08333333334</v>
       </c>
     </row>
     <row r="665">
@@ -29703,13 +29701,13 @@
         </is>
       </c>
       <c r="G665" s="3" t="n">
-        <v>46330.89166666667</v>
+        <v>46333.62430555555</v>
       </c>
       <c r="H665" s="3" t="n">
-        <v>46330.93333333333</v>
+        <v>46333.66597222222</v>
       </c>
       <c r="I665" s="3" t="n">
-        <v>46331.64166666667</v>
+        <v>46334.37430555555</v>
       </c>
     </row>
     <row r="666">
@@ -29744,13 +29742,13 @@
         </is>
       </c>
       <c r="G666" s="3" t="n">
-        <v>46331.85</v>
+        <v>46334.58263888889</v>
       </c>
       <c r="H666" s="3" t="n">
-        <v>46331.89166666667</v>
+        <v>46334.62430555555</v>
       </c>
       <c r="I666" s="3" t="n">
-        <v>46332.225</v>
+        <v>46334.95763888889</v>
       </c>
     </row>
     <row r="667">
@@ -29785,13 +29783,13 @@
         </is>
       </c>
       <c r="G667" s="3" t="n">
-        <v>46335.05833333333</v>
+        <v>46337.79097222222</v>
       </c>
       <c r="H667" s="3" t="n">
-        <v>46335.1</v>
+        <v>46337.83263888889</v>
       </c>
       <c r="I667" s="3" t="n">
-        <v>46335.475</v>
+        <v>46338.20763888889</v>
       </c>
     </row>
     <row r="668">
@@ -29826,13 +29824,13 @@
         </is>
       </c>
       <c r="G668" s="3" t="n">
-        <v>46337.93333333333</v>
+        <v>46340.66597222222</v>
       </c>
       <c r="H668" s="3" t="n">
-        <v>46338.1</v>
+        <v>46340.83263888889</v>
       </c>
       <c r="I668" s="3" t="n">
-        <v>46338.64166666667</v>
+        <v>46341.37430555555</v>
       </c>
     </row>
     <row r="669">
@@ -29867,13 +29865,13 @@
         </is>
       </c>
       <c r="G669" s="3" t="n">
-        <v>46340.43333333333</v>
+        <v>46343.16597222222</v>
       </c>
       <c r="H669" s="3" t="n">
-        <v>46340.475</v>
+        <v>46343.20763888889</v>
       </c>
       <c r="I669" s="3" t="n">
-        <v>46340.725</v>
+        <v>46343.45763888889</v>
       </c>
     </row>
     <row r="670">
@@ -29908,13 +29906,13 @@
         </is>
       </c>
       <c r="G670" s="3" t="n">
-        <v>46341.14166666667</v>
+        <v>46343.87430555555</v>
       </c>
       <c r="H670" s="3" t="n">
-        <v>46341.26666666667</v>
+        <v>46343.99930555555</v>
       </c>
       <c r="I670" s="3" t="n">
-        <v>46342.39166666667</v>
+        <v>46345.12430555555</v>
       </c>
     </row>
     <row r="671">
@@ -29949,13 +29947,13 @@
         </is>
       </c>
       <c r="G671" s="3" t="n">
-        <v>46342.725</v>
+        <v>46345.45763888889</v>
       </c>
       <c r="H671" s="3" t="n">
-        <v>46342.76666666667</v>
+        <v>46345.49930555555</v>
       </c>
       <c r="I671" s="3" t="n">
-        <v>46343.1</v>
+        <v>46345.83263888889</v>
       </c>
     </row>
     <row r="672">
@@ -29990,13 +29988,13 @@
         </is>
       </c>
       <c r="G672" s="3" t="n">
-        <v>46346.975</v>
+        <v>46349.70763888889</v>
       </c>
       <c r="H672" s="3" t="n">
-        <v>46347.01666666667</v>
+        <v>46349.74930555555</v>
       </c>
       <c r="I672" s="3" t="n">
-        <v>46347.43333333333</v>
+        <v>46350.16597222222</v>
       </c>
     </row>
     <row r="673">
@@ -30031,13 +30029,13 @@
         </is>
       </c>
       <c r="G673" s="3" t="n">
-        <v>46347.68333333333</v>
+        <v>46350.41597222222</v>
       </c>
       <c r="H673" s="3" t="n">
-        <v>46347.68333333333</v>
+        <v>46350.41597222222</v>
       </c>
       <c r="I673" s="3" t="n">
-        <v>46348.05833333333</v>
+        <v>46350.79097222222</v>
       </c>
     </row>
     <row r="674">
@@ -30072,13 +30070,13 @@
         </is>
       </c>
       <c r="G674" s="3" t="n">
-        <v>46349.30833333333</v>
+        <v>46352.04097222222</v>
       </c>
       <c r="H674" s="3" t="n">
-        <v>46349.30833333333</v>
+        <v>46352.04097222222</v>
       </c>
       <c r="I674" s="3" t="n">
-        <v>46349.55833333333</v>
+        <v>46352.29097222222</v>
       </c>
     </row>
     <row r="675">
@@ -30113,13 +30111,13 @@
         </is>
       </c>
       <c r="G675" s="3" t="n">
-        <v>46351.89166666667</v>
+        <v>46354.62430555555</v>
       </c>
       <c r="H675" s="3" t="n">
-        <v>46351.93333333333</v>
+        <v>46354.66597222222</v>
       </c>
       <c r="I675" s="3" t="n">
-        <v>46352.64166666667</v>
+        <v>46355.37430555555</v>
       </c>
     </row>
     <row r="676">
@@ -30154,13 +30152,13 @@
         </is>
       </c>
       <c r="G676" s="3" t="n">
-        <v>46352.85</v>
+        <v>46355.58263888889</v>
       </c>
       <c r="H676" s="3" t="n">
-        <v>46352.89166666667</v>
+        <v>46355.62430555555</v>
       </c>
       <c r="I676" s="3" t="n">
-        <v>46353.225</v>
+        <v>46355.95763888889</v>
       </c>
     </row>
     <row r="677">
@@ -30195,13 +30193,13 @@
         </is>
       </c>
       <c r="G677" s="3" t="n">
-        <v>46356.05833333333</v>
+        <v>46358.79097222222</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>46356.1</v>
+        <v>46358.83263888889</v>
       </c>
       <c r="I677" s="3" t="n">
-        <v>46356.475</v>
+        <v>46359.20763888889</v>
       </c>
     </row>
     <row r="678">
@@ -30236,13 +30234,13 @@
         </is>
       </c>
       <c r="G678" s="3" t="n">
-        <v>46358.93333333333</v>
+        <v>46361.66597222222</v>
       </c>
       <c r="H678" s="3" t="n">
-        <v>46359.1</v>
+        <v>46361.83263888889</v>
       </c>
       <c r="I678" s="3" t="n">
-        <v>46359.64166666667</v>
+        <v>46362.37430555555</v>
       </c>
     </row>
     <row r="679">
@@ -30277,13 +30275,13 @@
         </is>
       </c>
       <c r="G679" s="3" t="n">
-        <v>46361.43333333333</v>
+        <v>46364.16597222222</v>
       </c>
       <c r="H679" s="3" t="n">
-        <v>46361.475</v>
+        <v>46364.20763888889</v>
       </c>
       <c r="I679" s="3" t="n">
-        <v>46361.725</v>
+        <v>46364.45763888889</v>
       </c>
     </row>
     <row r="680">
@@ -30318,13 +30316,13 @@
         </is>
       </c>
       <c r="G680" s="3" t="n">
-        <v>46362.14166666667</v>
+        <v>46364.87430555555</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>46362.26666666667</v>
+        <v>46364.99930555555</v>
       </c>
       <c r="I680" s="3" t="n">
-        <v>46363.39166666667</v>
+        <v>46366.12430555555</v>
       </c>
     </row>
     <row r="681">
@@ -30359,13 +30357,13 @@
         </is>
       </c>
       <c r="G681" s="3" t="n">
-        <v>46363.725</v>
+        <v>46366.45763888889</v>
       </c>
       <c r="H681" s="3" t="n">
-        <v>46363.76666666667</v>
+        <v>46366.49930555555</v>
       </c>
       <c r="I681" s="3" t="n">
-        <v>46364.1</v>
+        <v>46366.83263888889</v>
       </c>
     </row>
     <row r="682">
@@ -30400,13 +30398,13 @@
         </is>
       </c>
       <c r="G682" s="3" t="n">
-        <v>46367.975</v>
+        <v>46370.70763888889</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>46368.01666666667</v>
+        <v>46370.74930555555</v>
       </c>
       <c r="I682" s="3" t="n">
-        <v>46368.43333333333</v>
+        <v>46371.16597222222</v>
       </c>
     </row>
     <row r="683">
@@ -30441,13 +30439,13 @@
         </is>
       </c>
       <c r="G683" s="3" t="n">
-        <v>46368.68333333333</v>
+        <v>46371.41597222222</v>
       </c>
       <c r="H683" s="3" t="n">
-        <v>46368.68333333333</v>
+        <v>46371.41597222222</v>
       </c>
       <c r="I683" s="3" t="n">
-        <v>46369.05833333333</v>
+        <v>46371.79097222222</v>
       </c>
     </row>
     <row r="684">
@@ -30480,13 +30478,13 @@
         <v/>
       </c>
       <c r="G684" s="3" t="n">
-        <v>46370.30833333333</v>
+        <v>46373.04097222222</v>
       </c>
       <c r="H684" s="3" t="n">
-        <v>46370.30833333333</v>
+        <v>46373.04097222222</v>
       </c>
       <c r="I684" s="3" t="n">
-        <v>46370.55833333333</v>
+        <v>46373.29097222222</v>
       </c>
     </row>
     <row r="685">
@@ -32815,13 +32813,13 @@
         </is>
       </c>
       <c r="G741" s="3" t="n">
-        <v>46299.25</v>
+        <v>46299.375</v>
       </c>
       <c r="H741" s="3" t="n">
-        <v>46299.29166666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="I741" s="3" t="n">
-        <v>46299.58333333334</v>
+        <v>46299.70833333334</v>
       </c>
     </row>
     <row r="742">
@@ -32856,13 +32854,13 @@
         </is>
       </c>
       <c r="G742" s="3" t="n">
-        <v>46299.875</v>
+        <v>46300</v>
       </c>
       <c r="H742" s="3" t="n">
-        <v>46299.875</v>
+        <v>46300</v>
       </c>
       <c r="I742" s="3" t="n">
-        <v>46301.25</v>
+        <v>46301.375</v>
       </c>
     </row>
     <row r="743">
@@ -32897,13 +32895,13 @@
         </is>
       </c>
       <c r="G743" s="3" t="n">
-        <v>46301.5</v>
+        <v>46301.625</v>
       </c>
       <c r="H743" s="3" t="n">
-        <v>46301.54166666666</v>
+        <v>46301.66666666666</v>
       </c>
       <c r="I743" s="3" t="n">
-        <v>46302</v>
+        <v>46302.125</v>
       </c>
     </row>
     <row r="744">
@@ -32938,13 +32936,13 @@
         </is>
       </c>
       <c r="G744" s="3" t="n">
-        <v>46305.83333333334</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="H744" s="3" t="n">
-        <v>46305.83333333334</v>
+        <v>46305.95833333334</v>
       </c>
       <c r="I744" s="3" t="n">
-        <v>46306.29166666666</v>
+        <v>46306.41666666666</v>
       </c>
     </row>
     <row r="745">
@@ -32979,13 +32977,13 @@
         </is>
       </c>
       <c r="G745" s="3" t="n">
-        <v>46307.29166666666</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="H745" s="3" t="n">
-        <v>46307.29166666666</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="I745" s="3" t="n">
-        <v>46307.75</v>
+        <v>46307.875</v>
       </c>
     </row>
     <row r="746">
@@ -33020,13 +33018,13 @@
         </is>
       </c>
       <c r="G746" s="3" t="n">
-        <v>46310.22916666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>46310.27083333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="I746" s="3" t="n">
-        <v>46310.89583333334</v>
+        <v>46311.02083333334</v>
       </c>
     </row>
     <row r="747">
@@ -33061,13 +33059,13 @@
         </is>
       </c>
       <c r="G747" s="3" t="n">
-        <v>46311.89583333334</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="H747" s="3" t="n">
-        <v>46311.9375</v>
+        <v>46312.0625</v>
       </c>
       <c r="I747" s="3" t="n">
-        <v>46312.4375</v>
+        <v>46312.5625</v>
       </c>
     </row>
     <row r="748">
@@ -33102,13 +33100,13 @@
         </is>
       </c>
       <c r="G748" s="3" t="n">
-        <v>46313.52083333334</v>
+        <v>46313.64583333334</v>
       </c>
       <c r="H748" s="3" t="n">
-        <v>46313.6875</v>
+        <v>46313.8125</v>
       </c>
       <c r="I748" s="3" t="n">
-        <v>46314.47916666666</v>
+        <v>46314.60416666666</v>
       </c>
     </row>
     <row r="749">
@@ -33143,13 +33141,13 @@
         </is>
       </c>
       <c r="G749" s="3" t="n">
-        <v>46320.22916666666</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="H749" s="3" t="n">
-        <v>46320.27083333334</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="I749" s="3" t="n">
-        <v>46320.5625</v>
+        <v>46320.6875</v>
       </c>
     </row>
     <row r="750">
@@ -33184,13 +33182,13 @@
         </is>
       </c>
       <c r="G750" s="3" t="n">
-        <v>46320.85416666666</v>
+        <v>46320.97916666666</v>
       </c>
       <c r="H750" s="3" t="n">
-        <v>46320.85416666666</v>
+        <v>46320.97916666666</v>
       </c>
       <c r="I750" s="3" t="n">
-        <v>46322.22916666666</v>
+        <v>46322.35416666666</v>
       </c>
     </row>
     <row r="751">
@@ -33225,13 +33223,13 @@
         </is>
       </c>
       <c r="G751" s="3" t="n">
-        <v>46322.47916666666</v>
+        <v>46322.60416666666</v>
       </c>
       <c r="H751" s="3" t="n">
-        <v>46322.52083333334</v>
+        <v>46322.64583333334</v>
       </c>
       <c r="I751" s="3" t="n">
-        <v>46322.97916666666</v>
+        <v>46323.10416666666</v>
       </c>
     </row>
     <row r="752">
@@ -33266,13 +33264,13 @@
         </is>
       </c>
       <c r="G752" s="3" t="n">
-        <v>46326.8125</v>
+        <v>46326.9375</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>46326.8125</v>
+        <v>46326.9375</v>
       </c>
       <c r="I752" s="3" t="n">
-        <v>46327.27083333334</v>
+        <v>46327.39583333334</v>
       </c>
     </row>
     <row r="753">
@@ -33307,13 +33305,13 @@
         </is>
       </c>
       <c r="G753" s="3" t="n">
-        <v>46328.27083333334</v>
+        <v>46328.39583333334</v>
       </c>
       <c r="H753" s="3" t="n">
-        <v>46328.27083333334</v>
+        <v>46328.39583333334</v>
       </c>
       <c r="I753" s="3" t="n">
-        <v>46328.77083333334</v>
+        <v>46328.89583333334</v>
       </c>
     </row>
     <row r="754">
@@ -48680,10 +48678,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -48721,7 +48719,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260927-0636-SKED.xlsx)</t>
+          <t>New ETA (auto-20260927-1441-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -48738,84 +48736,84 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2608E</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46258.75</v>
+        <v>46293.875</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46258.54166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-5</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CNNGB</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46295.66666666666</v>
+        <v>46295</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46296.375</v>
+        <v>46294.75</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>17</v>
+        <v>-6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CNNGB</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -48825,28 +48823,28 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46297.6875</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46298.39583333334</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>17</v>
+        <v>-6</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -48856,236 +48854,238 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>INNSA</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46302.22916666666</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46302.9375</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>17</v>
+        <v>-6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>INNSA</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>INMUN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46315.02083333334</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46315.72916666666</v>
+        <v>46302.91666666666</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17</v>
+        <v>-6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>INMUN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PKKHI</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46318.02083333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46318.72916666666</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>17</v>
+        <v>-6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>KMTC JAKARTA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PKKHI</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MYPKL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46319.52083333334</v>
+        <v>46258.75</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46320.22916666666</v>
+        <v>46258.54166666666</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>SAWASDEE ALTAIR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>MYPKL</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46329.0625</v>
+        <v>46292.79166666666</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46329.77083333334</v>
+        <v>46292.66666666666</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>17</v>
+        <v>-3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>SAWASDEE ALTAIR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v/>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46339.47916666666</v>
+        <v>46294.16666666666</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46340.1875</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>17</v>
+        <v>-9</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>SAWASDEE ALTAIR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46295.60416666666</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46295.47916666666</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -49096,68 +49096,68 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>SAWASDEE ALTAIR</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46297.97916666666</v>
+        <v>46302.66666666666</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46297.85416666666</v>
+        <v>46302.83333333334</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>SAWASDEE ALTAIR</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46300.47916666666</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46300.35416666666</v>
+        <v>46304.875</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -49173,31 +49173,31 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46301.1875</v>
+        <v>46292.10416666666</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46301.0625</v>
+        <v>46292.16666666666</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-3</v>
+        <v>1.5</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
@@ -49209,31 +49209,31 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46302.77083333334</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46302.64583333334</v>
+        <v>46295.875</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-3</v>
+        <v>9.5</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
@@ -49245,31 +49245,31 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46307.02083333334</v>
+        <v>46297.85416666666</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46306.89583333334</v>
+        <v>46298.25</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-3</v>
+        <v>9.5</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
@@ -49281,31 +49281,31 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46307.72916666666</v>
+        <v>46300.35416666666</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46307.60416666666</v>
+        <v>46300.75</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-3</v>
+        <v>9.5</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
@@ -49317,31 +49317,1721 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46301.0625</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>46303.04166666666</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46306.89583333334</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>TWKEL</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46307.60416666666</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46309.51458333333</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>46309.70833333334</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>KRUSN</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>46309.28541666667</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46310.24305555555</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>46312.95833333334</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>46314.05833333333</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>46316.58333333334</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46316.93333333333</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>46319.45833333334</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46319.43333333333</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>46321.95833333334</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46320.14166666667</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>46322.66666666666</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>46321.725</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>46324.25</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46325.975</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>46328.5</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>46326.68333333333</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>46329.20833333334</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46328.30833333333</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>46330.83333333334</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46330.89166666667</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>46333.62430555555</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46331.85</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>46334.58263888889</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46335.05833333333</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46337.79097222222</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46337.93333333333</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46340.66597222222</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46340.43333333333</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46343.16597222222</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46341.14166666667</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46343.87430555555</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46342.725</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46345.45763888889</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46346.975</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46349.70763888889</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46347.68333333333</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46350.41597222222</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46349.30833333333</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46352.04097222222</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>46351.89166666667</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>46354.62430555555</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46352.85</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>46355.58263888889</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>46356.05833333333</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>46358.79097222222</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>46358.93333333333</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>46361.66597222222</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>46361.43333333333</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>46364.16597222222</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>46362.14166666667</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>46364.87430555555</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>46363.725</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>46366.45763888889</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>46367.975</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>46370.70763888889</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>46368.68333333333</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>46371.41597222222</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>46370.30833333333</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>46373.04097222222</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>46299.25</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>46299.375</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>2610N</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>46309.63958333333</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>46309.51458333333</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
+      <c r="E54" s="3" t="n">
+        <v>46299.875</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>46301.5</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>46301.625</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>46305.83333333334</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>46305.95833333334</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>46307.41666666666</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>46310.22916666666</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>46310.35416666666</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>46311.89583333334</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>46312.02083333334</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>46313.52083333334</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>46313.64583333334</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>46320.22916666666</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>46320.35416666666</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>46320.85416666666</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>46320.97916666666</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>46322.47916666666</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>46322.60416666666</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>46326.8125</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>46326.9375</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE DENEB</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>46328.27083333334</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>46328.39583333334</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -913,20 +913,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>KRKAN -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-29T00:30:00</t>
+          <t>Alongside, departs to THLCH ~2026-09-29T13:30:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1043,20 +1045,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; HKHKG</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v/>
+          <t>HKHKG (HKG03)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-29T04:00:00</t>
+          <t>Alongside, departs to CNSHK ~2026-09-29T18:30:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -47973,10 +47977,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -48014,7 +48018,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260928-1520-SKED.xlsx)</t>
+          <t>New ETA (auto-20260928-2152-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -48059,6040 +48063,6 @@
         <v>-5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46291.58333333334</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46292.16666666666</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46295.39583333334</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46296.39583333334</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>46301.5625</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46300.4375</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>-27</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46305.875</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>46304.25</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>-39</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46307.04166666666</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>46304.91666666666</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>46310.58333333334</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>46308.45833333334</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46312.27083333334</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>46310.14583333334</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>46310.875</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>46314.47916666666</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>46312.35416666666</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>46319.3125</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>46317.1875</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>46321.97916666666</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>46319.85416666666</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>46326.02083333334</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>46323.89583333334</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>46330.22916666666</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>46328.10416666666</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>46333.77083333334</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>46331.64583333334</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>46334.5625</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>46332.4375</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>-51</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>46338.1875</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>46336.27083333334</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>46339.97916666666</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>46338.0625</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>46340.79166666666</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>46338.875</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>46342.47916666666</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>46340.5625</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>46347.3125</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>46345.39583333334</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>46349.97916666666</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>46348.0625</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46354.02083333334</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>46352.10416666666</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>46358.22916666666</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>46356.3125</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>46361.77083333334</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>46359.85416666666</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>KMTC SURABAYA</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>46362.5625</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>46360.64583333334</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>KMTC ULSAN</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2615S</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>46287.20833333334</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>46287.04166666666</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>KMTC ULSAN</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>46287.625</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>46287.41666666666</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>KMTC ULSAN</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>46290.20833333334</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>46288.70833333334</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>-36</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>KMTC ULSAN</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>46292.58333333334</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>46291.83333333334</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>-18</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>46292.47916666666</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>46293.29166666666</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>46293.20833333334</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>46295.125</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>46294.64583333334</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>46296.70833333334</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>46301.22916666666</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>46301.29166666666</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>46304.75</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>46304.33333333334</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>46308.5625</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>46308.14583333334</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>46313.79166666666</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>46313.375</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>46317.10416666666</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>46316.6875</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46317.89583333334</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>46317.47916666666</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46321.52083333334</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>46321.10416666666</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>46323.3125</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>46322.89583333334</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>46324.125</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>46323.70833333334</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>46325.8125</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>46325.39583333334</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>46330.64583333334</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>46330.22916666666</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>46333.3125</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>46332.89583333334</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>46337.35416666666</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>46336.9375</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>46341.5625</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>46341.14583333334</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>46345.10416666666</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>46344.6875</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>46345.89583333334</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>46345.47916666666</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>46349.52083333334</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>46349.10416666666</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>46351.3125</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>46350.89583333334</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>46352.125</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>46351.70833333334</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>46353.8125</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>46353.39583333334</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>46358.64583333334</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>46358.22916666666</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>46361.3125</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>46360.89583333334</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>46365.35416666666</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>46364.9375</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>46369.5625</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>46369.14583333334</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>46373.10416666666</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>46372.6875</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>KMTC XIAMEN</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>46373.89583333334</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>46373.47916666666</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>46297.3125</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>46297.79166666666</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>46298.10416666666</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>46303.83333333334</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>46304.14583333334</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>46306.22916666666</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>46306.64583333334</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>46306.75</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>46307.16666666666</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>46308.04166666666</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>46308.45833333334</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>46310.39583333334</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>46310.8125</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>46319.5</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>46317.66666666666</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>-44</v>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>46320.375</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>46318.54166666666</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>-44</v>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>46321.58333333334</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>46319.75</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>-44</v>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>46322.33333333334</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>46320.5</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>-44</v>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>46327.875</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>46325.95833333334</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>46330.27083333334</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>46328.3125</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>-47</v>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>46330.79166666666</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>46328.83333333334</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>-47</v>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>46332.08333333334</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>46330.125</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>-47</v>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>46334.4375</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>46332.47916666666</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>-47</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>46341.79166666666</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>46338.25</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>-85</v>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>46342.66666666666</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>46339.125</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>-85</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>46343.875</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>46340.33333333334</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>-85</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>46344.625</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>46341.08333333334</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>-85</v>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>46350.16666666666</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>46346.54166666666</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>-87</v>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>46352.5625</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>46348.93958333333</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>-87</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>46353.08333333334</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>46349.46041666667</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>-87</v>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>46354.375</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>46350.75208333333</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>-87</v>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>46356.72916666666</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>46353.10625</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>-87</v>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>46298.72916666666</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>46299.375</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>46299.97916666666</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>46300.70833333334</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>46300.79166666666</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>46301.54166666666</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>46302.54166666666</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>46303.29166666666</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>46309.91666666666</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>46311.20833333334</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>46313.125</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>46314.41666666666</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>46313.75</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>46315.04166666666</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>46315.125</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>46316.41666666666</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>46317.08333333334</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>46318.375</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>46324.6875</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>46326.02083333334</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>46325.9375</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>46327.29166666666</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>46326.75</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>46328.125</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>46328.5</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>46329.875</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>46333.875</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>46335.25</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>46336.08333333334</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>46337.45833333334</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>46336.70833333334</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>46338.08333333334</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>46338.08333333334</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>46339.45833333334</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>46340.04166666666</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>46341.41666666666</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>46345.6875</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>46347.0625</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>46346.9375</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>46348.32083333333</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>46347.75</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>46349.14166666667</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>46349.5</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>46350.89166666667</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>46354.875</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>46356.26666666667</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>46357.08333333334</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>46358.475</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>46357.70833333334</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>46359.1</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>46359.08333333334</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>46360.475</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE MIMOSA</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>46361.04166666666</v>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>46362.43333333333</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>46300.9375</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>46303.0625</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>46305.64583333334</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>46307.77083333334</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>46312.41666666666</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>46314.54166666666</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>46314.6875</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>46316.8125</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>46316.02083333334</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>46318.14583333334</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>46318.1875</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>46320.3125</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>46326.0625</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>46328.1875</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>46328.0625</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>46330.1875</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>46332.64583333334</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>46334.77083333334</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>46339.77083333334</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>46341.89583333334</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>46342.10416666666</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>46344.22916666666</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>46343.77083333334</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>46345.89583333334</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>46345.9375</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>46348.0625</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>46353.8125</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>46355.9375</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>46355.8125</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>46357.9375</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>46360.39583333334</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>46362.52083333334</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE RIGEL</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>46367.52083333334</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>46369.64583333334</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>46297.79166666666</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>46297.125</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>46302.10416666666</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>46301.4375</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>46308.875</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>46308.20833333334</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>46311.14583333334</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>46310.47916666666</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>46312.47916666666</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>46311.8125</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>46314.60416666666</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>46313.9375</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>46322.47916666666</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>46321.8125</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>46324.47916666666</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>46323.8125</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>46329.0625</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>46328.39583333334</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>46336.1875</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>46335.52083333334</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>46338.77083333334</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>46338.10416666666</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>46340.4375</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>46339.77083333334</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>46342.60416666666</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>46341.9375</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>46350.47916666666</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>46349.8125</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>46352.47916666666</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>46351.8125</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>46357.0625</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>46356.39583333334</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>46364.1875</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>46363.52083333334</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>46290.75</v>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>46291.41666666666</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>46295.85416666666</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>46295.5</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>46299.02083333334</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>46298.66666666666</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>46299.70833333334</v>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>46299.35416666666</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>46303.375</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>46303.02083333334</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>46305.16666666666</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>46304.8125</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>46305.97916666666</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>46305.625</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>46307.66666666666</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>46307.3125</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>46312.5</v>
-      </c>
-      <c r="F155" s="3" t="n">
-        <v>46312.14583333334</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>46315.16666666666</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>46314.8125</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>46319.20833333334</v>
-      </c>
-      <c r="F157" s="3" t="n">
-        <v>46318.85416666666</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>46323.41666666666</v>
-      </c>
-      <c r="F158" s="3" t="n">
-        <v>46323.0625</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>46326.95833333334</v>
-      </c>
-      <c r="F159" s="3" t="n">
-        <v>46326.60416666666</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>46327.75</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>46327.39583333334</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>46331.375</v>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>46331.02083333334</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>46333.16666666666</v>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>46332.8125</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>46333.97916666666</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>46333.625</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="n">
-        <v>46335.66666666666</v>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>46335.3125</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="n">
-        <v>46340.5</v>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>46340.14583333334</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>46343.16666666666</v>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>46342.8125</v>
-      </c>
-      <c r="G166" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="n">
-        <v>46347.20833333334</v>
-      </c>
-      <c r="F167" s="3" t="n">
-        <v>46346.85416666666</v>
-      </c>
-      <c r="G167" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>46351.41666666666</v>
-      </c>
-      <c r="F168" s="3" t="n">
-        <v>46351.0625</v>
-      </c>
-      <c r="G168" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>46354.95833333334</v>
-      </c>
-      <c r="F169" s="3" t="n">
-        <v>46354.60416666666</v>
-      </c>
-      <c r="G169" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="n">
-        <v>46355.75</v>
-      </c>
-      <c r="F170" s="3" t="n">
-        <v>46355.39583333334</v>
-      </c>
-      <c r="G170" s="2" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Early</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -615,22 +615,20 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>KRINC (INC07)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>0152S</t>
-        </is>
+          <t>KRINC -&gt; KRPTK</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v/>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPTK ~2026-09-29T07:00:00</t>
+          <t>In transit, ETA 2026-09-29T11:00:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -979,22 +977,20 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>THBKK (BKK04)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>THBKK -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v/>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-29T05:00:00</t>
+          <t>In transit, ETA 2026-09-29T10:00:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
@@ -2099,20 +2095,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>CNXMN -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUSH4)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-29T08:30:00</t>
+          <t>Alongside, departs to KRKAN ~2026-09-30T23:00:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
@@ -2234,11 +2232,11 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-02T16:30:00</t>
+          <t>In transit, ETA 2026-10-02T15:00:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>46312.1875</v>
+        <v>46312.125</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2251,7 +2249,7 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46311.8125</v>
+        <v>46311.75</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2407,22 +2405,20 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUS05)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
+          <t>KRPUS -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v/>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRUSN ~2026-09-29T08:00:00</t>
+          <t>In transit, ETA 2026-10-05T00:00:00</t>
         </is>
       </c>
       <c r="I32" s="3" t="n"/>
@@ -22453,7 +22449,7 @@
         <v>46290.45833333334</v>
       </c>
       <c r="H488" s="3" t="n">
-        <v>46293.79166666666</v>
+        <v>46293.775</v>
       </c>
       <c r="I488" s="3" t="n">
         <v>46296.08333333334</v>
@@ -22535,7 +22531,7 @@
         <v>46290.45833333334</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>46293.79166666666</v>
+        <v>46293.775</v>
       </c>
       <c r="I490" s="3" t="n">
         <v>46296.08333333334</v>
@@ -43376,10 +43372,10 @@
         <v>46293.29166666666</v>
       </c>
       <c r="H999" s="3" t="n">
-        <v>46293.33333333334</v>
+        <v>46293.4375</v>
       </c>
       <c r="I999" s="3" t="n">
-        <v>46293.66666666666</v>
+        <v>46293.8125</v>
       </c>
     </row>
     <row r="1000">
@@ -43414,13 +43410,13 @@
         </is>
       </c>
       <c r="G1000" s="3" t="n">
+        <v>46297.625</v>
+      </c>
+      <c r="H1000" s="3" t="n">
         <v>46297.6875</v>
       </c>
-      <c r="H1000" s="3" t="n">
-        <v>46297.75</v>
-      </c>
       <c r="I1000" s="3" t="n">
-        <v>46298.25</v>
+        <v>46298.1875</v>
       </c>
     </row>
     <row r="1001">
@@ -43455,13 +43451,13 @@
         </is>
       </c>
       <c r="G1001" s="3" t="n">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="H1001" s="3" t="n">
         <v>46299.27083333334</v>
       </c>
-      <c r="H1001" s="3" t="n">
-        <v>46299.33333333334</v>
-      </c>
       <c r="I1001" s="3" t="n">
-        <v>46299.95833333334</v>
+        <v>46299.89583333334</v>
       </c>
     </row>
     <row r="1002">
@@ -43496,13 +43492,13 @@
         </is>
       </c>
       <c r="G1002" s="3" t="n">
-        <v>46302.3125</v>
+        <v>46302.25</v>
       </c>
       <c r="H1002" s="3" t="n">
-        <v>46302.35416666666</v>
+        <v>46302.29166666666</v>
       </c>
       <c r="I1002" s="3" t="n">
-        <v>46303.0625</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="1003">
@@ -43537,13 +43533,13 @@
         </is>
       </c>
       <c r="G1003" s="3" t="n">
+        <v>46303.29166666666</v>
+      </c>
+      <c r="H1003" s="3" t="n">
         <v>46303.35416666666</v>
       </c>
-      <c r="H1003" s="3" t="n">
-        <v>46303.41666666666</v>
-      </c>
       <c r="I1003" s="3" t="n">
-        <v>46303.75</v>
+        <v>46303.6875</v>
       </c>
     </row>
     <row r="1004">
@@ -43578,13 +43574,13 @@
         </is>
       </c>
       <c r="G1004" s="3" t="n">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="H1004" s="3" t="n">
         <v>46306.64583333334</v>
       </c>
-      <c r="H1004" s="3" t="n">
-        <v>46306.70833333334</v>
-      </c>
       <c r="I1004" s="3" t="n">
-        <v>46307.20833333334</v>
+        <v>46307.14583333334</v>
       </c>
     </row>
     <row r="1005">
@@ -43619,13 +43615,13 @@
         </is>
       </c>
       <c r="G1005" s="3" t="n">
-        <v>46309.4375</v>
+        <v>46309.375</v>
       </c>
       <c r="H1005" s="3" t="n">
-        <v>46309.60416666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="I1005" s="3" t="n">
-        <v>46310.22916666666</v>
+        <v>46310.16666666666</v>
       </c>
     </row>
     <row r="1006">
@@ -43660,13 +43656,13 @@
         </is>
       </c>
       <c r="G1006" s="3" t="n">
-        <v>46311.8125</v>
+        <v>46311.75</v>
       </c>
       <c r="H1006" s="3" t="n">
-        <v>46311.85416666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="I1006" s="3" t="n">
-        <v>46312.0625</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="1007">
@@ -43701,13 +43697,13 @@
         </is>
       </c>
       <c r="G1007" s="3" t="n">
-        <v>46312.1875</v>
+        <v>46312.125</v>
       </c>
       <c r="H1007" s="3" t="n">
-        <v>46312.3125</v>
+        <v>46312.25</v>
       </c>
       <c r="I1007" s="3" t="n">
-        <v>46313.77083333334</v>
+        <v>46313.70833333334</v>
       </c>
     </row>
     <row r="1008">
@@ -43742,13 +43738,13 @@
         </is>
       </c>
       <c r="G1008" s="3" t="n">
-        <v>46313.97916666666</v>
+        <v>46313.91666666666</v>
       </c>
       <c r="H1008" s="3" t="n">
-        <v>46314.02083333334</v>
+        <v>46313.95833333334</v>
       </c>
       <c r="I1008" s="3" t="n">
-        <v>46314.35416666666</v>
+        <v>46314.29166666666</v>
       </c>
     </row>
     <row r="1009">
@@ -43783,13 +43779,13 @@
         </is>
       </c>
       <c r="G1009" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="H1009" s="3" t="n">
         <v>46318.0625</v>
       </c>
-      <c r="H1009" s="3" t="n">
-        <v>46318.125</v>
-      </c>
       <c r="I1009" s="3" t="n">
-        <v>46318.625</v>
+        <v>46318.5625</v>
       </c>
     </row>
     <row r="1010">
@@ -43824,13 +43820,13 @@
         </is>
       </c>
       <c r="G1010" s="3" t="n">
+        <v>46319.375</v>
+      </c>
+      <c r="H1010" s="3" t="n">
         <v>46319.4375</v>
       </c>
-      <c r="H1010" s="3" t="n">
-        <v>46319.5</v>
-      </c>
       <c r="I1010" s="3" t="n">
-        <v>46320.125</v>
+        <v>46320.0625</v>
       </c>
     </row>
     <row r="1011">
@@ -47977,7 +47973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -48018,7 +48014,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260928-2152-SKED.xlsx)</t>
+          <t>New ETA (auto-20260929-0150-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -48063,6 +48059,402 @@
         <v>-5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46297.6875</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46297.625</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46299.27083333334</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46302.3125</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>46302.25</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46303.35416666666</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46303.29166666666</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46306.64583333334</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46306.58333333334</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46309.4375</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>46309.375</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46311.8125</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>46311.75</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46312.1875</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46312.125</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46313.97916666666</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>46313.91666666666</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46318.0625</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SKY ORION</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46319.4375</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>46319.375</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Early</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -615,20 +615,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>KRINC -&gt; KRPTK</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v/>
+          <t>KRPTK (PTK02)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>0152S</t>
+        </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-29T11:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-09-30T06:00:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -977,20 +979,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>THBKK -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH05)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-29T10:00:00</t>
+          <t>Alongside, departs to HKHKG ~2026-09-30T04:00:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
@@ -1007,7 +1011,7 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>46294.41666666666</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1016,7 +1020,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611S</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1424,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T21:30:00</t>
+          <t>In transit, ETA 2026-10-01T12:00:00</t>
         </is>
       </c>
       <c r="I16" s="3" t="n"/>
@@ -1587,22 +1591,20 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH01)</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
+          <t>THLCH -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v/>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-09-29T12:00:00</t>
+          <t>In transit, ETA 2026-09-30T23:00:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1666,11 +1668,11 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T21:00:00</t>
+          <t>In transit, ETA 2026-10-01T02:00:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46301.45833333334</v>
+        <v>46301.91666666666</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1683,7 +1685,7 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46300.75</v>
+        <v>46301.20833333334</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1862,7 +1864,7 @@
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46306.66666666666</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1875,7 +1877,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46306.29166666666</v>
+        <v>46307.16666666666</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1926,7 +1928,7 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>46315.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -1939,7 +1941,7 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>46314.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -22493,7 +22495,7 @@
         <v>46293.79166666666</v>
       </c>
       <c r="I489" s="3" t="n">
-        <v>46296.08333333334</v>
+        <v>46296.25</v>
       </c>
     </row>
     <row r="490">
@@ -22610,13 +22612,13 @@
         </is>
       </c>
       <c r="G492" s="3" t="n">
-        <v>46296.375</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="H492" s="3" t="n">
-        <v>46296.4375</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="I492" s="3" t="n">
-        <v>46296.95833333334</v>
+        <v>46297.125</v>
       </c>
     </row>
     <row r="493">
@@ -22651,13 +22653,13 @@
         </is>
       </c>
       <c r="G493" s="3" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>46299.5</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="I493" s="3" t="n">
-        <v>46300</v>
+        <v>46300.16666666666</v>
       </c>
     </row>
     <row r="494">
@@ -22692,13 +22694,13 @@
         </is>
       </c>
       <c r="G494" s="3" t="n">
-        <v>46302.95833333334</v>
+        <v>46303.125</v>
       </c>
       <c r="H494" s="3" t="n">
-        <v>46303.08333333334</v>
+        <v>46303.25</v>
       </c>
       <c r="I494" s="3" t="n">
-        <v>46303.5</v>
+        <v>46303.66666666666</v>
       </c>
     </row>
     <row r="495">
@@ -22733,13 +22735,13 @@
         </is>
       </c>
       <c r="G495" s="3" t="n">
-        <v>46315.75</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="H495" s="3" t="n">
-        <v>46316.83333333334</v>
+        <v>46317</v>
       </c>
       <c r="I495" s="3" t="n">
-        <v>46317.5</v>
+        <v>46317.66666666666</v>
       </c>
     </row>
     <row r="496">
@@ -22774,13 +22776,13 @@
         </is>
       </c>
       <c r="G496" s="3" t="n">
-        <v>46318.75</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="H496" s="3" t="n">
-        <v>46318.83333333334</v>
+        <v>46319</v>
       </c>
       <c r="I496" s="3" t="n">
-        <v>46319.33333333334</v>
+        <v>46319.5</v>
       </c>
     </row>
     <row r="497">
@@ -22815,13 +22817,13 @@
         </is>
       </c>
       <c r="G497" s="3" t="n">
-        <v>46320.25</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>46320.33333333334</v>
+        <v>46320.5</v>
       </c>
       <c r="I497" s="3" t="n">
-        <v>46320.91666666666</v>
+        <v>46321.08333333334</v>
       </c>
     </row>
     <row r="498">
@@ -22856,13 +22858,13 @@
         </is>
       </c>
       <c r="G498" s="3" t="n">
-        <v>46329.79166666666</v>
+        <v>46329.95833333334</v>
       </c>
       <c r="H498" s="3" t="n">
-        <v>46330.83333333334</v>
+        <v>46331</v>
       </c>
       <c r="I498" s="3" t="n">
-        <v>46331.41666666666</v>
+        <v>46331.58333333334</v>
       </c>
     </row>
     <row r="499">
@@ -22895,13 +22897,13 @@
         <v/>
       </c>
       <c r="G499" s="3" t="n">
-        <v>46340.20833333334</v>
+        <v>46340.375</v>
       </c>
       <c r="H499" s="3" t="n">
-        <v>46340.25</v>
+        <v>46340.41666666666</v>
       </c>
       <c r="I499" s="3" t="n">
-        <v>46341</v>
+        <v>46341.16666666666</v>
       </c>
     </row>
     <row r="500">
@@ -23305,13 +23307,13 @@
         </is>
       </c>
       <c r="G509" s="3" t="n">
-        <v>46295.89583333334</v>
+        <v>46296.5</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>46295.95833333334</v>
+        <v>46296.5625</v>
       </c>
       <c r="I509" s="3" t="n">
-        <v>46296.70833333334</v>
+        <v>46297.3125</v>
       </c>
     </row>
     <row r="510">
@@ -23373,7 +23375,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -23387,13 +23389,13 @@
         </is>
       </c>
       <c r="G511" s="3" t="n">
-        <v>46302.97916666666</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>46304.14583333334</v>
+        <v>46304.75</v>
       </c>
       <c r="I511" s="3" t="n">
-        <v>46304.97916666666</v>
+        <v>46305.58333333334</v>
       </c>
     </row>
     <row r="512">
@@ -23445,12 +23447,12 @@
       </c>
       <c r="B513" s="2" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2606N</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
@@ -23475,7 +23477,7 @@
         <v>46306.27083333334</v>
       </c>
       <c r="I513" s="3" t="n">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
     </row>
     <row r="514">
@@ -23486,12 +23488,12 @@
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>2606N</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
@@ -23510,13 +23512,13 @@
         </is>
       </c>
       <c r="G514" s="3" t="n">
-        <v>46306.22916666666</v>
+        <v>46306.83333333334</v>
       </c>
       <c r="H514" s="3" t="n">
-        <v>46306.27083333334</v>
+        <v>46306.875</v>
       </c>
       <c r="I514" s="3" t="n">
-        <v>46308.27083333334</v>
+        <v>46307.875</v>
       </c>
     </row>
     <row r="515">
@@ -23551,13 +23553,13 @@
         </is>
       </c>
       <c r="G515" s="3" t="n">
-        <v>46309.79166666666</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="H515" s="3" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="I515" s="3" t="n">
-        <v>46311.79166666666</v>
+        <v>46311.95833333334</v>
       </c>
     </row>
     <row r="516">
@@ -23592,13 +23594,13 @@
         </is>
       </c>
       <c r="G516" s="3" t="n">
-        <v>46312.79166666666</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="H516" s="3" t="n">
-        <v>46315.79166666666</v>
+        <v>46314.95833333334</v>
       </c>
       <c r="I516" s="3" t="n">
-        <v>46316.375</v>
+        <v>46315.54166666666</v>
       </c>
     </row>
     <row r="517">
@@ -23633,13 +23635,13 @@
         </is>
       </c>
       <c r="G517" s="3" t="n">
-        <v>46317.125</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="H517" s="3" t="n">
-        <v>46318.20833333334</v>
+        <v>46317.375</v>
       </c>
       <c r="I517" s="3" t="n">
-        <v>46318.875</v>
+        <v>46318.04166666666</v>
       </c>
     </row>
     <row r="518">
@@ -23674,13 +23676,13 @@
         </is>
       </c>
       <c r="G518" s="3" t="n">
-        <v>46321.875</v>
+        <v>46321.04166666666</v>
       </c>
       <c r="H518" s="3" t="n">
-        <v>46322</v>
+        <v>46321.16666666666</v>
       </c>
       <c r="I518" s="3" t="n">
-        <v>46322.75</v>
+        <v>46321.91666666666</v>
       </c>
     </row>
     <row r="519">
@@ -23715,13 +23717,13 @@
         </is>
       </c>
       <c r="G519" s="3" t="n">
-        <v>46338</v>
+        <v>46337.16666666666</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>46343.04166666666</v>
+        <v>46342.20833333334</v>
       </c>
       <c r="I519" s="3" t="n">
-        <v>46346.04166666666</v>
+        <v>46345.20833333334</v>
       </c>
     </row>
     <row r="520">
@@ -23754,13 +23756,13 @@
         <v/>
       </c>
       <c r="G520" s="3" t="n">
-        <v>46364.29166666666</v>
+        <v>46363.45833333334</v>
       </c>
       <c r="H520" s="3" t="n">
-        <v>46364.33333333334</v>
+        <v>46363.5</v>
       </c>
       <c r="I520" s="3" t="n">
-        <v>46365</v>
+        <v>46364.16666666666</v>
       </c>
     </row>
     <row r="521">
@@ -28668,13 +28670,13 @@
         </is>
       </c>
       <c r="G640" s="3" t="n">
-        <v>46295.875</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>46295.91666666666</v>
+        <v>46296.125</v>
       </c>
       <c r="I640" s="3" t="n">
-        <v>46296.29166666666</v>
+        <v>46296.75</v>
       </c>
     </row>
     <row r="641">
@@ -28709,13 +28711,13 @@
         </is>
       </c>
       <c r="G641" s="3" t="n">
-        <v>46298.25</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="H641" s="3" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.875</v>
       </c>
       <c r="I641" s="3" t="n">
-        <v>46298.95833333334</v>
+        <v>46299.41666666666</v>
       </c>
     </row>
     <row r="642">
@@ -28750,13 +28752,13 @@
         </is>
       </c>
       <c r="G642" s="3" t="n">
-        <v>46300.75</v>
+        <v>46301.20833333334</v>
       </c>
       <c r="H642" s="3" t="n">
-        <v>46300.79166666666</v>
+        <v>46301.25</v>
       </c>
       <c r="I642" s="3" t="n">
-        <v>46301.04166666666</v>
+        <v>46301.5</v>
       </c>
     </row>
     <row r="643">
@@ -28791,13 +28793,13 @@
         </is>
       </c>
       <c r="G643" s="3" t="n">
-        <v>46301.45833333334</v>
+        <v>46301.91666666666</v>
       </c>
       <c r="H643" s="3" t="n">
-        <v>46301.58333333334</v>
+        <v>46302.04166666666</v>
       </c>
       <c r="I643" s="3" t="n">
-        <v>46302.70833333334</v>
+        <v>46303.16666666666</v>
       </c>
     </row>
     <row r="644">
@@ -28832,13 +28834,13 @@
         </is>
       </c>
       <c r="G644" s="3" t="n">
-        <v>46303.04166666666</v>
+        <v>46303.5</v>
       </c>
       <c r="H644" s="3" t="n">
-        <v>46303.08333333334</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="I644" s="3" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.875</v>
       </c>
     </row>
     <row r="645">
@@ -28873,13 +28875,13 @@
         </is>
       </c>
       <c r="G645" s="3" t="n">
-        <v>46307.29166666666</v>
+        <v>46307.75</v>
       </c>
       <c r="H645" s="3" t="n">
-        <v>46307.33333333334</v>
+        <v>46307.79166666666</v>
       </c>
       <c r="I645" s="3" t="n">
-        <v>46307.75</v>
+        <v>46308.20833333334</v>
       </c>
     </row>
     <row r="646">
@@ -28914,13 +28916,13 @@
         </is>
       </c>
       <c r="G646" s="3" t="n">
-        <v>46308</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="H646" s="3" t="n">
-        <v>46308</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="I646" s="3" t="n">
-        <v>46308.375</v>
+        <v>46308.83333333334</v>
       </c>
     </row>
     <row r="647">
@@ -28955,13 +28957,13 @@
         </is>
       </c>
       <c r="G647" s="3" t="n">
-        <v>46309.70833333334</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="H647" s="3" t="n">
-        <v>46309.70833333334</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="I647" s="3" t="n">
-        <v>46309.95833333334</v>
+        <v>46310.41666666666</v>
       </c>
     </row>
     <row r="648">
@@ -28996,13 +28998,13 @@
         </is>
       </c>
       <c r="G648" s="3" t="n">
-        <v>46312</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="H648" s="3" t="n">
-        <v>46312.04166666666</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="I648" s="3" t="n">
-        <v>46312.75</v>
+        <v>46313.16666666666</v>
       </c>
     </row>
     <row r="649">
@@ -29037,13 +29039,13 @@
         </is>
       </c>
       <c r="G649" s="3" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.375</v>
       </c>
       <c r="H649" s="3" t="n">
-        <v>46313</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="I649" s="3" t="n">
-        <v>46313.33333333334</v>
+        <v>46313.75</v>
       </c>
     </row>
     <row r="650">
@@ -29078,13 +29080,13 @@
         </is>
       </c>
       <c r="G650" s="3" t="n">
-        <v>46316.58333333334</v>
+        <v>46317</v>
       </c>
       <c r="H650" s="3" t="n">
-        <v>46316.625</v>
+        <v>46317.04166666666</v>
       </c>
       <c r="I650" s="3" t="n">
-        <v>46317</v>
+        <v>46317.41666666666</v>
       </c>
     </row>
     <row r="651">
@@ -29119,13 +29121,13 @@
         </is>
       </c>
       <c r="G651" s="3" t="n">
-        <v>46319.45833333334</v>
+        <v>46319.875</v>
       </c>
       <c r="H651" s="3" t="n">
-        <v>46319.625</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="I651" s="3" t="n">
-        <v>46320.16666666666</v>
+        <v>46320.58333333334</v>
       </c>
     </row>
     <row r="652">
@@ -29160,13 +29162,13 @@
         </is>
       </c>
       <c r="G652" s="3" t="n">
-        <v>46321.95833333334</v>
+        <v>46322.375</v>
       </c>
       <c r="H652" s="3" t="n">
-        <v>46322</v>
+        <v>46322.41666666666</v>
       </c>
       <c r="I652" s="3" t="n">
-        <v>46322.25</v>
+        <v>46322.66666666666</v>
       </c>
     </row>
     <row r="653">
@@ -29201,13 +29203,13 @@
         </is>
       </c>
       <c r="G653" s="3" t="n">
-        <v>46322.66666666666</v>
+        <v>46323.08333333334</v>
       </c>
       <c r="H653" s="3" t="n">
-        <v>46322.79166666666</v>
+        <v>46323.20833333334</v>
       </c>
       <c r="I653" s="3" t="n">
-        <v>46323.91666666666</v>
+        <v>46324.33333333334</v>
       </c>
     </row>
     <row r="654">
@@ -29242,13 +29244,13 @@
         </is>
       </c>
       <c r="G654" s="3" t="n">
-        <v>46324.25</v>
+        <v>46324.66666666666</v>
       </c>
       <c r="H654" s="3" t="n">
-        <v>46324.29166666666</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="I654" s="3" t="n">
-        <v>46324.625</v>
+        <v>46325.04166666666</v>
       </c>
     </row>
     <row r="655">
@@ -29283,13 +29285,13 @@
         </is>
       </c>
       <c r="G655" s="3" t="n">
-        <v>46328.5</v>
+        <v>46328.91666666666</v>
       </c>
       <c r="H655" s="3" t="n">
-        <v>46328.54166666666</v>
+        <v>46328.95833333334</v>
       </c>
       <c r="I655" s="3" t="n">
-        <v>46328.95833333334</v>
+        <v>46329.375</v>
       </c>
     </row>
     <row r="656">
@@ -29324,13 +29326,13 @@
         </is>
       </c>
       <c r="G656" s="3" t="n">
-        <v>46329.20833333334</v>
+        <v>46329.625</v>
       </c>
       <c r="H656" s="3" t="n">
-        <v>46329.20833333334</v>
+        <v>46329.625</v>
       </c>
       <c r="I656" s="3" t="n">
-        <v>46329.58333333334</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="657">
@@ -29365,13 +29367,13 @@
         </is>
       </c>
       <c r="G657" s="3" t="n">
-        <v>46330.83333333334</v>
+        <v>46331.25</v>
       </c>
       <c r="H657" s="3" t="n">
-        <v>46330.83333333334</v>
+        <v>46331.25</v>
       </c>
       <c r="I657" s="3" t="n">
-        <v>46331.08333333334</v>
+        <v>46331.5</v>
       </c>
     </row>
     <row r="658">
@@ -29406,13 +29408,13 @@
         </is>
       </c>
       <c r="G658" s="3" t="n">
-        <v>46333.62430555555</v>
+        <v>46334.04097222222</v>
       </c>
       <c r="H658" s="3" t="n">
-        <v>46333.66597222222</v>
+        <v>46334.08263888889</v>
       </c>
       <c r="I658" s="3" t="n">
-        <v>46334.37430555555</v>
+        <v>46334.79097222222</v>
       </c>
     </row>
     <row r="659">
@@ -29447,13 +29449,13 @@
         </is>
       </c>
       <c r="G659" s="3" t="n">
-        <v>46334.58263888889</v>
+        <v>46334.99930555555</v>
       </c>
       <c r="H659" s="3" t="n">
-        <v>46334.62430555555</v>
+        <v>46335.04097222222</v>
       </c>
       <c r="I659" s="3" t="n">
-        <v>46334.95763888889</v>
+        <v>46335.37430555555</v>
       </c>
     </row>
     <row r="660">
@@ -29488,13 +29490,13 @@
         </is>
       </c>
       <c r="G660" s="3" t="n">
-        <v>46337.79097222222</v>
+        <v>46338.20763888889</v>
       </c>
       <c r="H660" s="3" t="n">
-        <v>46337.83263888889</v>
+        <v>46338.24930555555</v>
       </c>
       <c r="I660" s="3" t="n">
-        <v>46338.20763888889</v>
+        <v>46338.62430555555</v>
       </c>
     </row>
     <row r="661">
@@ -29529,13 +29531,13 @@
         </is>
       </c>
       <c r="G661" s="3" t="n">
-        <v>46340.66597222222</v>
+        <v>46341.08263888889</v>
       </c>
       <c r="H661" s="3" t="n">
-        <v>46340.83263888889</v>
+        <v>46341.24930555555</v>
       </c>
       <c r="I661" s="3" t="n">
-        <v>46341.37430555555</v>
+        <v>46341.79097222222</v>
       </c>
     </row>
     <row r="662">
@@ -29570,13 +29572,13 @@
         </is>
       </c>
       <c r="G662" s="3" t="n">
-        <v>46343.16597222222</v>
+        <v>46343.58263888889</v>
       </c>
       <c r="H662" s="3" t="n">
-        <v>46343.20763888889</v>
+        <v>46343.62430555555</v>
       </c>
       <c r="I662" s="3" t="n">
-        <v>46343.45763888889</v>
+        <v>46343.87430555555</v>
       </c>
     </row>
     <row r="663">
@@ -29611,13 +29613,13 @@
         </is>
       </c>
       <c r="G663" s="3" t="n">
-        <v>46343.87430555555</v>
+        <v>46344.29097222222</v>
       </c>
       <c r="H663" s="3" t="n">
-        <v>46343.99930555555</v>
+        <v>46344.41597222222</v>
       </c>
       <c r="I663" s="3" t="n">
-        <v>46345.12430555555</v>
+        <v>46345.54097222222</v>
       </c>
     </row>
     <row r="664">
@@ -29652,13 +29654,13 @@
         </is>
       </c>
       <c r="G664" s="3" t="n">
-        <v>46345.45763888889</v>
+        <v>46345.87430555555</v>
       </c>
       <c r="H664" s="3" t="n">
-        <v>46345.49930555555</v>
+        <v>46345.91597222222</v>
       </c>
       <c r="I664" s="3" t="n">
-        <v>46345.83263888889</v>
+        <v>46346.24930555555</v>
       </c>
     </row>
     <row r="665">
@@ -29693,13 +29695,13 @@
         </is>
       </c>
       <c r="G665" s="3" t="n">
-        <v>46349.70763888889</v>
+        <v>46350.12430555555</v>
       </c>
       <c r="H665" s="3" t="n">
-        <v>46349.74930555555</v>
+        <v>46350.16597222222</v>
       </c>
       <c r="I665" s="3" t="n">
-        <v>46350.16597222222</v>
+        <v>46350.58263888889</v>
       </c>
     </row>
     <row r="666">
@@ -29734,13 +29736,13 @@
         </is>
       </c>
       <c r="G666" s="3" t="n">
-        <v>46350.41597222222</v>
+        <v>46350.83263888889</v>
       </c>
       <c r="H666" s="3" t="n">
-        <v>46350.41597222222</v>
+        <v>46350.83263888889</v>
       </c>
       <c r="I666" s="3" t="n">
-        <v>46350.79097222222</v>
+        <v>46351.20763888889</v>
       </c>
     </row>
     <row r="667">
@@ -29775,13 +29777,13 @@
         </is>
       </c>
       <c r="G667" s="3" t="n">
-        <v>46352.04097222222</v>
+        <v>46352.45763888889</v>
       </c>
       <c r="H667" s="3" t="n">
-        <v>46352.04097222222</v>
+        <v>46352.45763888889</v>
       </c>
       <c r="I667" s="3" t="n">
-        <v>46352.29097222222</v>
+        <v>46352.70763888889</v>
       </c>
     </row>
     <row r="668">
@@ -29816,13 +29818,13 @@
         </is>
       </c>
       <c r="G668" s="3" t="n">
-        <v>46354.62430555555</v>
+        <v>46355.04097222222</v>
       </c>
       <c r="H668" s="3" t="n">
-        <v>46354.66597222222</v>
+        <v>46355.08263888889</v>
       </c>
       <c r="I668" s="3" t="n">
-        <v>46355.37430555555</v>
+        <v>46355.79097222222</v>
       </c>
     </row>
     <row r="669">
@@ -29857,13 +29859,13 @@
         </is>
       </c>
       <c r="G669" s="3" t="n">
-        <v>46355.58263888889</v>
+        <v>46355.99930555555</v>
       </c>
       <c r="H669" s="3" t="n">
-        <v>46355.62430555555</v>
+        <v>46356.04097222222</v>
       </c>
       <c r="I669" s="3" t="n">
-        <v>46355.95763888889</v>
+        <v>46356.37430555555</v>
       </c>
     </row>
     <row r="670">
@@ -29898,13 +29900,13 @@
         </is>
       </c>
       <c r="G670" s="3" t="n">
-        <v>46358.79097222222</v>
+        <v>46359.20763888889</v>
       </c>
       <c r="H670" s="3" t="n">
-        <v>46358.83263888889</v>
+        <v>46359.24930555555</v>
       </c>
       <c r="I670" s="3" t="n">
-        <v>46359.20763888889</v>
+        <v>46359.62430555555</v>
       </c>
     </row>
     <row r="671">
@@ -29939,13 +29941,13 @@
         </is>
       </c>
       <c r="G671" s="3" t="n">
-        <v>46361.66597222222</v>
+        <v>46362.08263888889</v>
       </c>
       <c r="H671" s="3" t="n">
-        <v>46361.83263888889</v>
+        <v>46362.24930555555</v>
       </c>
       <c r="I671" s="3" t="n">
-        <v>46362.37430555555</v>
+        <v>46362.79097222222</v>
       </c>
     </row>
     <row r="672">
@@ -29980,13 +29982,13 @@
         </is>
       </c>
       <c r="G672" s="3" t="n">
-        <v>46364.16597222222</v>
+        <v>46364.58263888889</v>
       </c>
       <c r="H672" s="3" t="n">
-        <v>46364.20763888889</v>
+        <v>46364.62430555555</v>
       </c>
       <c r="I672" s="3" t="n">
-        <v>46364.45763888889</v>
+        <v>46364.87430555555</v>
       </c>
     </row>
     <row r="673">
@@ -30021,13 +30023,13 @@
         </is>
       </c>
       <c r="G673" s="3" t="n">
-        <v>46364.87430555555</v>
+        <v>46365.29097222222</v>
       </c>
       <c r="H673" s="3" t="n">
-        <v>46364.99930555555</v>
+        <v>46365.41597222222</v>
       </c>
       <c r="I673" s="3" t="n">
-        <v>46366.12430555555</v>
+        <v>46366.54097222222</v>
       </c>
     </row>
     <row r="674">
@@ -30062,13 +30064,13 @@
         </is>
       </c>
       <c r="G674" s="3" t="n">
-        <v>46366.45763888889</v>
+        <v>46366.87430555555</v>
       </c>
       <c r="H674" s="3" t="n">
-        <v>46366.49930555555</v>
+        <v>46366.91597222222</v>
       </c>
       <c r="I674" s="3" t="n">
-        <v>46366.83263888889</v>
+        <v>46367.24930555555</v>
       </c>
     </row>
     <row r="675">
@@ -30103,13 +30105,13 @@
         </is>
       </c>
       <c r="G675" s="3" t="n">
-        <v>46370.70763888889</v>
+        <v>46371.12430555555</v>
       </c>
       <c r="H675" s="3" t="n">
-        <v>46370.74930555555</v>
+        <v>46371.16597222222</v>
       </c>
       <c r="I675" s="3" t="n">
-        <v>46371.16597222222</v>
+        <v>46371.58263888889</v>
       </c>
     </row>
     <row r="676">
@@ -30144,13 +30146,13 @@
         </is>
       </c>
       <c r="G676" s="3" t="n">
-        <v>46371.41597222222</v>
+        <v>46371.83263888889</v>
       </c>
       <c r="H676" s="3" t="n">
-        <v>46371.41597222222</v>
+        <v>46371.83263888889</v>
       </c>
       <c r="I676" s="3" t="n">
-        <v>46371.79097222222</v>
+        <v>46372.20763888889</v>
       </c>
     </row>
     <row r="677">
@@ -30183,13 +30185,13 @@
         <v/>
       </c>
       <c r="G677" s="3" t="n">
-        <v>46373.04097222222</v>
+        <v>46373.45763888889</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>46373.04097222222</v>
+        <v>46373.45763888889</v>
       </c>
       <c r="I677" s="3" t="n">
-        <v>46373.29097222222</v>
+        <v>46373.70763888889</v>
       </c>
     </row>
     <row r="678">
@@ -34364,10 +34366,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="H779" s="3" t="n">
-        <v>46296.45833333334</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="I779" s="3" t="n">
-        <v>46297.54166666666</v>
+        <v>46298.41666666666</v>
       </c>
     </row>
     <row r="780">
@@ -34402,13 +34404,13 @@
         </is>
       </c>
       <c r="G780" s="3" t="n">
-        <v>46297.66666666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>46297.70833333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="I780" s="3" t="n">
-        <v>46297.95833333334</v>
+        <v>46298.83333333334</v>
       </c>
     </row>
     <row r="781">
@@ -34443,13 +34445,13 @@
         </is>
       </c>
       <c r="G781" s="3" t="n">
-        <v>46298.45833333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="H781" s="3" t="n">
-        <v>46298.54166666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="I781" s="3" t="n">
-        <v>46298.875</v>
+        <v>46299.75</v>
       </c>
     </row>
     <row r="782">
@@ -34484,13 +34486,13 @@
         </is>
       </c>
       <c r="G782" s="3" t="n">
-        <v>46303.83333333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>46304</v>
+        <v>46304.875</v>
       </c>
       <c r="I782" s="3" t="n">
-        <v>46304.625</v>
+        <v>46305.5</v>
       </c>
     </row>
     <row r="783">
@@ -34525,13 +34527,13 @@
         </is>
       </c>
       <c r="G783" s="3" t="n">
-        <v>46306.29166666666</v>
+        <v>46307.16666666666</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>46306.33333333334</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="I783" s="3" t="n">
-        <v>46306.58333333334</v>
+        <v>46307.45833333334</v>
       </c>
     </row>
     <row r="784">
@@ -34566,13 +34568,13 @@
         </is>
       </c>
       <c r="G784" s="3" t="n">
-        <v>46306.66666666666</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>46306.79166666666</v>
+        <v>46307.66666666666</v>
       </c>
       <c r="I784" s="3" t="n">
-        <v>46308.29166666666</v>
+        <v>46309.16666666666</v>
       </c>
     </row>
     <row r="785">
@@ -34607,13 +34609,13 @@
         </is>
       </c>
       <c r="G785" s="3" t="n">
-        <v>46308.5</v>
+        <v>46309.375</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>46308.54166666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="I785" s="3" t="n">
-        <v>46308.95833333334</v>
+        <v>46309.83333333334</v>
       </c>
     </row>
     <row r="786">
@@ -34648,13 +34650,13 @@
         </is>
       </c>
       <c r="G786" s="3" t="n">
-        <v>46310.58333333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>46310.75</v>
+        <v>46311.625</v>
       </c>
       <c r="I786" s="3" t="n">
-        <v>46311.29166666666</v>
+        <v>46312.16666666666</v>
       </c>
     </row>
     <row r="787">
@@ -34689,13 +34691,13 @@
         </is>
       </c>
       <c r="G787" s="3" t="n">
-        <v>46316.58333333334</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>46316.625</v>
+        <v>46317.5</v>
       </c>
       <c r="I787" s="3" t="n">
-        <v>46317.70833333334</v>
+        <v>46318.58333333334</v>
       </c>
     </row>
     <row r="788">
@@ -34730,13 +34732,13 @@
         </is>
       </c>
       <c r="G788" s="3" t="n">
-        <v>46317.83333333334</v>
+        <v>46318.70833333334</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>46317.875</v>
+        <v>46318.75</v>
       </c>
       <c r="I788" s="3" t="n">
-        <v>46318.125</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="789">
@@ -34771,13 +34773,13 @@
         </is>
       </c>
       <c r="G789" s="3" t="n">
-        <v>46318.625</v>
+        <v>46319.5</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>46318.70833333334</v>
+        <v>46319.58333333334</v>
       </c>
       <c r="I789" s="3" t="n">
-        <v>46319.04166666666</v>
+        <v>46319.91666666666</v>
       </c>
     </row>
     <row r="790">
@@ -34812,13 +34814,13 @@
         </is>
       </c>
       <c r="G790" s="3" t="n">
-        <v>46323.91666666666</v>
+        <v>46324.79166666666</v>
       </c>
       <c r="H790" s="3" t="n">
-        <v>46324.08333333334</v>
+        <v>46324.95833333334</v>
       </c>
       <c r="I790" s="3" t="n">
-        <v>46324.70833333334</v>
+        <v>46325.58333333334</v>
       </c>
     </row>
     <row r="791">
@@ -34853,13 +34855,13 @@
         </is>
       </c>
       <c r="G791" s="3" t="n">
-        <v>46326.375</v>
+        <v>46327.25</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>46326.41666666666</v>
+        <v>46327.29166666666</v>
       </c>
       <c r="I791" s="3" t="n">
-        <v>46326.66666666666</v>
+        <v>46327.54166666666</v>
       </c>
     </row>
     <row r="792">
@@ -34894,13 +34896,13 @@
         </is>
       </c>
       <c r="G792" s="3" t="n">
-        <v>46326.79166666666</v>
+        <v>46327.66666666666</v>
       </c>
       <c r="H792" s="3" t="n">
-        <v>46326.91666666666</v>
+        <v>46327.79166666666</v>
       </c>
       <c r="I792" s="3" t="n">
-        <v>46328.41666666666</v>
+        <v>46329.29166666666</v>
       </c>
     </row>
     <row r="793">
@@ -34935,13 +34937,13 @@
         </is>
       </c>
       <c r="G793" s="3" t="n">
-        <v>46328.625</v>
+        <v>46329.5</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>46328.66666666666</v>
+        <v>46329.54166666666</v>
       </c>
       <c r="I793" s="3" t="n">
-        <v>46329.08333333334</v>
+        <v>46329.95833333334</v>
       </c>
     </row>
     <row r="794">
@@ -34976,13 +34978,13 @@
         </is>
       </c>
       <c r="G794" s="3" t="n">
-        <v>46330.625</v>
+        <v>46331.5</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>46330.79166666666</v>
+        <v>46331.66666666666</v>
       </c>
       <c r="I794" s="3" t="n">
-        <v>46331.33333333334</v>
+        <v>46332.20833333334</v>
       </c>
     </row>
     <row r="795">
@@ -35017,13 +35019,13 @@
         </is>
       </c>
       <c r="G795" s="3" t="n">
-        <v>46336.70833333334</v>
+        <v>46337.58333333334</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>46336.75</v>
+        <v>46337.625</v>
       </c>
       <c r="I795" s="3" t="n">
-        <v>46337.83333333334</v>
+        <v>46338.70833333334</v>
       </c>
     </row>
     <row r="796">
@@ -35058,13 +35060,13 @@
         </is>
       </c>
       <c r="G796" s="3" t="n">
-        <v>46338</v>
+        <v>46338.875</v>
       </c>
       <c r="H796" s="3" t="n">
-        <v>46338.04166666666</v>
+        <v>46338.91666666666</v>
       </c>
       <c r="I796" s="3" t="n">
-        <v>46338.29166666666</v>
+        <v>46339.16666666666</v>
       </c>
     </row>
     <row r="797">
@@ -35099,13 +35101,13 @@
         </is>
       </c>
       <c r="G797" s="3" t="n">
-        <v>46338.75</v>
+        <v>46339.625</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>46338.83333333334</v>
+        <v>46339.70833333334</v>
       </c>
       <c r="I797" s="3" t="n">
-        <v>46339.16666666666</v>
+        <v>46340.04166666666</v>
       </c>
     </row>
     <row r="798">
@@ -35140,13 +35142,13 @@
         </is>
       </c>
       <c r="G798" s="3" t="n">
-        <v>46344.16666666666</v>
+        <v>46345.04166666666</v>
       </c>
       <c r="H798" s="3" t="n">
-        <v>46344.33333333334</v>
+        <v>46345.20833333334</v>
       </c>
       <c r="I798" s="3" t="n">
-        <v>46344.95833333334</v>
+        <v>46345.83333333334</v>
       </c>
     </row>
     <row r="799">
@@ -35181,13 +35183,13 @@
         </is>
       </c>
       <c r="G799" s="3" t="n">
-        <v>46346.75</v>
+        <v>46347.625</v>
       </c>
       <c r="H799" s="3" t="n">
-        <v>46346.79166666666</v>
+        <v>46347.66666666666</v>
       </c>
       <c r="I799" s="3" t="n">
-        <v>46347.04166666666</v>
+        <v>46347.91666666666</v>
       </c>
     </row>
     <row r="800">
@@ -35222,13 +35224,13 @@
         </is>
       </c>
       <c r="G800" s="3" t="n">
-        <v>46347.33333333334</v>
+        <v>46348.20833333334</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>46347.45833333334</v>
+        <v>46348.33333333334</v>
       </c>
       <c r="I800" s="3" t="n">
-        <v>46348.95833333334</v>
+        <v>46349.83333333334</v>
       </c>
     </row>
     <row r="801">
@@ -35263,13 +35265,13 @@
         </is>
       </c>
       <c r="G801" s="3" t="n">
-        <v>46349.16666666666</v>
+        <v>46350.04166666666</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>46349.20833333334</v>
+        <v>46350.08333333334</v>
       </c>
       <c r="I801" s="3" t="n">
-        <v>46349.625</v>
+        <v>46350.5</v>
       </c>
     </row>
     <row r="802">
@@ -35302,13 +35304,13 @@
         <v/>
       </c>
       <c r="G802" s="3" t="n">
-        <v>46351.20833333334</v>
+        <v>46352.08333333334</v>
       </c>
       <c r="H802" s="3" t="n">
-        <v>46351.375</v>
+        <v>46352.25</v>
       </c>
       <c r="I802" s="3" t="n">
-        <v>46351.91666666666</v>
+        <v>46352.79166666666</v>
       </c>
     </row>
     <row r="803">
@@ -35677,7 +35679,7 @@
         <v>46293.25416666667</v>
       </c>
       <c r="I811" s="3" t="n">
-        <v>46293.70833333334</v>
+        <v>46293.94166666667</v>
       </c>
     </row>
     <row r="812">
@@ -35835,13 +35837,13 @@
         </is>
       </c>
       <c r="G815" s="3" t="n">
-        <v>46303.29166666666</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="H815" s="3" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I815" s="3" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="816">
@@ -35876,13 +35878,13 @@
         </is>
       </c>
       <c r="G816" s="3" t="n">
-        <v>46311.20833333334</v>
+        <v>46312.20833333334</v>
       </c>
       <c r="H816" s="3" t="n">
-        <v>46312.33333333334</v>
+        <v>46313.33333333334</v>
       </c>
       <c r="I816" s="3" t="n">
-        <v>46312.83333333334</v>
+        <v>46313.83333333334</v>
       </c>
     </row>
     <row r="817">
@@ -35917,13 +35919,13 @@
         </is>
       </c>
       <c r="G817" s="3" t="n">
-        <v>46314.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="H817" s="3" t="n">
-        <v>46314.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="I817" s="3" t="n">
-        <v>46314.875</v>
+        <v>46315.875</v>
       </c>
     </row>
     <row r="818">
@@ -35958,13 +35960,13 @@
         </is>
       </c>
       <c r="G818" s="3" t="n">
-        <v>46315.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="H818" s="3" t="n">
-        <v>46315.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="I818" s="3" t="n">
-        <v>46316.16666666666</v>
+        <v>46317.16666666666</v>
       </c>
     </row>
     <row r="819">
@@ -35999,13 +36001,13 @@
         </is>
       </c>
       <c r="G819" s="3" t="n">
-        <v>46316.41666666666</v>
+        <v>46317.41666666666</v>
       </c>
       <c r="H819" s="3" t="n">
-        <v>46316.45833333334</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="I819" s="3" t="n">
-        <v>46316.875</v>
+        <v>46317.875</v>
       </c>
     </row>
     <row r="820">
@@ -36040,13 +36042,13 @@
         </is>
       </c>
       <c r="G820" s="3" t="n">
-        <v>46318.375</v>
+        <v>46319.375</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>46319.5</v>
+        <v>46320.5</v>
       </c>
       <c r="I820" s="3" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="821">
@@ -36081,13 +36083,13 @@
         </is>
       </c>
       <c r="G821" s="3" t="n">
-        <v>46326.02083333334</v>
+        <v>46327.10416666666</v>
       </c>
       <c r="H821" s="3" t="n">
-        <v>46326.08333333334</v>
+        <v>46327.16666666666</v>
       </c>
       <c r="I821" s="3" t="n">
-        <v>46326.33333333334</v>
+        <v>46327.41666666666</v>
       </c>
     </row>
     <row r="822">
@@ -36122,13 +36124,13 @@
         </is>
       </c>
       <c r="G822" s="3" t="n">
-        <v>46327.29166666666</v>
+        <v>46328.375</v>
       </c>
       <c r="H822" s="3" t="n">
-        <v>46327.35416666666</v>
+        <v>46328.4375</v>
       </c>
       <c r="I822" s="3" t="n">
-        <v>46327.77083333334</v>
+        <v>46328.85416666666</v>
       </c>
     </row>
     <row r="823">
@@ -36163,13 +36165,13 @@
         </is>
       </c>
       <c r="G823" s="3" t="n">
-        <v>46328.125</v>
+        <v>46329.20833333334</v>
       </c>
       <c r="H823" s="3" t="n">
-        <v>46328.16666666666</v>
+        <v>46329.25</v>
       </c>
       <c r="I823" s="3" t="n">
-        <v>46328.79166666666</v>
+        <v>46329.875</v>
       </c>
     </row>
     <row r="824">
@@ -36204,13 +36206,13 @@
         </is>
       </c>
       <c r="G824" s="3" t="n">
-        <v>46329.875</v>
+        <v>46330.95833333334</v>
       </c>
       <c r="H824" s="3" t="n">
-        <v>46330.04166666666</v>
+        <v>46331.125</v>
       </c>
       <c r="I824" s="3" t="n">
-        <v>46331.04166666666</v>
+        <v>46332.125</v>
       </c>
     </row>
     <row r="825">
@@ -36245,13 +36247,13 @@
         </is>
       </c>
       <c r="G825" s="3" t="n">
-        <v>46335.25</v>
+        <v>46336.33333333334</v>
       </c>
       <c r="H825" s="3" t="n">
-        <v>46335.375</v>
+        <v>46336.45833333334</v>
       </c>
       <c r="I825" s="3" t="n">
-        <v>46335.875</v>
+        <v>46336.95833333334</v>
       </c>
     </row>
     <row r="826">
@@ -36286,13 +36288,13 @@
         </is>
       </c>
       <c r="G826" s="3" t="n">
-        <v>46337.45833333334</v>
+        <v>46338.54166666666</v>
       </c>
       <c r="H826" s="3" t="n">
-        <v>46337.5</v>
+        <v>46338.58333333334</v>
       </c>
       <c r="I826" s="3" t="n">
-        <v>46337.91666666666</v>
+        <v>46339</v>
       </c>
     </row>
     <row r="827">
@@ -36327,13 +36329,13 @@
         </is>
       </c>
       <c r="G827" s="3" t="n">
-        <v>46338.08333333334</v>
+        <v>46339.16666666666</v>
       </c>
       <c r="H827" s="3" t="n">
-        <v>46338.20833333334</v>
+        <v>46339.29166666666</v>
       </c>
       <c r="I827" s="3" t="n">
-        <v>46339.20833333334</v>
+        <v>46340.29166666666</v>
       </c>
     </row>
     <row r="828">
@@ -36368,13 +36370,13 @@
         </is>
       </c>
       <c r="G828" s="3" t="n">
-        <v>46339.45833333334</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="H828" s="3" t="n">
-        <v>46339.5</v>
+        <v>46340.58333333334</v>
       </c>
       <c r="I828" s="3" t="n">
-        <v>46339.91666666666</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="829">
@@ -36409,13 +36411,13 @@
         </is>
       </c>
       <c r="G829" s="3" t="n">
-        <v>46341.41666666666</v>
+        <v>46342.5</v>
       </c>
       <c r="H829" s="3" t="n">
-        <v>46341.54166666666</v>
+        <v>46342.625</v>
       </c>
       <c r="I829" s="3" t="n">
-        <v>46342.04166666666</v>
+        <v>46343.125</v>
       </c>
     </row>
     <row r="830">
@@ -36450,13 +36452,13 @@
         </is>
       </c>
       <c r="G830" s="3" t="n">
-        <v>46347.0625</v>
+        <v>46348.14583333334</v>
       </c>
       <c r="H830" s="3" t="n">
-        <v>46347.125</v>
+        <v>46348.20833333334</v>
       </c>
       <c r="I830" s="3" t="n">
-        <v>46347.375</v>
+        <v>46348.45833333334</v>
       </c>
     </row>
     <row r="831">
@@ -36491,13 +36493,13 @@
         </is>
       </c>
       <c r="G831" s="3" t="n">
-        <v>46348.32083333333</v>
+        <v>46349.40416666667</v>
       </c>
       <c r="H831" s="3" t="n">
-        <v>46348.38333333333</v>
+        <v>46349.46666666667</v>
       </c>
       <c r="I831" s="3" t="n">
-        <v>46348.8</v>
+        <v>46349.88333333333</v>
       </c>
     </row>
     <row r="832">
@@ -36532,13 +36534,13 @@
         </is>
       </c>
       <c r="G832" s="3" t="n">
-        <v>46349.14166666667</v>
+        <v>46350.225</v>
       </c>
       <c r="H832" s="3" t="n">
-        <v>46349.18333333333</v>
+        <v>46350.26666666667</v>
       </c>
       <c r="I832" s="3" t="n">
-        <v>46349.80833333333</v>
+        <v>46350.89166666667</v>
       </c>
     </row>
     <row r="833">
@@ -36573,13 +36575,13 @@
         </is>
       </c>
       <c r="G833" s="3" t="n">
-        <v>46350.89166666667</v>
+        <v>46351.975</v>
       </c>
       <c r="H833" s="3" t="n">
-        <v>46351.05833333333</v>
+        <v>46352.14166666667</v>
       </c>
       <c r="I833" s="3" t="n">
-        <v>46352.05833333333</v>
+        <v>46353.14166666667</v>
       </c>
     </row>
     <row r="834">
@@ -36614,13 +36616,13 @@
         </is>
       </c>
       <c r="G834" s="3" t="n">
-        <v>46356.26666666667</v>
+        <v>46357.35</v>
       </c>
       <c r="H834" s="3" t="n">
-        <v>46356.39166666667</v>
+        <v>46357.475</v>
       </c>
       <c r="I834" s="3" t="n">
-        <v>46356.89166666667</v>
+        <v>46357.975</v>
       </c>
     </row>
     <row r="835">
@@ -36655,13 +36657,13 @@
         </is>
       </c>
       <c r="G835" s="3" t="n">
-        <v>46358.475</v>
+        <v>46359.55833333333</v>
       </c>
       <c r="H835" s="3" t="n">
-        <v>46358.51666666667</v>
+        <v>46359.6</v>
       </c>
       <c r="I835" s="3" t="n">
-        <v>46358.93333333333</v>
+        <v>46360.01666666667</v>
       </c>
     </row>
     <row r="836">
@@ -36696,13 +36698,13 @@
         </is>
       </c>
       <c r="G836" s="3" t="n">
-        <v>46359.1</v>
+        <v>46360.18333333333</v>
       </c>
       <c r="H836" s="3" t="n">
-        <v>46359.225</v>
+        <v>46360.30833333333</v>
       </c>
       <c r="I836" s="3" t="n">
-        <v>46360.225</v>
+        <v>46361.30833333333</v>
       </c>
     </row>
     <row r="837">
@@ -36737,13 +36739,13 @@
         </is>
       </c>
       <c r="G837" s="3" t="n">
-        <v>46360.475</v>
+        <v>46361.55833333333</v>
       </c>
       <c r="H837" s="3" t="n">
-        <v>46360.51666666667</v>
+        <v>46361.6</v>
       </c>
       <c r="I837" s="3" t="n">
-        <v>46360.93333333333</v>
+        <v>46362.01666666667</v>
       </c>
     </row>
     <row r="838">
@@ -36776,13 +36778,13 @@
         <v/>
       </c>
       <c r="G838" s="3" t="n">
-        <v>46362.43333333333</v>
+        <v>46363.51666666667</v>
       </c>
       <c r="H838" s="3" t="n">
-        <v>46362.55833333333</v>
+        <v>46363.64166666667</v>
       </c>
       <c r="I838" s="3" t="n">
-        <v>46363.05833333333</v>
+        <v>46364.14166666667</v>
       </c>
     </row>
     <row r="839">
@@ -47973,10 +47975,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -48014,7 +48016,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260929-0150-SKED.xlsx)</t>
+          <t>New ETA (auto-20260929-0511-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -48067,396 +48069,3662 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46297.6875</v>
+        <v>46296.375</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46297.625</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46299.27083333334</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46299.20833333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>INNSA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46302.3125</v>
+        <v>46302.95833333334</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46302.25</v>
+        <v>46303.125</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>INNSA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>INMUN</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46303.35416666666</v>
+        <v>46315.75</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46303.29166666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>INMUN</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>PKKHI</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46306.64583333334</v>
+        <v>46318.75</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46306.58333333334</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>PKKHI</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>MYPKL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46309.4375</v>
+        <v>46320.25</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46309.375</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>MYPKL</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46311.8125</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46311.75</v>
+        <v>46329.95833333334</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>LAEM CHABANG VOYAGER</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v/>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46312.1875</v>
+        <v>46340.20833333334</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46312.125</v>
+        <v>46340.375</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>MYPKL</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46313.97916666666</v>
+        <v>46295.89583333334</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46313.91666666666</v>
+        <v>46296.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-1.5</v>
+        <v>14.5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46318.0625</v>
+        <v>46302.97916666666</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46318</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-1.5</v>
+        <v>14.5</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2604E</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46306.22916666666</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MELBOURNE BRIDGE</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>46309.79166666666</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>46309.95833333334</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MELBOURNE BRIDGE</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>CNNGB</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46312.79166666666</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>46312.95833333334</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MELBOURNE BRIDGE</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CNNGB</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>46317.125</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>46316.29166666666</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MELBOURNE BRIDGE</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>AEKLF</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>46321.875</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46321.04166666666</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MELBOURNE BRIDGE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>AEKLF</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2607E</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>46337.16666666666</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>MELBOURNE BRIDGE</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2607E</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46364.29166666666</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>46363.45833333334</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46295.875</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>46296.08333333334</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46298.25</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>46298.70833333334</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46300.75</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46303.04166666666</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>46303.5</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>46307.29166666666</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>46307.75</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>46308.45833333334</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46309.70833333334</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>46310.16666666666</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>46312.41666666666</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>46312.95833333334</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>46313.375</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46316.58333333334</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>46319.45833333334</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>46319.875</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46321.95833333334</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>46322.375</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46322.66666666666</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>46323.08333333334</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46324.25</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>46324.66666666666</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46328.5</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46328.91666666666</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46329.20833333334</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46329.625</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46330.83333333334</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46331.25</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46333.62430555555</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46334.04097222222</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46334.58263888889</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46334.99930555555</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46337.79097222222</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46338.20763888889</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46340.66597222222</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46341.08263888889</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>46343.16597222222</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46343.58263888889</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2612N</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>46319.4375</v>
-      </c>
-      <c r="F13" s="3" t="n">
+      <c r="E43" s="3" t="n">
+        <v>46343.87430555555</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>46344.29097222222</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>46345.45763888889</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>46345.87430555555</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>46349.70763888889</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>46350.12430555555</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>46350.41597222222</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>46350.83263888889</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>46352.04097222222</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>46352.45763888889</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>46354.62430555555</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>46355.04097222222</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>46355.58263888889</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>46355.99930555555</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>46358.79097222222</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>46359.20763888889</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>46361.66597222222</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>46362.08263888889</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>46364.16597222222</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>46364.58263888889</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>46364.87430555555</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>46365.29097222222</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>46366.45763888889</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>46366.87430555555</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>46370.70763888889</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>46371.12430555555</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>46371.41597222222</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>46371.83263888889</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>46373.04097222222</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>46373.45763888889</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>46297.66666666666</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>46298.54166666666</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>46298.45833333334</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>46303.83333333334</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>46304.70833333334</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>46307.16666666666</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>46306.66666666666</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>46307.54166666666</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>46308.5</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>46309.375</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>46310.58333333334</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>46311.45833333334</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>46316.58333333334</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>46317.45833333334</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>46317.83333333334</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>46318.70833333334</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>46318.625</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>46319.5</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>46323.91666666666</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>46324.79166666666</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>46326.375</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>46327.25</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>46326.79166666666</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>46327.66666666666</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>46328.625</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>46329.5</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>46330.625</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>46331.5</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>46336.70833333334</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>46337.58333333334</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>46338</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>46338.875</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>46338.75</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>46339.625</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>46344.16666666666</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>46345.04166666666</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>46346.75</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>46347.625</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>46347.33333333334</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>46348.20833333334</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>46349.16666666666</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>46350.04166666666</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>46351.20833333334</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>46352.08333333334</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>46303.29166666666</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>46303.39583333334</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>46311.20833333334</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>46312.20833333334</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>46314.41666666666</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>46315.41666666666</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46315.04166666666</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>46316.04166666666</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>46316.41666666666</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>46317.41666666666</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>46318.375</v>
+      </c>
+      <c r="F86" s="3" t="n">
         <v>46319.375</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
+      <c r="G86" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46326.02083333334</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>46327.10416666666</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46327.29166666666</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>46328.375</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>46328.125</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>46329.20833333334</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>46329.875</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>46330.95833333334</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>46335.25</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>46336.33333333334</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>46337.45833333334</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>46338.54166666666</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>46338.08333333334</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>46339.16666666666</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>46339.45833333334</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>46340.54166666666</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46341.41666666666</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>46342.5</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>46347.0625</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>46348.14583333334</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>46348.32083333333</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>46349.40416666667</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>46349.14166666667</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>46350.225</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>46350.89166666667</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>46351.975</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>46356.26666666667</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>46357.35</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>46358.475</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>46359.55833333333</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>46359.1</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>46360.18333333333</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>46360.475</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>46361.55833333333</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE MIMOSA</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>46362.43333333333</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>46363.51666666667</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -630,11 +630,11 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-09-30T06:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-09-30T02:00:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46305.33333333334</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>46304.8125</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -928,11 +928,11 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-29T13:30:00</t>
+          <t>Alongside, departs to THLCH ~2026-09-30T00:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>46296.75</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -2112,11 +2112,11 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-09-30T23:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-01T12:00:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46304.75</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>46304.29166666666</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>46313.5</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46312.875</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>46293.625</v>
+        <v>46293.75</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>46293.66666666666</v>
+        <v>46293.79166666666</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>46294.29166666666</v>
@@ -4971,7 +4971,7 @@
         <v>46294.52083333334</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>46295.25</v>
+        <v>46295.08333333334</v>
       </c>
     </row>
     <row r="62">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>46296.14583333334</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>46296.20833333334</v>
+        <v>46296.08333333334</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>46296.60416666666</v>
+        <v>46296.5</v>
       </c>
     </row>
     <row r="63">
@@ -5047,13 +5047,13 @@
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>46296.875</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>46296.89583333334</v>
+        <v>46297</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>46297.5</v>
+        <v>46297.95833333334</v>
       </c>
     </row>
     <row r="64">
@@ -5088,13 +5088,13 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>46302.41666666666</v>
+        <v>46302.875</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>46302.58333333334</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>46303.16666666666</v>
+        <v>46303.625</v>
       </c>
     </row>
     <row r="65">
@@ -5129,13 +5129,13 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>46304.8125</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>46304.85416666666</v>
+        <v>46305.3125</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.66666666666</v>
       </c>
     </row>
     <row r="66">
@@ -5170,13 +5170,13 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>46305.33333333334</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>46305.41666666666</v>
+        <v>46305.875</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>46306.41666666666</v>
+        <v>46306.875</v>
       </c>
     </row>
     <row r="67">
@@ -5211,13 +5211,13 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>46306.625</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>46306.66666666666</v>
+        <v>46307.125</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>46307.16666666666</v>
+        <v>46307.625</v>
       </c>
     </row>
     <row r="68">
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>46308.97916666666</v>
+        <v>46309.4375</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>46309.14583333334</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>46309.83333333334</v>
+        <v>46310.29166666666</v>
       </c>
     </row>
     <row r="69">
@@ -5293,13 +5293,13 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>46315.04166666666</v>
+        <v>46315.5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>46315.08333333334</v>
+        <v>46315.54166666666</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>46315.75</v>
+        <v>46316.20833333334</v>
       </c>
     </row>
     <row r="70">
@@ -5334,13 +5334,13 @@
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>46315.91666666666</v>
+        <v>46316.375</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>46315.97916666666</v>
+        <v>46316.4375</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>46316.22916666666</v>
+        <v>46316.6875</v>
       </c>
     </row>
     <row r="71">
@@ -5375,13 +5375,13 @@
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>46317.125</v>
+        <v>46317.58333333334</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>46317.1875</v>
+        <v>46317.64583333334</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>46317.60416666666</v>
+        <v>46318.0625</v>
       </c>
     </row>
     <row r="72">
@@ -5416,13 +5416,13 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>46317.875</v>
+        <v>46318.33333333334</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>46317.89583333334</v>
+        <v>46318.35416666666</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>46318.5</v>
+        <v>46318.95833333334</v>
       </c>
     </row>
     <row r="73">
@@ -5457,13 +5457,13 @@
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>46323.41666666666</v>
+        <v>46323.875</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>46323.58333333334</v>
+        <v>46324.04166666666</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>46324.16666666666</v>
+        <v>46324.625</v>
       </c>
     </row>
     <row r="74">
@@ -5498,13 +5498,13 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>46325.8125</v>
+        <v>46326.27083333334</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>46325.85416666666</v>
+        <v>46326.3125</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>46326.20833333334</v>
+        <v>46326.66666666666</v>
       </c>
     </row>
     <row r="75">
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>46326.33333333334</v>
+        <v>46326.79166666666</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>46326.41666666666</v>
+        <v>46326.875</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>46327.41666666666</v>
+        <v>46327.875</v>
       </c>
     </row>
     <row r="76">
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>46327.625</v>
+        <v>46328.08333333334</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>46327.66666666666</v>
+        <v>46328.125</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>46328.16666666666</v>
+        <v>46328.625</v>
       </c>
     </row>
     <row r="77">
@@ -5621,13 +5621,13 @@
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>46329.97916666666</v>
+        <v>46330.4375</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>46330.14583333334</v>
+        <v>46330.60416666666</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>46330.83333333334</v>
+        <v>46331.29166666666</v>
       </c>
     </row>
     <row r="78">
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>46336.04166666666</v>
+        <v>46336.5</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>46336.08333333334</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>46336.75</v>
+        <v>46337.20833333334</v>
       </c>
     </row>
     <row r="79">
@@ -5703,13 +5703,13 @@
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>46336.91666666666</v>
+        <v>46337.375</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>46336.97916666666</v>
+        <v>46337.4375</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>46337.22916666666</v>
+        <v>46337.6875</v>
       </c>
     </row>
     <row r="80">
@@ -5744,13 +5744,13 @@
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>46338.125</v>
+        <v>46338.58333333334</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>46338.1875</v>
+        <v>46338.64583333334</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>46338.60416666666</v>
+        <v>46339.0625</v>
       </c>
     </row>
     <row r="81">
@@ -5785,13 +5785,13 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>46338.875</v>
+        <v>46339.33333333334</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>46338.89583333334</v>
+        <v>46339.35416666666</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>46339.5</v>
+        <v>46339.95833333334</v>
       </c>
     </row>
     <row r="82">
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>46344.41666666666</v>
+        <v>46344.875</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>46344.58333333334</v>
+        <v>46345.04166666666</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>46345.16666666666</v>
+        <v>46345.625</v>
       </c>
     </row>
     <row r="83">
@@ -5867,13 +5867,13 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>46346.8125</v>
+        <v>46347.27083333334</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>46346.85416666666</v>
+        <v>46347.3125</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>46347.20833333334</v>
+        <v>46347.66666666666</v>
       </c>
     </row>
     <row r="84">
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>46347.33333333334</v>
+        <v>46347.79166666666</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>46347.41666666666</v>
+        <v>46347.875</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>46348.41666666666</v>
+        <v>46348.875</v>
       </c>
     </row>
     <row r="85">
@@ -5949,13 +5949,13 @@
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>46348.625</v>
+        <v>46349.08333333334</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>46348.66666666666</v>
+        <v>46349.125</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>46349.16666666666</v>
+        <v>46349.625</v>
       </c>
     </row>
     <row r="86">
@@ -5988,13 +5988,13 @@
         <v/>
       </c>
       <c r="G86" s="3" t="n">
-        <v>46350.97916666666</v>
+        <v>46351.4375</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>46351.14583333334</v>
+        <v>46351.60416666666</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>46351.83333333334</v>
+        <v>46352.29166666666</v>
       </c>
     </row>
     <row r="87">
@@ -10941,13 +10941,13 @@
         </is>
       </c>
       <c r="G207" s="3" t="n">
-        <v>46294.02083333334</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>46294.1875</v>
+        <v>46294.25</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>46294.5625</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="208">
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="G208" s="3" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="H208" s="3" t="n">
-        <v>46296.375</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>46296.625</v>
+        <v>46297.08333333334</v>
       </c>
     </row>
     <row r="209">
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="G209" s="3" t="n">
-        <v>46296.75</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="H209" s="3" t="n">
-        <v>46296.875</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>46298.375</v>
+        <v>46298.83333333334</v>
       </c>
     </row>
     <row r="210">
@@ -11064,13 +11064,13 @@
         </is>
       </c>
       <c r="G210" s="3" t="n">
-        <v>46298.58333333334</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="H210" s="3" t="n">
-        <v>46298.625</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>46299.04166666666</v>
+        <v>46299.5</v>
       </c>
     </row>
     <row r="211">
@@ -11105,13 +11105,13 @@
         </is>
       </c>
       <c r="G211" s="3" t="n">
-        <v>46300.66666666666</v>
+        <v>46301.125</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>46300.83333333334</v>
+        <v>46301.29166666666</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>46301.375</v>
+        <v>46301.83333333334</v>
       </c>
     </row>
     <row r="212">
@@ -11146,13 +11146,13 @@
         </is>
       </c>
       <c r="G212" s="3" t="n">
-        <v>46306.95833333334</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="H212" s="3" t="n">
-        <v>46307</v>
+        <v>46307.45833333334</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>46308.08333333334</v>
+        <v>46308.54166666666</v>
       </c>
     </row>
     <row r="213">
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="G213" s="3" t="n">
-        <v>46308.20833333334</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="H213" s="3" t="n">
-        <v>46308.25</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>46308.5</v>
+        <v>46308.95833333334</v>
       </c>
     </row>
     <row r="214">
@@ -11228,13 +11228,13 @@
         </is>
       </c>
       <c r="G214" s="3" t="n">
-        <v>46308.875</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>46308.9375</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>46309.27083333334</v>
+        <v>46309.72916666666</v>
       </c>
     </row>
     <row r="215">
@@ -11269,13 +11269,13 @@
         </is>
       </c>
       <c r="G215" s="3" t="n">
-        <v>46314.29166666666</v>
+        <v>46314.75</v>
       </c>
       <c r="H215" s="3" t="n">
-        <v>46314.45833333334</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>46315.08333333334</v>
+        <v>46315.54166666666</v>
       </c>
     </row>
     <row r="216">
@@ -11310,13 +11310,13 @@
         </is>
       </c>
       <c r="G216" s="3" t="n">
-        <v>46316.875</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="H216" s="3" t="n">
-        <v>46316.91666666666</v>
+        <v>46317.375</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>46317.16666666666</v>
+        <v>46317.625</v>
       </c>
     </row>
     <row r="217">
@@ -11351,13 +11351,13 @@
         </is>
       </c>
       <c r="G217" s="3" t="n">
-        <v>46317.45833333334</v>
+        <v>46317.91666666666</v>
       </c>
       <c r="H217" s="3" t="n">
-        <v>46317.58333333334</v>
+        <v>46318.04166666666</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>46319.08333333334</v>
+        <v>46319.54166666666</v>
       </c>
     </row>
     <row r="218">
@@ -11392,13 +11392,13 @@
         </is>
       </c>
       <c r="G218" s="3" t="n">
-        <v>46319.29166666666</v>
+        <v>46319.75</v>
       </c>
       <c r="H218" s="3" t="n">
-        <v>46319.33333333334</v>
+        <v>46319.79166666666</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>46319.75</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="219">
@@ -11433,13 +11433,13 @@
         </is>
       </c>
       <c r="G219" s="3" t="n">
-        <v>46321.33333333334</v>
+        <v>46321.79166666666</v>
       </c>
       <c r="H219" s="3" t="n">
-        <v>46321.5</v>
+        <v>46321.95833333334</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>46322.04166666666</v>
+        <v>46322.5</v>
       </c>
     </row>
     <row r="220">
@@ -11474,13 +11474,13 @@
         </is>
       </c>
       <c r="G220" s="3" t="n">
-        <v>46325.95833333334</v>
+        <v>46326.41666666666</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>46326</v>
+        <v>46326.45833333334</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>46327.08333333334</v>
+        <v>46327.54166666666</v>
       </c>
     </row>
     <row r="221">
@@ -11515,13 +11515,13 @@
         </is>
       </c>
       <c r="G221" s="3" t="n">
-        <v>46327.20833333334</v>
+        <v>46327.66666666666</v>
       </c>
       <c r="H221" s="3" t="n">
-        <v>46327.25</v>
+        <v>46327.70833333334</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>46327.5</v>
+        <v>46327.95833333334</v>
       </c>
     </row>
     <row r="222">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="G222" s="3" t="n">
-        <v>46327.91666666666</v>
+        <v>46328.375</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>46328</v>
+        <v>46328.45833333334</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>46328.33333333334</v>
+        <v>46328.79166666666</v>
       </c>
     </row>
     <row r="223">
@@ -11597,13 +11597,13 @@
         </is>
       </c>
       <c r="G223" s="3" t="n">
-        <v>46333.33333333334</v>
+        <v>46333.79166666666</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>46333.5</v>
+        <v>46333.95833333334</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>46334.125</v>
+        <v>46334.58333333334</v>
       </c>
     </row>
     <row r="224">
@@ -11638,13 +11638,13 @@
         </is>
       </c>
       <c r="G224" s="3" t="n">
-        <v>46335.91666666666</v>
+        <v>46336.375</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>46335.95833333334</v>
+        <v>46336.41666666666</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>46336.20833333334</v>
+        <v>46336.66666666666</v>
       </c>
     </row>
     <row r="225">
@@ -11679,13 +11679,13 @@
         </is>
       </c>
       <c r="G225" s="3" t="n">
-        <v>46336.5</v>
+        <v>46336.95833333334</v>
       </c>
       <c r="H225" s="3" t="n">
-        <v>46336.625</v>
+        <v>46337.08333333334</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>46338.125</v>
+        <v>46338.58333333334</v>
       </c>
     </row>
     <row r="226">
@@ -11720,13 +11720,13 @@
         </is>
       </c>
       <c r="G226" s="3" t="n">
-        <v>46338.33333333334</v>
+        <v>46338.79166666666</v>
       </c>
       <c r="H226" s="3" t="n">
-        <v>46338.375</v>
+        <v>46338.83333333334</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>46338.79166666666</v>
+        <v>46339.25</v>
       </c>
     </row>
     <row r="227">
@@ -11761,13 +11761,13 @@
         </is>
       </c>
       <c r="G227" s="3" t="n">
-        <v>46340.375</v>
+        <v>46340.83333333334</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>46340.54166666666</v>
+        <v>46341</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>46341.08333333334</v>
+        <v>46341.54166666666</v>
       </c>
     </row>
     <row r="228">
@@ -11802,13 +11802,13 @@
         </is>
       </c>
       <c r="G228" s="3" t="n">
-        <v>46344.625</v>
+        <v>46345.08333333334</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>46344.66666666666</v>
+        <v>46345.125</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>46345.75</v>
+        <v>46346.20833333334</v>
       </c>
     </row>
     <row r="229">
@@ -11843,13 +11843,13 @@
         </is>
       </c>
       <c r="G229" s="3" t="n">
-        <v>46345.875</v>
+        <v>46346.33333333334</v>
       </c>
       <c r="H229" s="3" t="n">
-        <v>46345.91666666666</v>
+        <v>46346.375</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>46346.16666666666</v>
+        <v>46346.625</v>
       </c>
     </row>
     <row r="230">
@@ -11884,13 +11884,13 @@
         </is>
       </c>
       <c r="G230" s="3" t="n">
-        <v>46346.58333333334</v>
+        <v>46347.04166666666</v>
       </c>
       <c r="H230" s="3" t="n">
-        <v>46346.66666666666</v>
+        <v>46347.125</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>46347</v>
+        <v>46347.45833333334</v>
       </c>
     </row>
     <row r="231">
@@ -11925,13 +11925,13 @@
         </is>
       </c>
       <c r="G231" s="3" t="n">
-        <v>46352</v>
+        <v>46352.45833333334</v>
       </c>
       <c r="H231" s="3" t="n">
-        <v>46352.16666666666</v>
+        <v>46352.625</v>
       </c>
       <c r="I231" s="3" t="n">
-        <v>46352.79166666666</v>
+        <v>46353.25</v>
       </c>
     </row>
     <row r="232">
@@ -11966,13 +11966,13 @@
         </is>
       </c>
       <c r="G232" s="3" t="n">
-        <v>46354.58333333334</v>
+        <v>46355.04166666666</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>46354.625</v>
+        <v>46355.08333333334</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>46354.875</v>
+        <v>46355.33333333334</v>
       </c>
     </row>
     <row r="233">
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="G233" s="3" t="n">
-        <v>46355.16666666666</v>
+        <v>46355.625</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>46355.29166666666</v>
+        <v>46355.75</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>46356.79166666666</v>
+        <v>46357.25</v>
       </c>
     </row>
     <row r="234">
@@ -12048,13 +12048,13 @@
         </is>
       </c>
       <c r="G234" s="3" t="n">
-        <v>46357</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="H234" s="3" t="n">
-        <v>46357.04166666666</v>
+        <v>46357.5</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>46357.45833333334</v>
+        <v>46357.91666666666</v>
       </c>
     </row>
     <row r="235">
@@ -12087,13 +12087,13 @@
         <v/>
       </c>
       <c r="G235" s="3" t="n">
-        <v>46359.04166666666</v>
+        <v>46359.5</v>
       </c>
       <c r="H235" s="3" t="n">
-        <v>46359.20833333334</v>
+        <v>46359.66666666666</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>46359.75</v>
+        <v>46360.20833333334</v>
       </c>
     </row>
     <row r="236">
@@ -40139,10 +40139,10 @@
         <v>46294.35416666666</v>
       </c>
       <c r="H920" s="3" t="n">
-        <v>46295.04166666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="I920" s="3" t="n">
-        <v>46295.95833333334</v>
+        <v>46296.5</v>
       </c>
     </row>
     <row r="921">
@@ -40177,13 +40177,13 @@
         </is>
       </c>
       <c r="G921" s="3" t="n">
-        <v>46296.25</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="H921" s="3" t="n">
-        <v>46296.3125</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="I921" s="3" t="n">
-        <v>46296.58333333334</v>
+        <v>46297.125</v>
       </c>
     </row>
     <row r="922">
@@ -40218,13 +40218,13 @@
         </is>
       </c>
       <c r="G922" s="3" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="H922" s="3" t="n">
-        <v>46299.45833333334</v>
+        <v>46300</v>
       </c>
       <c r="I922" s="3" t="n">
-        <v>46299.91666666666</v>
+        <v>46300.45833333334</v>
       </c>
     </row>
     <row r="923">
@@ -40259,13 +40259,13 @@
         </is>
       </c>
       <c r="G923" s="3" t="n">
-        <v>46302.08333333334</v>
+        <v>46302.625</v>
       </c>
       <c r="H923" s="3" t="n">
-        <v>46302.25</v>
+        <v>46302.79166666666</v>
       </c>
       <c r="I923" s="3" t="n">
-        <v>46302.70833333334</v>
+        <v>46303.25</v>
       </c>
     </row>
     <row r="924">
@@ -40300,13 +40300,13 @@
         </is>
       </c>
       <c r="G924" s="3" t="n">
-        <v>46304.29166666666</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="H924" s="3" t="n">
-        <v>46304.33333333334</v>
+        <v>46304.875</v>
       </c>
       <c r="I924" s="3" t="n">
-        <v>46304.58333333334</v>
+        <v>46305.125</v>
       </c>
     </row>
     <row r="925">
@@ -40341,13 +40341,13 @@
         </is>
       </c>
       <c r="G925" s="3" t="n">
-        <v>46304.75</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="H925" s="3" t="n">
-        <v>46304.875</v>
+        <v>46305.41666666666</v>
       </c>
       <c r="I925" s="3" t="n">
-        <v>46306.375</v>
+        <v>46306.91666666666</v>
       </c>
     </row>
     <row r="926">
@@ -40382,13 +40382,13 @@
         </is>
       </c>
       <c r="G926" s="3" t="n">
-        <v>46306.54166666666</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="H926" s="3" t="n">
-        <v>46306.58333333334</v>
+        <v>46307.125</v>
       </c>
       <c r="I926" s="3" t="n">
-        <v>46306.83333333334</v>
+        <v>46307.375</v>
       </c>
     </row>
     <row r="927">
@@ -40423,13 +40423,13 @@
         </is>
       </c>
       <c r="G927" s="3" t="n">
-        <v>46310.5625</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>46310.625</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="I927" s="3" t="n">
-        <v>46311.08333333334</v>
+        <v>46311.625</v>
       </c>
     </row>
     <row r="928">
@@ -40464,13 +40464,13 @@
         </is>
       </c>
       <c r="G928" s="3" t="n">
-        <v>46311.95833333334</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="H928" s="3" t="n">
-        <v>46312</v>
+        <v>46312.45833333334</v>
       </c>
       <c r="I928" s="3" t="n">
-        <v>46312.58333333334</v>
+        <v>46313.04166666666</v>
       </c>
     </row>
     <row r="929">
@@ -40505,13 +40505,13 @@
         </is>
       </c>
       <c r="G929" s="3" t="n">
-        <v>46314.41666666666</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>46314.45833333334</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="I929" s="3" t="n">
-        <v>46315.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
     </row>
     <row r="930">
@@ -40546,13 +40546,13 @@
         </is>
       </c>
       <c r="G930" s="3" t="n">
-        <v>46315.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="H930" s="3" t="n">
-        <v>46315.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="I930" s="3" t="n">
-        <v>46315.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
     </row>
     <row r="931">
@@ -40587,13 +40587,13 @@
         </is>
       </c>
       <c r="G931" s="3" t="n">
-        <v>46318.70833333334</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="H931" s="3" t="n">
-        <v>46318.75</v>
+        <v>46319.75</v>
       </c>
       <c r="I931" s="3" t="n">
-        <v>46319.20833333334</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="932">
@@ -40628,13 +40628,13 @@
         </is>
       </c>
       <c r="G932" s="3" t="n">
-        <v>46321.41666666666</v>
+        <v>46322.41666666666</v>
       </c>
       <c r="H932" s="3" t="n">
-        <v>46321.58333333334</v>
+        <v>46322.58333333334</v>
       </c>
       <c r="I932" s="3" t="n">
-        <v>46322.04166666666</v>
+        <v>46323.04166666666</v>
       </c>
     </row>
     <row r="933">
@@ -40669,13 +40669,13 @@
         </is>
       </c>
       <c r="G933" s="3" t="n">
-        <v>46323.70833333334</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>46323.75</v>
+        <v>46324.75</v>
       </c>
       <c r="I933" s="3" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="934">
@@ -40710,13 +40710,13 @@
         </is>
       </c>
       <c r="G934" s="3" t="n">
-        <v>46324.16666666666</v>
+        <v>46325.16666666666</v>
       </c>
       <c r="H934" s="3" t="n">
-        <v>46324.29166666666</v>
+        <v>46325.29166666666</v>
       </c>
       <c r="I934" s="3" t="n">
-        <v>46325.79166666666</v>
+        <v>46326.79166666666</v>
       </c>
     </row>
     <row r="935">
@@ -40751,13 +40751,13 @@
         </is>
       </c>
       <c r="G935" s="3" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="H935" s="3" t="n">
-        <v>46326.04166666666</v>
+        <v>46327.04166666666</v>
       </c>
       <c r="I935" s="3" t="n">
-        <v>46326.29166666666</v>
+        <v>46327.29166666666</v>
       </c>
     </row>
     <row r="936">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="G936" s="3" t="n">
-        <v>46330.125</v>
+        <v>46331.125</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>46330.16666666666</v>
+        <v>46331.16666666666</v>
       </c>
       <c r="I936" s="3" t="n">
-        <v>46330.625</v>
+        <v>46331.625</v>
       </c>
     </row>
     <row r="937">
@@ -40833,13 +40833,13 @@
         </is>
       </c>
       <c r="G937" s="3" t="n">
-        <v>46331.375</v>
+        <v>46332.375</v>
       </c>
       <c r="H937" s="3" t="n">
-        <v>46331.41666666666</v>
+        <v>46332.41666666666</v>
       </c>
       <c r="I937" s="3" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
     </row>
     <row r="938">
@@ -40874,13 +40874,13 @@
         </is>
       </c>
       <c r="G938" s="3" t="n">
-        <v>46334.16666666666</v>
+        <v>46335.29166666666</v>
       </c>
       <c r="H938" s="3" t="n">
-        <v>46334.20833333334</v>
+        <v>46335.33333333334</v>
       </c>
       <c r="I938" s="3" t="n">
-        <v>46334.91666666666</v>
+        <v>46336.04166666666</v>
       </c>
     </row>
     <row r="939">
@@ -40915,13 +40915,13 @@
         </is>
       </c>
       <c r="G939" s="3" t="n">
-        <v>46335.25</v>
+        <v>46336.375</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>46335.33333333334</v>
+        <v>46336.45833333334</v>
       </c>
       <c r="I939" s="3" t="n">
-        <v>46335.58333333334</v>
+        <v>46336.70833333334</v>
       </c>
     </row>
     <row r="940">
@@ -40956,13 +40956,13 @@
         </is>
       </c>
       <c r="G940" s="3" t="n">
-        <v>46338.5</v>
+        <v>46339.625</v>
       </c>
       <c r="H940" s="3" t="n">
-        <v>46338.54166666666</v>
+        <v>46339.66666666666</v>
       </c>
       <c r="I940" s="3" t="n">
-        <v>46339</v>
+        <v>46340.125</v>
       </c>
     </row>
     <row r="941">
@@ -40997,13 +40997,13 @@
         </is>
       </c>
       <c r="G941" s="3" t="n">
-        <v>46341.20833333334</v>
+        <v>46342.33333333334</v>
       </c>
       <c r="H941" s="3" t="n">
-        <v>46341.375</v>
+        <v>46342.5</v>
       </c>
       <c r="I941" s="3" t="n">
-        <v>46341.83333333334</v>
+        <v>46342.95833333334</v>
       </c>
     </row>
     <row r="942">
@@ -41038,13 +41038,13 @@
         </is>
       </c>
       <c r="G942" s="3" t="n">
-        <v>46343.58333333334</v>
+        <v>46344.70833333334</v>
       </c>
       <c r="H942" s="3" t="n">
-        <v>46343.625</v>
+        <v>46344.75</v>
       </c>
       <c r="I942" s="3" t="n">
-        <v>46343.79166666666</v>
+        <v>46344.91666666666</v>
       </c>
     </row>
     <row r="943">
@@ -41079,13 +41079,13 @@
         </is>
       </c>
       <c r="G943" s="3" t="n">
-        <v>46344.04166666666</v>
+        <v>46345.16666666666</v>
       </c>
       <c r="H943" s="3" t="n">
-        <v>46344.16666666666</v>
+        <v>46345.29166666666</v>
       </c>
       <c r="I943" s="3" t="n">
-        <v>46345.5</v>
+        <v>46346.625</v>
       </c>
     </row>
     <row r="944">
@@ -41120,13 +41120,13 @@
         </is>
       </c>
       <c r="G944" s="3" t="n">
-        <v>46346</v>
+        <v>46347.125</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>46346.04166666666</v>
+        <v>46347.16666666666</v>
       </c>
       <c r="I944" s="3" t="n">
-        <v>46346.33333333334</v>
+        <v>46347.45833333334</v>
       </c>
     </row>
     <row r="945">
@@ -41161,13 +41161,13 @@
         </is>
       </c>
       <c r="G945" s="3" t="n">
-        <v>46350.41666666666</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="H945" s="3" t="n">
-        <v>46350.45833333334</v>
+        <v>46351.58333333334</v>
       </c>
       <c r="I945" s="3" t="n">
-        <v>46350.91666666666</v>
+        <v>46352.04166666666</v>
       </c>
     </row>
     <row r="946">
@@ -41202,13 +41202,13 @@
         </is>
       </c>
       <c r="G946" s="3" t="n">
-        <v>46352</v>
+        <v>46353.125</v>
       </c>
       <c r="H946" s="3" t="n">
-        <v>46352.04166666666</v>
+        <v>46353.16666666666</v>
       </c>
       <c r="I946" s="3" t="n">
-        <v>46352.625</v>
+        <v>46353.75</v>
       </c>
     </row>
     <row r="947">
@@ -45827,13 +45827,13 @@
         </is>
       </c>
       <c r="G1059" s="3" t="n">
-        <v>46301.95833333334</v>
+        <v>46308</v>
       </c>
       <c r="H1059" s="3" t="n">
-        <v>46302.04166666666</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="I1059" s="3" t="n">
-        <v>46302.875</v>
+        <v>46308.91666666666</v>
       </c>
     </row>
     <row r="1060">
@@ -45868,13 +45868,13 @@
         </is>
       </c>
       <c r="G1060" s="3" t="n">
-        <v>46303.875</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="H1060" s="3" t="n">
-        <v>46303.95833333334</v>
+        <v>46310</v>
       </c>
       <c r="I1060" s="3" t="n">
-        <v>46304.45833333334</v>
+        <v>46310.5</v>
       </c>
     </row>
     <row r="1061">
@@ -45909,13 +45909,13 @@
         </is>
       </c>
       <c r="G1061" s="3" t="n">
-        <v>46305.625</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="H1061" s="3" t="n">
-        <v>46305.79166666666</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="I1061" s="3" t="n">
-        <v>46306.54166666666</v>
+        <v>46312.58333333334</v>
       </c>
     </row>
     <row r="1062">
@@ -45950,13 +45950,13 @@
         </is>
       </c>
       <c r="G1062" s="3" t="n">
-        <v>46312.875</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="H1062" s="3" t="n">
-        <v>46312.91666666666</v>
+        <v>46318.95833333334</v>
       </c>
       <c r="I1062" s="3" t="n">
-        <v>46313.20833333334</v>
+        <v>46319.25</v>
       </c>
     </row>
     <row r="1063">
@@ -45991,13 +45991,13 @@
         </is>
       </c>
       <c r="G1063" s="3" t="n">
-        <v>46313.5</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="H1063" s="3" t="n">
-        <v>46313.5</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="I1063" s="3" t="n">
-        <v>46314.875</v>
+        <v>46320.91666666666</v>
       </c>
     </row>
     <row r="1064">
@@ -46032,13 +46032,13 @@
         </is>
       </c>
       <c r="G1064" s="3" t="n">
-        <v>46315.125</v>
+        <v>46321.16666666666</v>
       </c>
       <c r="H1064" s="3" t="n">
-        <v>46315.16666666666</v>
+        <v>46321.20833333334</v>
       </c>
       <c r="I1064" s="3" t="n">
-        <v>46315.625</v>
+        <v>46321.66666666666</v>
       </c>
     </row>
     <row r="1065">
@@ -46073,13 +46073,13 @@
         </is>
       </c>
       <c r="G1065" s="3" t="n">
-        <v>46319.45833333334</v>
+        <v>46325.5</v>
       </c>
       <c r="H1065" s="3" t="n">
-        <v>46319.45833333334</v>
+        <v>46325.5</v>
       </c>
       <c r="I1065" s="3" t="n">
-        <v>46319.91666666666</v>
+        <v>46325.95833333334</v>
       </c>
     </row>
     <row r="1066">
@@ -46114,13 +46114,13 @@
         </is>
       </c>
       <c r="G1066" s="3" t="n">
-        <v>46320.91666666666</v>
+        <v>46326.95833333334</v>
       </c>
       <c r="H1066" s="3" t="n">
-        <v>46320.91666666666</v>
+        <v>46326.95833333334</v>
       </c>
       <c r="I1066" s="3" t="n">
-        <v>46321.41666666666</v>
+        <v>46327.45833333334</v>
       </c>
     </row>
     <row r="1067">
@@ -46155,13 +46155,13 @@
         </is>
       </c>
       <c r="G1067" s="3" t="n">
-        <v>46323.875</v>
+        <v>46329.91666666666</v>
       </c>
       <c r="H1067" s="3" t="n">
-        <v>46323.91666666666</v>
+        <v>46329.95833333334</v>
       </c>
       <c r="I1067" s="3" t="n">
-        <v>46324.54166666666</v>
+        <v>46330.58333333334</v>
       </c>
     </row>
     <row r="1068">
@@ -46196,13 +46196,13 @@
         </is>
       </c>
       <c r="G1068" s="3" t="n">
-        <v>46325.54166666666</v>
+        <v>46331.58333333334</v>
       </c>
       <c r="H1068" s="3" t="n">
-        <v>46325.58333333334</v>
+        <v>46331.625</v>
       </c>
       <c r="I1068" s="3" t="n">
-        <v>46326.08333333334</v>
+        <v>46332.125</v>
       </c>
     </row>
     <row r="1069">
@@ -46237,13 +46237,13 @@
         </is>
       </c>
       <c r="G1069" s="3" t="n">
-        <v>46327.16666666666</v>
+        <v>46333.20833333334</v>
       </c>
       <c r="H1069" s="3" t="n">
-        <v>46327.33333333334</v>
+        <v>46333.375</v>
       </c>
       <c r="I1069" s="3" t="n">
-        <v>46328.125</v>
+        <v>46334.16666666666</v>
       </c>
     </row>
     <row r="1070">
@@ -46278,13 +46278,13 @@
         </is>
       </c>
       <c r="G1070" s="3" t="n">
-        <v>46333.875</v>
+        <v>46339.91666666666</v>
       </c>
       <c r="H1070" s="3" t="n">
-        <v>46333.91666666666</v>
+        <v>46339.95833333334</v>
       </c>
       <c r="I1070" s="3" t="n">
-        <v>46334.20833333334</v>
+        <v>46340.25</v>
       </c>
     </row>
     <row r="1071">
@@ -46319,13 +46319,13 @@
         </is>
       </c>
       <c r="G1071" s="3" t="n">
-        <v>46334.5</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="H1071" s="3" t="n">
-        <v>46334.5</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="I1071" s="3" t="n">
-        <v>46335.875</v>
+        <v>46341.91666666666</v>
       </c>
     </row>
     <row r="1072">
@@ -46360,13 +46360,13 @@
         </is>
       </c>
       <c r="G1072" s="3" t="n">
-        <v>46336.125</v>
+        <v>46342.16666666666</v>
       </c>
       <c r="H1072" s="3" t="n">
-        <v>46336.16666666666</v>
+        <v>46342.20833333334</v>
       </c>
       <c r="I1072" s="3" t="n">
-        <v>46336.625</v>
+        <v>46342.66666666666</v>
       </c>
     </row>
     <row r="1073">
@@ -46401,13 +46401,13 @@
         </is>
       </c>
       <c r="G1073" s="3" t="n">
-        <v>46340.45833333334</v>
+        <v>46346.5</v>
       </c>
       <c r="H1073" s="3" t="n">
-        <v>46340.45833333334</v>
+        <v>46346.5</v>
       </c>
       <c r="I1073" s="3" t="n">
-        <v>46340.91666666666</v>
+        <v>46346.95833333334</v>
       </c>
     </row>
     <row r="1074">
@@ -46442,13 +46442,13 @@
         </is>
       </c>
       <c r="G1074" s="3" t="n">
-        <v>46341.91666666666</v>
+        <v>46347.95833333334</v>
       </c>
       <c r="H1074" s="3" t="n">
-        <v>46341.91666666666</v>
+        <v>46347.95833333334</v>
       </c>
       <c r="I1074" s="3" t="n">
-        <v>46342.41666666666</v>
+        <v>46348.45833333334</v>
       </c>
     </row>
     <row r="1075">
@@ -46483,13 +46483,13 @@
         </is>
       </c>
       <c r="G1075" s="3" t="n">
-        <v>46344.875</v>
+        <v>46350.91666666666</v>
       </c>
       <c r="H1075" s="3" t="n">
-        <v>46344.91666666666</v>
+        <v>46350.95833333334</v>
       </c>
       <c r="I1075" s="3" t="n">
-        <v>46345.54166666666</v>
+        <v>46351.58333333334</v>
       </c>
     </row>
     <row r="1076">
@@ -46524,13 +46524,13 @@
         </is>
       </c>
       <c r="G1076" s="3" t="n">
-        <v>46346.54166666666</v>
+        <v>46352.58333333334</v>
       </c>
       <c r="H1076" s="3" t="n">
-        <v>46346.58333333334</v>
+        <v>46352.625</v>
       </c>
       <c r="I1076" s="3" t="n">
-        <v>46347.08333333334</v>
+        <v>46353.125</v>
       </c>
     </row>
     <row r="1077">
@@ -46565,13 +46565,13 @@
         </is>
       </c>
       <c r="G1077" s="3" t="n">
-        <v>46348.16666666666</v>
+        <v>46354.20833333334</v>
       </c>
       <c r="H1077" s="3" t="n">
-        <v>46348.33333333334</v>
+        <v>46354.375</v>
       </c>
       <c r="I1077" s="3" t="n">
-        <v>46349.125</v>
+        <v>46355.16666666666</v>
       </c>
     </row>
     <row r="1078">
@@ -46606,13 +46606,13 @@
         </is>
       </c>
       <c r="G1078" s="3" t="n">
-        <v>46354.875</v>
+        <v>46360.91666666666</v>
       </c>
       <c r="H1078" s="3" t="n">
-        <v>46354.91666666666</v>
+        <v>46360.95833333334</v>
       </c>
       <c r="I1078" s="3" t="n">
-        <v>46355.20833333334</v>
+        <v>46361.25</v>
       </c>
     </row>
     <row r="1079">
@@ -46647,13 +46647,13 @@
         </is>
       </c>
       <c r="G1079" s="3" t="n">
-        <v>46355.5</v>
+        <v>46361.54166666666</v>
       </c>
       <c r="H1079" s="3" t="n">
-        <v>46355.5</v>
+        <v>46361.54166666666</v>
       </c>
       <c r="I1079" s="3" t="n">
-        <v>46356.875</v>
+        <v>46362.91666666666</v>
       </c>
     </row>
     <row r="1080">
@@ -46688,13 +46688,13 @@
         </is>
       </c>
       <c r="G1080" s="3" t="n">
-        <v>46357.125</v>
+        <v>46363.16666666666</v>
       </c>
       <c r="H1080" s="3" t="n">
-        <v>46357.16666666666</v>
+        <v>46363.20833333334</v>
       </c>
       <c r="I1080" s="3" t="n">
-        <v>46357.625</v>
+        <v>46363.66666666666</v>
       </c>
     </row>
     <row r="1081">
@@ -46729,13 +46729,13 @@
         </is>
       </c>
       <c r="G1081" s="3" t="n">
-        <v>46361.45833333334</v>
+        <v>46367.5</v>
       </c>
       <c r="H1081" s="3" t="n">
-        <v>46361.45833333334</v>
+        <v>46367.5</v>
       </c>
       <c r="I1081" s="3" t="n">
-        <v>46361.91666666666</v>
+        <v>46367.95833333334</v>
       </c>
     </row>
     <row r="1082">
@@ -46768,13 +46768,13 @@
         <v/>
       </c>
       <c r="G1082" s="3" t="n">
-        <v>46362.91666666666</v>
+        <v>46368.95833333334</v>
       </c>
       <c r="H1082" s="3" t="n">
-        <v>46362.91666666666</v>
+        <v>46368.95833333334</v>
       </c>
       <c r="I1082" s="3" t="n">
-        <v>46363.41666666666</v>
+        <v>46369.45833333334</v>
       </c>
     </row>
     <row r="1083">
@@ -47975,10 +47975,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -48016,7 +48016,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260929-0511-SKED.xlsx)</t>
+          <t>New ETA (auto-20260929-0822-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -48033,43 +48033,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46258.75</v>
+        <v>46293.625</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46258.54166666666</v>
+        <v>46293.75</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -48079,94 +48079,94 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CNNGB</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46296.375</v>
+        <v>46296.14583333334</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46296.54166666666</v>
+        <v>46296.02083333334</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CNNGB</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46298.41666666666</v>
+        <v>46296.875</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46298.58333333334</v>
+        <v>46296.77083333334</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>-2.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>INNSA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46302.95833333334</v>
+        <v>46302.41666666666</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46303.125</v>
+        <v>46302.875</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -48177,32 +48177,32 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>INNSA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>INMUN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46315.75</v>
+        <v>46304.8125</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46315.91666666666</v>
+        <v>46305.27083333334</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -48213,32 +48213,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>INMUN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PKKHI</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46318.75</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46318.91666666666</v>
+        <v>46305.79166666666</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -48249,32 +48249,32 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PKKHI</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>MYPKL</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46320.25</v>
+        <v>46306.625</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46320.41666666666</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -48285,32 +48285,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>MYPKL</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46329.79166666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46329.95833333334</v>
+        <v>46309.4375</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -48321,30 +48321,32 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LAEM CHABANG VOYAGER</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v/>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46340.20833333334</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46340.375</v>
+        <v>46315.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -48355,32 +48357,32 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MYPKL</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46295.89583333334</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46296.5</v>
+        <v>46316.375</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -48391,12 +48393,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -48406,17 +48408,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46302.97916666666</v>
+        <v>46317.125</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46303.58333333334</v>
+        <v>46317.58333333334</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -48427,7 +48429,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -48437,22 +48439,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46306.22916666666</v>
+        <v>46317.875</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46306.83333333334</v>
+        <v>46318.33333333334</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -48463,32 +48465,32 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46309.79166666666</v>
+        <v>46323.41666666666</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46309.95833333334</v>
+        <v>46323.875</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -48499,32 +48501,32 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CNNGB</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>0153S</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46312.79166666666</v>
+        <v>46325.8125</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46312.95833333334</v>
+        <v>46326.27083333334</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -48535,174 +48537,176 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CNNGB</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46317.125</v>
+        <v>46326.33333333334</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46316.29166666666</v>
+        <v>46326.79166666666</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-20</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AEKLF</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46321.875</v>
+        <v>46327.625</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46321.04166666666</v>
+        <v>46328.08333333334</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-20</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>AEKLF</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46338</v>
+        <v>46329.97916666666</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46337.16666666666</v>
+        <v>46330.4375</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-20</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MELBOURNE BRIDGE</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v/>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2607E</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46364.29166666666</v>
+        <v>46336.04166666666</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46363.45833333334</v>
+        <v>46336.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-20</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46295.875</v>
+        <v>46336.91666666666</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>46296.08333333334</v>
+        <v>46337.375</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -48713,29 +48717,29 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46298.25</v>
+        <v>46338.125</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>46298.70833333334</v>
+        <v>46338.58333333334</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>11</v>
@@ -48749,29 +48753,29 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46300.75</v>
+        <v>46338.875</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46301.20833333334</v>
+        <v>46339.33333333334</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>11</v>
@@ -48785,12 +48789,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -48800,14 +48804,14 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46301.45833333334</v>
+        <v>46344.41666666666</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>46301.91666666666</v>
+        <v>46344.875</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>11</v>
@@ -48821,7 +48825,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -48831,19 +48835,19 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>0154S</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46303.04166666666</v>
+        <v>46346.8125</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46303.5</v>
+        <v>46347.27083333334</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>11</v>
@@ -48857,29 +48861,29 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>0154N</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46307.29166666666</v>
+        <v>46347.33333333334</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>46307.75</v>
+        <v>46347.79166666666</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>11</v>
@@ -48893,29 +48897,29 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>0154N</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46308</v>
+        <v>46348.625</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>46308.45833333334</v>
+        <v>46349.08333333334</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>11</v>
@@ -48929,29 +48933,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v/>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>0154N</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46309.70833333334</v>
+        <v>46350.97916666666</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>46310.16666666666</v>
+        <v>46351.4375</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>11</v>
@@ -48965,17 +48967,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -48984,13 +48986,13 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46312</v>
+        <v>46294.02083333334</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>46312.41666666666</v>
+        <v>46294.08333333334</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -49001,17 +49003,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -49020,13 +49022,13 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46312.95833333334</v>
+        <v>46296.33333333334</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46313.375</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -49037,32 +49039,32 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46316.58333333334</v>
+        <v>46296.75</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46317</v>
+        <v>46297.20833333334</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -49073,32 +49075,32 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46319.45833333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46319.875</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -49109,32 +49111,32 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46321.95833333334</v>
+        <v>46300.66666666666</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>46322.375</v>
+        <v>46301.125</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -49145,32 +49147,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46322.66666666666</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>46323.08333333334</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -49181,32 +49183,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46324.25</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>46324.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -49217,32 +49219,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46328.5</v>
+        <v>46308.875</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>46328.91666666666</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -49253,32 +49255,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>46329.20833333334</v>
+        <v>46314.29166666666</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>46329.625</v>
+        <v>46314.75</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -49289,32 +49291,32 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46330.83333333334</v>
+        <v>46316.875</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>46331.25</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -49325,32 +49327,32 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>46333.62430555555</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>46334.04097222222</v>
+        <v>46317.91666666666</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -49361,32 +49363,32 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>46334.58263888889</v>
+        <v>46319.29166666666</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>46334.99930555555</v>
+        <v>46319.75</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -49397,32 +49399,32 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>46337.79097222222</v>
+        <v>46321.33333333334</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>46338.20763888889</v>
+        <v>46321.79166666666</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -49433,32 +49435,32 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>46340.66597222222</v>
+        <v>46325.95833333334</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>46341.08263888889</v>
+        <v>46326.41666666666</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -49469,32 +49471,32 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>46343.16597222222</v>
+        <v>46327.20833333334</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>46343.58263888889</v>
+        <v>46327.66666666666</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -49505,32 +49507,32 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46343.87430555555</v>
+        <v>46327.91666666666</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>46344.29097222222</v>
+        <v>46328.375</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -49541,32 +49543,32 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46345.45763888889</v>
+        <v>46333.33333333334</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>46345.87430555555</v>
+        <v>46333.79166666666</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -49577,32 +49579,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46349.70763888889</v>
+        <v>46335.91666666666</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>46350.12430555555</v>
+        <v>46336.375</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -49613,32 +49615,32 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46350.41597222222</v>
+        <v>46336.5</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>46350.83263888889</v>
+        <v>46336.95833333334</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -49649,32 +49651,32 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>46352.04097222222</v>
+        <v>46338.33333333334</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>46352.45763888889</v>
+        <v>46338.79166666666</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -49685,32 +49687,32 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46354.62430555555</v>
+        <v>46340.375</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>46355.04097222222</v>
+        <v>46340.83333333334</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -49721,32 +49723,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
           <t>KRUSN</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>46355.58263888889</v>
+        <v>46344.625</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>46355.99930555555</v>
+        <v>46345.08333333334</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -49757,32 +49759,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>46358.79097222222</v>
+        <v>46345.875</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>46359.20763888889</v>
+        <v>46346.33333333334</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -49793,32 +49795,32 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>46361.66597222222</v>
+        <v>46346.58333333334</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>46362.08263888889</v>
+        <v>46347.04166666666</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -49829,32 +49831,32 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>46364.16597222222</v>
+        <v>46352</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>46364.58263888889</v>
+        <v>46352.45833333334</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -49865,32 +49867,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2614S</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>46364.87430555555</v>
+        <v>46354.58333333334</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>46365.29097222222</v>
+        <v>46355.04166666666</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -49901,32 +49903,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46366.45763888889</v>
+        <v>46355.16666666666</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46366.87430555555</v>
+        <v>46355.625</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -49937,32 +49939,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>46370.70763888889</v>
+        <v>46357</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>46371.12430555555</v>
+        <v>46357.45833333334</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -49973,32 +49975,30 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC BANGKOK</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v/>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46371.41597222222</v>
+        <v>46359.04166666666</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>46371.83263888889</v>
+        <v>46359.5</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -50009,51 +50009,53 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>KMTC JAKARTA</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v/>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46373.04097222222</v>
+        <v>46258.75</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>46373.45763888889</v>
+        <v>46258.54166666666</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -50062,13 +50064,13 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>46297.66666666666</v>
+        <v>46296.25</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>46298.54166666666</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -50079,12 +50081,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -50098,13 +50100,13 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46298.45833333334</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -50115,7 +50117,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -50134,13 +50136,13 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46303.83333333334</v>
+        <v>46302.08333333334</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46302.625</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -50151,7 +50153,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -50170,13 +50172,13 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46306.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>46307.16666666666</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -50187,7 +50189,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -50206,13 +50208,13 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>46306.66666666666</v>
+        <v>46304.75</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>46307.54166666666</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -50223,7 +50225,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -50233,7 +50235,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -50242,13 +50244,13 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>46308.5</v>
+        <v>46306.54166666666</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>46309.375</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -50259,17 +50261,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -50278,13 +50280,13 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46310.58333333334</v>
+        <v>46310.5625</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>46311.45833333334</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -50295,32 +50297,32 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>46316.58333333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>46317.45833333334</v>
+        <v>46312.41666666666</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -50331,12 +50333,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -50350,13 +50352,13 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>46317.83333333334</v>
+        <v>46314.41666666666</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>46318.70833333334</v>
+        <v>46315.41666666666</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -50367,7 +50369,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -50377,7 +50379,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -50386,13 +50388,13 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>46318.625</v>
+        <v>46315.45833333334</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46319.5</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -50403,32 +50405,32 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>2612S</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46323.91666666666</v>
+        <v>46318.70833333334</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>46324.79166666666</v>
+        <v>46319.70833333334</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -50439,32 +50441,32 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
           <t>2612S</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>46326.375</v>
+        <v>46321.41666666666</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>46327.25</v>
+        <v>46322.41666666666</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -50475,32 +50477,32 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2612S</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>46326.79166666666</v>
+        <v>46323.70833333334</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>46327.66666666666</v>
+        <v>46324.70833333334</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -50511,32 +50513,32 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
           <t>2612N</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>46328.625</v>
+        <v>46324.16666666666</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>46329.5</v>
+        <v>46325.16666666666</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -50547,17 +50549,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -50566,13 +50568,13 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>46330.625</v>
+        <v>46326</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>46331.5</v>
+        <v>46327</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -50583,32 +50585,32 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46336.70833333334</v>
+        <v>46330.125</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>46337.58333333334</v>
+        <v>46331.125</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -50619,32 +50621,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46338</v>
+        <v>46331.375</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>46338.875</v>
+        <v>46332.375</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -50655,32 +50657,32 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
           <t>KRKAN</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
           <t>2613S</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46338.75</v>
+        <v>46334.16666666666</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>46339.625</v>
+        <v>46335.29166666666</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -50691,17 +50693,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -50710,13 +50712,13 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46344.16666666666</v>
+        <v>46335.25</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>46345.04166666666</v>
+        <v>46336.375</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -50727,17 +50729,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -50746,13 +50748,13 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46346.75</v>
+        <v>46338.5</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>46347.625</v>
+        <v>46339.625</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -50763,12 +50765,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -50778,17 +50780,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>46347.33333333334</v>
+        <v>46341.20833333334</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>46348.20833333334</v>
+        <v>46342.33333333334</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -50799,7 +50801,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -50809,22 +50811,22 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2613S</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46349.16666666666</v>
+        <v>46343.58333333334</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>46350.04166666666</v>
+        <v>46344.70833333334</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -50835,16 +50837,18 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v/>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
@@ -50852,13 +50856,13 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>46351.20833333334</v>
+        <v>46344.04166666666</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46352.08333333334</v>
+        <v>46345.16666666666</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -50869,32 +50873,32 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>46303.29166666666</v>
+        <v>46346</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>46303.39583333334</v>
+        <v>46347.125</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>2.5</v>
+        <v>27</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -50905,32 +50909,32 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>46311.20833333334</v>
+        <v>46350.41666666666</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>46312.20833333334</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -50941,32 +50945,32 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>SAWASDEE SUNRISE</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>46314.41666666666</v>
+        <v>46352</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>46315.41666666666</v>
+        <v>46353.125</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -50977,32 +50981,32 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46315.04166666666</v>
+        <v>46301.95833333334</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>46316.04166666666</v>
+        <v>46308</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -51013,32 +51017,32 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>46316.41666666666</v>
+        <v>46303.875</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>46317.41666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -51049,32 +51053,32 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>46318.375</v>
+        <v>46305.625</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>46319.375</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -51085,32 +51089,32 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>46326.02083333334</v>
+        <v>46312.875</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>46327.10416666666</v>
+        <v>46318.91666666666</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -51121,32 +51125,32 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>46327.29166666666</v>
+        <v>46313.5</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>46328.375</v>
+        <v>46319.54166666666</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -51157,32 +51161,32 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>46328.125</v>
+        <v>46315.125</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>46329.20833333334</v>
+        <v>46321.16666666666</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -51193,32 +51197,32 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>46329.875</v>
+        <v>46319.45833333334</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>46330.95833333334</v>
+        <v>46325.5</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -51229,32 +51233,32 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>46335.25</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>46336.33333333334</v>
+        <v>46326.95833333334</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -51265,32 +51269,32 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>46337.45833333334</v>
+        <v>46323.875</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>46338.54166666666</v>
+        <v>46329.91666666666</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -51301,32 +51305,32 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>46338.08333333334</v>
+        <v>46325.54166666666</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>46339.16666666666</v>
+        <v>46331.58333333334</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -51337,32 +51341,32 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>46339.45833333334</v>
+        <v>46327.16666666666</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>46340.54166666666</v>
+        <v>46333.20833333334</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -51373,32 +51377,32 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>46341.41666666666</v>
+        <v>46333.875</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>46342.5</v>
+        <v>46339.91666666666</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -51409,32 +51413,32 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>46347.0625</v>
+        <v>46334.5</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>46348.14583333334</v>
+        <v>46340.54166666666</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -51445,32 +51449,32 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>46348.32083333333</v>
+        <v>46336.125</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>46349.40416666667</v>
+        <v>46342.16666666666</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -51481,32 +51485,32 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>46349.14166666667</v>
+        <v>46340.45833333334</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>46350.225</v>
+        <v>46346.5</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -51517,32 +51521,32 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>46350.89166666667</v>
+        <v>46341.91666666666</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>46351.975</v>
+        <v>46347.95833333334</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -51553,32 +51557,32 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2620S</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>46356.26666666667</v>
+        <v>46344.875</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>46357.35</v>
+        <v>46350.91666666666</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -51589,32 +51593,32 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2620S</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>46358.475</v>
+        <v>46346.54166666666</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46359.55833333333</v>
+        <v>46352.58333333334</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -51625,12 +51629,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -51640,17 +51644,17 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2620S</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>46359.1</v>
+        <v>46348.16666666666</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>46360.18333333333</v>
+        <v>46354.20833333334</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -51661,7 +51665,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -51671,22 +51675,22 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2620S</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>46360.475</v>
+        <v>46354.875</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>46361.55833333333</v>
+        <v>46360.91666666666</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -51697,32 +51701,140 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE MIMOSA</t>
+          <t>TS XIAMEN</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>2620N</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>46355.5</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>46361.54166666666</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>2620N</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>46357.125</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>46363.16666666666</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>2620N</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>46361.45833333334</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>46367.5</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>TS XIAMEN</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
         <v/>
       </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>46362.43333333333</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>46363.51666666667</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>2620N</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>46362.91666666666</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>46368.95833333334</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Delay</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -615,22 +615,20 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>KRPTK (PTK02)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>0152S</t>
-        </is>
+          <t>KRPTK -&gt; KRKAN</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v/>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-09-30T02:00:00</t>
+          <t>In transit, ETA 2026-10-01T00:30:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -917,22 +915,20 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
+          <t>VNSGN -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v/>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-09-30T00:00:00</t>
+          <t>In transit, ETA 2026-10-01T19:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1306,7 +1302,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUSH4)</t>
+          <t>KRUSN (USN03)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1316,7 +1312,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRUSN ~2026-09-30T00:00:00</t>
+          <t>Alongside, departs to CNSHA ~2026-09-30T15:00:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
@@ -1723,20 +1719,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>VNSGN -&gt; KRINC</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v/>
+          <t>KRINC (INC07)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2616S</t>
+        </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-29T23:00:00</t>
+          <t>Alongside, departs to KRPTK ~2026-09-30T12:00:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
@@ -2167,20 +2165,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CNSHA -&gt; IDJKT</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v/>
+          <t>IDJKT (JKT02)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-29T23:30:00</t>
+          <t>Alongside, departs to IDSRG ~2026-10-01T10:00:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
@@ -47938,10 +47938,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -47979,7 +47979,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260929-1542-SKED.xlsx)</t>
+          <t>New ETA (auto-20260929-2041-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47996,1614 +47996,34 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>KMTC JAKARTA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46297.79166666666</v>
+        <v>46258.75</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46298.29166666666</v>
+        <v>46258.54166666666</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>12</v>
+        <v>-5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46299.97916666666</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46300.47916666666</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46307.85416666666</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46308.35416666666</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>46309.85416666666</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46310.35416666666</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46314.4375</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>46314.9375</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46321.5625</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>46322.0625</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>46333.70833333334</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>46331.79166666666</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46336.33333333334</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>46334.66666666666</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>46338.125</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>46336.70833333334</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>-34</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>46339.66666666666</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>46338.25</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>-34</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>IDSUB</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>46347.875</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>46346.45833333334</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>-34</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>IDSUB</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>46350.33333333334</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>46348.91666666666</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>-34</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>46354.83333333334</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>46353.41666666666</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>-34</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>46360.41666666666</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>46359</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>-34</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>KMTC JAKARTA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>46258.75</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>46258.54166666666</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>46295.375</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>46295.45833333334</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>46296.70833333334</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>46298</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>46301.29166666666</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>46302.91666666666</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>46304.20833333334</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>46305.375</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>46306.66666666666</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>46305.75</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>46307.04166666666</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>46307.54166666666</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>46308.83333333334</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46311.75</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>46313.04166666666</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>46313.33333333334</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>46314.45833333334</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>46315.08333333334</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>46315.95833333334</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>46316.16666666666</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>46317.04166666666</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>46319.41666666666</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>46320.29166666666</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>46322.125</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>46323</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>46324.5</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>46325.375</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>46324.95833333334</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>46325.83333333334</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>46326.91666666666</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>46327.79166666666</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>46331.33333333334</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>46332.20833333334</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>46332.91666666666</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>46333.79166666666</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>46335.83333333334</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>46336.70833333334</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>46336.91666666666</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>46337.79166666666</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>46340.16666666666</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>46341.04166666666</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>46342.875</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>46343.75</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>46345.25</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>46346.125</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46345.70833333334</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>46346.58333333334</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46347.66666666666</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>46348.54166666666</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>46352.08333333334</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>46352.95833333334</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>46353.66666666666</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>46354.54166666666</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>MYPKL</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2604E</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>46296.5</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>46295.83333333334</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2604E</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>46303.58333333334</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>46303.1875</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2604E</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>46306.83333333334</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>46306.4375</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Early</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T00:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T02:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -827,7 +827,7 @@
         <v/>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -979,22 +979,20 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH05)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>THLCH -&gt; HKHKG</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v/>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to HKHKG ~2026-09-30T04:00:00</t>
+          <t>In transit, ETA 2026-10-04T01:00:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
@@ -8533,10 +8531,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>46296.33333333334</v>
+        <v>46296.41666666666</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>46298</v>
+        <v>46298.08333333334</v>
       </c>
     </row>
     <row r="149">
@@ -8571,13 +8569,13 @@
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>46298.29166666666</v>
+        <v>46298.375</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>46298.35416666666</v>
+        <v>46298.4375</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>46298.97916666666</v>
+        <v>46299.0625</v>
       </c>
     </row>
     <row r="150">
@@ -8612,13 +8610,13 @@
         </is>
       </c>
       <c r="G150" s="3" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.5625</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>46300.6875</v>
+        <v>46300.77083333334</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.4375</v>
       </c>
     </row>
     <row r="151">
@@ -8653,13 +8651,13 @@
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>46308.35416666666</v>
+        <v>46308.4375</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>46308.4375</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>46309.27083333334</v>
+        <v>46309.35416666666</v>
       </c>
     </row>
     <row r="152">
@@ -8694,13 +8692,13 @@
         </is>
       </c>
       <c r="G152" s="3" t="n">
-        <v>46310.35416666666</v>
+        <v>46310.4375</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>46310.4375</v>
+        <v>46310.52083333334</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>46310.9375</v>
+        <v>46311.02083333334</v>
       </c>
     </row>
     <row r="153">
@@ -8735,13 +8733,13 @@
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>46314.97916666666</v>
+        <v>46315.0625</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>46315.64583333334</v>
+        <v>46315.72916666666</v>
       </c>
     </row>
     <row r="154">
@@ -8776,13 +8774,13 @@
         </is>
       </c>
       <c r="G154" s="3" t="n">
-        <v>46322.0625</v>
+        <v>46322.14583333334</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>46322.27083333334</v>
+        <v>46322.35416666666</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>46322.9375</v>
+        <v>46323.02083333334</v>
       </c>
     </row>
     <row r="155">
@@ -22458,7 +22456,7 @@
         <v>46293.79166666666</v>
       </c>
       <c r="I488" s="3" t="n">
-        <v>46296.25</v>
+        <v>46296.33333333334</v>
       </c>
     </row>
     <row r="489">
@@ -22575,13 +22573,13 @@
         </is>
       </c>
       <c r="G491" s="3" t="n">
-        <v>46296.54166666666</v>
+        <v>46296.625</v>
       </c>
       <c r="H491" s="3" t="n">
-        <v>46296.60416666666</v>
+        <v>46296.6875</v>
       </c>
       <c r="I491" s="3" t="n">
-        <v>46297.125</v>
+        <v>46297.20833333334</v>
       </c>
     </row>
     <row r="492">
@@ -22616,13 +22614,13 @@
         </is>
       </c>
       <c r="G492" s="3" t="n">
-        <v>46298.58333333334</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="H492" s="3" t="n">
-        <v>46299.66666666666</v>
+        <v>46299.75</v>
       </c>
       <c r="I492" s="3" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.25</v>
       </c>
     </row>
     <row r="493">
@@ -22657,13 +22655,13 @@
         </is>
       </c>
       <c r="G493" s="3" t="n">
-        <v>46303.125</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>46303.25</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="I493" s="3" t="n">
-        <v>46303.66666666666</v>
+        <v>46303.75</v>
       </c>
     </row>
     <row r="494">
@@ -22698,13 +22696,13 @@
         </is>
       </c>
       <c r="G494" s="3" t="n">
-        <v>46315.91666666666</v>
+        <v>46316</v>
       </c>
       <c r="H494" s="3" t="n">
-        <v>46317</v>
+        <v>46317.08333333334</v>
       </c>
       <c r="I494" s="3" t="n">
-        <v>46317.66666666666</v>
+        <v>46317.75</v>
       </c>
     </row>
     <row r="495">
@@ -22739,13 +22737,13 @@
         </is>
       </c>
       <c r="G495" s="3" t="n">
-        <v>46318.91666666666</v>
+        <v>46319</v>
       </c>
       <c r="H495" s="3" t="n">
-        <v>46319</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="I495" s="3" t="n">
-        <v>46319.5</v>
+        <v>46319.58333333334</v>
       </c>
     </row>
     <row r="496">
@@ -22780,13 +22778,13 @@
         </is>
       </c>
       <c r="G496" s="3" t="n">
-        <v>46320.41666666666</v>
+        <v>46320.5</v>
       </c>
       <c r="H496" s="3" t="n">
-        <v>46320.5</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="I496" s="3" t="n">
-        <v>46321.08333333334</v>
+        <v>46321.16666666666</v>
       </c>
     </row>
     <row r="497">
@@ -22821,13 +22819,13 @@
         </is>
       </c>
       <c r="G497" s="3" t="n">
-        <v>46329.95833333334</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>46331</v>
+        <v>46331.08333333334</v>
       </c>
       <c r="I497" s="3" t="n">
-        <v>46331.58333333334</v>
+        <v>46331.66666666666</v>
       </c>
     </row>
     <row r="498">
@@ -22860,13 +22858,13 @@
         <v/>
       </c>
       <c r="G498" s="3" t="n">
-        <v>46340.375</v>
+        <v>46340.45833333334</v>
       </c>
       <c r="H498" s="3" t="n">
-        <v>46340.41666666666</v>
+        <v>46340.5</v>
       </c>
       <c r="I498" s="3" t="n">
-        <v>46341.16666666666</v>
+        <v>46341.25</v>
       </c>
     </row>
     <row r="499">
@@ -47938,10 +47936,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -47979,7 +47977,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260929-2041-SKED.xlsx)</t>
+          <t>New ETA (auto-20260930-0021-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47996,36 +47994,538 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46298.29166666666</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46298.375</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46308.35416666666</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46308.4375</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46310.35416666666</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>46310.4375</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46314.9375</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46315.02083333334</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46322.0625</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46322.14583333334</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>KMTC JAKARTA</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>THBKK</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2609N</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>46258.75</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>46258.54166666666</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>-5</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>LAEM CHABANG VOYAGER</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CNNGB</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46296.54166666666</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>46296.625</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LAEM CHABANG VOYAGER</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CNNGB</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46298.58333333334</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46298.66666666666</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LAEM CHABANG VOYAGER</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>INNSA</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46303.125</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>46303.20833333334</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LAEM CHABANG VOYAGER</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>INNSA</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>INMUN</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2607E</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46315.91666666666</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LAEM CHABANG VOYAGER</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>INMUN</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>PKKHI</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2607E</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46318.91666666666</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LAEM CHABANG VOYAGER</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>PKKHI</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>MYPKL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2607E</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>46320.41666666666</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>46320.5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>LAEM CHABANG VOYAGER</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>MYPKL</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2607E</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46329.95833333334</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>46330.04166666666</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>LAEM CHABANG VOYAGER</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2607E</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>46340.375</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>46340.45833333334</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47943,7 +47943,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47972,7 +47972,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (prev)</t>
+          <t>Old ETA (auto-20260929-2041-SKED.xlsx)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -551,26 +551,24 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>HKHKG (HKG03)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
+          <t>HKHKG -&gt; CNSHK</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v/>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNSHK ~2026-10-01T01:00:00</t>
+          <t>In transit, ETA 2026-09-30T23:00:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>46311.58333333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -583,7 +581,7 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>46311.125</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -818,7 +816,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T00:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T06:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -829,7 +827,7 @@
         <v/>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46315.1875</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -1411,20 +1409,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>PKKHI -&gt; MYPKL</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v/>
+          <t>MYPKL (PKL01)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2604E</t>
+        </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T20:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-10-01T22:00:00</t>
         </is>
       </c>
       <c r="I16" s="3" t="n"/>
@@ -1719,22 +1719,20 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>KRINC (INC07)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
+          <t>KRINC -&gt; KRPTK</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v/>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPTK ~2026-09-30T15:00:00</t>
+          <t>In transit, ETA 2026-09-30T22:00:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
@@ -2289,20 +2287,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>IDJKT -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T14:00:00</t>
+          <t>Alongside, departs to HKHKG ~2026-10-01T07:30:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
@@ -2329,17 +2329,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TSXM</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KRPUS -&gt; KRPUS</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
@@ -2360,89 +2360,25 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>46319.54166666666</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>BKK04</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
+          <t>In transit, ETA 2026-10-05T00:00:00</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46318.91666666666</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v/>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>transit</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v/>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>In transit, ETA 2026-10-05T00:00:00</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="2" t="n">
-        <v/>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>46313.41666666666</v>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>LCH04</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>2608S</t>
         </is>
@@ -2459,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1108"/>
+  <dimension ref="A1:I1084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3249,13 +3185,13 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>46295.5</v>
+        <v>46295.25</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46295.5625</v>
+        <v>46295.3125</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>46296.04166666666</v>
+        <v>46295.8125</v>
       </c>
     </row>
     <row r="20">
@@ -3290,13 +3226,13 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>46296.125</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>46296.16666666666</v>
+        <v>46296.625</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46296.54166666666</v>
+        <v>46297.10416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3331,13 +3267,13 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>46298.08333333334</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>46298.125</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>46298.625</v>
+        <v>46299.33333333334</v>
       </c>
     </row>
     <row r="22">
@@ -3372,13 +3308,13 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>46300.25</v>
+        <v>46301.70833333334</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>46300.29166666666</v>
+        <v>46301.75</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>46301.29166666666</v>
+        <v>46302.75</v>
       </c>
     </row>
     <row r="23">
@@ -3413,13 +3349,13 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>46301.41666666666</v>
+        <v>46302.875</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>46301.45833333334</v>
+        <v>46302.91666666666</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46301.83333333334</v>
+        <v>46303.29166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3454,13 +3390,13 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>46305.25</v>
+        <v>46306.79166666666</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>46305.3125</v>
+        <v>46306.85416666666</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>46305.72916666666</v>
+        <v>46307.27083333334</v>
       </c>
     </row>
     <row r="25">
@@ -3495,13 +3431,13 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>46308.45833333334</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>46308.625</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>46309.33333333334</v>
+        <v>46310.91666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3536,13 +3472,13 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>46311.125</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>46311.16666666666</v>
+        <v>46312.875</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46311.41666666666</v>
+        <v>46313.16666666666</v>
       </c>
     </row>
     <row r="27">
@@ -3577,13 +3513,13 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>46311.58333333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>46311.70833333334</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46312.95833333334</v>
+        <v>46314.66666666666</v>
       </c>
     </row>
     <row r="28">
@@ -3618,13 +3554,13 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>46313.16666666666</v>
+        <v>46314.875</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>46313.20833333334</v>
+        <v>46314.91666666666</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46313.66666666666</v>
+        <v>46315.375</v>
       </c>
     </row>
     <row r="29">
@@ -3659,13 +3595,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>46317.95833333334</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>46318.02083333334</v>
+        <v>46319.72916666666</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>46318.5</v>
+        <v>46320.20833333334</v>
       </c>
     </row>
     <row r="30">
@@ -3700,13 +3636,13 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>46318.58333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>46318.625</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46319</v>
+        <v>46320.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -3741,13 +3677,13 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>46322.75</v>
+        <v>46324.45833333334</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>46322.79166666666</v>
+        <v>46324.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>46323.79166666666</v>
+        <v>46325.5</v>
       </c>
     </row>
     <row r="32">
@@ -3782,13 +3718,13 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>46323.91666666666</v>
+        <v>46325.625</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>46323.95833333334</v>
+        <v>46325.66666666666</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>46324.33333333334</v>
+        <v>46326.04166666666</v>
       </c>
     </row>
     <row r="33">
@@ -3823,13 +3759,13 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>46327.16666666666</v>
+        <v>46328.875</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>46327.20833333334</v>
+        <v>46328.91666666666</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>46327.58333333334</v>
+        <v>46329.29166666666</v>
       </c>
     </row>
     <row r="34">
@@ -3864,13 +3800,13 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>46330.04166666666</v>
+        <v>46331.75</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>46330.20833333334</v>
+        <v>46331.91666666666</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>46330.75</v>
+        <v>46332.45833333334</v>
       </c>
     </row>
     <row r="35">
@@ -3905,13 +3841,13 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>46332.54166666666</v>
+        <v>46334.25</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>46332.58333333334</v>
+        <v>46334.29166666666</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>46332.83333333334</v>
+        <v>46334.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -3946,13 +3882,13 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>46333.25</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>46333.375</v>
+        <v>46335.08333333334</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>46334.5</v>
+        <v>46336.20833333334</v>
       </c>
     </row>
     <row r="37">
@@ -3987,13 +3923,13 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>46334.83333333334</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46334.875</v>
+        <v>46336.58333333334</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>46335.20833333334</v>
+        <v>46336.91666666666</v>
       </c>
     </row>
     <row r="38">
@@ -4028,13 +3964,13 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>46339.08333333334</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>46339.125</v>
+        <v>46340.83333333334</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>46339.54166666666</v>
+        <v>46341.25</v>
       </c>
     </row>
     <row r="39">
@@ -4069,13 +4005,13 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>46339.79166666666</v>
+        <v>46341.5</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>46339.79166666666</v>
+        <v>46341.5</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>46340.16666666666</v>
+        <v>46341.875</v>
       </c>
     </row>
     <row r="40">
@@ -4110,13 +4046,13 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>46341.41666666666</v>
+        <v>46343.125</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>46341.41666666666</v>
+        <v>46343.125</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>46341.66666666666</v>
+        <v>46343.375</v>
       </c>
     </row>
     <row r="41">
@@ -4151,13 +4087,13 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>46342.625</v>
+        <v>46344.33333333334</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>46342.66666666666</v>
+        <v>46344.375</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>46343.375</v>
+        <v>46345.08333333334</v>
       </c>
     </row>
     <row r="42">
@@ -4192,13 +4128,13 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>46343.58333333334</v>
+        <v>46345.29166666666</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>46343.625</v>
+        <v>46345.33333333334</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>46343.95833333334</v>
+        <v>46345.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -4233,13 +4169,13 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>46346.79166666666</v>
+        <v>46348.5</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>46346.83333333334</v>
+        <v>46348.54166666666</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46347.20833333334</v>
+        <v>46348.91666666666</v>
       </c>
     </row>
     <row r="44">
@@ -4274,13 +4210,13 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>46349.66666666666</v>
+        <v>46351.375</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>46349.83333333334</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46350.375</v>
+        <v>46352.08333333334</v>
       </c>
     </row>
     <row r="45">
@@ -4315,13 +4251,13 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>46352.16666666666</v>
+        <v>46353.875</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>46352.20833333334</v>
+        <v>46353.91666666666</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>46352.45833333334</v>
+        <v>46354.16666666666</v>
       </c>
     </row>
     <row r="46">
@@ -4356,13 +4292,13 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>46352.875</v>
+        <v>46354.58333333334</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>46353</v>
+        <v>46354.70833333334</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>46354.125</v>
+        <v>46355.83333333334</v>
       </c>
     </row>
     <row r="47">
@@ -4397,13 +4333,13 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>46354.45833333334</v>
+        <v>46356.16666666666</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46354.5</v>
+        <v>46356.20833333334</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>46354.83333333334</v>
+        <v>46356.54166666666</v>
       </c>
     </row>
     <row r="48">
@@ -4438,13 +4374,13 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>46358.70833333334</v>
+        <v>46360.41666666666</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>46358.75</v>
+        <v>46360.45833333334</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>46359.16666666666</v>
+        <v>46360.875</v>
       </c>
     </row>
     <row r="49">
@@ -4479,13 +4415,13 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>46359.41666666666</v>
+        <v>46361.125</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>46359.41666666666</v>
+        <v>46361.125</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46359.79166666666</v>
+        <v>46361.5</v>
       </c>
     </row>
     <row r="50">
@@ -4518,13 +4454,13 @@
         <v/>
       </c>
       <c r="G50" s="3" t="n">
-        <v>46361.04166666666</v>
+        <v>46362.75</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>46361.04166666666</v>
+        <v>46362.75</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>46361.29166666666</v>
+        <v>46363</v>
       </c>
     </row>
     <row r="51">
@@ -8533,10 +8469,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>46296.41666666666</v>
+        <v>46296.5</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>46298</v>
+        <v>46298.25</v>
       </c>
     </row>
     <row r="149">
@@ -8571,13 +8507,13 @@
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>46298.29166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>46298.35416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>46298.97916666666</v>
+        <v>46299.22916666666</v>
       </c>
     </row>
     <row r="150">
@@ -8612,13 +8548,13 @@
         </is>
       </c>
       <c r="G150" s="3" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>46300.6875</v>
+        <v>46300.9375</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.60416666666</v>
       </c>
     </row>
     <row r="151">
@@ -8653,13 +8589,13 @@
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>46308.35416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>46308.4375</v>
+        <v>46308.6875</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>46309.27083333334</v>
+        <v>46309.52083333334</v>
       </c>
     </row>
     <row r="152">
@@ -8694,13 +8630,13 @@
         </is>
       </c>
       <c r="G152" s="3" t="n">
-        <v>46310.35416666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>46310.4375</v>
+        <v>46310.6875</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>46310.9375</v>
+        <v>46311.1875</v>
       </c>
     </row>
     <row r="153">
@@ -8735,13 +8671,13 @@
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46315.1875</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>46314.97916666666</v>
+        <v>46315.22916666666</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>46315.64583333334</v>
+        <v>46315.89583333334</v>
       </c>
     </row>
     <row r="154">
@@ -8776,13 +8712,13 @@
         </is>
       </c>
       <c r="G154" s="3" t="n">
-        <v>46322.0625</v>
+        <v>46322.3125</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>46322.27083333334</v>
+        <v>46322.52083333334</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>46322.9375</v>
+        <v>46323.1875</v>
       </c>
     </row>
     <row r="155">
@@ -23287,12 +23223,12 @@
       </c>
       <c r="B509" s="2" t="inlineStr">
         <is>
-          <t>SIS2</t>
+          <t>ADHS</t>
         </is>
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>2604E</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
@@ -23317,7 +23253,7 @@
         <v>46304.375</v>
       </c>
       <c r="I509" s="3" t="n">
-        <v>46305.375</v>
+        <v>46306.375</v>
       </c>
     </row>
     <row r="510">
@@ -23328,12 +23264,12 @@
       </c>
       <c r="B510" s="2" t="inlineStr">
         <is>
-          <t>ADHS</t>
+          <t>SIS2</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>2607W</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
@@ -23352,13 +23288,13 @@
         </is>
       </c>
       <c r="G510" s="3" t="n">
-        <v>46304.33333333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>46304.375</v>
+        <v>46305.375</v>
       </c>
       <c r="I510" s="3" t="n">
-        <v>46306.375</v>
+        <v>46307.375</v>
       </c>
     </row>
     <row r="511">
@@ -23393,13 +23329,13 @@
         </is>
       </c>
       <c r="G511" s="3" t="n">
-        <v>46306.75</v>
+        <v>46308.75</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>46309.95833333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="I511" s="3" t="n">
-        <v>46310.95833333334</v>
+        <v>46312.95833333334</v>
       </c>
     </row>
     <row r="512">
@@ -23434,13 +23370,13 @@
         </is>
       </c>
       <c r="G512" s="3" t="n">
-        <v>46307.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>46308.91666666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="I512" s="3" t="n">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
     </row>
     <row r="513">
@@ -23475,13 +23411,13 @@
         </is>
       </c>
       <c r="G513" s="3" t="n">
-        <v>46310.91666666666</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="H513" s="3" t="n">
-        <v>46312.91666666666</v>
+        <v>46315.91666666666</v>
       </c>
       <c r="I513" s="3" t="n">
-        <v>46313.5</v>
+        <v>46316.5</v>
       </c>
     </row>
     <row r="514">
@@ -23516,13 +23452,13 @@
         </is>
       </c>
       <c r="G514" s="3" t="n">
-        <v>46314.25</v>
+        <v>46317.25</v>
       </c>
       <c r="H514" s="3" t="n">
-        <v>46315.33333333334</v>
+        <v>46318.33333333334</v>
       </c>
       <c r="I514" s="3" t="n">
-        <v>46316</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="515">
@@ -23557,13 +23493,13 @@
         </is>
       </c>
       <c r="G515" s="3" t="n">
-        <v>46319</v>
+        <v>46322</v>
       </c>
       <c r="H515" s="3" t="n">
-        <v>46319.125</v>
+        <v>46322.125</v>
       </c>
       <c r="I515" s="3" t="n">
-        <v>46319.875</v>
+        <v>46322.875</v>
       </c>
     </row>
     <row r="516">
@@ -23598,13 +23534,13 @@
         </is>
       </c>
       <c r="G516" s="3" t="n">
-        <v>46335.125</v>
+        <v>46338.125</v>
       </c>
       <c r="H516" s="3" t="n">
-        <v>46340.16666666666</v>
+        <v>46343.16666666666</v>
       </c>
       <c r="I516" s="3" t="n">
-        <v>46343.16666666666</v>
+        <v>46346.16666666666</v>
       </c>
     </row>
     <row r="517">
@@ -23637,13 +23573,13 @@
         <v/>
       </c>
       <c r="G517" s="3" t="n">
-        <v>46361.41666666666</v>
+        <v>46364.41666666666</v>
       </c>
       <c r="H517" s="3" t="n">
-        <v>46361.45833333334</v>
+        <v>46364.45833333334</v>
       </c>
       <c r="I517" s="3" t="n">
-        <v>46362.125</v>
+        <v>46365.125</v>
       </c>
     </row>
     <row r="518">
@@ -45679,68 +45615,68 @@
     <row r="1056">
       <c r="A1056" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1056" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1056" s="2" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D1056" s="2" t="inlineStr">
         <is>
-          <t>INC03</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="E1056" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="F1056" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="G1056" s="3" t="n">
-        <v>46308</v>
+        <v>46257.41666666666</v>
       </c>
       <c r="H1056" s="3" t="n">
-        <v>46308.08333333334</v>
+        <v>46257.45833333334</v>
       </c>
       <c r="I1056" s="3" t="n">
-        <v>46308.91666666666</v>
+        <v>46258.625</v>
       </c>
     </row>
     <row r="1057">
       <c r="A1057" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1057" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1057" s="2" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D1057" s="2" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="E1057" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="F1057" s="2" t="inlineStr">
@@ -45749,29 +45685,29 @@
         </is>
       </c>
       <c r="G1057" s="3" t="n">
-        <v>46309.91666666666</v>
+        <v>46258.97916666666</v>
       </c>
       <c r="H1057" s="3" t="n">
-        <v>46310</v>
+        <v>46259.04166666666</v>
       </c>
       <c r="I1057" s="3" t="n">
-        <v>46310.5</v>
+        <v>46259.6125</v>
       </c>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1058" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1058" s="2" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D1058" s="2" t="inlineStr">
@@ -45786,84 +45722,84 @@
       </c>
       <c r="F1058" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="G1058" s="3" t="n">
-        <v>46311.66666666666</v>
+        <v>46260.58333333334</v>
       </c>
       <c r="H1058" s="3" t="n">
-        <v>46311.83333333334</v>
+        <v>46262.97916666666</v>
       </c>
       <c r="I1058" s="3" t="n">
-        <v>46312.58333333334</v>
+        <v>46264.00416666667</v>
       </c>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1059" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1059" s="2" t="inlineStr">
         <is>
-          <t>2618S</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="D1059" s="2" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>JKT01</t>
         </is>
       </c>
       <c r="E1059" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="F1059" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="G1059" s="3" t="n">
-        <v>46318.91666666666</v>
+        <v>46272.16666666666</v>
       </c>
       <c r="H1059" s="3" t="n">
-        <v>46318.95833333334</v>
+        <v>46272.34583333333</v>
       </c>
       <c r="I1059" s="3" t="n">
-        <v>46319.25</v>
+        <v>46273.925</v>
       </c>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1060" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1060" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="D1060" s="2" t="inlineStr">
         <is>
-          <t>BKK04</t>
+          <t>SRG02</t>
         </is>
       </c>
       <c r="E1060" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="F1060" s="2" t="inlineStr">
@@ -45872,34 +45808,34 @@
         </is>
       </c>
       <c r="G1060" s="3" t="n">
-        <v>46319.54166666666</v>
+        <v>46274.625</v>
       </c>
       <c r="H1060" s="3" t="n">
-        <v>46319.54166666666</v>
+        <v>46274.9</v>
       </c>
       <c r="I1060" s="3" t="n">
-        <v>46320.91666666666</v>
+        <v>46275.72916666666</v>
       </c>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1061" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1061" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="D1061" s="2" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>LCH06</t>
         </is>
       </c>
       <c r="E1061" s="2" t="inlineStr">
@@ -45909,753 +45845,755 @@
       </c>
       <c r="F1061" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="G1061" s="3" t="n">
-        <v>46321.16666666666</v>
+        <v>46280.41666666666</v>
       </c>
       <c r="H1061" s="3" t="n">
-        <v>46321.20833333334</v>
+        <v>46280.45833333334</v>
       </c>
       <c r="I1061" s="3" t="n">
-        <v>46321.66666666666</v>
+        <v>46281.54166666666</v>
       </c>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1062" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1062" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="D1062" s="2" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>SHAW5</t>
         </is>
       </c>
       <c r="E1062" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="F1062" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="G1062" s="3" t="n">
-        <v>46325.5</v>
+        <v>46287.625</v>
       </c>
       <c r="H1062" s="3" t="n">
-        <v>46325.5</v>
+        <v>46289.95833333334</v>
       </c>
       <c r="I1062" s="3" t="n">
-        <v>46325.95833333334</v>
+        <v>46290.8375</v>
       </c>
     </row>
     <row r="1063">
       <c r="A1063" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1063" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1063" s="2" t="inlineStr">
         <is>
-          <t>2618N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="D1063" s="2" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>KAN04</t>
         </is>
       </c>
       <c r="E1063" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="F1063" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="G1063" s="3" t="n">
-        <v>46326.95833333334</v>
+        <v>46292</v>
       </c>
       <c r="H1063" s="3" t="n">
-        <v>46326.95833333334</v>
+        <v>46292.08333333334</v>
       </c>
       <c r="I1063" s="3" t="n">
-        <v>46327.45833333334</v>
+        <v>46292.3625</v>
       </c>
     </row>
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1064" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>PCI2</t>
         </is>
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="D1064" s="2" t="inlineStr">
         <is>
-          <t>INC03</t>
+          <t>PUS05</t>
         </is>
       </c>
       <c r="E1064" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="F1064" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="G1064" s="3" t="n">
-        <v>46329.91666666666</v>
+        <v>46292.65416666667</v>
       </c>
       <c r="H1064" s="3" t="n">
-        <v>46329.95833333334</v>
+        <v>46292.97916666666</v>
       </c>
       <c r="I1064" s="3" t="n">
-        <v>46330.58333333334</v>
+        <v>46294.33333333334</v>
       </c>
     </row>
     <row r="1065">
       <c r="A1065" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1065" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1065" s="2" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D1065" s="2" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="E1065" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="F1065" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="G1065" s="3" t="n">
-        <v>46331.58333333334</v>
+        <v>46300</v>
       </c>
       <c r="H1065" s="3" t="n">
-        <v>46331.625</v>
+        <v>46300.5</v>
       </c>
       <c r="I1065" s="3" t="n">
-        <v>46332.125</v>
+        <v>46301.08333333334</v>
       </c>
     </row>
     <row r="1066">
       <c r="A1066" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1066" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D1066" s="2" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="E1066" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="F1066" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="G1066" s="3" t="n">
-        <v>46333.20833333334</v>
+        <v>46302.1875</v>
       </c>
       <c r="H1066" s="3" t="n">
-        <v>46333.375</v>
+        <v>46302.25</v>
       </c>
       <c r="I1066" s="3" t="n">
-        <v>46334.16666666666</v>
+        <v>46302.58333333334</v>
       </c>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1067" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1067" s="2" t="inlineStr">
         <is>
-          <t>2619S</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D1067" s="2" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="E1067" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="F1067" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="G1067" s="3" t="n">
-        <v>46339.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="H1067" s="3" t="n">
-        <v>46339.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="I1067" s="3" t="n">
-        <v>46340.25</v>
+        <v>46304.625</v>
       </c>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1068" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1068" s="2" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D1068" s="2" t="inlineStr">
         <is>
-          <t>BKK04</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="E1068" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="F1068" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="G1068" s="3" t="n">
-        <v>46340.54166666666</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="H1068" s="3" t="n">
-        <v>46340.54166666666</v>
+        <v>46306.08333333334</v>
       </c>
       <c r="I1068" s="3" t="n">
-        <v>46341.91666666666</v>
+        <v>46306.58333333334</v>
       </c>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1069" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1069" s="2" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D1069" s="2" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="E1069" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="F1069" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="F1069" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="G1069" s="3" t="n">
-        <v>46342.16666666666</v>
+        <v>46310.75</v>
       </c>
       <c r="H1069" s="3" t="n">
-        <v>46342.20833333334</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="I1069" s="3" t="n">
-        <v>46342.66666666666</v>
+        <v>46311.75</v>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1070" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D1070" s="2" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="E1070" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="F1070" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="G1070" s="3" t="n">
-        <v>46346.5</v>
+        <v>46313.41666666666</v>
       </c>
       <c r="H1070" s="3" t="n">
-        <v>46346.5</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="I1070" s="3" t="n">
-        <v>46346.95833333334</v>
+        <v>46314.29166666666</v>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
         <is>
-          <t>2619N</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="D1071" s="2" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="E1071" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="F1071" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="G1071" s="3" t="n">
-        <v>46347.95833333334</v>
+        <v>46317.45833333334</v>
       </c>
       <c r="H1071" s="3" t="n">
-        <v>46347.95833333334</v>
+        <v>46317.54166666666</v>
       </c>
       <c r="I1071" s="3" t="n">
-        <v>46348.45833333334</v>
+        <v>46319.20833333334</v>
       </c>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1072" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="D1072" s="2" t="inlineStr">
         <is>
-          <t>INC03</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="E1072" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="F1072" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="G1072" s="3" t="n">
-        <v>46350.91666666666</v>
+        <v>46321.66666666666</v>
       </c>
       <c r="H1072" s="3" t="n">
-        <v>46350.95833333334</v>
+        <v>46321.83333333334</v>
       </c>
       <c r="I1072" s="3" t="n">
-        <v>46351.58333333334</v>
+        <v>46322.66666666666</v>
       </c>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1073" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1073" s="2" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="D1073" s="2" t="inlineStr">
         <is>
-          <t>TAO04</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="E1073" s="2" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="F1073" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="G1073" s="3" t="n">
-        <v>46352.58333333334</v>
+        <v>46325.20833333334</v>
       </c>
       <c r="H1073" s="3" t="n">
-        <v>46352.625</v>
+        <v>46325.27083333334</v>
       </c>
       <c r="I1073" s="3" t="n">
-        <v>46353.125</v>
+        <v>46325.77083333334</v>
       </c>
     </row>
     <row r="1074">
       <c r="A1074" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1074" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1074" s="2" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2608N</t>
         </is>
       </c>
       <c r="D1074" s="2" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="E1074" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="F1074" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="G1074" s="3" t="n">
-        <v>46354.20833333334</v>
+        <v>46326</v>
       </c>
       <c r="H1074" s="3" t="n">
-        <v>46354.375</v>
+        <v>46326.04166666666</v>
       </c>
       <c r="I1074" s="3" t="n">
-        <v>46355.16666666666</v>
+        <v>46326.54166666666</v>
       </c>
     </row>
     <row r="1075">
       <c r="A1075" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1075" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1075" s="2" t="inlineStr">
         <is>
-          <t>2620S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D1075" s="2" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>INC08</t>
         </is>
       </c>
       <c r="E1075" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="F1075" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="G1075" s="3" t="n">
-        <v>46360.91666666666</v>
+        <v>46329.625</v>
       </c>
       <c r="H1075" s="3" t="n">
-        <v>46360.95833333334</v>
+        <v>46329.66666666666</v>
       </c>
       <c r="I1075" s="3" t="n">
-        <v>46361.25</v>
+        <v>46330.33333333334</v>
       </c>
     </row>
     <row r="1076">
       <c r="A1076" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1076" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1076" s="2" t="inlineStr">
         <is>
-          <t>2620N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D1076" s="2" t="inlineStr">
         <is>
-          <t>BKK04</t>
+          <t>PUSH4</t>
         </is>
       </c>
       <c r="E1076" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="F1076" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="G1076" s="3" t="n">
-        <v>46361.54166666666</v>
+        <v>46331.41666666666</v>
       </c>
       <c r="H1076" s="3" t="n">
-        <v>46361.54166666666</v>
+        <v>46331.45833333334</v>
       </c>
       <c r="I1076" s="3" t="n">
-        <v>46362.91666666666</v>
+        <v>46332.04166666666</v>
       </c>
     </row>
     <row r="1077">
       <c r="A1077" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1077" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1077" s="2" t="inlineStr">
         <is>
-          <t>2620N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D1077" s="2" t="inlineStr">
         <is>
-          <t>LCH05</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="E1077" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="F1077" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="G1077" s="3" t="n">
-        <v>46363.16666666666</v>
+        <v>46332.22916666666</v>
       </c>
       <c r="H1077" s="3" t="n">
-        <v>46363.20833333334</v>
+        <v>46332.29166666666</v>
       </c>
       <c r="I1077" s="3" t="n">
-        <v>46363.66666666666</v>
+        <v>46332.625</v>
       </c>
     </row>
     <row r="1078">
       <c r="A1078" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1078" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1078" s="2" t="inlineStr">
         <is>
-          <t>2620N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D1078" s="2" t="inlineStr">
         <is>
-          <t>HKG03</t>
+          <t>SHAW2</t>
         </is>
       </c>
       <c r="E1078" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="F1078" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="G1078" s="3" t="n">
-        <v>46367.5</v>
+        <v>46333.91666666666</v>
       </c>
       <c r="H1078" s="3" t="n">
-        <v>46367.5</v>
+        <v>46334.08333333334</v>
       </c>
       <c r="I1078" s="3" t="n">
-        <v>46367.95833333334</v>
+        <v>46334.58333333334</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" s="2" t="inlineStr">
         <is>
-          <t>TS XIAMEN</t>
+          <t>YEOSU VOYAGER</t>
         </is>
       </c>
       <c r="B1079" s="2" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1079" s="2" t="inlineStr">
         <is>
-          <t>2620N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D1079" s="2" t="inlineStr">
         <is>
-          <t>XMN01</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="E1079" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="F1079" s="2" t="n">
-        <v/>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="F1079" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
       </c>
       <c r="G1079" s="3" t="n">
-        <v>46368.95833333334</v>
+        <v>46338.75</v>
       </c>
       <c r="H1079" s="3" t="n">
-        <v>46368.95833333334</v>
+        <v>46338.91666666666</v>
       </c>
       <c r="I1079" s="3" t="n">
-        <v>46369.45833333334</v>
+        <v>46339.75</v>
       </c>
     </row>
     <row r="1080">
@@ -46666,37 +46604,37 @@
       </c>
       <c r="B1080" s="2" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1080" s="2" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D1080" s="2" t="inlineStr">
         <is>
-          <t>PUS05</t>
+          <t>LCH04</t>
         </is>
       </c>
       <c r="E1080" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="F1080" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="G1080" s="3" t="n">
-        <v>46257.41666666666</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="H1080" s="3" t="n">
-        <v>46257.45833333334</v>
+        <v>46341.45833333334</v>
       </c>
       <c r="I1080" s="3" t="n">
-        <v>46258.625</v>
+        <v>46342.29166666666</v>
       </c>
     </row>
     <row r="1081">
@@ -46707,37 +46645,37 @@
       </c>
       <c r="B1081" s="2" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1081" s="2" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D1081" s="2" t="inlineStr">
         <is>
-          <t>KAN04</t>
+          <t>JKT02</t>
         </is>
       </c>
       <c r="E1081" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="F1081" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="G1081" s="3" t="n">
-        <v>46258.97916666666</v>
+        <v>46345.45833333334</v>
       </c>
       <c r="H1081" s="3" t="n">
-        <v>46259.04166666666</v>
+        <v>46345.54166666666</v>
       </c>
       <c r="I1081" s="3" t="n">
-        <v>46259.6125</v>
+        <v>46347.20833333334</v>
       </c>
     </row>
     <row r="1082">
@@ -46748,37 +46686,37 @@
       </c>
       <c r="B1082" s="2" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1082" s="2" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D1082" s="2" t="inlineStr">
         <is>
-          <t>SHAW1</t>
+          <t>SGN03</t>
         </is>
       </c>
       <c r="E1082" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="F1082" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="G1082" s="3" t="n">
-        <v>46260.58333333334</v>
+        <v>46349.66666666666</v>
       </c>
       <c r="H1082" s="3" t="n">
-        <v>46262.97916666666</v>
+        <v>46349.83333333334</v>
       </c>
       <c r="I1082" s="3" t="n">
-        <v>46264.00416666667</v>
+        <v>46350.66666666666</v>
       </c>
     </row>
     <row r="1083">
@@ -46789,37 +46727,37 @@
       </c>
       <c r="B1083" s="2" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1083" s="2" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D1083" s="2" t="inlineStr">
         <is>
-          <t>JKT01</t>
+          <t>HKG03</t>
         </is>
       </c>
       <c r="E1083" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="F1083" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="G1083" s="3" t="n">
-        <v>46272.16666666666</v>
+        <v>46353.20833333334</v>
       </c>
       <c r="H1083" s="3" t="n">
-        <v>46272.34583333333</v>
+        <v>46353.27083333334</v>
       </c>
       <c r="I1083" s="3" t="n">
-        <v>46273.925</v>
+        <v>46353.77083333334</v>
       </c>
     </row>
     <row r="1084">
@@ -46830,1018 +46768,34 @@
       </c>
       <c r="B1084" s="2" t="inlineStr">
         <is>
-          <t>PCI2</t>
+          <t>ANX</t>
         </is>
       </c>
       <c r="C1084" s="2" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D1084" s="2" t="inlineStr">
         <is>
-          <t>SRG02</t>
+          <t>SHE04</t>
         </is>
       </c>
       <c r="E1084" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="F1084" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="F1084" s="2" t="n">
+        <v/>
       </c>
       <c r="G1084" s="3" t="n">
-        <v>46274.625</v>
+        <v>46354</v>
       </c>
       <c r="H1084" s="3" t="n">
-        <v>46274.9</v>
+        <v>46354.04166666666</v>
       </c>
       <c r="I1084" s="3" t="n">
-        <v>46275.72916666666</v>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1085" s="2" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="C1085" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="D1085" s="2" t="inlineStr">
-        <is>
-          <t>LCH06</t>
-        </is>
-      </c>
-      <c r="E1085" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="F1085" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="G1085" s="3" t="n">
-        <v>46280.41666666666</v>
-      </c>
-      <c r="H1085" s="3" t="n">
-        <v>46280.45833333334</v>
-      </c>
-      <c r="I1085" s="3" t="n">
-        <v>46281.54166666666</v>
-      </c>
-    </row>
-    <row r="1086">
-      <c r="A1086" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1086" s="2" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="C1086" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="D1086" s="2" t="inlineStr">
-        <is>
-          <t>SHAW5</t>
-        </is>
-      </c>
-      <c r="E1086" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="F1086" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="G1086" s="3" t="n">
-        <v>46287.625</v>
-      </c>
-      <c r="H1086" s="3" t="n">
-        <v>46289.95833333334</v>
-      </c>
-      <c r="I1086" s="3" t="n">
-        <v>46290.8375</v>
-      </c>
-    </row>
-    <row r="1087">
-      <c r="A1087" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1087" s="2" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="C1087" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="D1087" s="2" t="inlineStr">
-        <is>
-          <t>KAN04</t>
-        </is>
-      </c>
-      <c r="E1087" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="F1087" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="G1087" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="H1087" s="3" t="n">
-        <v>46292.08333333334</v>
-      </c>
-      <c r="I1087" s="3" t="n">
-        <v>46292.3625</v>
-      </c>
-    </row>
-    <row r="1088">
-      <c r="A1088" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1088" s="2" t="inlineStr">
-        <is>
-          <t>PCI2</t>
-        </is>
-      </c>
-      <c r="C1088" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="D1088" s="2" t="inlineStr">
-        <is>
-          <t>PUS05</t>
-        </is>
-      </c>
-      <c r="E1088" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="F1088" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="G1088" s="3" t="n">
-        <v>46292.65416666667</v>
-      </c>
-      <c r="H1088" s="3" t="n">
-        <v>46292.97916666666</v>
-      </c>
-      <c r="I1088" s="3" t="n">
-        <v>46294.33333333334</v>
-      </c>
-    </row>
-    <row r="1089">
-      <c r="A1089" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1089" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1089" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D1089" s="2" t="inlineStr">
-        <is>
-          <t>PUSH4</t>
-        </is>
-      </c>
-      <c r="E1089" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="F1089" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="G1089" s="3" t="n">
-        <v>46300</v>
-      </c>
-      <c r="H1089" s="3" t="n">
-        <v>46300.5</v>
-      </c>
-      <c r="I1089" s="3" t="n">
-        <v>46301.08333333334</v>
-      </c>
-    </row>
-    <row r="1090">
-      <c r="A1090" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1090" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1090" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D1090" s="2" t="inlineStr">
-        <is>
-          <t>USN03</t>
-        </is>
-      </c>
-      <c r="E1090" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="F1090" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="G1090" s="3" t="n">
-        <v>46302.1875</v>
-      </c>
-      <c r="H1090" s="3" t="n">
-        <v>46302.25</v>
-      </c>
-      <c r="I1090" s="3" t="n">
-        <v>46302.58333333334</v>
-      </c>
-    </row>
-    <row r="1091">
-      <c r="A1091" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1091" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1091" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D1091" s="2" t="inlineStr">
-        <is>
-          <t>INC08</t>
-        </is>
-      </c>
-      <c r="E1091" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="F1091" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="G1091" s="3" t="n">
-        <v>46303.91666666666</v>
-      </c>
-      <c r="H1091" s="3" t="n">
-        <v>46303.95833333334</v>
-      </c>
-      <c r="I1091" s="3" t="n">
-        <v>46304.625</v>
-      </c>
-    </row>
-    <row r="1092">
-      <c r="A1092" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1092" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1092" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D1092" s="2" t="inlineStr">
-        <is>
-          <t>SHAW2</t>
-        </is>
-      </c>
-      <c r="E1092" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="F1092" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="G1092" s="3" t="n">
-        <v>46305.91666666666</v>
-      </c>
-      <c r="H1092" s="3" t="n">
-        <v>46306.08333333334</v>
-      </c>
-      <c r="I1092" s="3" t="n">
-        <v>46306.58333333334</v>
-      </c>
-    </row>
-    <row r="1093">
-      <c r="A1093" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1093" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1093" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D1093" s="2" t="inlineStr">
-        <is>
-          <t>SGN03</t>
-        </is>
-      </c>
-      <c r="E1093" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="F1093" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G1093" s="3" t="n">
-        <v>46310.75</v>
-      </c>
-      <c r="H1093" s="3" t="n">
-        <v>46310.91666666666</v>
-      </c>
-      <c r="I1093" s="3" t="n">
-        <v>46311.75</v>
-      </c>
-    </row>
-    <row r="1094">
-      <c r="A1094" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1094" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1094" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D1094" s="2" t="inlineStr">
-        <is>
-          <t>LCH04</t>
-        </is>
-      </c>
-      <c r="E1094" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="F1094" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="G1094" s="3" t="n">
-        <v>46313.41666666666</v>
-      </c>
-      <c r="H1094" s="3" t="n">
-        <v>46313.45833333334</v>
-      </c>
-      <c r="I1094" s="3" t="n">
-        <v>46314.29166666666</v>
-      </c>
-    </row>
-    <row r="1095">
-      <c r="A1095" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1095" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1095" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="D1095" s="2" t="inlineStr">
-        <is>
-          <t>JKT02</t>
-        </is>
-      </c>
-      <c r="E1095" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="F1095" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="G1095" s="3" t="n">
-        <v>46317.45833333334</v>
-      </c>
-      <c r="H1095" s="3" t="n">
-        <v>46317.54166666666</v>
-      </c>
-      <c r="I1095" s="3" t="n">
-        <v>46319.20833333334</v>
-      </c>
-    </row>
-    <row r="1096">
-      <c r="A1096" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1096" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1096" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="D1096" s="2" t="inlineStr">
-        <is>
-          <t>SGN03</t>
-        </is>
-      </c>
-      <c r="E1096" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="F1096" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="G1096" s="3" t="n">
-        <v>46321.66666666666</v>
-      </c>
-      <c r="H1096" s="3" t="n">
-        <v>46321.83333333334</v>
-      </c>
-      <c r="I1096" s="3" t="n">
-        <v>46322.66666666666</v>
-      </c>
-    </row>
-    <row r="1097">
-      <c r="A1097" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1097" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1097" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="D1097" s="2" t="inlineStr">
-        <is>
-          <t>HKG03</t>
-        </is>
-      </c>
-      <c r="E1097" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="F1097" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="G1097" s="3" t="n">
-        <v>46325.20833333334</v>
-      </c>
-      <c r="H1097" s="3" t="n">
-        <v>46325.27083333334</v>
-      </c>
-      <c r="I1097" s="3" t="n">
-        <v>46325.77083333334</v>
-      </c>
-    </row>
-    <row r="1098">
-      <c r="A1098" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1098" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1098" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="D1098" s="2" t="inlineStr">
-        <is>
-          <t>SHE04</t>
-        </is>
-      </c>
-      <c r="E1098" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="F1098" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="G1098" s="3" t="n">
-        <v>46326</v>
-      </c>
-      <c r="H1098" s="3" t="n">
-        <v>46326.04166666666</v>
-      </c>
-      <c r="I1098" s="3" t="n">
-        <v>46326.54166666666</v>
-      </c>
-    </row>
-    <row r="1099">
-      <c r="A1099" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1099" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1099" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D1099" s="2" t="inlineStr">
-        <is>
-          <t>INC08</t>
-        </is>
-      </c>
-      <c r="E1099" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="F1099" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="G1099" s="3" t="n">
-        <v>46329.625</v>
-      </c>
-      <c r="H1099" s="3" t="n">
-        <v>46329.66666666666</v>
-      </c>
-      <c r="I1099" s="3" t="n">
-        <v>46330.33333333334</v>
-      </c>
-    </row>
-    <row r="1100">
-      <c r="A1100" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1100" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1100" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D1100" s="2" t="inlineStr">
-        <is>
-          <t>PUSH4</t>
-        </is>
-      </c>
-      <c r="E1100" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="F1100" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="G1100" s="3" t="n">
-        <v>46331.41666666666</v>
-      </c>
-      <c r="H1100" s="3" t="n">
-        <v>46331.45833333334</v>
-      </c>
-      <c r="I1100" s="3" t="n">
-        <v>46332.04166666666</v>
-      </c>
-    </row>
-    <row r="1101">
-      <c r="A1101" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1101" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1101" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D1101" s="2" t="inlineStr">
-        <is>
-          <t>USN03</t>
-        </is>
-      </c>
-      <c r="E1101" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="F1101" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="G1101" s="3" t="n">
-        <v>46332.22916666666</v>
-      </c>
-      <c r="H1101" s="3" t="n">
-        <v>46332.29166666666</v>
-      </c>
-      <c r="I1101" s="3" t="n">
-        <v>46332.625</v>
-      </c>
-    </row>
-    <row r="1102">
-      <c r="A1102" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1102" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1102" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D1102" s="2" t="inlineStr">
-        <is>
-          <t>SHAW2</t>
-        </is>
-      </c>
-      <c r="E1102" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="F1102" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="G1102" s="3" t="n">
-        <v>46333.91666666666</v>
-      </c>
-      <c r="H1102" s="3" t="n">
-        <v>46334.08333333334</v>
-      </c>
-      <c r="I1102" s="3" t="n">
-        <v>46334.58333333334</v>
-      </c>
-    </row>
-    <row r="1103">
-      <c r="A1103" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1103" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1103" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D1103" s="2" t="inlineStr">
-        <is>
-          <t>SGN03</t>
-        </is>
-      </c>
-      <c r="E1103" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="F1103" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G1103" s="3" t="n">
-        <v>46338.75</v>
-      </c>
-      <c r="H1103" s="3" t="n">
-        <v>46338.91666666666</v>
-      </c>
-      <c r="I1103" s="3" t="n">
-        <v>46339.75</v>
-      </c>
-    </row>
-    <row r="1104">
-      <c r="A1104" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1104" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1104" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D1104" s="2" t="inlineStr">
-        <is>
-          <t>LCH04</t>
-        </is>
-      </c>
-      <c r="E1104" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="F1104" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="G1104" s="3" t="n">
-        <v>46341.41666666666</v>
-      </c>
-      <c r="H1104" s="3" t="n">
-        <v>46341.45833333334</v>
-      </c>
-      <c r="I1104" s="3" t="n">
-        <v>46342.29166666666</v>
-      </c>
-    </row>
-    <row r="1105">
-      <c r="A1105" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1105" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1105" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D1105" s="2" t="inlineStr">
-        <is>
-          <t>JKT02</t>
-        </is>
-      </c>
-      <c r="E1105" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="F1105" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="G1105" s="3" t="n">
-        <v>46345.45833333334</v>
-      </c>
-      <c r="H1105" s="3" t="n">
-        <v>46345.54166666666</v>
-      </c>
-      <c r="I1105" s="3" t="n">
-        <v>46347.20833333334</v>
-      </c>
-    </row>
-    <row r="1106">
-      <c r="A1106" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1106" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1106" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D1106" s="2" t="inlineStr">
-        <is>
-          <t>SGN03</t>
-        </is>
-      </c>
-      <c r="E1106" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="F1106" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="G1106" s="3" t="n">
-        <v>46349.66666666666</v>
-      </c>
-      <c r="H1106" s="3" t="n">
-        <v>46349.83333333334</v>
-      </c>
-      <c r="I1106" s="3" t="n">
-        <v>46350.66666666666</v>
-      </c>
-    </row>
-    <row r="1107">
-      <c r="A1107" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1107" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1107" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D1107" s="2" t="inlineStr">
-        <is>
-          <t>HKG03</t>
-        </is>
-      </c>
-      <c r="E1107" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="F1107" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="G1107" s="3" t="n">
-        <v>46353.20833333334</v>
-      </c>
-      <c r="H1107" s="3" t="n">
-        <v>46353.27083333334</v>
-      </c>
-      <c r="I1107" s="3" t="n">
-        <v>46353.77083333334</v>
-      </c>
-    </row>
-    <row r="1108">
-      <c r="A1108" s="2" t="inlineStr">
-        <is>
-          <t>YEOSU VOYAGER</t>
-        </is>
-      </c>
-      <c r="B1108" s="2" t="inlineStr">
-        <is>
-          <t>ANX</t>
-        </is>
-      </c>
-      <c r="C1108" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D1108" s="2" t="inlineStr">
-        <is>
-          <t>SHE04</t>
-        </is>
-      </c>
-      <c r="E1108" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="F1108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="G1108" s="3" t="n">
-        <v>46354</v>
-      </c>
-      <c r="H1108" s="3" t="n">
-        <v>46354.04166666666</v>
-      </c>
-      <c r="I1108" s="3" t="n">
         <v>46354.54166666666</v>
       </c>
     </row>
@@ -47856,7 +46810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -47897,7 +46851,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260930-0637-SKED.xlsx)</t>
+          <t>New ETA (auto-20260930-1337-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47914,788 +46868,788 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0152S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46296.02083333334</v>
+        <v>46295.5</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46296.14583333334</v>
+        <v>46295.25</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0152S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46296.77083333334</v>
+        <v>46296.125</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46296.85416666666</v>
+        <v>46295.95833333334</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0152S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46305.27083333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46305.04166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-5.5</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46305.79166666666</v>
+        <v>46300.25</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46305.54166666666</v>
+        <v>46301.70833333334</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-6</v>
+        <v>35</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46307.08333333334</v>
+        <v>46301.41666666666</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46306.83333333334</v>
+        <v>46302.875</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-6</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46309.4375</v>
+        <v>46305.25</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46309.1875</v>
+        <v>46306.79166666666</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-6</v>
+        <v>37</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0153S</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46315.5</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46315.25</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-6</v>
+        <v>38</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0153S</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46316.375</v>
+        <v>46311.125</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46316.125</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-6</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0153S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46317.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46317.33333333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-6</v>
+        <v>41</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0153S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46318.33333333334</v>
+        <v>46313.16666666666</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46318.08333333334</v>
+        <v>46314.875</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-6</v>
+        <v>41</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0153S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46323.875</v>
+        <v>46317.95833333334</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46323.625</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-6</v>
+        <v>41</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0153S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46326.27083333334</v>
+        <v>46318.58333333334</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46326.02083333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-6</v>
+        <v>41</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0153N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46326.79166666666</v>
+        <v>46322.75</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46326.54166666666</v>
+        <v>46324.45833333334</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-6</v>
+        <v>41</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0153N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46328.08333333334</v>
+        <v>46323.91666666666</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46327.83333333334</v>
+        <v>46325.625</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-6</v>
+        <v>41</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0153N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46330.4375</v>
+        <v>46327.16666666666</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46330.1875</v>
+        <v>46328.875</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-6</v>
+        <v>41</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46298.375</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46298.29166666666</v>
+        <v>46331.75</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-2</v>
+        <v>41</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46300.5625</v>
+        <v>46332.54166666666</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46300.47916666666</v>
+        <v>46334.25</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-2</v>
+        <v>41</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46308.4375</v>
+        <v>46333.25</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46308.35416666666</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-2</v>
+        <v>41</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46310.4375</v>
+        <v>46334.83333333334</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>46310.35416666666</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-2</v>
+        <v>41</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46315.02083333334</v>
+        <v>46339.08333333334</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-2</v>
+        <v>41</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46322.14583333334</v>
+        <v>46339.79166666666</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46322.0625</v>
+        <v>46341.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-2</v>
+        <v>41</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46297.20833333334</v>
+        <v>46341.41666666666</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>46297.25</v>
+        <v>46343.125</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -48706,192 +47660,192 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46299.04166666666</v>
+        <v>46342.625</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46298.91666666666</v>
+        <v>46344.33333333334</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46301.125</v>
+        <v>46343.58333333334</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>46301</v>
+        <v>46345.29166666666</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46307.41666666666</v>
+        <v>46346.79166666666</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>46307.29166666666</v>
+        <v>46348.5</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46308.66666666666</v>
+        <v>46349.66666666666</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>46308.54166666666</v>
+        <v>46351.375</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46309.33333333334</v>
+        <v>46352.16666666666</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>46309.20833333334</v>
+        <v>46353.875</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -48901,28 +47855,28 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46314.75</v>
+        <v>46352.875</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46314.625</v>
+        <v>46354.58333333334</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -48932,254 +47886,252 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46317.33333333334</v>
+        <v>46354.45833333334</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46317.20833333334</v>
+        <v>46356.16666666666</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46317.91666666666</v>
+        <v>46358.70833333334</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46317.79166666666</v>
+        <v>46360.41666666666</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46319.75</v>
+        <v>46359.41666666666</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>46319.625</v>
+        <v>46361.125</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v/>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46321.79166666666</v>
+        <v>46361.04166666666</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>46321.66666666666</v>
+        <v>46362.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-3</v>
+        <v>41</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46326.41666666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>46326.29166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46327.66666666666</v>
+        <v>46300.47916666666</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>46327.54166666666</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>46328.375</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>46328.25</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -49189,28 +48141,28 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46333.79166666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>46333.66666666666</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -49220,94 +48172,94 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>46336.375</v>
+        <v>46314.9375</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>46336.25</v>
+        <v>46315.1875</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>46336.95833333334</v>
+        <v>46322.0625</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>46336.83333333334</v>
+        <v>46322.3125</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>KMTC JAKARTA</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>46338.79166666666</v>
+        <v>46258.75</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>46338.66666666666</v>
+        <v>46258.54166666666</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -49318,608 +48270,286 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>46340.83333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>46340.70833333334</v>
+        <v>46305.33333333334</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-3</v>
+        <v>24</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2604E</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>46345.08333333334</v>
+        <v>46306.75</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>46344.95833333334</v>
+        <v>46308.75</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-3</v>
+        <v>48</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46346.33333333334</v>
+        <v>46307.91666666666</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>46346.20833333334</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-3</v>
+        <v>48</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46347.04166666666</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>46346.91666666666</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-3</v>
+        <v>48</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNNGB</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46352.45833333334</v>
+        <v>46314.25</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>46352.33333333334</v>
+        <v>46317.25</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-3</v>
+        <v>72</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>AEKLF</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2614S</t>
+          <t>2607W</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46355.04166666666</v>
+        <v>46319</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>46354.91666666666</v>
+        <v>46322</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-3</v>
+        <v>72</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>AEKLF</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>46355.625</v>
+        <v>46335.125</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>46355.5</v>
+        <v>46338.125</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-3</v>
+        <v>72</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KMTC BANGKOK</t>
+          <t>MELBOURNE BRIDGE</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v/>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2607E</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46357.45833333334</v>
+        <v>46361.41666666666</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>46357.33333333334</v>
+        <v>46364.41666666666</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>-3</v>
+        <v>72</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>46359.5</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>46359.375</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>KMTC JAKARTA</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>46258.75</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>46258.54166666666</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>46306.20833333334</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>46304.33333333334</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>-45</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>46309.95833333334</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>46307.91666666666</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>-49</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>CNNGB</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>46312.95833333334</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>46310.91666666666</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>-49</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>CNNGB</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>46316.29166666666</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>46314.25</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>-49</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>AEKLF</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>46321.04166666666</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>46319</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>-49</v>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>AEKLF</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2607E</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>46337.16666666666</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>46335.125</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>-49</v>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2607E</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>46363.45833333334</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>46361.41666666666</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>-49</v>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -551,20 +551,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>HKHKG -&gt; CNSHK</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v/>
+          <t>CNSHK (SHE04)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T23:00:00</t>
+          <t>Alongside, departs to TWKEL ~2026-10-02T02:30:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -816,7 +818,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T06:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T08:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -827,7 +829,7 @@
         <v/>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46315.1875</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -1295,22 +1297,20 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>KRUSN (USN03)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
+          <t>KRUSN -&gt; CNSHA</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v/>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNSHA ~2026-09-30T23:00:00</t>
+          <t>In transit, ETA 2026-10-02T01:00:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
@@ -1591,20 +1591,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T23:00:00</t>
+          <t>Alongside, departs to KRINC ~2026-10-02T02:00:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1719,20 +1721,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>KRINC -&gt; KRPTK</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v/>
+          <t>KRPTK (PTK02)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2616S</t>
+        </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-09-30T22:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-02T15:00:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
@@ -8469,10 +8473,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>46296.5</v>
+        <v>46296.58333333334</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>46298.25</v>
+        <v>46298.33333333334</v>
       </c>
     </row>
     <row r="149">
@@ -8507,13 +8511,13 @@
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>46298.54166666666</v>
+        <v>46298.625</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>46298.60416666666</v>
+        <v>46298.6875</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>46299.22916666666</v>
+        <v>46299.3125</v>
       </c>
     </row>
     <row r="150">
@@ -8548,13 +8552,13 @@
         </is>
       </c>
       <c r="G150" s="3" t="n">
-        <v>46300.72916666666</v>
+        <v>46300.8125</v>
       </c>
       <c r="H150" s="3" t="n">
-        <v>46300.9375</v>
+        <v>46301.02083333334</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>46301.60416666666</v>
+        <v>46301.6875</v>
       </c>
     </row>
     <row r="151">
@@ -8589,13 +8593,13 @@
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>46308.60416666666</v>
+        <v>46308.6875</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>46308.6875</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>46309.52083333334</v>
+        <v>46309.60416666666</v>
       </c>
     </row>
     <row r="152">
@@ -8630,13 +8634,13 @@
         </is>
       </c>
       <c r="G152" s="3" t="n">
-        <v>46310.60416666666</v>
+        <v>46310.6875</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>46310.6875</v>
+        <v>46310.77083333334</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>46311.1875</v>
+        <v>46311.27083333334</v>
       </c>
     </row>
     <row r="153">
@@ -8671,13 +8675,13 @@
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>46315.1875</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>46315.22916666666</v>
+        <v>46315.3125</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>46315.89583333334</v>
+        <v>46315.97916666666</v>
       </c>
     </row>
     <row r="154">
@@ -8712,13 +8716,13 @@
         </is>
       </c>
       <c r="G154" s="3" t="n">
-        <v>46322.3125</v>
+        <v>46322.39583333334</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>46322.52083333334</v>
+        <v>46322.60416666666</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>46323.1875</v>
+        <v>46323.27083333334</v>
       </c>
     </row>
     <row r="155">
@@ -46810,7 +46814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -46851,7 +46855,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260930-1337-SKED.xlsx)</t>
+          <t>New ETA (auto-20260930-1910-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -46868,104 +46872,104 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46295.5</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46295.25</v>
+        <v>46298.625</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46296.125</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46295.95833333334</v>
+        <v>46300.8125</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46298.08333333334</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46298.79166666666</v>
+        <v>46308.6875</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -46976,32 +46980,32 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46300.25</v>
+        <v>46310.60416666666</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46301.70833333334</v>
+        <v>46310.6875</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -47012,32 +47016,32 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46301.41666666666</v>
+        <v>46315.1875</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46302.875</v>
+        <v>46315.27083333334</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -47048,32 +47052,32 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46305.25</v>
+        <v>46322.3125</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46306.79166666666</v>
+        <v>46322.39583333334</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -47084,12 +47088,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>KMTC JAKARTA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -47099,1457 +47103,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46308.45833333334</v>
+        <v>46258.75</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46310.04166666666</v>
+        <v>46258.54166666666</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>38</v>
+        <v>-5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2615S</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46311.125</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>46312.83333333334</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>46311.58333333334</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>46313.29166666666</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>46313.16666666666</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>46314.875</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>46317.95833333334</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>46319.66666666666</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>46318.58333333334</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>46320.29166666666</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>46322.75</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>46324.45833333334</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>46323.91666666666</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>46325.625</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>46327.16666666666</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>46328.875</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>46330.04166666666</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>46331.75</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>46332.54166666666</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>46334.25</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>46333.25</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>46334.95833333334</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>46334.83333333334</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>46336.54166666666</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>46339.08333333334</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>46340.79166666666</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>46339.79166666666</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>46341.5</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>46341.41666666666</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>46343.125</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46342.625</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>46344.33333333334</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>46343.58333333334</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>46345.29166666666</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>46346.79166666666</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>46348.5</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>46349.66666666666</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>46351.375</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>46352.16666666666</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>46353.875</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>46352.875</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>46354.58333333334</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>46354.45833333334</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>46356.16666666666</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>46358.70833333334</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>46360.41666666666</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>46359.41666666666</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>46361.125</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>46361.04166666666</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>46362.75</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>46298.29166666666</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>46298.54166666666</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>46300.47916666666</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>46300.72916666666</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>46308.35416666666</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>46308.60416666666</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>46310.35416666666</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>46310.60416666666</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>46314.9375</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>46315.1875</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>46322.0625</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>46322.3125</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>KMTC JAKARTA</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46258.75</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>46258.54166666666</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
           <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2604E</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46304.33333333334</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>46305.33333333334</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2604E</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>46306.75</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>46308.75</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>46307.91666666666</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>46309.91666666666</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>CNNGB</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>46310.91666666666</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>46312.91666666666</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>CNNGB</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>46314.25</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>46317.25</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>AEKLF</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>46319</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>AEKLF</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2607E</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>46335.125</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>46338.125</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2607E</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>46361.41666666666</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>46364.41666666666</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -617,20 +617,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>KRPTK -&gt; KRKAN</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v/>
+          <t>KRKAN (KAN04)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>0152S</t>
+        </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-01T03:30:00</t>
+          <t>Alongside, departs to KRPUS ~2026-10-01T14:00:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -1657,20 +1659,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>KRUSN -&gt; HKHKG</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v/>
+          <t>HKHKG (HKG03)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-01T05:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-10-01T22:00:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -46814,10 +46818,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -46855,7 +46859,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20260930-1910-SKED.xlsx)</t>
+          <t>New ETA (auto-20260930-2258-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -46872,250 +46876,34 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>KMTC JAKARTA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46298.54166666666</v>
+        <v>46258.75</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46298.625</v>
+        <v>46258.54166666666</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46300.72916666666</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46300.8125</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46308.60416666666</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46308.6875</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>46310.60416666666</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46310.6875</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46315.1875</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>46315.27083333334</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46322.3125</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>46322.39583333334</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>KMTC JAKARTA</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>46258.75</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>46258.54166666666</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Early</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2295,22 +2295,20 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
+          <t>VNSGN -&gt; HKHKG</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v/>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to HKHKG ~2026-10-01T07:30:00</t>
+          <t>In transit, ETA 2026-10-03T16:00:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
@@ -46825,7 +46823,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -46854,7 +46852,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (prev)</t>
+          <t>Old ETA (auto-20260930-1910-SKED.xlsx)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1357,22 +1357,20 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUS05)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2605W</t>
-        </is>
+          <t>KRPUS -&gt; KRKAN</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v/>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-01T08:00:00</t>
+          <t>In transit, ETA 2026-10-01T15:00:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="n"/>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47885,7 +47885,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47914,7 +47914,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (prev)</t>
+          <t>Old ETA (auto-20260930-2258-SKED.xlsx)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,11 +566,11 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to TWKEL ~2026-10-02T02:30:00</t>
+          <t>Alongside, departs to TWKEL ~2026-10-02T06:30:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>46313.29166666666</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>46312.83333333334</v>
+        <v>46313</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -617,22 +617,20 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>KRKAN (KAN04)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>0152S</t>
-        </is>
+          <t>KRKAN -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v/>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-10-01T14:00:00</t>
+          <t>In transit, ETA 2026-10-01T20:30:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -820,7 +818,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-02T23:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T00:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -831,7 +829,7 @@
         <v/>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46314.89583333334</v>
+        <v>46314.9375</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -878,7 +876,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T02:00:00</t>
+          <t>In transit, ETA 2026-10-03T04:00:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -1111,20 +1109,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; IDJKT</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v/>
+          <t>IDJKT (JKT02)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-01T09:30:00</t>
+          <t>Alongside, departs to VNSGN ~2026-10-03T01:00:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="n"/>
@@ -1357,20 +1357,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>KRPUS -&gt; KRKAN</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v/>
+          <t>KRKAN (KAN04)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-01T15:00:00</t>
+          <t>Alongside, departs to CNNGB ~2026-10-02T04:00:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="n"/>
@@ -1493,7 +1495,7 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>46306.79166666666</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1738,11 +1740,11 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-02T15:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-02T21:00:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>46308.5625</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1755,7 +1757,7 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.1875</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -1853,24 +1855,26 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUS05)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T13:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46307.45833333334</v>
+        <v>46308.875</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1887,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46307.08333333334</v>
+        <v>46308.5</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2122,7 +2126,7 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46305.91666666666</v>
+        <v>46306.14583333334</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2135,7 +2139,7 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>46305.45833333334</v>
+        <v>46305.6875</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
@@ -2182,7 +2186,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-02T01:00:00</t>
+          <t>In transit, ETA 2026-10-02T08:00:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
@@ -2193,7 +2197,7 @@
         <v/>
       </c>
       <c r="L28" s="3" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.64583333334</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2308,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T16:00:00</t>
+          <t>In transit, ETA 2026-10-03T21:00:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
@@ -2315,7 +2319,7 @@
         <v/>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46314.8125</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2828,7 @@
         <v>46296.625</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>46297.10416666666</v>
+        <v>46297.27083333334</v>
       </c>
     </row>
     <row r="11">
@@ -2859,13 +2863,13 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>46298.79166666666</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>46298.83333333334</v>
+        <v>46299</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.5</v>
       </c>
     </row>
     <row r="12">
@@ -2900,13 +2904,13 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>46301.70833333334</v>
+        <v>46301.875</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>46301.75</v>
+        <v>46301.91666666666</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46302.75</v>
+        <v>46302.91666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2941,13 +2945,13 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>46302.875</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>46302.91666666666</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46303.29166666666</v>
+        <v>46303.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2982,13 +2986,13 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>46306.79166666666</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>46306.85416666666</v>
+        <v>46307.02083333334</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>46307.27083333334</v>
+        <v>46307.4375</v>
       </c>
     </row>
     <row r="15">
@@ -3023,13 +3027,13 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>46310.04166666666</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>46310.20833333334</v>
+        <v>46310.375</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>46310.91666666666</v>
+        <v>46311.08333333334</v>
       </c>
     </row>
     <row r="16">
@@ -3064,13 +3068,13 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>46312.83333333334</v>
+        <v>46313</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>46312.875</v>
+        <v>46313.04166666666</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>46313.16666666666</v>
+        <v>46313.33333333334</v>
       </c>
     </row>
     <row r="17">
@@ -3105,13 +3109,13 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>46313.29166666666</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>46313.41666666666</v>
+        <v>46313.58333333334</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>46314.66666666666</v>
+        <v>46314.83333333334</v>
       </c>
     </row>
     <row r="18">
@@ -3146,13 +3150,13 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>46314.875</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>46314.91666666666</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>46315.375</v>
+        <v>46315.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -3187,13 +3191,13 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>46319.66666666666</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46319.72916666666</v>
+        <v>46319.89583333334</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>46320.20833333334</v>
+        <v>46320.375</v>
       </c>
     </row>
     <row r="20">
@@ -3228,13 +3232,13 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>46320.29166666666</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>46320.33333333334</v>
+        <v>46320.5</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46320.70833333334</v>
+        <v>46320.875</v>
       </c>
     </row>
     <row r="21">
@@ -3269,13 +3273,13 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>46324.45833333334</v>
+        <v>46324.625</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>46324.5</v>
+        <v>46324.66666666666</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>46325.5</v>
+        <v>46325.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3310,13 +3314,13 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>46325.625</v>
+        <v>46325.79166666666</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>46325.66666666666</v>
+        <v>46325.83333333334</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>46326.04166666666</v>
+        <v>46326.20833333334</v>
       </c>
     </row>
     <row r="23">
@@ -3351,13 +3355,13 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>46328.875</v>
+        <v>46329.04166666666</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>46328.91666666666</v>
+        <v>46329.08333333334</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46329.29166666666</v>
+        <v>46329.45833333334</v>
       </c>
     </row>
     <row r="24">
@@ -3392,13 +3396,13 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>46331.75</v>
+        <v>46331.91666666666</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>46331.91666666666</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>46332.45833333334</v>
+        <v>46332.625</v>
       </c>
     </row>
     <row r="25">
@@ -3433,13 +3437,13 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>46334.25</v>
+        <v>46334.41666666666</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>46334.29166666666</v>
+        <v>46334.45833333334</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>46334.54166666666</v>
+        <v>46334.70833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3474,13 +3478,13 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>46334.95833333334</v>
+        <v>46335.125</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>46335.08333333334</v>
+        <v>46335.25</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46336.20833333334</v>
+        <v>46336.375</v>
       </c>
     </row>
     <row r="27">
@@ -3515,13 +3519,13 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>46336.54166666666</v>
+        <v>46336.70833333334</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>46336.58333333334</v>
+        <v>46336.75</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46336.91666666666</v>
+        <v>46337.08333333334</v>
       </c>
     </row>
     <row r="28">
@@ -3556,13 +3560,13 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>46340.79166666666</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>46340.83333333334</v>
+        <v>46341</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46341.25</v>
+        <v>46341.41666666666</v>
       </c>
     </row>
     <row r="29">
@@ -3597,13 +3601,13 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>46341.5</v>
+        <v>46341.66666666666</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>46341.5</v>
+        <v>46341.66666666666</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>46341.875</v>
+        <v>46342.04166666666</v>
       </c>
     </row>
     <row r="30">
@@ -3638,13 +3642,13 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>46343.125</v>
+        <v>46343.29166666666</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>46343.125</v>
+        <v>46343.29166666666</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46343.375</v>
+        <v>46343.54166666666</v>
       </c>
     </row>
     <row r="31">
@@ -3679,13 +3683,13 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>46344.33333333334</v>
+        <v>46344.5</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>46344.375</v>
+        <v>46344.54166666666</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>46345.08333333334</v>
+        <v>46345.25</v>
       </c>
     </row>
     <row r="32">
@@ -3720,13 +3724,13 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>46345.29166666666</v>
+        <v>46345.45833333334</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>46345.33333333334</v>
+        <v>46345.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>46345.66666666666</v>
+        <v>46345.83333333334</v>
       </c>
     </row>
     <row r="33">
@@ -3761,13 +3765,13 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>46348.5</v>
+        <v>46348.66666666666</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>46348.54166666666</v>
+        <v>46348.70833333334</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>46348.91666666666</v>
+        <v>46349.08333333334</v>
       </c>
     </row>
     <row r="34">
@@ -3802,13 +3806,13 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>46351.375</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>46351.54166666666</v>
+        <v>46351.70833333334</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>46352.08333333334</v>
+        <v>46352.25</v>
       </c>
     </row>
     <row r="35">
@@ -3843,13 +3847,13 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>46353.875</v>
+        <v>46354.04166666666</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>46353.91666666666</v>
+        <v>46354.08333333334</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>46354.16666666666</v>
+        <v>46354.33333333334</v>
       </c>
     </row>
     <row r="36">
@@ -3884,13 +3888,13 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>46354.58333333334</v>
+        <v>46354.75</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>46354.70833333334</v>
+        <v>46354.875</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>46355.83333333334</v>
+        <v>46356</v>
       </c>
     </row>
     <row r="37">
@@ -3925,13 +3929,13 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>46356.16666666666</v>
+        <v>46356.33333333334</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46356.20833333334</v>
+        <v>46356.375</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>46356.54166666666</v>
+        <v>46356.70833333334</v>
       </c>
     </row>
     <row r="38">
@@ -3966,13 +3970,13 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>46360.41666666666</v>
+        <v>46360.58333333334</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>46360.45833333334</v>
+        <v>46360.625</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>46360.875</v>
+        <v>46361.04166666666</v>
       </c>
     </row>
     <row r="39">
@@ -4007,13 +4011,13 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>46361.125</v>
+        <v>46361.29166666666</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>46361.125</v>
+        <v>46361.29166666666</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>46361.5</v>
+        <v>46361.66666666666</v>
       </c>
     </row>
     <row r="40">
@@ -4048,13 +4052,13 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>46362.75</v>
+        <v>46362.91666666666</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>46362.75</v>
+        <v>46362.91666666666</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>46363</v>
+        <v>46363.16666666666</v>
       </c>
     </row>
     <row r="41">
@@ -4089,13 +4093,13 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>46365.33333333334</v>
+        <v>46365.5</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>46365.375</v>
+        <v>46365.54166666666</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>46366.08333333334</v>
+        <v>46366.25</v>
       </c>
     </row>
     <row r="42">
@@ -4130,13 +4134,13 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>46366.29166666666</v>
+        <v>46366.45833333334</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>46366.33333333334</v>
+        <v>46366.5</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>46366.66666666666</v>
+        <v>46366.83333333334</v>
       </c>
     </row>
     <row r="43">
@@ -4171,13 +4175,13 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>46369.5</v>
+        <v>46369.66666666666</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>46369.54166666666</v>
+        <v>46369.70833333334</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46369.91666666666</v>
+        <v>46370.08333333334</v>
       </c>
     </row>
     <row r="44">
@@ -4212,13 +4216,13 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>46372.375</v>
+        <v>46372.54166666666</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>46372.54166666666</v>
+        <v>46372.70833333334</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46373.08333333334</v>
+        <v>46373.25</v>
       </c>
     </row>
     <row r="45">
@@ -4253,13 +4257,13 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>46374.875</v>
+        <v>46375.04166666666</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>46374.91666666666</v>
+        <v>46375.08333333334</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>46375.16666666666</v>
+        <v>46375.33333333334</v>
       </c>
     </row>
     <row r="46">
@@ -4294,13 +4298,13 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>46375.58333333334</v>
+        <v>46375.75</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>46375.70833333334</v>
+        <v>46375.875</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>46376.83333333334</v>
+        <v>46377</v>
       </c>
     </row>
     <row r="47">
@@ -4335,13 +4339,13 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>46377.16666666666</v>
+        <v>46377.33333333334</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46377.20833333334</v>
+        <v>46377.375</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>46377.54166666666</v>
+        <v>46377.70833333334</v>
       </c>
     </row>
     <row r="48">
@@ -4376,13 +4380,13 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>46381.41666666666</v>
+        <v>46381.58333333334</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>46381.45833333334</v>
+        <v>46381.625</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>46381.875</v>
+        <v>46382.04166666666</v>
       </c>
     </row>
     <row r="49">
@@ -4417,13 +4421,13 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>46382.125</v>
+        <v>46382.29166666666</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>46382.125</v>
+        <v>46382.29166666666</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46382.5</v>
+        <v>46382.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -4458,13 +4462,13 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>46383.75</v>
+        <v>46383.91666666666</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>46383.75</v>
+        <v>46383.91666666666</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>46384</v>
+        <v>46384.16666666666</v>
       </c>
     </row>
     <row r="51">
@@ -4499,13 +4503,13 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>46386.33333333334</v>
+        <v>46386.5</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>46386.375</v>
+        <v>46386.54166666666</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>46387.08333333334</v>
+        <v>46387.25</v>
       </c>
     </row>
     <row r="52">
@@ -4540,13 +4544,13 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>46387.29166666666</v>
+        <v>46387.45833333334</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>46387.33333333334</v>
+        <v>46387.5</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>46387.66666666666</v>
+        <v>46387.83333333334</v>
       </c>
     </row>
     <row r="53">
@@ -4581,13 +4585,13 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>46390.5</v>
+        <v>46390.66666666666</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>46390.54166666666</v>
+        <v>46390.70833333334</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>46390.91666666666</v>
+        <v>46391.08333333334</v>
       </c>
     </row>
     <row r="54">
@@ -4622,13 +4626,13 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>46393.375</v>
+        <v>46393.54166666666</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>46393.54166666666</v>
+        <v>46393.70833333334</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>46394.08333333334</v>
+        <v>46394.25</v>
       </c>
     </row>
     <row r="55">
@@ -4663,13 +4667,13 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>46395.875</v>
+        <v>46396.04166666666</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>46395.91666666666</v>
+        <v>46396.08333333334</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>46396.16666666666</v>
+        <v>46396.33333333334</v>
       </c>
     </row>
     <row r="56">
@@ -4704,13 +4708,13 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>46396.58333333334</v>
+        <v>46396.75</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>46396.70833333334</v>
+        <v>46396.875</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>46397.83333333334</v>
+        <v>46398</v>
       </c>
     </row>
     <row r="57">
@@ -4745,13 +4749,13 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>46398.16666666666</v>
+        <v>46398.33333333334</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>46398.20833333334</v>
+        <v>46398.375</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>46398.54166666666</v>
+        <v>46398.70833333334</v>
       </c>
     </row>
     <row r="58">
@@ -4786,13 +4790,13 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>46402.41666666666</v>
+        <v>46402.58333333334</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>46402.45833333334</v>
+        <v>46402.625</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>46402.875</v>
+        <v>46403.04166666666</v>
       </c>
     </row>
     <row r="59">
@@ -4827,13 +4831,13 @@
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>46403.125</v>
+        <v>46403.29166666666</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>46403.125</v>
+        <v>46403.29166666666</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>46403.5</v>
+        <v>46403.66666666666</v>
       </c>
     </row>
     <row r="60">
@@ -4866,13 +4870,13 @@
         <v/>
       </c>
       <c r="G60" s="3" t="n">
-        <v>46404.75</v>
+        <v>46404.91666666666</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>46404.75</v>
+        <v>46404.91666666666</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>46405</v>
+        <v>46405.16666666666</v>
       </c>
     </row>
     <row r="61">
@@ -9209,10 +9213,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>46296.125</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="I166" s="3" t="n">
-        <v>46297.79166666666</v>
+        <v>46297.91666666666</v>
       </c>
     </row>
     <row r="167">
@@ -9250,10 +9254,10 @@
         <v>46294.91666666666</v>
       </c>
       <c r="H167" s="3" t="n">
-        <v>46296.625</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>46297.95833333334</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="168">
@@ -9288,13 +9292,13 @@
         </is>
       </c>
       <c r="G168" s="3" t="n">
-        <v>46298.25</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>46298.3125</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>46298.9375</v>
+        <v>46298.97916666666</v>
       </c>
     </row>
     <row r="169">
@@ -9329,13 +9333,13 @@
         </is>
       </c>
       <c r="G169" s="3" t="n">
-        <v>46300.4375</v>
+        <v>46300.47916666666</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>46300.64583333334</v>
+        <v>46300.6875</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>46301.3125</v>
+        <v>46301.35416666666</v>
       </c>
     </row>
     <row r="170">
@@ -9370,13 +9374,13 @@
         </is>
       </c>
       <c r="G170" s="3" t="n">
-        <v>46308.3125</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>46308.39583333334</v>
+        <v>46308.4375</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>46309.22916666666</v>
+        <v>46309.27083333334</v>
       </c>
     </row>
     <row r="171">
@@ -9411,13 +9415,13 @@
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>46310.3125</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>46310.39583333334</v>
+        <v>46310.4375</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>46310.89583333334</v>
+        <v>46310.9375</v>
       </c>
     </row>
     <row r="172">
@@ -9452,13 +9456,13 @@
         </is>
       </c>
       <c r="G172" s="3" t="n">
-        <v>46314.89583333334</v>
+        <v>46314.9375</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46314.97916666666</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>46315.60416666666</v>
+        <v>46315.64583333334</v>
       </c>
     </row>
     <row r="173">
@@ -9493,13 +9497,13 @@
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>46322.02083333334</v>
+        <v>46322.0625</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>46322.22916666666</v>
+        <v>46322.27083333334</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>46322.89583333334</v>
+        <v>46322.9375</v>
       </c>
     </row>
     <row r="174">
@@ -10399,7 +10403,7 @@
         <v>46295</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>46295.54166666666</v>
+        <v>46295.75</v>
       </c>
     </row>
     <row r="196">
@@ -10434,13 +10438,13 @@
         </is>
       </c>
       <c r="G196" s="3" t="n">
-        <v>46298.08333333334</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>46298.14583333334</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>46298.64583333334</v>
+        <v>46298.72916666666</v>
       </c>
     </row>
     <row r="197">
@@ -10475,13 +10479,13 @@
         </is>
       </c>
       <c r="G197" s="3" t="n">
-        <v>46298.875</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>46298.91666666666</v>
+        <v>46299</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.5</v>
       </c>
     </row>
     <row r="198">
@@ -10516,13 +10520,13 @@
         </is>
       </c>
       <c r="G198" s="3" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.79166666666</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>46302.75</v>
+        <v>46302.83333333334</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.5</v>
       </c>
     </row>
     <row r="199">
@@ -10557,13 +10561,13 @@
         </is>
       </c>
       <c r="G199" s="3" t="n">
-        <v>46304.5</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>46304.54166666666</v>
+        <v>46304.625</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>46305.125</v>
+        <v>46305.20833333334</v>
       </c>
     </row>
     <row r="200">
@@ -20180,10 +20184,10 @@
         </is>
       </c>
       <c r="G434" s="3" t="n">
+        <v>46297.95833333334</v>
+      </c>
+      <c r="H434" s="3" t="n">
         <v>46298</v>
-      </c>
-      <c r="H434" s="3" t="n">
-        <v>46298.04166666666</v>
       </c>
       <c r="I434" s="3" t="n">
         <v>46298.625</v>
@@ -24354,13 +24358,13 @@
         </is>
       </c>
       <c r="G536" s="3" t="n">
-        <v>46296.83333333334</v>
+        <v>46296.8125</v>
       </c>
       <c r="H536" s="3" t="n">
-        <v>46296.875</v>
+        <v>46296.85416666666</v>
       </c>
       <c r="I536" s="3" t="n">
-        <v>46297.5</v>
+        <v>46297.29166666666</v>
       </c>
     </row>
     <row r="537">
@@ -24395,13 +24399,13 @@
         </is>
       </c>
       <c r="G537" s="3" t="n">
-        <v>46298.58333333334</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="H537" s="3" t="n">
-        <v>46298.625</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="I537" s="3" t="n">
-        <v>46299.25</v>
+        <v>46299.45833333334</v>
       </c>
     </row>
     <row r="538">
@@ -24436,13 +24440,13 @@
         </is>
       </c>
       <c r="G538" s="3" t="n">
-        <v>46304.5</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="H538" s="3" t="n">
-        <v>46304.66666666666</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="I538" s="3" t="n">
-        <v>46305.08333333334</v>
+        <v>46305.33333333334</v>
       </c>
     </row>
     <row r="539">
@@ -24477,13 +24481,13 @@
         </is>
       </c>
       <c r="G539" s="3" t="n">
-        <v>46306.79166666666</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="H539" s="3" t="n">
-        <v>46306.83333333334</v>
+        <v>46307</v>
       </c>
       <c r="I539" s="3" t="n">
-        <v>46307.25</v>
+        <v>46307.66666666666</v>
       </c>
     </row>
     <row r="540">
@@ -24518,13 +24522,13 @@
         </is>
       </c>
       <c r="G540" s="3" t="n">
-        <v>46308.875</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="H540" s="3" t="n">
-        <v>46309</v>
+        <v>46309.375</v>
       </c>
       <c r="I540" s="3" t="n">
-        <v>46309.58333333334</v>
+        <v>46309.95833333334</v>
       </c>
     </row>
     <row r="541">
@@ -31360,10 +31364,10 @@
         <v>46295.91666666666</v>
       </c>
       <c r="H707" s="3" t="n">
-        <v>46296.95833333334</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="I707" s="3" t="n">
-        <v>46297.625</v>
+        <v>46297.875</v>
       </c>
     </row>
     <row r="708">
@@ -31398,13 +31402,13 @@
         </is>
       </c>
       <c r="G708" s="3" t="n">
-        <v>46298.66666666666</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="H708" s="3" t="n">
-        <v>46298.72916666666</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="I708" s="3" t="n">
-        <v>46299.14583333334</v>
+        <v>46299.3125</v>
       </c>
     </row>
     <row r="709">
@@ -31439,13 +31443,13 @@
         </is>
       </c>
       <c r="G709" s="3" t="n">
-        <v>46299.45833333334</v>
+        <v>46299.625</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>46299.5</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="I709" s="3" t="n">
-        <v>46300.10416666666</v>
+        <v>46300.25</v>
       </c>
     </row>
     <row r="710">
@@ -31480,13 +31484,13 @@
         </is>
       </c>
       <c r="G710" s="3" t="n">
-        <v>46305.52083333334</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="H710" s="3" t="n">
-        <v>46305.6875</v>
+        <v>46305.83333333334</v>
       </c>
       <c r="I710" s="3" t="n">
-        <v>46306.27083333334</v>
+        <v>46306.41666666666</v>
       </c>
     </row>
     <row r="711">
@@ -31521,13 +31525,13 @@
         </is>
       </c>
       <c r="G711" s="3" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.1875</v>
       </c>
       <c r="H711" s="3" t="n">
-        <v>46308.08333333334</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="I711" s="3" t="n">
-        <v>46308.4375</v>
+        <v>46308.58333333334</v>
       </c>
     </row>
     <row r="712">
@@ -31562,13 +31566,13 @@
         </is>
       </c>
       <c r="G712" s="3" t="n">
-        <v>46308.5625</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="H712" s="3" t="n">
-        <v>46308.64583333334</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="I712" s="3" t="n">
-        <v>46309.64583333334</v>
+        <v>46309.79166666666</v>
       </c>
     </row>
     <row r="713">
@@ -31603,13 +31607,13 @@
         </is>
       </c>
       <c r="G713" s="3" t="n">
-        <v>46309.85416666666</v>
+        <v>46310</v>
       </c>
       <c r="H713" s="3" t="n">
-        <v>46309.89583333334</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="I713" s="3" t="n">
-        <v>46310.39583333334</v>
+        <v>46310.54166666666</v>
       </c>
     </row>
     <row r="714">
@@ -31644,13 +31648,13 @@
         </is>
       </c>
       <c r="G714" s="3" t="n">
-        <v>46312.20833333334</v>
+        <v>46312.35416666666</v>
       </c>
       <c r="H714" s="3" t="n">
-        <v>46312.375</v>
+        <v>46312.52083333334</v>
       </c>
       <c r="I714" s="3" t="n">
-        <v>46313.0625</v>
+        <v>46313.20833333334</v>
       </c>
     </row>
     <row r="715">
@@ -31685,13 +31689,13 @@
         </is>
       </c>
       <c r="G715" s="3" t="n">
-        <v>46319.04166666666</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="H715" s="3" t="n">
-        <v>46319.08333333334</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="I715" s="3" t="n">
-        <v>46319.75</v>
+        <v>46321.5</v>
       </c>
     </row>
     <row r="716">
@@ -31726,13 +31730,13 @@
         </is>
       </c>
       <c r="G716" s="3" t="n">
-        <v>46319.91666666666</v>
+        <v>46321.66666666666</v>
       </c>
       <c r="H716" s="3" t="n">
-        <v>46319.97916666666</v>
+        <v>46321.72916666666</v>
       </c>
       <c r="I716" s="3" t="n">
-        <v>46320.22916666666</v>
+        <v>46321.97916666666</v>
       </c>
     </row>
     <row r="717">
@@ -31767,13 +31771,13 @@
         </is>
       </c>
       <c r="G717" s="3" t="n">
-        <v>46321.125</v>
+        <v>46322.875</v>
       </c>
       <c r="H717" s="3" t="n">
-        <v>46321.1875</v>
+        <v>46322.9375</v>
       </c>
       <c r="I717" s="3" t="n">
-        <v>46321.60416666666</v>
+        <v>46323.35416666666</v>
       </c>
     </row>
     <row r="718">
@@ -31808,13 +31812,13 @@
         </is>
       </c>
       <c r="G718" s="3" t="n">
-        <v>46321.875</v>
+        <v>46323.625</v>
       </c>
       <c r="H718" s="3" t="n">
-        <v>46321.89583333334</v>
+        <v>46323.64583333334</v>
       </c>
       <c r="I718" s="3" t="n">
-        <v>46322.5</v>
+        <v>46324.25</v>
       </c>
     </row>
     <row r="719">
@@ -31849,13 +31853,13 @@
         </is>
       </c>
       <c r="G719" s="3" t="n">
-        <v>46327.33333333334</v>
+        <v>46329.16666666666</v>
       </c>
       <c r="H719" s="3" t="n">
-        <v>46327.5</v>
+        <v>46329.33333333334</v>
       </c>
       <c r="I719" s="3" t="n">
-        <v>46328.08333333334</v>
+        <v>46329.91666666666</v>
       </c>
     </row>
     <row r="720">
@@ -31890,13 +31894,13 @@
         </is>
       </c>
       <c r="G720" s="3" t="n">
-        <v>46329.6875</v>
+        <v>46331.5625</v>
       </c>
       <c r="H720" s="3" t="n">
-        <v>46329.72916666666</v>
+        <v>46331.60416666666</v>
       </c>
       <c r="I720" s="3" t="n">
-        <v>46330.08333333334</v>
+        <v>46331.95833333334</v>
       </c>
     </row>
     <row r="721">
@@ -31931,13 +31935,13 @@
         </is>
       </c>
       <c r="G721" s="3" t="n">
-        <v>46330.20833333334</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="H721" s="3" t="n">
-        <v>46330.29166666666</v>
+        <v>46332.16666666666</v>
       </c>
       <c r="I721" s="3" t="n">
-        <v>46331.29166666666</v>
+        <v>46333.16666666666</v>
       </c>
     </row>
     <row r="722">
@@ -31972,13 +31976,13 @@
         </is>
       </c>
       <c r="G722" s="3" t="n">
-        <v>46331.5</v>
+        <v>46333.375</v>
       </c>
       <c r="H722" s="3" t="n">
-        <v>46331.54166666666</v>
+        <v>46333.41666666666</v>
       </c>
       <c r="I722" s="3" t="n">
-        <v>46332.04166666666</v>
+        <v>46333.91666666666</v>
       </c>
     </row>
     <row r="723">
@@ -32013,13 +32017,13 @@
         </is>
       </c>
       <c r="G723" s="3" t="n">
-        <v>46333.85416666666</v>
+        <v>46335.72916666666</v>
       </c>
       <c r="H723" s="3" t="n">
-        <v>46334.02083333334</v>
+        <v>46335.89583333334</v>
       </c>
       <c r="I723" s="3" t="n">
-        <v>46334.70833333334</v>
+        <v>46336.58333333334</v>
       </c>
     </row>
     <row r="724">
@@ -32054,13 +32058,13 @@
         </is>
       </c>
       <c r="G724" s="3" t="n">
-        <v>46339.91666666666</v>
+        <v>46341.79166666666</v>
       </c>
       <c r="H724" s="3" t="n">
-        <v>46339.95833333334</v>
+        <v>46341.83333333334</v>
       </c>
       <c r="I724" s="3" t="n">
-        <v>46340.625</v>
+        <v>46342.5</v>
       </c>
     </row>
     <row r="725">
@@ -32095,13 +32099,13 @@
         </is>
       </c>
       <c r="G725" s="3" t="n">
-        <v>46340.79166666666</v>
+        <v>46342.66666666666</v>
       </c>
       <c r="H725" s="3" t="n">
-        <v>46340.85416666666</v>
+        <v>46342.72916666666</v>
       </c>
       <c r="I725" s="3" t="n">
-        <v>46341.10416666666</v>
+        <v>46342.97916666666</v>
       </c>
     </row>
     <row r="726">
@@ -32136,13 +32140,13 @@
         </is>
       </c>
       <c r="G726" s="3" t="n">
-        <v>46342</v>
+        <v>46343.875</v>
       </c>
       <c r="H726" s="3" t="n">
-        <v>46342.0625</v>
+        <v>46343.9375</v>
       </c>
       <c r="I726" s="3" t="n">
-        <v>46342.47916666666</v>
+        <v>46344.35416666666</v>
       </c>
     </row>
     <row r="727">
@@ -32177,13 +32181,13 @@
         </is>
       </c>
       <c r="G727" s="3" t="n">
-        <v>46342.75</v>
+        <v>46344.625</v>
       </c>
       <c r="H727" s="3" t="n">
-        <v>46342.77083333334</v>
+        <v>46344.64583333334</v>
       </c>
       <c r="I727" s="3" t="n">
-        <v>46343.375</v>
+        <v>46345.25</v>
       </c>
     </row>
     <row r="728">
@@ -32218,13 +32222,13 @@
         </is>
       </c>
       <c r="G728" s="3" t="n">
-        <v>46348.20833333334</v>
+        <v>46350.16666666666</v>
       </c>
       <c r="H728" s="3" t="n">
-        <v>46348.375</v>
+        <v>46350.33333333334</v>
       </c>
       <c r="I728" s="3" t="n">
-        <v>46348.95833333334</v>
+        <v>46350.91666666666</v>
       </c>
     </row>
     <row r="729">
@@ -32259,13 +32263,13 @@
         </is>
       </c>
       <c r="G729" s="3" t="n">
-        <v>46350.60625</v>
+        <v>46352.5625</v>
       </c>
       <c r="H729" s="3" t="n">
-        <v>46350.64791666667</v>
+        <v>46352.60416666666</v>
       </c>
       <c r="I729" s="3" t="n">
-        <v>46351.00208333333</v>
+        <v>46352.95833333334</v>
       </c>
     </row>
     <row r="730">
@@ -32300,13 +32304,13 @@
         </is>
       </c>
       <c r="G730" s="3" t="n">
-        <v>46351.12708333333</v>
+        <v>46353.08333333334</v>
       </c>
       <c r="H730" s="3" t="n">
-        <v>46351.21041666667</v>
+        <v>46353.16666666666</v>
       </c>
       <c r="I730" s="3" t="n">
-        <v>46352.21041666667</v>
+        <v>46354.16666666666</v>
       </c>
     </row>
     <row r="731">
@@ -32341,13 +32345,13 @@
         </is>
       </c>
       <c r="G731" s="3" t="n">
-        <v>46352.41875</v>
+        <v>46354.375</v>
       </c>
       <c r="H731" s="3" t="n">
-        <v>46352.46041666667</v>
+        <v>46354.41666666666</v>
       </c>
       <c r="I731" s="3" t="n">
-        <v>46352.96041666667</v>
+        <v>46354.91666666666</v>
       </c>
     </row>
     <row r="732">
@@ -32382,13 +32386,13 @@
         </is>
       </c>
       <c r="G732" s="3" t="n">
-        <v>46354.77291666667</v>
+        <v>46356.72916666666</v>
       </c>
       <c r="H732" s="3" t="n">
-        <v>46354.93958333333</v>
+        <v>46356.89583333334</v>
       </c>
       <c r="I732" s="3" t="n">
-        <v>46355.62708333333</v>
+        <v>46357.58333333334</v>
       </c>
     </row>
     <row r="733">
@@ -34424,7 +34428,7 @@
       </c>
       <c r="F782" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="G782" s="3" t="n">
@@ -34434,7 +34438,7 @@
         <v>46297.08333333334</v>
       </c>
       <c r="I782" s="3" t="n">
-        <v>46298.33333333334</v>
+        <v>46298.54166666666</v>
       </c>
     </row>
     <row r="783">
@@ -34455,27 +34459,27 @@
       </c>
       <c r="D783" s="2" t="inlineStr">
         <is>
-          <t>USN03</t>
+          <t>KAN06</t>
         </is>
       </c>
       <c r="E783" s="2" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
           <t>KRUSN</t>
         </is>
       </c>
-      <c r="F783" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
       <c r="G783" s="3" t="n">
-        <v>46298.45833333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>46298.5</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="I783" s="3" t="n">
-        <v>46298.75</v>
+        <v>46299.29166666666</v>
       </c>
     </row>
     <row r="784">
@@ -34496,12 +34500,12 @@
       </c>
       <c r="D784" s="2" t="inlineStr">
         <is>
-          <t>KAN06</t>
+          <t>USN03</t>
         </is>
       </c>
       <c r="E784" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="F784" s="2" t="inlineStr">
@@ -34510,13 +34514,13 @@
         </is>
       </c>
       <c r="G784" s="3" t="n">
-        <v>46299.25</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="I784" s="3" t="n">
-        <v>46299.66666666666</v>
+        <v>46301.08333333334</v>
       </c>
     </row>
     <row r="785">
@@ -34551,13 +34555,13 @@
         </is>
       </c>
       <c r="G785" s="3" t="n">
-        <v>46304.625</v>
+        <v>46306.04166666666</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>46304.79166666666</v>
+        <v>46306.20833333334</v>
       </c>
       <c r="I785" s="3" t="n">
-        <v>46305.41666666666</v>
+        <v>46306.83333333334</v>
       </c>
     </row>
     <row r="786">
@@ -34592,13 +34596,13 @@
         </is>
       </c>
       <c r="G786" s="3" t="n">
-        <v>46307.08333333334</v>
+        <v>46308.5</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>46307.125</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="I786" s="3" t="n">
-        <v>46307.375</v>
+        <v>46308.79166666666</v>
       </c>
     </row>
     <row r="787">
@@ -34633,13 +34637,13 @@
         </is>
       </c>
       <c r="G787" s="3" t="n">
-        <v>46307.45833333334</v>
+        <v>46308.875</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>46307.58333333334</v>
+        <v>46309</v>
       </c>
       <c r="I787" s="3" t="n">
-        <v>46309.08333333334</v>
+        <v>46310.5</v>
       </c>
     </row>
     <row r="788">
@@ -34674,13 +34678,13 @@
         </is>
       </c>
       <c r="G788" s="3" t="n">
-        <v>46309.29166666666</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>46309.33333333334</v>
+        <v>46310.75</v>
       </c>
       <c r="I788" s="3" t="n">
-        <v>46309.75</v>
+        <v>46311.16666666666</v>
       </c>
     </row>
     <row r="789">
@@ -34715,13 +34719,13 @@
         </is>
       </c>
       <c r="G789" s="3" t="n">
-        <v>46311.375</v>
+        <v>46312.79166666666</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>46311.54166666666</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="I789" s="3" t="n">
-        <v>46312.08333333334</v>
+        <v>46313.5</v>
       </c>
     </row>
     <row r="790">
@@ -34756,13 +34760,13 @@
         </is>
       </c>
       <c r="G790" s="3" t="n">
-        <v>46317.29166666666</v>
+        <v>46318.79166666666</v>
       </c>
       <c r="H790" s="3" t="n">
-        <v>46317.33333333334</v>
+        <v>46318.83333333334</v>
       </c>
       <c r="I790" s="3" t="n">
-        <v>46318.41666666666</v>
+        <v>46319.91666666666</v>
       </c>
     </row>
     <row r="791">
@@ -34797,13 +34801,13 @@
         </is>
       </c>
       <c r="G791" s="3" t="n">
-        <v>46318.54166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>46318.58333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="I791" s="3" t="n">
-        <v>46318.83333333334</v>
+        <v>46320.33333333334</v>
       </c>
     </row>
     <row r="792">
@@ -34838,13 +34842,13 @@
         </is>
       </c>
       <c r="G792" s="3" t="n">
-        <v>46319.33333333334</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="H792" s="3" t="n">
-        <v>46319.41666666666</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="I792" s="3" t="n">
-        <v>46319.75</v>
+        <v>46321.25</v>
       </c>
     </row>
     <row r="793">
@@ -34879,13 +34883,13 @@
         </is>
       </c>
       <c r="G793" s="3" t="n">
-        <v>46324.625</v>
+        <v>46326.125</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>46324.79166666666</v>
+        <v>46326.29166666666</v>
       </c>
       <c r="I793" s="3" t="n">
-        <v>46325.41666666666</v>
+        <v>46326.91666666666</v>
       </c>
     </row>
     <row r="794">
@@ -34920,13 +34924,13 @@
         </is>
       </c>
       <c r="G794" s="3" t="n">
-        <v>46327.08333333334</v>
+        <v>46328.58333333334</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>46327.125</v>
+        <v>46328.625</v>
       </c>
       <c r="I794" s="3" t="n">
-        <v>46327.375</v>
+        <v>46328.875</v>
       </c>
     </row>
     <row r="795">
@@ -34961,13 +34965,13 @@
         </is>
       </c>
       <c r="G795" s="3" t="n">
-        <v>46327.5</v>
+        <v>46329</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>46327.625</v>
+        <v>46329.125</v>
       </c>
       <c r="I795" s="3" t="n">
-        <v>46329.125</v>
+        <v>46330.625</v>
       </c>
     </row>
     <row r="796">
@@ -35002,13 +35006,13 @@
         </is>
       </c>
       <c r="G796" s="3" t="n">
-        <v>46329.33333333334</v>
+        <v>46330.83333333334</v>
       </c>
       <c r="H796" s="3" t="n">
-        <v>46329.375</v>
+        <v>46330.875</v>
       </c>
       <c r="I796" s="3" t="n">
-        <v>46329.79166666666</v>
+        <v>46331.29166666666</v>
       </c>
     </row>
     <row r="797">
@@ -35043,13 +35047,13 @@
         </is>
       </c>
       <c r="G797" s="3" t="n">
-        <v>46331.33333333334</v>
+        <v>46332.83333333334</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>46331.5</v>
+        <v>46333</v>
       </c>
       <c r="I797" s="3" t="n">
-        <v>46332.04166666666</v>
+        <v>46333.54166666666</v>
       </c>
     </row>
     <row r="798">
@@ -35084,13 +35088,13 @@
         </is>
       </c>
       <c r="G798" s="3" t="n">
-        <v>46337.41666666666</v>
+        <v>46338.91666666666</v>
       </c>
       <c r="H798" s="3" t="n">
-        <v>46337.45833333334</v>
+        <v>46338.95833333334</v>
       </c>
       <c r="I798" s="3" t="n">
-        <v>46338.54166666666</v>
+        <v>46340.04166666666</v>
       </c>
     </row>
     <row r="799">
@@ -35125,13 +35129,13 @@
         </is>
       </c>
       <c r="G799" s="3" t="n">
-        <v>46338.70833333334</v>
+        <v>46340.20833333334</v>
       </c>
       <c r="H799" s="3" t="n">
-        <v>46338.75</v>
+        <v>46340.25</v>
       </c>
       <c r="I799" s="3" t="n">
-        <v>46339</v>
+        <v>46340.5</v>
       </c>
     </row>
     <row r="800">
@@ -35166,13 +35170,13 @@
         </is>
       </c>
       <c r="G800" s="3" t="n">
-        <v>46339.45833333334</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>46339.54166666666</v>
+        <v>46341.04166666666</v>
       </c>
       <c r="I800" s="3" t="n">
-        <v>46339.875</v>
+        <v>46341.375</v>
       </c>
     </row>
     <row r="801">
@@ -35207,13 +35211,13 @@
         </is>
       </c>
       <c r="G801" s="3" t="n">
-        <v>46344.875</v>
+        <v>46346.375</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>46345.04166666666</v>
+        <v>46346.54166666666</v>
       </c>
       <c r="I801" s="3" t="n">
-        <v>46345.66666666666</v>
+        <v>46347.16666666666</v>
       </c>
     </row>
     <row r="802">
@@ -35248,13 +35252,13 @@
         </is>
       </c>
       <c r="G802" s="3" t="n">
-        <v>46347.45833333334</v>
+        <v>46348.95833333334</v>
       </c>
       <c r="H802" s="3" t="n">
-        <v>46347.5</v>
+        <v>46349</v>
       </c>
       <c r="I802" s="3" t="n">
-        <v>46347.75</v>
+        <v>46349.25</v>
       </c>
     </row>
     <row r="803">
@@ -35289,13 +35293,13 @@
         </is>
       </c>
       <c r="G803" s="3" t="n">
-        <v>46348.04166666666</v>
+        <v>46349.54166666666</v>
       </c>
       <c r="H803" s="3" t="n">
-        <v>46348.16666666666</v>
+        <v>46349.66666666666</v>
       </c>
       <c r="I803" s="3" t="n">
-        <v>46349.66666666666</v>
+        <v>46351.16666666666</v>
       </c>
     </row>
     <row r="804">
@@ -35330,13 +35334,13 @@
         </is>
       </c>
       <c r="G804" s="3" t="n">
-        <v>46349.875</v>
+        <v>46351.375</v>
       </c>
       <c r="H804" s="3" t="n">
-        <v>46349.91666666666</v>
+        <v>46351.41666666666</v>
       </c>
       <c r="I804" s="3" t="n">
-        <v>46350.33333333334</v>
+        <v>46351.83333333334</v>
       </c>
     </row>
     <row r="805">
@@ -35371,13 +35375,13 @@
         </is>
       </c>
       <c r="G805" s="3" t="n">
-        <v>46351.91666666666</v>
+        <v>46353.41666666666</v>
       </c>
       <c r="H805" s="3" t="n">
-        <v>46352.08333333334</v>
+        <v>46353.58333333334</v>
       </c>
       <c r="I805" s="3" t="n">
-        <v>46352.625</v>
+        <v>46354.125</v>
       </c>
     </row>
     <row r="806">
@@ -35412,13 +35416,13 @@
         </is>
       </c>
       <c r="G806" s="3" t="n">
-        <v>46358.33333333334</v>
+        <v>46359.83333333334</v>
       </c>
       <c r="H806" s="3" t="n">
-        <v>46358.375</v>
+        <v>46359.875</v>
       </c>
       <c r="I806" s="3" t="n">
-        <v>46359.45833333334</v>
+        <v>46360.95833333334</v>
       </c>
     </row>
     <row r="807">
@@ -35453,13 +35457,13 @@
         </is>
       </c>
       <c r="G807" s="3" t="n">
-        <v>46359.58333333334</v>
+        <v>46361.08333333334</v>
       </c>
       <c r="H807" s="3" t="n">
-        <v>46359.625</v>
+        <v>46361.125</v>
       </c>
       <c r="I807" s="3" t="n">
-        <v>46359.875</v>
+        <v>46361.375</v>
       </c>
     </row>
     <row r="808">
@@ -35494,13 +35498,13 @@
         </is>
       </c>
       <c r="G808" s="3" t="n">
-        <v>46360.33333333334</v>
+        <v>46361.83333333334</v>
       </c>
       <c r="H808" s="3" t="n">
-        <v>46360.41666666666</v>
+        <v>46361.91666666666</v>
       </c>
       <c r="I808" s="3" t="n">
-        <v>46360.75</v>
+        <v>46362.25</v>
       </c>
     </row>
     <row r="809">
@@ -35535,13 +35539,13 @@
         </is>
       </c>
       <c r="G809" s="3" t="n">
-        <v>46365.75</v>
+        <v>46367.25</v>
       </c>
       <c r="H809" s="3" t="n">
-        <v>46365.91666666666</v>
+        <v>46367.41666666666</v>
       </c>
       <c r="I809" s="3" t="n">
-        <v>46366.54166666666</v>
+        <v>46368.04166666666</v>
       </c>
     </row>
     <row r="810">
@@ -35576,13 +35580,13 @@
         </is>
       </c>
       <c r="G810" s="3" t="n">
-        <v>46368.33333333334</v>
+        <v>46369.83333333334</v>
       </c>
       <c r="H810" s="3" t="n">
-        <v>46368.375</v>
+        <v>46369.875</v>
       </c>
       <c r="I810" s="3" t="n">
-        <v>46368.625</v>
+        <v>46370.125</v>
       </c>
     </row>
     <row r="811">
@@ -35617,13 +35621,13 @@
         </is>
       </c>
       <c r="G811" s="3" t="n">
-        <v>46368.91666666666</v>
+        <v>46370.41666666666</v>
       </c>
       <c r="H811" s="3" t="n">
-        <v>46369.04166666666</v>
+        <v>46370.54166666666</v>
       </c>
       <c r="I811" s="3" t="n">
-        <v>46370.54166666666</v>
+        <v>46372.04166666666</v>
       </c>
     </row>
     <row r="812">
@@ -35658,13 +35662,13 @@
         </is>
       </c>
       <c r="G812" s="3" t="n">
-        <v>46370.75</v>
+        <v>46372.25</v>
       </c>
       <c r="H812" s="3" t="n">
-        <v>46370.79166666666</v>
+        <v>46372.29166666666</v>
       </c>
       <c r="I812" s="3" t="n">
-        <v>46371.20833333334</v>
+        <v>46372.70833333334</v>
       </c>
     </row>
     <row r="813">
@@ -35699,13 +35703,13 @@
         </is>
       </c>
       <c r="G813" s="3" t="n">
-        <v>46372.75</v>
+        <v>46374.25</v>
       </c>
       <c r="H813" s="3" t="n">
-        <v>46372.91666666666</v>
+        <v>46374.41666666666</v>
       </c>
       <c r="I813" s="3" t="n">
-        <v>46373.45833333334</v>
+        <v>46374.95833333334</v>
       </c>
     </row>
     <row r="814">
@@ -40201,13 +40205,13 @@
         </is>
       </c>
       <c r="G923" s="3" t="n">
-        <v>46297.41666666666</v>
+        <v>46297.45833333334</v>
       </c>
       <c r="H923" s="3" t="n">
-        <v>46297.47916666666</v>
+        <v>46297.52083333334</v>
       </c>
       <c r="I923" s="3" t="n">
-        <v>46297.75</v>
+        <v>46297.97916666666</v>
       </c>
     </row>
     <row r="924">
@@ -40242,13 +40246,13 @@
         </is>
       </c>
       <c r="G924" s="3" t="n">
-        <v>46300.58333333334</v>
+        <v>46300.8125</v>
       </c>
       <c r="H924" s="3" t="n">
-        <v>46300.625</v>
+        <v>46300.85416666666</v>
       </c>
       <c r="I924" s="3" t="n">
-        <v>46301.08333333334</v>
+        <v>46301.3125</v>
       </c>
     </row>
     <row r="925">
@@ -40283,13 +40287,13 @@
         </is>
       </c>
       <c r="G925" s="3" t="n">
-        <v>46303.25</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="H925" s="3" t="n">
-        <v>46303.41666666666</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="I925" s="3" t="n">
-        <v>46303.875</v>
+        <v>46304.10416666666</v>
       </c>
     </row>
     <row r="926">
@@ -40324,13 +40328,13 @@
         </is>
       </c>
       <c r="G926" s="3" t="n">
-        <v>46305.45833333334</v>
+        <v>46305.6875</v>
       </c>
       <c r="H926" s="3" t="n">
-        <v>46305.5</v>
+        <v>46305.72916666666</v>
       </c>
       <c r="I926" s="3" t="n">
-        <v>46305.75</v>
+        <v>46305.97916666666</v>
       </c>
     </row>
     <row r="927">
@@ -40365,13 +40369,13 @@
         </is>
       </c>
       <c r="G927" s="3" t="n">
-        <v>46305.91666666666</v>
+        <v>46306.14583333334</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>46306.04166666666</v>
+        <v>46306.27083333334</v>
       </c>
       <c r="I927" s="3" t="n">
-        <v>46307.54166666666</v>
+        <v>46307.77083333334</v>
       </c>
     </row>
     <row r="928">
@@ -40406,13 +40410,13 @@
         </is>
       </c>
       <c r="G928" s="3" t="n">
-        <v>46307.70833333334</v>
+        <v>46307.9375</v>
       </c>
       <c r="H928" s="3" t="n">
-        <v>46307.75</v>
+        <v>46307.97916666666</v>
       </c>
       <c r="I928" s="3" t="n">
-        <v>46308</v>
+        <v>46308.22916666666</v>
       </c>
     </row>
     <row r="929">
@@ -40447,13 +40451,13 @@
         </is>
       </c>
       <c r="G929" s="3" t="n">
-        <v>46311.72916666666</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>46311.79166666666</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="I929" s="3" t="n">
-        <v>46312.25</v>
+        <v>46312.47916666666</v>
       </c>
     </row>
     <row r="930">
@@ -40488,13 +40492,13 @@
         </is>
       </c>
       <c r="G930" s="3" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.27083333334</v>
       </c>
       <c r="H930" s="3" t="n">
-        <v>46313.08333333334</v>
+        <v>46313.3125</v>
       </c>
       <c r="I930" s="3" t="n">
-        <v>46313.66666666666</v>
+        <v>46313.89583333334</v>
       </c>
     </row>
     <row r="931">
@@ -40529,13 +40533,13 @@
         </is>
       </c>
       <c r="G931" s="3" t="n">
-        <v>46316.04166666666</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="H931" s="3" t="n">
-        <v>46316.08333333334</v>
+        <v>46316.3125</v>
       </c>
       <c r="I931" s="3" t="n">
-        <v>46316.79166666666</v>
+        <v>46317.02083333334</v>
       </c>
     </row>
     <row r="932">
@@ -40570,13 +40574,13 @@
         </is>
       </c>
       <c r="G932" s="3" t="n">
-        <v>46317.08333333334</v>
+        <v>46317.3125</v>
       </c>
       <c r="H932" s="3" t="n">
-        <v>46317.14583333334</v>
+        <v>46317.375</v>
       </c>
       <c r="I932" s="3" t="n">
-        <v>46317.41666666666</v>
+        <v>46317.64583333334</v>
       </c>
     </row>
     <row r="933">
@@ -40611,13 +40615,13 @@
         </is>
       </c>
       <c r="G933" s="3" t="n">
-        <v>46320.33333333334</v>
+        <v>46320.5625</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>46320.375</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="I933" s="3" t="n">
-        <v>46320.83333333334</v>
+        <v>46321.0625</v>
       </c>
     </row>
     <row r="934">
@@ -40652,13 +40656,13 @@
         </is>
       </c>
       <c r="G934" s="3" t="n">
-        <v>46323.04166666666</v>
+        <v>46323.27083333334</v>
       </c>
       <c r="H934" s="3" t="n">
-        <v>46323.20833333334</v>
+        <v>46323.4375</v>
       </c>
       <c r="I934" s="3" t="n">
-        <v>46323.66666666666</v>
+        <v>46323.89583333334</v>
       </c>
     </row>
     <row r="935">
@@ -40693,13 +40697,13 @@
         </is>
       </c>
       <c r="G935" s="3" t="n">
-        <v>46325.33333333334</v>
+        <v>46325.5625</v>
       </c>
       <c r="H935" s="3" t="n">
-        <v>46325.375</v>
+        <v>46325.60416666666</v>
       </c>
       <c r="I935" s="3" t="n">
-        <v>46325.625</v>
+        <v>46325.85416666666</v>
       </c>
     </row>
     <row r="936">
@@ -40734,13 +40738,13 @@
         </is>
       </c>
       <c r="G936" s="3" t="n">
-        <v>46325.79166666666</v>
+        <v>46326.02083333334</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>46325.91666666666</v>
+        <v>46326.14583333334</v>
       </c>
       <c r="I936" s="3" t="n">
-        <v>46327.41666666666</v>
+        <v>46327.64583333334</v>
       </c>
     </row>
     <row r="937">
@@ -40775,13 +40779,13 @@
         </is>
       </c>
       <c r="G937" s="3" t="n">
-        <v>46327.625</v>
+        <v>46327.85416666666</v>
       </c>
       <c r="H937" s="3" t="n">
-        <v>46327.66666666666</v>
+        <v>46327.89583333334</v>
       </c>
       <c r="I937" s="3" t="n">
-        <v>46327.91666666666</v>
+        <v>46328.14583333334</v>
       </c>
     </row>
     <row r="938">
@@ -40816,13 +40820,13 @@
         </is>
       </c>
       <c r="G938" s="3" t="n">
-        <v>46331.75</v>
+        <v>46331.97916666666</v>
       </c>
       <c r="H938" s="3" t="n">
-        <v>46331.79166666666</v>
+        <v>46332.02083333334</v>
       </c>
       <c r="I938" s="3" t="n">
-        <v>46332.25</v>
+        <v>46332.47916666666</v>
       </c>
     </row>
     <row r="939">
@@ -40857,13 +40861,13 @@
         </is>
       </c>
       <c r="G939" s="3" t="n">
-        <v>46333</v>
+        <v>46333.22916666666</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>46333.04166666666</v>
+        <v>46333.27083333334</v>
       </c>
       <c r="I939" s="3" t="n">
-        <v>46333.625</v>
+        <v>46333.85416666666</v>
       </c>
     </row>
     <row r="940">
@@ -42167,13 +42171,13 @@
         </is>
       </c>
       <c r="G971" s="3" t="n">
-        <v>46297.04166666666</v>
+        <v>46297.33333333334</v>
       </c>
       <c r="H971" s="3" t="n">
-        <v>46297.125</v>
+        <v>46297.41666666666</v>
       </c>
       <c r="I971" s="3" t="n">
-        <v>46297.625</v>
+        <v>46297.91666666666</v>
       </c>
     </row>
     <row r="972">
@@ -42208,13 +42212,13 @@
         </is>
       </c>
       <c r="G972" s="3" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.64583333334</v>
       </c>
       <c r="H972" s="3" t="n">
-        <v>46301.39583333334</v>
+        <v>46301.6875</v>
       </c>
       <c r="I972" s="3" t="n">
-        <v>46302.0625</v>
+        <v>46302.35416666666</v>
       </c>
     </row>
     <row r="973">
@@ -42249,13 +42253,13 @@
         </is>
       </c>
       <c r="G973" s="3" t="n">
-        <v>46308.125</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="H973" s="3" t="n">
-        <v>46308.33333333334</v>
+        <v>46308.625</v>
       </c>
       <c r="I973" s="3" t="n">
-        <v>46309</v>
+        <v>46309.29166666666</v>
       </c>
     </row>
     <row r="974">
@@ -42290,13 +42294,13 @@
         </is>
       </c>
       <c r="G974" s="3" t="n">
-        <v>46310.39583333334</v>
+        <v>46310.6875</v>
       </c>
       <c r="H974" s="3" t="n">
-        <v>46310.4375</v>
+        <v>46310.72916666666</v>
       </c>
       <c r="I974" s="3" t="n">
-        <v>46311.4375</v>
+        <v>46311.72916666666</v>
       </c>
     </row>
     <row r="975">
@@ -42331,13 +42335,13 @@
         </is>
       </c>
       <c r="G975" s="3" t="n">
-        <v>46311.72916666666</v>
+        <v>46312.02083333334</v>
       </c>
       <c r="H975" s="3" t="n">
-        <v>46311.77083333334</v>
+        <v>46312.0625</v>
       </c>
       <c r="I975" s="3" t="n">
-        <v>46312.39583333334</v>
+        <v>46312.6875</v>
       </c>
     </row>
     <row r="976">
@@ -42372,13 +42376,13 @@
         </is>
       </c>
       <c r="G976" s="3" t="n">
-        <v>46313.85416666666</v>
+        <v>46314.14583333334</v>
       </c>
       <c r="H976" s="3" t="n">
-        <v>46314.0625</v>
+        <v>46314.35416666666</v>
       </c>
       <c r="I976" s="3" t="n">
-        <v>46314.72916666666</v>
+        <v>46315.02083333334</v>
       </c>
     </row>
     <row r="977">
@@ -42413,13 +42417,13 @@
         </is>
       </c>
       <c r="G977" s="3" t="n">
-        <v>46321.72916666666</v>
+        <v>46322.02083333334</v>
       </c>
       <c r="H977" s="3" t="n">
-        <v>46321.8125</v>
+        <v>46322.10416666666</v>
       </c>
       <c r="I977" s="3" t="n">
-        <v>46322.64583333334</v>
+        <v>46322.9375</v>
       </c>
     </row>
     <row r="978">
@@ -42454,13 +42458,13 @@
         </is>
       </c>
       <c r="G978" s="3" t="n">
-        <v>46323.72916666666</v>
+        <v>46324.02083333334</v>
       </c>
       <c r="H978" s="3" t="n">
-        <v>46323.8125</v>
+        <v>46324.10416666666</v>
       </c>
       <c r="I978" s="3" t="n">
-        <v>46324.3125</v>
+        <v>46324.60416666666</v>
       </c>
     </row>
     <row r="979">
@@ -42495,13 +42499,13 @@
         </is>
       </c>
       <c r="G979" s="3" t="n">
-        <v>46328.3125</v>
+        <v>46328.60416666666</v>
       </c>
       <c r="H979" s="3" t="n">
-        <v>46328.35416666666</v>
+        <v>46328.64583333334</v>
       </c>
       <c r="I979" s="3" t="n">
-        <v>46329.02083333334</v>
+        <v>46329.3125</v>
       </c>
     </row>
     <row r="980">
@@ -42536,13 +42540,13 @@
         </is>
       </c>
       <c r="G980" s="3" t="n">
-        <v>46335.4375</v>
+        <v>46335.72916666666</v>
       </c>
       <c r="H980" s="3" t="n">
-        <v>46335.64583333334</v>
+        <v>46335.9375</v>
       </c>
       <c r="I980" s="3" t="n">
-        <v>46336.3125</v>
+        <v>46336.60416666666</v>
       </c>
     </row>
     <row r="981">
@@ -44910,13 +44914,13 @@
         </is>
       </c>
       <c r="G1038" s="3" t="n">
-        <v>46295.58333333334</v>
+        <v>46295.625</v>
       </c>
       <c r="H1038" s="3" t="n">
-        <v>46295.75</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="I1038" s="3" t="n">
-        <v>46296.3125</v>
+        <v>46296.52083333334</v>
       </c>
     </row>
     <row r="1039">
@@ -44951,13 +44955,13 @@
         </is>
       </c>
       <c r="G1039" s="3" t="n">
-        <v>46298.66666666666</v>
+        <v>46298.875</v>
       </c>
       <c r="H1039" s="3" t="n">
-        <v>46298.72916666666</v>
+        <v>46298.9375</v>
       </c>
       <c r="I1039" s="3" t="n">
-        <v>46299.22916666666</v>
+        <v>46299.4375</v>
       </c>
     </row>
     <row r="1040">
@@ -44992,13 +44996,13 @@
         </is>
       </c>
       <c r="G1040" s="3" t="n">
-        <v>46299.35416666666</v>
+        <v>46299.5625</v>
       </c>
       <c r="H1040" s="3" t="n">
-        <v>46299.47916666666</v>
+        <v>46299.6875</v>
       </c>
       <c r="I1040" s="3" t="n">
-        <v>46299.9375</v>
+        <v>46300.14583333334</v>
       </c>
     </row>
     <row r="1041">
@@ -45033,13 +45037,13 @@
         </is>
       </c>
       <c r="G1041" s="3" t="n">
-        <v>46303.02083333334</v>
+        <v>46303.25</v>
       </c>
       <c r="H1041" s="3" t="n">
-        <v>46303.0625</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="I1041" s="3" t="n">
-        <v>46303.72916666666</v>
+        <v>46303.95833333334</v>
       </c>
     </row>
     <row r="1042">
@@ -45074,13 +45078,13 @@
         </is>
       </c>
       <c r="G1042" s="3" t="n">
-        <v>46304.8125</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="H1042" s="3" t="n">
-        <v>46304.85416666666</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="I1042" s="3" t="n">
-        <v>46305.4375</v>
+        <v>46305.66666666666</v>
       </c>
     </row>
     <row r="1043">
@@ -45115,13 +45119,13 @@
         </is>
       </c>
       <c r="G1043" s="3" t="n">
-        <v>46305.625</v>
+        <v>46305.875</v>
       </c>
       <c r="H1043" s="3" t="n">
-        <v>46305.6875</v>
+        <v>46305.91666666666</v>
       </c>
       <c r="I1043" s="3" t="n">
-        <v>46306.02083333334</v>
+        <v>46306.25</v>
       </c>
     </row>
     <row r="1044">
@@ -45156,13 +45160,13 @@
         </is>
       </c>
       <c r="G1044" s="3" t="n">
-        <v>46307.3125</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="H1044" s="3" t="n">
-        <v>46307.47916666666</v>
+        <v>46307.70833333334</v>
       </c>
       <c r="I1044" s="3" t="n">
-        <v>46307.97916666666</v>
+        <v>46308.20833333334</v>
       </c>
     </row>
     <row r="1045">
@@ -45197,13 +45201,13 @@
         </is>
       </c>
       <c r="G1045" s="3" t="n">
-        <v>46312.14583333334</v>
+        <v>46312.375</v>
       </c>
       <c r="H1045" s="3" t="n">
-        <v>46312.3125</v>
+        <v>46312.54166666666</v>
       </c>
       <c r="I1045" s="3" t="n">
-        <v>46313.14583333334</v>
+        <v>46313.375</v>
       </c>
     </row>
     <row r="1046">
@@ -45238,13 +45242,13 @@
         </is>
       </c>
       <c r="G1046" s="3" t="n">
-        <v>46314.8125</v>
+        <v>46315.08333333334</v>
       </c>
       <c r="H1046" s="3" t="n">
-        <v>46314.85416666666</v>
+        <v>46315.125</v>
       </c>
       <c r="I1046" s="3" t="n">
-        <v>46315.6875</v>
+        <v>46315.95833333334</v>
       </c>
     </row>
     <row r="1047">
@@ -45279,13 +45283,13 @@
         </is>
       </c>
       <c r="G1047" s="3" t="n">
-        <v>46318.85416666666</v>
+        <v>46319.125</v>
       </c>
       <c r="H1047" s="3" t="n">
-        <v>46318.9375</v>
+        <v>46319.16666666666</v>
       </c>
       <c r="I1047" s="3" t="n">
-        <v>46320.60416666666</v>
+        <v>46320.85416666666</v>
       </c>
     </row>
     <row r="1048">
@@ -45320,13 +45324,13 @@
         </is>
       </c>
       <c r="G1048" s="3" t="n">
-        <v>46323.0625</v>
+        <v>46322.97916666666</v>
       </c>
       <c r="H1048" s="3" t="n">
-        <v>46323.22916666666</v>
+        <v>46323.14583333334</v>
       </c>
       <c r="I1048" s="3" t="n">
-        <v>46324.0625</v>
+        <v>46323.97916666666</v>
       </c>
     </row>
     <row r="1049">
@@ -45361,13 +45365,13 @@
         </is>
       </c>
       <c r="G1049" s="3" t="n">
-        <v>46326.60416666666</v>
+        <v>46326.5</v>
       </c>
       <c r="H1049" s="3" t="n">
-        <v>46326.66666666666</v>
+        <v>46326.5625</v>
       </c>
       <c r="I1049" s="3" t="n">
-        <v>46327.16666666666</v>
+        <v>46327.0625</v>
       </c>
     </row>
     <row r="1050">
@@ -45402,13 +45406,13 @@
         </is>
       </c>
       <c r="G1050" s="3" t="n">
-        <v>46327.39583333334</v>
+        <v>46327.29166666666</v>
       </c>
       <c r="H1050" s="3" t="n">
-        <v>46327.4375</v>
+        <v>46327.33333333334</v>
       </c>
       <c r="I1050" s="3" t="n">
-        <v>46327.9375</v>
+        <v>46327.83333333334</v>
       </c>
     </row>
     <row r="1051">
@@ -47878,14 +47882,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47914,12 +47918,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (auto-20260930-2258-SKED.xlsx)</t>
+          <t>Old ETA (prev)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261001-0202-SKED.xlsx)</t>
+          <t>New ETA (auto-20261001-0857-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47936,248 +47940,248 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46298.625</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46298.25</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46300.8125</v>
+        <v>46301.70833333334</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46300.4375</v>
+        <v>46301.875</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46308.6875</v>
+        <v>46302.875</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46308.3125</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46310.6875</v>
+        <v>46306.79166666666</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46310.3125</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46315.27083333334</v>
+        <v>46310.04166666666</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46314.89583333334</v>
+        <v>46310.20833333334</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615S</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46322.39583333334</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46322.02083333334</v>
+        <v>46313</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46297.70833333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46298.41666666666</v>
+        <v>46313.45833333334</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -48188,32 +48192,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46298.75</v>
+        <v>46314.875</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46300.83333333334</v>
+        <v>46315.04166666666</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -48224,32 +48228,32 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46299.91666666666</v>
+        <v>46319.66666666666</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46302</v>
+        <v>46319.83333333334</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -48260,32 +48264,32 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46305.375</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46307.41666666666</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -48296,32 +48300,32 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46307.91666666666</v>
+        <v>46324.45833333334</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46309.95833333334</v>
+        <v>46324.625</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -48332,32 +48336,32 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46308.375</v>
+        <v>46325.625</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46310.41666666666</v>
+        <v>46325.79166666666</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -48368,32 +48372,32 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46310.08333333334</v>
+        <v>46328.875</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46312</v>
+        <v>46329.04166666666</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -48404,32 +48408,32 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46314.29166666666</v>
+        <v>46331.75</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46316.29166666666</v>
+        <v>46331.91666666666</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -48440,32 +48444,32 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46316.08333333334</v>
+        <v>46334.25</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46318.08333333334</v>
+        <v>46334.41666666666</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -48476,32 +48480,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46319.58333333334</v>
+        <v>46334.95833333334</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46321.58333333334</v>
+        <v>46335.125</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -48512,12 +48516,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -48527,17 +48531,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46320.54166666666</v>
+        <v>46336.54166666666</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46322.54166666666</v>
+        <v>46336.70833333334</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -48548,7 +48552,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -48558,22 +48562,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46323.75</v>
+        <v>46340.79166666666</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46325.75</v>
+        <v>46340.95833333334</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -48584,32 +48588,32 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>46326.625</v>
+        <v>46341.5</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>46328.625</v>
+        <v>46341.66666666666</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -48620,32 +48624,32 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>46329.125</v>
+        <v>46343.125</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>46331.125</v>
+        <v>46343.29166666666</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -48656,32 +48660,32 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46329.83333333334</v>
+        <v>46344.33333333334</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46331.83333333334</v>
+        <v>46344.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -48692,12 +48696,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -48707,17 +48711,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>46331.41666666666</v>
+        <v>46345.29166666666</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>46333.41666666666</v>
+        <v>46345.45833333334</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -48728,7 +48732,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -48738,22 +48742,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>46335.66666666666</v>
+        <v>46348.5</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46337.66666666666</v>
+        <v>46348.66666666666</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -48764,32 +48768,32 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>46336.375</v>
+        <v>46351.375</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>46338.375</v>
+        <v>46351.54166666666</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -48800,32 +48804,32 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2617S</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>46338</v>
+        <v>46353.875</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>46340</v>
+        <v>46354.04166666666</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -48836,32 +48840,32 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46340.58333333334</v>
+        <v>46354.58333333334</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>46342.58333333334</v>
+        <v>46354.75</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -48872,12 +48876,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -48887,17 +48891,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>46341.54166666666</v>
+        <v>46356.16666666666</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>46343.54166666666</v>
+        <v>46356.33333333334</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -48908,7 +48912,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -48918,22 +48922,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46344.75</v>
+        <v>46360.41666666666</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46346.75</v>
+        <v>46360.58333333334</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -48944,32 +48948,32 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46347.625</v>
+        <v>46361.125</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46349.625</v>
+        <v>46361.29166666666</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -48980,32 +48984,32 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2617N</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>46350.125</v>
+        <v>46362.75</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46352.125</v>
+        <v>46362.91666666666</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -49016,32 +49020,32 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>46350.83333333334</v>
+        <v>46365.33333333334</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>46352.83333333334</v>
+        <v>46365.5</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -49052,12 +49056,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -49067,17 +49071,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>46352.41666666666</v>
+        <v>46366.29166666666</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>46354.41666666666</v>
+        <v>46366.45833333334</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -49088,7 +49092,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -49098,22 +49102,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>46356.66666666666</v>
+        <v>46369.5</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>46358.66666666666</v>
+        <v>46369.66666666666</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -49124,32 +49128,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46357.375</v>
+        <v>46372.375</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>46359.375</v>
+        <v>46372.54166666666</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -49160,32 +49164,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>KMTC JAKARTA</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>46359</v>
+        <v>46374.875</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>46361</v>
+        <v>46375.04166666666</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -49196,68 +49200,68 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE ATLANTIC</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>46296.20833333334</v>
+        <v>46375.58333333334</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>46296.16666666666</v>
+        <v>46375.75</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>46298.375</v>
+        <v>46377.16666666666</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>46298.45833333334</v>
+        <v>46377.33333333334</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -49268,32 +49272,32 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>46299.16666666666</v>
+        <v>46381.41666666666</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>46299.25</v>
+        <v>46381.58333333334</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -49304,32 +49308,32 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>46304.54166666666</v>
+        <v>46382.125</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>46304.625</v>
+        <v>46382.29166666666</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -49340,32 +49344,32 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>46307</v>
+        <v>46383.75</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>46307.08333333334</v>
+        <v>46383.91666666666</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -49376,32 +49380,32 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>46307.375</v>
+        <v>46386.33333333334</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>46307.45833333334</v>
+        <v>46386.5</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -49412,32 +49416,32 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>46309.20833333334</v>
+        <v>46387.29166666666</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>46309.29166666666</v>
+        <v>46387.45833333334</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -49448,32 +49452,32 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46311.29166666666</v>
+        <v>46390.5</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>46311.375</v>
+        <v>46390.66666666666</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -49484,32 +49488,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>46297.16666666666</v>
+        <v>46393.375</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>46297.41666666666</v>
+        <v>46393.54166666666</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -49520,32 +49524,32 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2619S</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>46300.33333333334</v>
+        <v>46395.875</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>46300.58333333334</v>
+        <v>46396.04166666666</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -49556,12 +49560,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -49571,17 +49575,17 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>46303</v>
+        <v>46396.58333333334</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>46303.25</v>
+        <v>46396.75</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -49592,7 +49596,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -49602,22 +49606,22 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>46305.20833333334</v>
+        <v>46398.16666666666</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>46305.45833333334</v>
+        <v>46398.33333333334</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -49628,32 +49632,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>46305.66666666666</v>
+        <v>46402.41666666666</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>46305.91666666666</v>
+        <v>46402.58333333334</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -49664,32 +49668,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>TWKEL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>46307.45833333334</v>
+        <v>46403.125</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>46307.70833333334</v>
+        <v>46403.29166666666</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -49700,32 +49704,30 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>CA MANILA</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v/>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2619N</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>46311.47916666666</v>
+        <v>46404.75</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>46311.72916666666</v>
+        <v>46404.91666666666</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -49736,32 +49738,32 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>46312.79166666666</v>
+        <v>46298.25</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>46313.04166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -49772,32 +49774,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>46315.79166666666</v>
+        <v>46300.4375</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>46316.04166666666</v>
+        <v>46300.47916666666</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -49808,32 +49810,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46316.83333333334</v>
+        <v>46308.3125</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46317.08333333334</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -49844,32 +49846,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>46320.08333333334</v>
+        <v>46310.3125</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>46320.33333333334</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -49880,32 +49882,32 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>46322.79166666666</v>
+        <v>46314.89583333334</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>46323.04166666666</v>
+        <v>46314.9375</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -49916,32 +49918,32 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>46325.08333333334</v>
+        <v>46322.02083333334</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>46325.33333333334</v>
+        <v>46322.0625</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -49952,32 +49954,32 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>46325.54166666666</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>46325.79166666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -49988,32 +49990,32 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>46327.375</v>
+        <v>46298.875</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>46327.625</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -50024,32 +50026,32 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>46331.5</v>
+        <v>46302.70833333334</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>46331.75</v>
+        <v>46302.79166666666</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -50060,32 +50062,32 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE SUNRISE</t>
+          <t>INCHEON VOYAGER</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>46332.75</v>
+        <v>46304.5</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>46333</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -50096,32 +50098,32 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>KMTC ULSAN</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>46297.16666666666</v>
+        <v>46298</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>46297.04166666666</v>
+        <v>46297.95833333334</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -50132,32 +50134,32 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>PANCON CHAMPION</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>46301.47916666666</v>
+        <v>46296.83333333334</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>46301.35416666666</v>
+        <v>46296.8125</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-3</v>
+        <v>-0.5</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -50168,32 +50170,32 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>PANCON CHAMPION</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46308.25</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>46308.125</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -50204,516 +50206,516 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>PANCON CHAMPION</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2610S</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>46310.52083333334</v>
+        <v>46304.5</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>46310.39583333334</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>PANCON CHAMPION</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>46311.85416666666</v>
+        <v>46306.79166666666</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>46311.72916666666</v>
+        <v>46306.95833333334</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>PANCON CHAMPION</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>2613S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>46313.97916666666</v>
+        <v>46308.875</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46313.85416666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-3</v>
+        <v>10</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>46321.85416666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>46321.72916666666</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>IDSRG</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>46323.85416666666</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>46323.72916666666</v>
+        <v>46299.625</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>46328.4375</v>
+        <v>46305.52083333334</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>46328.3125</v>
+        <v>46305.66666666666</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE VEGA</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>46335.5625</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>46335.4375</v>
+        <v>46308.1875</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>46297.625</v>
+        <v>46308.5625</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>46297.5</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>46299.20833333334</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>46299.08333333334</v>
+        <v>46310</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>46302.25</v>
+        <v>46312.20833333334</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>46302.125</v>
+        <v>46312.35416666666</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>46303.29166666666</v>
+        <v>46319.04166666666</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>46303.16666666666</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-3</v>
+        <v>42</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>46306.58333333334</v>
+        <v>46319.91666666666</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>46306.45833333334</v>
+        <v>46321.66666666666</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>-3</v>
+        <v>42</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>46309.375</v>
+        <v>46321.125</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>46309.25</v>
+        <v>46322.875</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>-3</v>
+        <v>42</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>2612S</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>46311.75</v>
+        <v>46321.875</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>46311.625</v>
+        <v>46323.625</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>-3</v>
+        <v>42</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -50723,28 +50725,28 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46312.125</v>
+        <v>46327.33333333334</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>46312</v>
+        <v>46329.16666666666</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>-3</v>
+        <v>44</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -50754,96 +50756,3012 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2618S</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>46313.91666666666</v>
+        <v>46329.6875</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>46313.79166666666</v>
+        <v>46331.5625</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>-3</v>
+        <v>45</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>46318</v>
+        <v>46330.20833333334</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>46317.875</v>
+        <v>46332.08333333334</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>-3</v>
+        <v>45</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SKY ORION</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>46331.5</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>46333.375</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>2618N</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>46333.85416666666</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>46335.72916666666</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46339.91666666666</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>46341.79166666666</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>46340.79166666666</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>46342.66666666666</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>46343.875</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46342.75</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>46344.625</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46348.20833333334</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>46350.16666666666</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>2619S</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>46350.60625</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>46352.5625</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>2619N</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>46351.12708333333</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>46353.08333333334</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>2619N</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>46352.41875</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>46354.375</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE BALTIC</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>2619N</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>46354.77291666667</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>46356.72916666666</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>46299.25</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>46298.83333333334</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>46298.45833333334</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>46299.70833333334</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>46304.625</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>46307.08333333334</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>46308.5</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>46307.45833333334</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>46308.875</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>46309.29166666666</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>46310.70833333334</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>46311.375</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>46312.79166666666</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>46317.29166666666</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>46318.79166666666</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>46318.54166666666</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>46320.04166666666</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>46319.33333333334</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>46320.83333333334</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>46324.625</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>46326.125</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>46327.08333333334</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>46328.58333333334</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>46327.5</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>46329</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>46329.33333333334</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>46330.83333333334</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>46331.33333333334</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>46332.83333333334</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>46337.41666666666</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>46338.91666666666</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>46338.70833333334</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>46340.20833333334</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>46339.45833333334</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>46340.95833333334</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>46344.875</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>46346.375</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>46347.45833333334</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>46348.95833333334</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>46348.04166666666</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>46349.54166666666</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>46349.875</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>46351.375</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>46351.91666666666</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>46353.41666666666</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>2614S</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>46358.33333333334</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>46359.83333333334</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>2614S</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>46359.58333333334</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>46361.08333333334</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>2614S</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>46360.33333333334</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>46361.83333333334</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>2614S</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>46365.75</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>46367.25</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>2614S</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>46368.33333333334</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>46369.83333333334</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>46368.91666666666</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>46370.41666666666</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>46370.75</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>46372.25</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>46372.75</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>46374.25</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>46297.41666666666</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>46297.45833333334</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>46300.8125</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>46303.25</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>46303.47916666666</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>46305.45833333334</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>46305.6875</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>46305.91666666666</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>46306.14583333334</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>46307.70833333334</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>46307.9375</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
           <t>CNXMN</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>46311.72916666666</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>46311.95833333334</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>46313.04166666666</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>46313.27083333334</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>46316.04166666666</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>46316.27083333334</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>46317.08333333334</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>46317.3125</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>46320.33333333334</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>46320.5625</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>46323.04166666666</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>46323.27083333334</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>46325.33333333334</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>2612N</t>
         </is>
       </c>
-      <c r="E82" s="3" t="n">
-        <v>46319.375</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>46319.25</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="E137" s="3" t="n">
+        <v>46325.79166666666</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>46326.02083333334</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>46327.625</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>46327.85416666666</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>46331.75</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>46331.97916666666</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SUNRISE</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>CNXMN</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>46333</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>46333.22916666666</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>46297.04166666666</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>46297.33333333334</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>46308.125</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>46308.41666666666</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>46310.39583333334</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>46310.6875</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>46311.72916666666</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>46312.02083333334</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>2613S</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>46313.85416666666</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>46314.14583333334</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>46321.72916666666</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>46322.02083333334</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>46323.72916666666</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>46324.02083333334</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>46328.3125</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>46328.60416666666</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE VEGA</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>2613N</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>46335.4375</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>46335.72916666666</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>46295.58333333334</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>46295.625</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>46298.66666666666</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>46298.875</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>46299.35416666666</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>46299.5625</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>46303.02083333334</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>46303.25</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>46304.8125</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>46305.04166666666</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>46305.625</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>46305.875</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>46307.3125</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>46307.54166666666</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>46312.14583333334</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>46312.375</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>46314.8125</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>46315.08333333334</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>46318.85416666666</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>46319.125</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>46323.0625</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>46322.97916666666</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>46326.60416666666</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>46326.5</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>STARSHIP JUPITER</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>2608N</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>46327.39583333334</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>46327.29166666666</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>Early</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46305.54166666666</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>46305.04166666666</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T00:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T01:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -829,7 +829,7 @@
         <v/>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46314.97916666666</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -915,20 +915,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>VNSGN -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH04)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-01T19:00:00</t>
+          <t>Alongside, departs to THBKK ~2026-10-02T03:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -945,7 +947,7 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>46296.79166666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -954,7 +956,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2611N</t>
         </is>
       </c>
     </row>
@@ -1870,11 +1872,11 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T13:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T14:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46308.875</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1887,7 +1889,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46308.5</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -5037,10 +5039,10 @@
         <v>46296.85416666666</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>46297.08333333334</v>
+        <v>46296.79166666666</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>46297.95833333334</v>
+        <v>46297.79166666666</v>
       </c>
     </row>
     <row r="65">
@@ -5075,13 +5077,13 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>46302.875</v>
+        <v>46302.54166666666</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>46303.04166666666</v>
+        <v>46302.70833333334</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>46303.54166666666</v>
+        <v>46303.20833333334</v>
       </c>
     </row>
     <row r="66">
@@ -5116,13 +5118,13 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>46305.04166666666</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="H66" s="3" t="n">
+        <v>46304.75</v>
+      </c>
+      <c r="I66" s="3" t="n">
         <v>46305.08333333334</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>46305.41666666666</v>
       </c>
     </row>
     <row r="67">
@@ -5157,13 +5159,13 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>46305.54166666666</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>46305.625</v>
+        <v>46305.29166666666</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>46306.625</v>
+        <v>46306.29166666666</v>
       </c>
     </row>
     <row r="68">
@@ -5198,13 +5200,13 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>46306.83333333334</v>
+        <v>46306.5</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>46306.875</v>
+        <v>46306.54166666666</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>46307.375</v>
+        <v>46307.04166666666</v>
       </c>
     </row>
     <row r="69">
@@ -5239,13 +5241,13 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>46309.1875</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>46309.35416666666</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>46310.04166666666</v>
+        <v>46309.70833333334</v>
       </c>
     </row>
     <row r="70">
@@ -9257,7 +9259,7 @@
         <v>46296.66666666666</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>46298</v>
+        <v>46298.04166666666</v>
       </c>
     </row>
     <row r="168">
@@ -9292,13 +9294,13 @@
         </is>
       </c>
       <c r="G168" s="3" t="n">
-        <v>46298.29166666666</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>46298.35416666666</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>46298.97916666666</v>
+        <v>46299.02083333334</v>
       </c>
     </row>
     <row r="169">
@@ -9333,13 +9335,13 @@
         </is>
       </c>
       <c r="G169" s="3" t="n">
-        <v>46300.47916666666</v>
+        <v>46300.52083333334</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>46300.6875</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>46301.35416666666</v>
+        <v>46301.39583333334</v>
       </c>
     </row>
     <row r="170">
@@ -9374,13 +9376,13 @@
         </is>
       </c>
       <c r="G170" s="3" t="n">
-        <v>46308.35416666666</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>46308.4375</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>46309.27083333334</v>
+        <v>46309.3125</v>
       </c>
     </row>
     <row r="171">
@@ -9415,13 +9417,13 @@
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>46310.35416666666</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>46310.4375</v>
+        <v>46310.47916666666</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>46310.9375</v>
+        <v>46310.97916666666</v>
       </c>
     </row>
     <row r="172">
@@ -9456,13 +9458,13 @@
         </is>
       </c>
       <c r="G172" s="3" t="n">
-        <v>46314.9375</v>
+        <v>46314.97916666666</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>46314.97916666666</v>
+        <v>46315.02083333334</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>46315.64583333334</v>
+        <v>46315.6875</v>
       </c>
     </row>
     <row r="173">
@@ -9497,13 +9499,13 @@
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>46322.0625</v>
+        <v>46322.10416666666</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>46322.27083333334</v>
+        <v>46322.3125</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>46322.9375</v>
+        <v>46322.97916666666</v>
       </c>
     </row>
     <row r="174">
@@ -34435,10 +34437,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>46297.08333333334</v>
+        <v>46297.16666666666</v>
       </c>
       <c r="I782" s="3" t="n">
-        <v>46298.54166666666</v>
+        <v>46298.58333333334</v>
       </c>
     </row>
     <row r="783">
@@ -34473,13 +34475,13 @@
         </is>
       </c>
       <c r="G783" s="3" t="n">
-        <v>46298.83333333334</v>
+        <v>46298.875</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>46298.89583333334</v>
+        <v>46298.9375</v>
       </c>
       <c r="I783" s="3" t="n">
-        <v>46299.29166666666</v>
+        <v>46299.33333333334</v>
       </c>
     </row>
     <row r="784">
@@ -34514,13 +34516,13 @@
         </is>
       </c>
       <c r="G784" s="3" t="n">
-        <v>46299.70833333334</v>
+        <v>46299.75</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>46300.72916666666</v>
+        <v>46300.77083333334</v>
       </c>
       <c r="I784" s="3" t="n">
-        <v>46301.08333333334</v>
+        <v>46301.125</v>
       </c>
     </row>
     <row r="785">
@@ -34555,13 +34557,13 @@
         </is>
       </c>
       <c r="G785" s="3" t="n">
-        <v>46306.04166666666</v>
+        <v>46306.08333333334</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>46306.20833333334</v>
+        <v>46306.25</v>
       </c>
       <c r="I785" s="3" t="n">
-        <v>46306.83333333334</v>
+        <v>46306.875</v>
       </c>
     </row>
     <row r="786">
@@ -34596,13 +34598,13 @@
         </is>
       </c>
       <c r="G786" s="3" t="n">
-        <v>46308.5</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="I786" s="3" t="n">
-        <v>46308.79166666666</v>
+        <v>46308.83333333334</v>
       </c>
     </row>
     <row r="787">
@@ -34637,13 +34639,13 @@
         </is>
       </c>
       <c r="G787" s="3" t="n">
-        <v>46308.875</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>46309</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="I787" s="3" t="n">
-        <v>46310.5</v>
+        <v>46310.54166666666</v>
       </c>
     </row>
     <row r="788">
@@ -34678,13 +34680,13 @@
         </is>
       </c>
       <c r="G788" s="3" t="n">
-        <v>46310.70833333334</v>
+        <v>46310.75</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>46310.75</v>
+        <v>46310.79166666666</v>
       </c>
       <c r="I788" s="3" t="n">
-        <v>46311.16666666666</v>
+        <v>46311.20833333334</v>
       </c>
     </row>
     <row r="789">
@@ -34719,13 +34721,13 @@
         </is>
       </c>
       <c r="G789" s="3" t="n">
-        <v>46312.79166666666</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>46312.95833333334</v>
+        <v>46313</v>
       </c>
       <c r="I789" s="3" t="n">
-        <v>46313.5</v>
+        <v>46313.54166666666</v>
       </c>
     </row>
     <row r="790">
@@ -47882,7 +47884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -47923,7 +47925,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261001-0857-SKED.xlsx)</t>
+          <t>New ETA (auto-20261001-1159-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47940,120 +47942,120 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>TWKEL</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46298.79166666666</v>
+        <v>46302.875</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46298.95833333334</v>
+        <v>46302.54166666666</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46301.70833333334</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46301.875</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46302.875</v>
+        <v>46305.54166666666</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46303.04166666666</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -48063,28 +48065,28 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46306.79166666666</v>
+        <v>46306.83333333334</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46306.95833333334</v>
+        <v>46306.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -48094,58 +48096,58 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46310.04166666666</v>
+        <v>46309.1875</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46310.20833333334</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2615S</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46312.83333333334</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46313</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -48156,32 +48158,32 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46313.29166666666</v>
+        <v>46300.47916666666</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46313.45833333334</v>
+        <v>46300.52083333334</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -48192,32 +48194,32 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>46314.875</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46315.04166666666</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -48228,32 +48230,32 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDSRG</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>46319.66666666666</v>
+        <v>46310.35416666666</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46319.83333333334</v>
+        <v>46310.39583333334</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -48264,32 +48266,32 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>46320.29166666666</v>
+        <v>46314.9375</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46320.45833333334</v>
+        <v>46314.97916666666</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -48300,32 +48302,32 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>HOCHIMINH VOYAGER</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2616S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>46324.45833333334</v>
+        <v>46322.0625</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46324.625</v>
+        <v>46322.10416666666</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -48336,32 +48338,32 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>KRUSN</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2616S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>46325.625</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46325.79166666666</v>
+        <v>46298.875</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -48372,12 +48374,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -48387,17 +48389,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2616S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>46328.875</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46329.04166666666</v>
+        <v>46299.75</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -48408,7 +48410,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -48423,17 +48425,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2616S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>46331.75</v>
+        <v>46306.04166666666</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46331.91666666666</v>
+        <v>46306.08333333334</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -48444,7 +48446,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -48459,17 +48461,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2616S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>46334.25</v>
+        <v>46308.5</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46334.41666666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -48480,7 +48482,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -48495,17 +48497,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>46334.95833333334</v>
+        <v>46308.875</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46335.125</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -48516,7 +48518,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -48526,22 +48528,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>46336.54166666666</v>
+        <v>46310.70833333334</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46336.70833333334</v>
+        <v>46310.75</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -48552,5218 +48554,36 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CA MANILA</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>46340.79166666666</v>
+        <v>46312.79166666666</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46340.95833333334</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>46341.5</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>46341.66666666666</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>46343.125</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>46343.29166666666</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>46344.33333333334</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>46344.5</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>46345.29166666666</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>46345.45833333334</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46348.5</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>46348.66666666666</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>46351.375</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>46351.54166666666</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2617S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>46353.875</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>46354.04166666666</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>46354.58333333334</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>46354.75</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>46356.16666666666</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>46356.33333333334</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>46360.41666666666</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>46360.58333333334</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>46361.125</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>46361.29166666666</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2617N</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>46362.75</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>46362.91666666666</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>46365.33333333334</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>46365.5</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>46366.29166666666</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>46366.45833333334</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>46369.5</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>46369.66666666666</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>46372.375</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>46372.54166666666</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>46374.875</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>46375.04166666666</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>46375.58333333334</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>46375.75</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>46377.16666666666</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>46377.33333333334</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>46381.41666666666</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>46381.58333333334</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46382.125</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>46382.29166666666</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46383.75</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>46383.91666666666</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>46386.33333333334</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>46386.5</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>46387.29166666666</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>46387.45833333334</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>46390.5</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>46390.66666666666</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>46393.375</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>46393.54166666666</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>46395.875</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>46396.04166666666</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>46396.58333333334</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>46396.75</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>46398.16666666666</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>46398.33333333334</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>46402.41666666666</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>46402.58333333334</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>46403.125</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>46403.29166666666</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CA MANILA</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>TWKEL</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>46404.75</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>46404.91666666666</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>46298.25</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>46298.29166666666</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>46300.4375</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>46300.47916666666</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>46308.3125</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>46308.35416666666</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>46310.3125</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>46310.35416666666</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>46314.89583333334</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>46314.9375</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>46322.02083333334</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>46322.0625</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>46298.08333333334</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>46298.16666666666</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>46298.875</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>46298.95833333334</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>46302.70833333334</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>46302.79166666666</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>46304.5</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>46304.58333333334</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>KMTC ULSAN</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>46298</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>46297.95833333334</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>PANCON CHAMPION</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>46296.83333333334</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>46296.8125</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>PANCON CHAMPION</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>46298.58333333334</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>46298.41666666666</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>PANCON CHAMPION</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>46304.5</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>46304.66666666666</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>PANCON CHAMPION</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>46306.79166666666</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>46306.95833333334</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>PANCON CHAMPION</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>46308.875</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>46309.29166666666</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>46298.66666666666</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>46298.83333333334</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>46299.45833333334</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>46299.625</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>46305.52083333334</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>46305.66666666666</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>46308.04166666666</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>46308.1875</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>46308.5625</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>46308.70833333334</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>46309.85416666666</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>46310</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>46312.20833333334</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>46312.35416666666</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>46319.04166666666</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>46320.79166666666</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>46319.91666666666</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>46321.66666666666</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>46321.125</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>46322.875</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>46321.875</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>46323.625</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>46327.33333333334</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>46329.16666666666</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>2618S</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>46329.6875</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>46331.5625</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>46330.20833333334</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>46332.08333333334</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>46331.5</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>46333.375</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>46333.85416666666</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>46335.72916666666</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>46339.91666666666</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>46341.79166666666</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>46340.79166666666</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>46342.66666666666</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>46342</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>46343.875</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>46342.75</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>46344.625</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>46348.20833333334</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>46350.16666666666</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>2619S</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>46350.60625</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>46352.5625</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>46351.12708333333</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>46353.08333333334</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>46352.41875</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>46354.375</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>2619N</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>46354.77291666667</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>46356.72916666666</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>46299.25</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>46298.83333333334</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>46298.45833333334</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>46299.70833333334</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>46304.625</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>46306.04166666666</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>46307.08333333334</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>46308.5</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>46307.45833333334</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>46308.875</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>46309.29166666666</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>46310.70833333334</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>46311.375</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>46312.79166666666</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>46317.29166666666</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>46318.79166666666</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>46318.54166666666</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>46320.04166666666</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>46319.33333333334</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>46320.83333333334</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>46324.625</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>46326.125</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>46327.08333333334</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>46328.58333333334</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>46327.5</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>46329</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>46329.33333333334</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>46330.83333333334</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>46331.33333333334</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>46332.83333333334</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>46337.41666666666</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>46338.91666666666</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>46338.70833333334</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>46340.20833333334</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>46339.45833333334</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>46340.95833333334</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>46344.875</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>46346.375</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>46347.45833333334</v>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>46348.95833333334</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>46348.04166666666</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>46349.54166666666</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>46349.875</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>46351.375</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>46351.91666666666</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>46353.41666666666</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>46358.33333333334</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>46359.83333333334</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>46359.58333333334</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>46361.08333333334</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>46360.33333333334</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>46361.83333333334</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>46365.75</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>46367.25</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>46368.33333333334</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>46369.83333333334</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>46368.91666666666</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>46370.41666666666</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>46370.75</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>46372.25</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>46372.75</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>46374.25</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>46297.41666666666</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>46297.45833333334</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>46300.58333333334</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>46300.8125</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>46303.25</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>46303.47916666666</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>46305.45833333334</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>46305.6875</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>46305.91666666666</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>46306.14583333334</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>46307.70833333334</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>46307.9375</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>46311.72916666666</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>46311.95833333334</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>46313.04166666666</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>46313.27083333334</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>46316.04166666666</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>46316.27083333334</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>46317.08333333334</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>46317.3125</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>46320.33333333334</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>46320.5625</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>46323.04166666666</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>46323.27083333334</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>46325.33333333334</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>46325.5625</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>46325.79166666666</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>46326.02083333334</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>46327.625</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>46327.85416666666</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>46331.75</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>46331.97916666666</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SUNRISE</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>46333</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>46333.22916666666</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="n">
-        <v>46297.04166666666</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>46297.33333333334</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="n">
-        <v>46301.35416666666</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>46301.64583333334</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>46308.125</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>46308.41666666666</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>46310.39583333334</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>46310.6875</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="n">
-        <v>46311.72916666666</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>46312.02083333334</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="n">
-        <v>46313.85416666666</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>46314.14583333334</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="n">
-        <v>46321.72916666666</v>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>46322.02083333334</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="n">
-        <v>46323.72916666666</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>46324.02083333334</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>46328.3125</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>46328.60416666666</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE VEGA</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>46335.4375</v>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>46335.72916666666</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>46295.58333333334</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>46295.625</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>46298.66666666666</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>46298.875</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>46299.35416666666</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>46299.5625</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="n">
-        <v>46303.02083333334</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>46303.25</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="n">
-        <v>46304.8125</v>
-      </c>
-      <c r="F155" s="3" t="n">
-        <v>46305.04166666666</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="n">
-        <v>46305.625</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>46305.875</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="n">
-        <v>46307.3125</v>
-      </c>
-      <c r="F157" s="3" t="n">
-        <v>46307.54166666666</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="n">
-        <v>46312.14583333334</v>
-      </c>
-      <c r="F158" s="3" t="n">
-        <v>46312.375</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="n">
-        <v>46314.8125</v>
-      </c>
-      <c r="F159" s="3" t="n">
-        <v>46315.08333333334</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>46318.85416666666</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>46319.125</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="n">
-        <v>46323.0625</v>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>46322.97916666666</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="n">
-        <v>46326.60416666666</v>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>46326.5</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>STARSHIP JUPITER</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="n">
-        <v>46327.39583333334</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>46327.29166666666</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -617,20 +617,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>KRKAN -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUS09)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>0152S</t>
+        </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-01T20:30:00</t>
+          <t>Alongside, departs to VNSGN ~2026-10-02T19:00:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -1413,22 +1415,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>MYPKL (PKL01)</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2604E</t>
-        </is>
+          <t>MYPKL -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v/>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-10-01T22:00:00</t>
+          <t>In transit, ETA 2026-10-09T08:00:00</t>
         </is>
       </c>
       <c r="I16" s="3" t="n"/>
@@ -1467,20 +1467,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v/>
+          <t>KRINC (INC07)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to KRPUS ~2026-10-02T07:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
@@ -1661,22 +1663,20 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>HKHKG (HKG03)</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
+          <t>HKHKG -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v/>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-10-01T22:00:00</t>
+          <t>In transit, ETA 2026-10-03T21:00:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -1872,11 +1872,11 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T14:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T16:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46308.91666666666</v>
+        <v>46309</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.625</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -34437,10 +34437,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>46297.16666666666</v>
+        <v>46297.25</v>
       </c>
       <c r="I782" s="3" t="n">
-        <v>46298.58333333334</v>
+        <v>46298.66666666666</v>
       </c>
     </row>
     <row r="783">
@@ -34475,13 +34475,13 @@
         </is>
       </c>
       <c r="G783" s="3" t="n">
-        <v>46298.875</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>46298.9375</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="I783" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.41666666666</v>
       </c>
     </row>
     <row r="784">
@@ -34516,13 +34516,13 @@
         </is>
       </c>
       <c r="G784" s="3" t="n">
-        <v>46299.75</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>46300.77083333334</v>
+        <v>46300.85416666666</v>
       </c>
       <c r="I784" s="3" t="n">
-        <v>46301.125</v>
+        <v>46301.20833333334</v>
       </c>
     </row>
     <row r="785">
@@ -34557,13 +34557,13 @@
         </is>
       </c>
       <c r="G785" s="3" t="n">
-        <v>46306.08333333334</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>46306.25</v>
+        <v>46306.33333333334</v>
       </c>
       <c r="I785" s="3" t="n">
-        <v>46306.875</v>
+        <v>46306.95833333334</v>
       </c>
     </row>
     <row r="786">
@@ -34598,13 +34598,13 @@
         </is>
       </c>
       <c r="G786" s="3" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.625</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>46308.58333333334</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="I786" s="3" t="n">
-        <v>46308.83333333334</v>
+        <v>46308.91666666666</v>
       </c>
     </row>
     <row r="787">
@@ -34639,13 +34639,13 @@
         </is>
       </c>
       <c r="G787" s="3" t="n">
-        <v>46308.91666666666</v>
+        <v>46309</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>46309.04166666666</v>
+        <v>46309.125</v>
       </c>
       <c r="I787" s="3" t="n">
-        <v>46310.54166666666</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="788">
@@ -34680,13 +34680,13 @@
         </is>
       </c>
       <c r="G788" s="3" t="n">
-        <v>46310.75</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>46310.79166666666</v>
+        <v>46310.875</v>
       </c>
       <c r="I788" s="3" t="n">
-        <v>46311.20833333334</v>
+        <v>46311.29166666666</v>
       </c>
     </row>
     <row r="789">
@@ -34721,13 +34721,13 @@
         </is>
       </c>
       <c r="G789" s="3" t="n">
-        <v>46312.83333333334</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>46313</v>
+        <v>46313.08333333334</v>
       </c>
       <c r="I789" s="3" t="n">
-        <v>46313.54166666666</v>
+        <v>46313.625</v>
       </c>
     </row>
     <row r="790">
@@ -47884,10 +47884,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -47925,7 +47925,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261001-1159-SKED.xlsx)</t>
+          <t>New ETA (auto-20261001-1620-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47942,84 +47942,84 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>0152S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46302.875</v>
+        <v>46298.875</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46302.54166666666</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>0152S</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46305.04166666666</v>
+        <v>46299.75</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -48029,28 +48029,28 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46305.54166666666</v>
+        <v>46306.08333333334</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46305.20833333334</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -48060,94 +48060,94 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46306.83333333334</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46306.5</v>
+        <v>46308.625</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DONGJIN CONFIDENT</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0152N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46309.1875</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46308.85416666666</v>
+        <v>46309</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Early</t>
+          <t>Delay</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46298.29166666666</v>
+        <v>46310.75</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46298.33333333334</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -48158,430 +48158,34 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HOCHIMINH VOYAGER</t>
+          <t>SAWASDEE INCHEON</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>46300.47916666666</v>
+        <v>46312.83333333334</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46300.52083333334</v>
+        <v>46312.91666666666</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46308.35416666666</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>46308.39583333334</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>46310.35416666666</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>46310.39583333334</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>46314.9375</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>46314.97916666666</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>46322.0625</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>46322.10416666666</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>46298.83333333334</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>46298.875</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>46299.70833333334</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>46299.75</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>46306.04166666666</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>46306.08333333334</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>46308.5</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>46308.54166666666</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>46308.875</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>46308.91666666666</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>46310.70833333334</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>46310.75</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>46312.79166666666</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>46312.83333333334</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Delay</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -632,11 +632,11 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-10-02T19:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-10-02T18:00:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46305.20833333334</v>
+        <v>46305.125</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46304.625</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -917,22 +917,20 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH04)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
+          <t>THLCH -&gt; THBKK</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v/>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THBKK ~2026-10-02T03:00:00</t>
+          <t>In transit, ETA 2026-10-02T06:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1047,22 +1045,20 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CNSHK (SHE04)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>CNSHK -&gt; TWKEL</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v/>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to TWKEL ~2026-10-02T02:30:00</t>
+          <t>In transit, ETA 2026-10-03T10:00:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -1303,20 +1299,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>KRUSN -&gt; CNSHA</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v/>
+          <t>CNSHA (SHAW2)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-02T01:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-10-02T19:00:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
@@ -1361,22 +1359,20 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>KRKAN (KAN04)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
+          <t>KRKAN -&gt; CNNGB</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v/>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNNGB ~2026-10-02T04:00:00</t>
+          <t>In transit, ETA 2026-10-03T15:00:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="n"/>
@@ -1597,22 +1593,20 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2608N</t>
-        </is>
+          <t>VNSGN -&gt; KRINC</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v/>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRINC ~2026-10-02T02:00:00</t>
+          <t>In transit, ETA 2026-10-07T10:00:00</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1872,11 +1866,11 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T16:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T17:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46309</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1883,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46308.625</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2109,22 +2103,20 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUSH4)</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
+          <t>KRPUS -&gt; KRKAN</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v/>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-02T03:00:00</t>
+          <t>In transit, ETA 2026-10-02T11:00:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
@@ -5042,7 +5034,7 @@
         <v>46296.79166666666</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>46297.79166666666</v>
+        <v>46297.75</v>
       </c>
     </row>
     <row r="65">
@@ -5077,13 +5069,13 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>46302.54166666666</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.625</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>46303.20833333334</v>
+        <v>46303.125</v>
       </c>
     </row>
     <row r="66">
@@ -5118,13 +5110,13 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46304.625</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>46304.75</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>46305.08333333334</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="67">
@@ -5159,13 +5151,13 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
+        <v>46305.125</v>
+      </c>
+      <c r="H67" s="3" t="n">
         <v>46305.20833333334</v>
       </c>
-      <c r="H67" s="3" t="n">
-        <v>46305.29166666666</v>
-      </c>
       <c r="I67" s="3" t="n">
-        <v>46306.29166666666</v>
+        <v>46306.20833333334</v>
       </c>
     </row>
     <row r="68">
@@ -5200,13 +5192,13 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>46306.5</v>
+        <v>46306.41666666666</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>46306.54166666666</v>
+        <v>46306.45833333334</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>46307.04166666666</v>
+        <v>46306.95833333334</v>
       </c>
     </row>
     <row r="69">
@@ -5241,13 +5233,13 @@
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>46308.85416666666</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>46309.02083333334</v>
+        <v>46308.9375</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>46309.70833333334</v>
+        <v>46309.625</v>
       </c>
     </row>
     <row r="70">
@@ -34437,10 +34429,10 @@
         <v>46296.41666666666</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>46297.25</v>
+        <v>46297.29166666666</v>
       </c>
       <c r="I782" s="3" t="n">
-        <v>46298.66666666666</v>
+        <v>46298.70833333334</v>
       </c>
     </row>
     <row r="783">
@@ -34475,13 +34467,13 @@
         </is>
       </c>
       <c r="G783" s="3" t="n">
-        <v>46298.95833333334</v>
+        <v>46299</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>46299.02083333334</v>
+        <v>46299.0625</v>
       </c>
       <c r="I783" s="3" t="n">
-        <v>46299.41666666666</v>
+        <v>46299.45833333334</v>
       </c>
     </row>
     <row r="784">
@@ -34516,13 +34508,13 @@
         </is>
       </c>
       <c r="G784" s="3" t="n">
-        <v>46299.83333333334</v>
+        <v>46299.875</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>46300.85416666666</v>
+        <v>46300.89583333334</v>
       </c>
       <c r="I784" s="3" t="n">
-        <v>46301.20833333334</v>
+        <v>46301.25</v>
       </c>
     </row>
     <row r="785">
@@ -34557,13 +34549,13 @@
         </is>
       </c>
       <c r="G785" s="3" t="n">
-        <v>46306.16666666666</v>
+        <v>46306.20833333334</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>46306.33333333334</v>
+        <v>46306.375</v>
       </c>
       <c r="I785" s="3" t="n">
-        <v>46306.95833333334</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="786">
@@ -34598,13 +34590,13 @@
         </is>
       </c>
       <c r="G786" s="3" t="n">
-        <v>46308.625</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>46308.66666666666</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="I786" s="3" t="n">
-        <v>46308.91666666666</v>
+        <v>46308.95833333334</v>
       </c>
     </row>
     <row r="787">
@@ -34639,13 +34631,13 @@
         </is>
       </c>
       <c r="G787" s="3" t="n">
-        <v>46309</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>46309.125</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="I787" s="3" t="n">
-        <v>46310.625</v>
+        <v>46310.66666666666</v>
       </c>
     </row>
     <row r="788">
@@ -34680,13 +34672,13 @@
         </is>
       </c>
       <c r="G788" s="3" t="n">
-        <v>46310.83333333334</v>
+        <v>46310.875</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>46310.875</v>
+        <v>46310.91666666666</v>
       </c>
       <c r="I788" s="3" t="n">
-        <v>46311.29166666666</v>
+        <v>46311.33333333334</v>
       </c>
     </row>
     <row r="789">
@@ -34721,13 +34713,13 @@
         </is>
       </c>
       <c r="G789" s="3" t="n">
-        <v>46312.91666666666</v>
+        <v>46312.95833333334</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>46313.08333333334</v>
+        <v>46313.125</v>
       </c>
       <c r="I789" s="3" t="n">
-        <v>46313.625</v>
+        <v>46313.66666666666</v>
       </c>
     </row>
     <row r="790">
@@ -47884,10 +47876,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -47925,7 +47917,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261001-1620-SKED.xlsx)</t>
+          <t>New ETA (auto-20261001-2146-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47942,84 +47934,84 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46298.875</v>
+        <v>46302.54166666666</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46298.95833333334</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>0152S</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46299.75</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46299.83333333334</v>
+        <v>46304.625</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -48029,28 +48021,28 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46306.08333333334</v>
+        <v>46305.20833333334</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46306.16666666666</v>
+        <v>46305.125</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -48060,62 +48052,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46308.54166666666</v>
+        <v>46306.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46308.625</v>
+        <v>46306.41666666666</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>DONGJIN CONFIDENT</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>0152N</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46308.91666666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46309</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Delay</t>
+          <t>Early</t>
         </is>
       </c>
     </row>
@@ -48127,27 +48119,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>KRKAN</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRUSN</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2611S</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46310.75</v>
+        <v>46298.95833333334</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46310.83333333334</v>
+        <v>46299</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -48163,29 +48155,209 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>46299.875</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46306.16666666666</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>46306.20833333334</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46308.625</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46308.66666666666</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>46309.04166666666</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46310.83333333334</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>46310.875</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>KRPUS</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2611N</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>46312.83333333334</v>
-      </c>
-      <c r="F8" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>46312.91666666666</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="F13" s="3" t="n">
+        <v>46312.95833333334</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Delay</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,22 +551,20 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>CNSHK (SHE04)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
+          <t>CNSHK -&gt; TWKEL</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v/>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to TWKEL ~2026-10-02T06:30:00</t>
+          <t>In transit, ETA 2026-10-03T23:00:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -917,24 +915,26 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; THBKK</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v/>
+          <t>THBKK (BKK01)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-02T06:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-10-03T17:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>46297.25</v>
+        <v>46317.79166666666</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="L8" s="3" t="n">
@@ -1463,22 +1463,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>KRINC (INC07)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
+          <t>KRINC -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v/>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-10-02T07:00:00</t>
+          <t>In transit, ETA 2026-10-03T10:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
@@ -2167,20 +2165,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>IDJKT -&gt; IDSRG</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v/>
+          <t>IDSRG (SRG02)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-02T08:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-10-02T22:00:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
@@ -47883,7 +47883,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47912,7 +47912,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (prev)</t>
+          <t>Old ETA (auto-20261001-1620-SKED.xlsx)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -615,22 +615,20 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUS09)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>0152S</t>
-        </is>
+          <t>KRPUS -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v/>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-10-02T18:00:00</t>
+          <t>In transit, ETA 2026-10-07T11:00:00</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
@@ -739,20 +737,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUS05)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9002N</t>
+        </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to RUVVO ~2026-10-03T19:00:00</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -1299,22 +1299,20 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>CNSHA (SHAW2)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2608S</t>
-        </is>
+          <t>CNSHA -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v/>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-10-02T19:00:00</t>
+          <t>In transit, ETA 2026-10-06T17:00:00</t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
@@ -1721,22 +1719,20 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>KRPTK (PTK02)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
+          <t>KRPTK -&gt; KRKAN</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v/>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-02T21:00:00</t>
+          <t>In transit, ETA 2026-10-03T23:00:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
@@ -2039,20 +2035,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>CNSHA -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-02T16:30:00</t>
+          <t>Alongside, departs to THLCH ~2026-10-03T14:30:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -2118,7 +2116,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to HKHKG ~2026-10-02T23:30:00</t>
+          <t>Alongside, departs to HKHKG ~2026-10-02T23:00:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
@@ -40170,7 +40168,7 @@
         <v>46297.52083333334</v>
       </c>
       <c r="I922" s="3" t="n">
-        <v>46297.97916666666</v>
+        <v>46297.95833333334</v>
       </c>
     </row>
     <row r="923">
@@ -47841,14 +47839,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47882,7 +47880,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261002-0824-SKED.xlsx)</t>
+          <t>New ETA (auto-20261002-1532-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47893,3384 +47891,6 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>HEUNG-A HOCHIMINH</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RUVVO</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>9002S</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>46300.58333333334</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>46300.66666666666</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HEUNG-A HOCHIMINH</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>9002S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46304.625</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46304.70833333334</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46298.95833333334</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46299.22916666666</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>46302.79166666666</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46303.0625</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>INCHEON VOYAGER</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46304.58333333334</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>46304.85416666666</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46296.79166666666</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>46296.77083333334</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>46314.625</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>46314.83333333334</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46317.20833333334</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>46317.41666666666</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>46317.79166666666</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>46318</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>46319.625</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>46319.83333333334</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>46321.66666666666</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>46321.875</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>46326.29166666666</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>46326.5</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>46327.54166666666</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>46327.75</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>46328.25</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>46328.45833333334</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>46333.66666666666</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>46333.875</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>46336.25</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>46336.45833333334</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>46336.83333333334</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>46337.04166666666</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>46338.66666666666</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>46338.875</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>46340.70833333334</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>46340.91666666666</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>46344.95833333334</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>46345.16666666666</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>46346.20833333334</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>46346.41666666666</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>46346.91666666666</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>46347.125</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46352.33333333334</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>46352.54166666666</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>46354.91666666666</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>46355.125</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>46355.5</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>46355.70833333334</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>46357.33333333334</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>46357.54166666666</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>46359.375</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>46359.58333333334</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2615S</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>46365.29166666666</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>46365.5</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2615S</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>46366.54166666666</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>46366.75</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2615S</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>46367.25</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>46367.45833333334</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2615S</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>46372.66666666666</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>46372.875</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2615S</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>46375.25</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>46375.45833333334</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>46375.83333333334</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>46376.04166666666</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>46377.66666666666</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>46377.875</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>KMTC BANGKOK</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>46379.70833333334</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>46379.91666666666</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>46299.16666666666</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>46299.08333333334</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>46300.54166666666</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>46300.625</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>46303.625</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>46303.70833333334</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46305.29166666666</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>46305.20833333334</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46306.91666666666</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>46306.83333333334</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>46313.625</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>46313.54166666666</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>46314.25</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>46314.16666666666</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>46315.875</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>46315.79166666666</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>46320.20833333334</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>46320.125</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>46321.66666666666</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>46321.58333333334</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>46324.625</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>46324.54166666666</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>46326.29166666666</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>46326.20833333334</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>46327.91666666666</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>46327.83333333334</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>46334.625</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>46334.54166666666</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>46335.25</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>46335.16666666666</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>46336.875</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>46336.79166666666</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>46341.20833333334</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>46341.125</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>46342.66666666666</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>46342.58333333334</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>46345.625</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>46345.54166666666</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>46347.29166666666</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>46347.20833333334</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>46348.91666666666</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>46348.83333333334</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>46355.625</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>46355.54166666666</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>46356.25</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>46356.16666666666</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>46357.875</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>46357.79166666666</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>46362.20833333334</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>46362.125</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>46363.66666666666</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>46363.58333333334</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>46366.625</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>46366.54166666666</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>46368.29166666666</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>46368.20833333334</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>46369.91666666666</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>46369.83333333334</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>2614S</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>46376.625</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>46376.54166666666</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>46377.25</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>46377.16666666666</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>46378.875</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>46378.79166666666</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>46383.20833333334</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>46383.125</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>KMTC GWANGYANG</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>46384.66666666666</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>46384.58333333334</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>46298.54166666666</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>46298.75</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>46301.83333333334</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>46302</v>
-      </c>
-      <c r="G72" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>46304.75</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>46304.91666666666</v>
-      </c>
-      <c r="G73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>46307.20833333334</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>46307.375</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>46307.58333333334</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>46307.75</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>46309.375</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>46309.54166666666</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>46313.58333333334</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>46313.75</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>46315.16666666666</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>46317.83333333334</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>46318.16666666666</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>46318.91666666666</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>46319.25</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>46322.16666666666</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>46322.5</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>46324.875</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>46325.20833333334</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>2613S</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>46327.25</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>46327.58333333334</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>46327.70833333334</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>46328.04166666666</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>46329.66666666666</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>46330</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>46334.08333333334</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>46334.41666666666</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>KMTC TAIPEIS</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>CNXMN</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>2613N</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>46335.66666666666</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>46336</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>2604E</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>46305.79166666666</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>-43</v>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>46305.79166666666</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>46304</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>-43</v>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>46309.91666666666</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>46307.25</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>-64</v>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>CNNGB</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>2604E</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>46309.20833333334</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>46307.41666666666</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>-43</v>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>CNNGB</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>46312.91666666666</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>46310.29166666666</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>-63</v>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>CNNGB</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n">
-        <v>46317.25</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>46313.375</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>-93</v>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>AEKLF</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>2607W</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>46317.04166666666</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>-119</v>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>MELBOURNE BRIDGE</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>AEKLF</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>2607E</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>46338.125</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>46329.20833333334</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>-214</v>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -818,7 +818,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T03:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T06:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -829,7 +829,7 @@
         <v/>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46314.625</v>
+        <v>46314.75</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>46296.66666666666</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>46298.125</v>
+        <v>46298.25</v>
       </c>
     </row>
     <row r="168">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="G168" s="3" t="n">
-        <v>46298.41666666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="H168" s="3" t="n">
-        <v>46298.47916666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>46299.10416666666</v>
+        <v>46299.22916666666</v>
       </c>
     </row>
     <row r="169">
@@ -9331,13 +9331,13 @@
         </is>
       </c>
       <c r="G169" s="3" t="n">
-        <v>46300.16666666666</v>
+        <v>46300.29166666666</v>
       </c>
       <c r="H169" s="3" t="n">
-        <v>46300.375</v>
+        <v>46300.5</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>46301.04166666666</v>
+        <v>46301.16666666666</v>
       </c>
     </row>
     <row r="170">
@@ -9372,13 +9372,13 @@
         </is>
       </c>
       <c r="G170" s="3" t="n">
-        <v>46308.04166666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="H170" s="3" t="n">
-        <v>46308.125</v>
+        <v>46308.25</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>46308.95833333334</v>
+        <v>46309.08333333334</v>
       </c>
     </row>
     <row r="171">
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>46310.04166666666</v>
+        <v>46310.16666666666</v>
       </c>
       <c r="H171" s="3" t="n">
-        <v>46310.125</v>
+        <v>46310.25</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>46310.625</v>
+        <v>46310.75</v>
       </c>
     </row>
     <row r="172">
@@ -9454,13 +9454,13 @@
         </is>
       </c>
       <c r="G172" s="3" t="n">
-        <v>46314.625</v>
+        <v>46314.75</v>
       </c>
       <c r="H172" s="3" t="n">
-        <v>46314.66666666666</v>
+        <v>46314.79166666666</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>46315.33333333334</v>
+        <v>46315.45833333334</v>
       </c>
     </row>
     <row r="173">
@@ -9495,13 +9495,13 @@
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>46321.75</v>
+        <v>46321.875</v>
       </c>
       <c r="H173" s="3" t="n">
-        <v>46321.95833333334</v>
+        <v>46322.08333333334</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>46322.625</v>
+        <v>46322.75</v>
       </c>
     </row>
     <row r="174">
@@ -47839,14 +47839,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261002-1532-SKED.xlsx)</t>
+          <t>New ETA (auto-20261002-1544-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47891,6 +47891,222 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46298.41666666666</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46298.54166666666</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46308.04166666666</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46308.16666666666</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>IDSRG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46310.04166666666</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>46310.16666666666</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46314.625</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46314.75</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HOCHIMINH VOYAGER</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46321.75</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46321.875</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1235,20 +1235,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v/>
+          <t>KRINC (INC07)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2616S</t>
+        </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to KRPUS ~2026-10-03T15:00:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -2101,22 +2103,20 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>KRKAN (KAN06)</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
+          <t>KRKAN -&gt; HKHKG</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v/>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to HKHKG ~2026-10-02T23:00:00</t>
+          <t>In transit, ETA 2026-10-05T20:00:00</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
@@ -2167,22 +2167,20 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>IDSRG (SRG02)</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
+          <t>IDSRG -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v/>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-10-02T23:00:00</t>
+          <t>In transit, ETA 2026-10-06T16:30:00</t>
         </is>
       </c>
       <c r="I28" s="3" t="n"/>
@@ -47846,7 +47844,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47875,7 +47873,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (prev)</t>
+          <t>Old ETA (auto-20261002-1532-SKED.xlsx)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Full Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Early-Delay" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1109,22 +1109,20 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>IDJKT (JKT02)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
+          <t>IDJKT -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v/>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-10-03T01:00:00</t>
+          <t>In transit, ETA 2026-10-05T10:30:00</t>
         </is>
       </c>
       <c r="I11" s="3" t="n"/>
@@ -47837,14 +47835,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47873,12 +47871,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Old ETA (auto-20261002-1532-SKED.xlsx)</t>
+          <t>Old ETA (prev)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261002-1544-SKED.xlsx)</t>
+          <t>New ETA (auto-20261002-1759-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47889,222 +47887,6 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>46298.41666666666</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>46298.54166666666</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46300.16666666666</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46300.29166666666</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46308.04166666666</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46308.16666666666</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>IDSRG</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>46310.04166666666</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46310.16666666666</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46314.625</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>46314.75</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>HOCHIMINH VOYAGER</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46321.75</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>46321.875</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1525,22 +1525,20 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>KRINC (INC07)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
+          <t>KRINC -&gt; KRPTK</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v/>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPTK ~2026-10-03T02:30:00</t>
+          <t>In transit, ETA 2026-10-03T05:00:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -2223,22 +2221,20 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>HKHKG (HKG03)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>HKHKG -&gt; CNXMN</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v/>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNXMN ~2026-10-03T01:30:00</t>
+          <t>In transit, ETA 2026-10-04T02:00:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
@@ -47876,7 +47872,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261002-1759-SKED.xlsx)</t>
+          <t>New ETA (auto-20261002-2039-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -679,20 +679,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; CNSHA</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v/>
+          <t>CNSHA (SHAW5)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T07:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-10-05T05:00:00</t>
         </is>
       </c>
       <c r="I4" s="3" t="n"/>
@@ -752,7 +754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to RUVVO ~2026-10-03T19:00:00</t>
+          <t>Alongside, departs to RUVVO ~2026-10-03T22:00:00</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -803,22 +805,20 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUS05)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
+          <t>KRPUS -&gt; KRKAN</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v/>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T06:00:00</t>
+          <t>In transit, ETA 2026-10-03T13:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -863,20 +863,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>VNSGN -&gt; HKHKG</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v/>
+          <t>HKHKG (HKG03)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T04:00:00</t>
+          <t>Alongside, departs to CNSHK ~2026-10-04T00:00:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -1525,20 +1527,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>KRINC -&gt; KRPTK</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v/>
+          <t>KRPTK (PTK02)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T05:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T21:00:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -1860,11 +1864,11 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T17:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T20:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46308.875</v>
+        <v>46309.125</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1877,7 +1881,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46308.5</v>
+        <v>46308.75</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -7732,7 +7736,7 @@
         <v>46297.83333333334</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>46298.79166666666</v>
+        <v>46298.91666666666</v>
       </c>
     </row>
     <row r="131">
@@ -7767,13 +7771,13 @@
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>46300.66666666666</v>
+        <v>46300.91666666666</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>46300.70833333334</v>
+        <v>46300.95833333334</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>46302.70833333334</v>
+        <v>46302.95833333334</v>
       </c>
     </row>
     <row r="132">
@@ -7849,13 +7853,13 @@
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46304.95833333334</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>46304.75</v>
+        <v>46305</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>46305.45833333334</v>
+        <v>46305.70833333334</v>
       </c>
     </row>
     <row r="134">
@@ -34387,7 +34391,7 @@
         <v>46297.29166666666</v>
       </c>
       <c r="I781" s="3" t="n">
-        <v>46298.70833333334</v>
+        <v>46298.83333333334</v>
       </c>
     </row>
     <row r="782">
@@ -34422,13 +34426,13 @@
         </is>
       </c>
       <c r="G782" s="3" t="n">
-        <v>46299</v>
+        <v>46299.25</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>46299.0625</v>
+        <v>46299.3125</v>
       </c>
       <c r="I782" s="3" t="n">
-        <v>46299.33333333334</v>
+        <v>46299.58333333334</v>
       </c>
     </row>
     <row r="783">
@@ -34463,13 +34467,13 @@
         </is>
       </c>
       <c r="G783" s="3" t="n">
-        <v>46299.70833333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>46300.75</v>
+        <v>46301</v>
       </c>
       <c r="I783" s="3" t="n">
-        <v>46301.08333333334</v>
+        <v>46301.33333333334</v>
       </c>
     </row>
     <row r="784">
@@ -34504,13 +34508,13 @@
         </is>
       </c>
       <c r="G784" s="3" t="n">
-        <v>46306.04166666666</v>
+        <v>46306.29166666666</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>46306.20833333334</v>
+        <v>46306.45833333334</v>
       </c>
       <c r="I784" s="3" t="n">
-        <v>46306.83333333334</v>
+        <v>46307.08333333334</v>
       </c>
     </row>
     <row r="785">
@@ -34545,13 +34549,13 @@
         </is>
       </c>
       <c r="G785" s="3" t="n">
-        <v>46308.5</v>
+        <v>46308.75</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>46308.54166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="I785" s="3" t="n">
-        <v>46308.79166666666</v>
+        <v>46309.04166666666</v>
       </c>
     </row>
     <row r="786">
@@ -34586,13 +34590,13 @@
         </is>
       </c>
       <c r="G786" s="3" t="n">
-        <v>46308.875</v>
+        <v>46309.125</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>46309</v>
+        <v>46309.25</v>
       </c>
       <c r="I786" s="3" t="n">
-        <v>46310.5</v>
+        <v>46310.75</v>
       </c>
     </row>
     <row r="787">
@@ -34627,13 +34631,13 @@
         </is>
       </c>
       <c r="G787" s="3" t="n">
-        <v>46310.70833333334</v>
+        <v>46310.95833333334</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>46310.75</v>
+        <v>46311</v>
       </c>
       <c r="I787" s="3" t="n">
-        <v>46311.16666666666</v>
+        <v>46311.41666666666</v>
       </c>
     </row>
     <row r="788">
@@ -34668,13 +34672,13 @@
         </is>
       </c>
       <c r="G788" s="3" t="n">
-        <v>46312.79166666666</v>
+        <v>46313.04166666666</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>46312.95833333334</v>
+        <v>46313.20833333334</v>
       </c>
       <c r="I788" s="3" t="n">
-        <v>46313.5</v>
+        <v>46313.75</v>
       </c>
     </row>
     <row r="789">
@@ -47831,14 +47835,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47872,7 +47876,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261002-2039-SKED.xlsx)</t>
+          <t>New ETA (auto-20261003-0025-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47883,6 +47887,330 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>HEUNG-A HOCHIMINH</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>RUVVO</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>9002S</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>HEUNG-A HOCHIMINH</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>9002S</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46304.70833333334</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46304.95833333334</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46299.25</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46299.70833333334</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46306.04166666666</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46308.5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46308.75</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46308.875</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>46309.125</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46310.70833333334</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>46310.95833333334</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46312.79166666666</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46313.04166666666</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -1169,22 +1169,20 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUSH4)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
+          <t>KRPUS -&gt; KRKAN</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v/>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T11:00:00</t>
+          <t>In transit, ETA 2026-10-03T18:00:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1463,20 +1461,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>KRINC -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUS05)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T10:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-10-04T11:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>46309.20833333334</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>46308.6875</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>46299.02083333334</v>
       </c>
       <c r="I707" s="3" t="n">
-        <v>46299.45833333334</v>
+        <v>46299.75</v>
       </c>
     </row>
     <row r="708">
@@ -31396,13 +31396,13 @@
         </is>
       </c>
       <c r="G708" s="3" t="n">
-        <v>46299.79166666666</v>
+        <v>46300.125</v>
       </c>
       <c r="H708" s="3" t="n">
-        <v>46299.83333333334</v>
+        <v>46300.16666666666</v>
       </c>
       <c r="I708" s="3" t="n">
-        <v>46300.75</v>
+        <v>46301.08333333334</v>
       </c>
     </row>
     <row r="709">
@@ -31437,13 +31437,13 @@
         </is>
       </c>
       <c r="G709" s="3" t="n">
-        <v>46306.16666666666</v>
+        <v>46306.5</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>46306.33333333334</v>
+        <v>46306.66666666666</v>
       </c>
       <c r="I709" s="3" t="n">
-        <v>46306.91666666666</v>
+        <v>46307.25</v>
       </c>
     </row>
     <row r="710">
@@ -31478,13 +31478,13 @@
         </is>
       </c>
       <c r="G710" s="3" t="n">
-        <v>46308.6875</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="H710" s="3" t="n">
-        <v>46308.72916666666</v>
+        <v>46309.0625</v>
       </c>
       <c r="I710" s="3" t="n">
-        <v>46309.08333333334</v>
+        <v>46309.41666666666</v>
       </c>
     </row>
     <row r="711">
@@ -31519,13 +31519,13 @@
         </is>
       </c>
       <c r="G711" s="3" t="n">
-        <v>46309.20833333334</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="H711" s="3" t="n">
-        <v>46309.29166666666</v>
+        <v>46309.625</v>
       </c>
       <c r="I711" s="3" t="n">
-        <v>46310.29166666666</v>
+        <v>46310.625</v>
       </c>
     </row>
     <row r="712">
@@ -31560,13 +31560,13 @@
         </is>
       </c>
       <c r="G712" s="3" t="n">
-        <v>46310.5</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="H712" s="3" t="n">
-        <v>46310.54166666666</v>
+        <v>46310.875</v>
       </c>
       <c r="I712" s="3" t="n">
-        <v>46311.04166666666</v>
+        <v>46311.375</v>
       </c>
     </row>
     <row r="713">
@@ -31601,13 +31601,13 @@
         </is>
       </c>
       <c r="G713" s="3" t="n">
-        <v>46312.85416666666</v>
+        <v>46313.1875</v>
       </c>
       <c r="H713" s="3" t="n">
-        <v>46313.02083333334</v>
+        <v>46313.35416666666</v>
       </c>
       <c r="I713" s="3" t="n">
-        <v>46313.70833333334</v>
+        <v>46314.04166666666</v>
       </c>
     </row>
     <row r="714">
@@ -47835,10 +47835,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -47876,7 +47876,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261003-0025-SKED.xlsx)</t>
+          <t>New ETA (auto-20261003-0441-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47893,32 +47893,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HEUNG-A HOCHIMINH</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>RUVVO</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>9002S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46300.66666666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46300.91666666666</v>
+        <v>46300.125</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -47929,32 +47929,32 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HEUNG-A HOCHIMINH</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>9002S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46304.70833333334</v>
+        <v>46306.16666666666</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46304.95833333334</v>
+        <v>46306.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -47965,32 +47965,32 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616S</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>46299</v>
+        <v>46308.6875</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46299.25</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -48001,32 +48001,32 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>THBKK</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>THLCH</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46299.70833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46299.95833333334</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -48037,32 +48037,32 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>46306.04166666666</v>
+        <v>46310.5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46306.29166666666</v>
+        <v>46310.83333333334</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -48073,142 +48073,34 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SAWASDEE INCHEON</t>
+          <t>SAWASDEE BALTIC</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>THLCH</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>THBKK</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2611S</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>46308.5</v>
+        <v>46312.85416666666</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46308.75</v>
+        <v>46313.1875</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>46308.875</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>46309.125</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46310.70833333334</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>46310.95833333334</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>46312.79166666666</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>46313.04166666666</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Delay</t>
         </is>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -805,20 +805,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>KRPUS -&gt; KRKAN</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v/>
+          <t>KRKAN (KAN04)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T13:00:00</t>
+          <t>Alongside, departs to CNSHA ~2026-10-04T05:30:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -1047,20 +1049,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CNSHK -&gt; TWKEL</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v/>
+          <t>TWKEL (KEL02)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T13:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-10-04T06:00:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -47835,14 +47839,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47876,7 +47880,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261003-0441-SKED.xlsx)</t>
+          <t>New ETA (auto-20261003-0623-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47887,222 +47891,6 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>46299.79166666666</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>46300.125</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46306.16666666666</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46306.5</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46308.6875</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46309.02083333334</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>46309.20833333334</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46309.54166666666</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46310.5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>46310.83333333334</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE BALTIC</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>KRINC</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2616N</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46312.85416666666</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>46313.1875</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to RUVVO ~2026-10-03T22:00:00</t>
+          <t>Alongside, departs to RUVVO ~2026-10-03T21:00:00</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -919,22 +919,20 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>THBKK (BKK01)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>THBKK -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v/>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-10-03T17:00:00</t>
+          <t>In transit, ETA 2026-10-03T22:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1173,20 +1171,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>KRPUS -&gt; KRKAN</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v/>
+          <t>KRKAN (KAN06)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T18:00:00</t>
+          <t>Alongside, departs to HKHKG ~2026-10-04T03:30:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1237,22 +1237,20 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>KRINC (INC07)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
+          <t>KRINC -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v/>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-10-03T15:00:00</t>
+          <t>In transit, ETA 2026-10-04T17:00:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -1868,11 +1866,11 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T20:00:00</t>
+          <t>Alongside, departs to KRKAN ~2026-10-03T21:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46309.125</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1885,7 +1883,7 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46308.75</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2041,26 +2039,24 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>VNSGN (SGN03)</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
+          <t>VNSGN -&gt; THLCH</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v/>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-10-03T14:30:00</t>
+          <t>In transit, ETA 2026-10-05T06:00:00</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46300.8125</v>
+        <v>46300.875</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2073,7 +2069,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>46300.1875</v>
+        <v>46300.25</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -7740,7 +7736,7 @@
         <v>46297.83333333334</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>46298.91666666666</v>
+        <v>46298.875</v>
       </c>
     </row>
     <row r="131">
@@ -7775,13 +7771,13 @@
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>46300.91666666666</v>
+        <v>46300.83333333334</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>46300.95833333334</v>
+        <v>46300.875</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>46302.95833333334</v>
+        <v>46302.875</v>
       </c>
     </row>
     <row r="132">
@@ -7857,13 +7853,13 @@
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>46304.95833333334</v>
+        <v>46304.875</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>46305</v>
+        <v>46304.91666666666</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>46305.70833333334</v>
+        <v>46305.625</v>
       </c>
     </row>
     <row r="134">
@@ -34395,7 +34391,7 @@
         <v>46297.29166666666</v>
       </c>
       <c r="I781" s="3" t="n">
-        <v>46298.83333333334</v>
+        <v>46298.875</v>
       </c>
     </row>
     <row r="782">
@@ -34430,13 +34426,13 @@
         </is>
       </c>
       <c r="G782" s="3" t="n">
-        <v>46299.25</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>46299.3125</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="I782" s="3" t="n">
-        <v>46299.58333333334</v>
+        <v>46299.66666666666</v>
       </c>
     </row>
     <row r="783">
@@ -34471,13 +34467,13 @@
         </is>
       </c>
       <c r="G783" s="3" t="n">
-        <v>46299.95833333334</v>
+        <v>46300.04166666666</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>46301</v>
+        <v>46301.08333333334</v>
       </c>
       <c r="I783" s="3" t="n">
-        <v>46301.33333333334</v>
+        <v>46301.41666666666</v>
       </c>
     </row>
     <row r="784">
@@ -34512,13 +34508,13 @@
         </is>
       </c>
       <c r="G784" s="3" t="n">
-        <v>46306.29166666666</v>
+        <v>46306.375</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>46306.45833333334</v>
+        <v>46306.54166666666</v>
       </c>
       <c r="I784" s="3" t="n">
-        <v>46307.08333333334</v>
+        <v>46307.16666666666</v>
       </c>
     </row>
     <row r="785">
@@ -34553,13 +34549,13 @@
         </is>
       </c>
       <c r="G785" s="3" t="n">
-        <v>46308.75</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>46308.79166666666</v>
+        <v>46308.875</v>
       </c>
       <c r="I785" s="3" t="n">
-        <v>46309.04166666666</v>
+        <v>46309.125</v>
       </c>
     </row>
     <row r="786">
@@ -34594,13 +34590,13 @@
         </is>
       </c>
       <c r="G786" s="3" t="n">
-        <v>46309.125</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>46309.25</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="I786" s="3" t="n">
-        <v>46310.75</v>
+        <v>46310.83333333334</v>
       </c>
     </row>
     <row r="787">
@@ -34635,13 +34631,13 @@
         </is>
       </c>
       <c r="G787" s="3" t="n">
-        <v>46310.95833333334</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>46311</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="I787" s="3" t="n">
-        <v>46311.41666666666</v>
+        <v>46311.5</v>
       </c>
     </row>
     <row r="788">
@@ -34676,13 +34672,13 @@
         </is>
       </c>
       <c r="G788" s="3" t="n">
-        <v>46313.04166666666</v>
+        <v>46313.125</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>46313.20833333334</v>
+        <v>46313.29166666666</v>
       </c>
       <c r="I788" s="3" t="n">
-        <v>46313.75</v>
+        <v>46313.83333333334</v>
       </c>
     </row>
     <row r="789">
@@ -38814,10 +38810,10 @@
         <v>46297.6875</v>
       </c>
       <c r="H889" s="3" t="n">
-        <v>46298.25</v>
+        <v>46298.3125</v>
       </c>
       <c r="I889" s="3" t="n">
-        <v>46298.60416666666</v>
+        <v>46298.66666666666</v>
       </c>
     </row>
     <row r="890">
@@ -38852,13 +38848,13 @@
         </is>
       </c>
       <c r="G890" s="3" t="n">
-        <v>46300.1875</v>
+        <v>46300.25</v>
       </c>
       <c r="H890" s="3" t="n">
-        <v>46300.22916666666</v>
+        <v>46300.29166666666</v>
       </c>
       <c r="I890" s="3" t="n">
-        <v>46300.64583333334</v>
+        <v>46300.70833333334</v>
       </c>
     </row>
     <row r="891">
@@ -38893,13 +38889,13 @@
         </is>
       </c>
       <c r="G891" s="3" t="n">
-        <v>46300.8125</v>
+        <v>46300.875</v>
       </c>
       <c r="H891" s="3" t="n">
-        <v>46300.9375</v>
+        <v>46301</v>
       </c>
       <c r="I891" s="3" t="n">
-        <v>46301.9375</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="892">
@@ -38934,13 +38930,13 @@
         </is>
       </c>
       <c r="G892" s="3" t="n">
-        <v>46302.1875</v>
+        <v>46302.25</v>
       </c>
       <c r="H892" s="3" t="n">
-        <v>46302.22916666666</v>
+        <v>46302.29166666666</v>
       </c>
       <c r="I892" s="3" t="n">
-        <v>46302.64583333334</v>
+        <v>46302.70833333334</v>
       </c>
     </row>
     <row r="893">
@@ -38975,13 +38971,13 @@
         </is>
       </c>
       <c r="G893" s="3" t="n">
-        <v>46304.14583333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="H893" s="3" t="n">
-        <v>46304.3125</v>
+        <v>46304.375</v>
       </c>
       <c r="I893" s="3" t="n">
-        <v>46304.8125</v>
+        <v>46304.875</v>
       </c>
     </row>
     <row r="894">
@@ -39016,13 +39012,13 @@
         </is>
       </c>
       <c r="G894" s="3" t="n">
-        <v>46309.83333333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="H894" s="3" t="n">
-        <v>46309.89583333334</v>
+        <v>46309.95833333334</v>
       </c>
       <c r="I894" s="3" t="n">
-        <v>46310.14583333334</v>
+        <v>46310.20833333334</v>
       </c>
     </row>
     <row r="895">
@@ -39057,13 +39053,13 @@
         </is>
       </c>
       <c r="G895" s="3" t="n">
-        <v>46311.08333333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>46311.14583333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="I895" s="3" t="n">
-        <v>46311.5625</v>
+        <v>46311.625</v>
       </c>
     </row>
     <row r="896">
@@ -39098,13 +39094,13 @@
         </is>
       </c>
       <c r="G896" s="3" t="n">
-        <v>46311.89583333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="H896" s="3" t="n">
-        <v>46311.9375</v>
+        <v>46312</v>
       </c>
       <c r="I896" s="3" t="n">
-        <v>46312.5625</v>
+        <v>46312.625</v>
       </c>
     </row>
     <row r="897">
@@ -39139,13 +39135,13 @@
         </is>
       </c>
       <c r="G897" s="3" t="n">
-        <v>46313.64583333334</v>
+        <v>46313.70833333334</v>
       </c>
       <c r="H897" s="3" t="n">
-        <v>46313.8125</v>
+        <v>46313.875</v>
       </c>
       <c r="I897" s="3" t="n">
-        <v>46314.8125</v>
+        <v>46314.875</v>
       </c>
     </row>
     <row r="898">
@@ -39180,13 +39176,13 @@
         </is>
       </c>
       <c r="G898" s="3" t="n">
-        <v>46319.02083333334</v>
+        <v>46319.08333333334</v>
       </c>
       <c r="H898" s="3" t="n">
-        <v>46319.14583333334</v>
+        <v>46319.20833333334</v>
       </c>
       <c r="I898" s="3" t="n">
-        <v>46319.64583333334</v>
+        <v>46319.70833333334</v>
       </c>
     </row>
     <row r="899">
@@ -39221,13 +39217,13 @@
         </is>
       </c>
       <c r="G899" s="3" t="n">
-        <v>46321.22916666666</v>
+        <v>46321.29166666666</v>
       </c>
       <c r="H899" s="3" t="n">
-        <v>46321.27083333334</v>
+        <v>46321.33333333334</v>
       </c>
       <c r="I899" s="3" t="n">
-        <v>46321.6875</v>
+        <v>46321.75</v>
       </c>
     </row>
     <row r="900">
@@ -39262,13 +39258,13 @@
         </is>
       </c>
       <c r="G900" s="3" t="n">
-        <v>46321.85416666666</v>
+        <v>46321.91666666666</v>
       </c>
       <c r="H900" s="3" t="n">
-        <v>46321.97916666666</v>
+        <v>46322.04166666666</v>
       </c>
       <c r="I900" s="3" t="n">
-        <v>46322.97916666666</v>
+        <v>46323.04166666666</v>
       </c>
     </row>
     <row r="901">
@@ -39303,13 +39299,13 @@
         </is>
       </c>
       <c r="G901" s="3" t="n">
-        <v>46323.22916666666</v>
+        <v>46323.29166666666</v>
       </c>
       <c r="H901" s="3" t="n">
-        <v>46323.27083333334</v>
+        <v>46323.33333333334</v>
       </c>
       <c r="I901" s="3" t="n">
-        <v>46323.6875</v>
+        <v>46323.75</v>
       </c>
     </row>
     <row r="902">
@@ -39344,13 +39340,13 @@
         </is>
       </c>
       <c r="G902" s="3" t="n">
-        <v>46325.1875</v>
+        <v>46325.25</v>
       </c>
       <c r="H902" s="3" t="n">
-        <v>46325.3125</v>
+        <v>46325.375</v>
       </c>
       <c r="I902" s="3" t="n">
-        <v>46325.8125</v>
+        <v>46325.875</v>
       </c>
     </row>
     <row r="903">
@@ -39385,13 +39381,13 @@
         </is>
       </c>
       <c r="G903" s="3" t="n">
-        <v>46332.375</v>
+        <v>46332.4375</v>
       </c>
       <c r="H903" s="3" t="n">
-        <v>46332.4375</v>
+        <v>46332.5</v>
       </c>
       <c r="I903" s="3" t="n">
-        <v>46332.6875</v>
+        <v>46332.75</v>
       </c>
     </row>
     <row r="904">
@@ -39426,13 +39422,13 @@
         </is>
       </c>
       <c r="G904" s="3" t="n">
-        <v>46333.625</v>
+        <v>46333.6875</v>
       </c>
       <c r="H904" s="3" t="n">
-        <v>46333.6875</v>
+        <v>46333.75</v>
       </c>
       <c r="I904" s="3" t="n">
-        <v>46334.10416666666</v>
+        <v>46334.16666666666</v>
       </c>
     </row>
     <row r="905">
@@ -39467,13 +39463,13 @@
         </is>
       </c>
       <c r="G905" s="3" t="n">
-        <v>46334.4375</v>
+        <v>46334.5</v>
       </c>
       <c r="H905" s="3" t="n">
-        <v>46334.47916666666</v>
+        <v>46334.54166666666</v>
       </c>
       <c r="I905" s="3" t="n">
-        <v>46335.10416666666</v>
+        <v>46335.16666666666</v>
       </c>
     </row>
     <row r="906">
@@ -39508,13 +39504,13 @@
         </is>
       </c>
       <c r="G906" s="3" t="n">
-        <v>46336.18472222222</v>
+        <v>46336.24722222222</v>
       </c>
       <c r="H906" s="3" t="n">
-        <v>46336.35138888889</v>
+        <v>46336.41388888889</v>
       </c>
       <c r="I906" s="3" t="n">
-        <v>46337.35138888889</v>
+        <v>46337.41388888889</v>
       </c>
     </row>
     <row r="907">
@@ -39549,13 +39545,13 @@
         </is>
       </c>
       <c r="G907" s="3" t="n">
-        <v>46341.55972222222</v>
+        <v>46341.62222222222</v>
       </c>
       <c r="H907" s="3" t="n">
-        <v>46341.68472222222</v>
+        <v>46341.74722222222</v>
       </c>
       <c r="I907" s="3" t="n">
-        <v>46342.18472222222</v>
+        <v>46342.24722222222</v>
       </c>
     </row>
     <row r="908">
@@ -39590,13 +39586,13 @@
         </is>
       </c>
       <c r="G908" s="3" t="n">
-        <v>46343.76805555556</v>
+        <v>46343.83055555556</v>
       </c>
       <c r="H908" s="3" t="n">
-        <v>46343.80972222222</v>
+        <v>46343.87222222222</v>
       </c>
       <c r="I908" s="3" t="n">
-        <v>46344.22638888889</v>
+        <v>46344.28888888889</v>
       </c>
     </row>
     <row r="909">
@@ -39631,13 +39627,13 @@
         </is>
       </c>
       <c r="G909" s="3" t="n">
-        <v>46344.39305555556</v>
+        <v>46344.45555555556</v>
       </c>
       <c r="H909" s="3" t="n">
-        <v>46344.51805555556</v>
+        <v>46344.58055555556</v>
       </c>
       <c r="I909" s="3" t="n">
-        <v>46345.51805555556</v>
+        <v>46345.58055555556</v>
       </c>
     </row>
     <row r="910">
@@ -39672,13 +39668,13 @@
         </is>
       </c>
       <c r="G910" s="3" t="n">
-        <v>46345.76805555556</v>
+        <v>46345.83055555556</v>
       </c>
       <c r="H910" s="3" t="n">
-        <v>46345.80972222222</v>
+        <v>46345.87222222222</v>
       </c>
       <c r="I910" s="3" t="n">
-        <v>46346.22638888889</v>
+        <v>46346.28888888889</v>
       </c>
     </row>
     <row r="911">
@@ -39713,13 +39709,13 @@
         </is>
       </c>
       <c r="G911" s="3" t="n">
-        <v>46347.72638888889</v>
+        <v>46347.78888888889</v>
       </c>
       <c r="H911" s="3" t="n">
-        <v>46347.85138888889</v>
+        <v>46347.91388888889</v>
       </c>
       <c r="I911" s="3" t="n">
-        <v>46348.35138888889</v>
+        <v>46348.41388888889</v>
       </c>
     </row>
     <row r="912">
@@ -39754,13 +39750,13 @@
         </is>
       </c>
       <c r="G912" s="3" t="n">
-        <v>46353.37222222222</v>
+        <v>46353.43472222222</v>
       </c>
       <c r="H912" s="3" t="n">
-        <v>46353.43472222222</v>
+        <v>46353.49722222222</v>
       </c>
       <c r="I912" s="3" t="n">
-        <v>46353.68472222222</v>
+        <v>46353.74722222222</v>
       </c>
     </row>
     <row r="913">
@@ -39795,13 +39791,13 @@
         </is>
       </c>
       <c r="G913" s="3" t="n">
-        <v>46354.62222222222</v>
+        <v>46354.68472222222</v>
       </c>
       <c r="H913" s="3" t="n">
-        <v>46354.68472222222</v>
+        <v>46354.74722222222</v>
       </c>
       <c r="I913" s="3" t="n">
-        <v>46355.10138888889</v>
+        <v>46355.16388888889</v>
       </c>
     </row>
     <row r="914">
@@ -39836,13 +39832,13 @@
         </is>
       </c>
       <c r="G914" s="3" t="n">
-        <v>46355.43472222222</v>
+        <v>46355.49722222222</v>
       </c>
       <c r="H914" s="3" t="n">
-        <v>46355.47638888889</v>
+        <v>46355.53888888889</v>
       </c>
       <c r="I914" s="3" t="n">
-        <v>46356.10138888889</v>
+        <v>46356.16388888889</v>
       </c>
     </row>
     <row r="915">
@@ -39877,13 +39873,13 @@
         </is>
       </c>
       <c r="G915" s="3" t="n">
-        <v>46357.18194444444</v>
+        <v>46357.24444444444</v>
       </c>
       <c r="H915" s="3" t="n">
-        <v>46357.34861111111</v>
+        <v>46357.41111111111</v>
       </c>
       <c r="I915" s="3" t="n">
-        <v>46358.34861111111</v>
+        <v>46358.41111111111</v>
       </c>
     </row>
     <row r="916">
@@ -39918,13 +39914,13 @@
         </is>
       </c>
       <c r="G916" s="3" t="n">
-        <v>46362.55694444444</v>
+        <v>46362.61944444444</v>
       </c>
       <c r="H916" s="3" t="n">
-        <v>46362.68194444444</v>
+        <v>46362.74444444444</v>
       </c>
       <c r="I916" s="3" t="n">
-        <v>46363.18194444444</v>
+        <v>46363.24444444444</v>
       </c>
     </row>
     <row r="917">
@@ -39959,13 +39955,13 @@
         </is>
       </c>
       <c r="G917" s="3" t="n">
-        <v>46364.76527777778</v>
+        <v>46364.82777777778</v>
       </c>
       <c r="H917" s="3" t="n">
-        <v>46364.80694444444</v>
+        <v>46364.86944444444</v>
       </c>
       <c r="I917" s="3" t="n">
-        <v>46365.22361111111</v>
+        <v>46365.28611111111</v>
       </c>
     </row>
     <row r="918">
@@ -40000,13 +39996,13 @@
         </is>
       </c>
       <c r="G918" s="3" t="n">
-        <v>46365.39027777778</v>
+        <v>46365.45277777778</v>
       </c>
       <c r="H918" s="3" t="n">
-        <v>46365.51527777778</v>
+        <v>46365.57777777778</v>
       </c>
       <c r="I918" s="3" t="n">
-        <v>46366.51527777778</v>
+        <v>46366.57777777778</v>
       </c>
     </row>
     <row r="919">
@@ -40041,13 +40037,13 @@
         </is>
       </c>
       <c r="G919" s="3" t="n">
-        <v>46366.76527777778</v>
+        <v>46366.82777777778</v>
       </c>
       <c r="H919" s="3" t="n">
-        <v>46366.80694444444</v>
+        <v>46366.86944444444</v>
       </c>
       <c r="I919" s="3" t="n">
-        <v>46367.22361111111</v>
+        <v>46367.28611111111</v>
       </c>
     </row>
     <row r="920">
@@ -40080,13 +40076,13 @@
         <v/>
       </c>
       <c r="G920" s="3" t="n">
-        <v>46368.72361111111</v>
+        <v>46368.78611111111</v>
       </c>
       <c r="H920" s="3" t="n">
-        <v>46368.84861111111</v>
+        <v>46368.91111111111</v>
       </c>
       <c r="I920" s="3" t="n">
-        <v>46369.34861111111</v>
+        <v>46369.41111111111</v>
       </c>
     </row>
     <row r="921">
@@ -47839,14 +47835,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47880,7 +47876,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261003-0623-SKED.xlsx)</t>
+          <t>New ETA (auto-20261003-1227-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47891,6 +47887,1444 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>HEUNG-A HOCHIMINH</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>RUVVO</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>9002S</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>HEUNG-A HOCHIMINH</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>9002S</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46304.95833333334</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46304.875</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46299.25</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>KRUSN</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46306.29166666666</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46306.375</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46308.75</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46308.83333333334</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46309.125</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>46309.20833333334</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46310.95833333334</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>46311.04166666666</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE INCHEON</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>46313.04166666666</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46313.125</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>46300.1875</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>46300.25</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46300.8125</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>46300.875</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>46302.1875</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>46302.25</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>46304.14583333334</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>46304.20833333334</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>46309.83333333334</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>46309.89583333334</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>46311.08333333334</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>46311.14583333334</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>46311.89583333334</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46311.95833333334</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>46313.64583333334</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>46313.70833333334</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>46319.02083333334</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>46319.08333333334</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>46321.22916666666</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>46321.29166666666</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>46321.85416666666</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>46321.91666666666</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46323.22916666666</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>46323.29166666666</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>46325.1875</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46325.25</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46332.375</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>46332.4375</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>46333.625</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>46333.6875</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46334.4375</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>46334.5</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>46336.18472222222</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>46336.24722222222</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46341.55972222222</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>46341.62222222222</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>46343.76805555556</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>46343.83055555556</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46344.39305555556</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>46344.45555555556</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>46345.76805555556</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>46345.83055555556</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46347.72638888889</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>46347.78888888889</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>46353.37222222222</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>46353.43472222222</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>46354.62222222222</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>46354.68472222222</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>46355.43472222222</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46355.49722222222</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46357.18194444444</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46357.24444444444</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46362.55694444444</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46362.61944444444</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46364.76527777778</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46364.82777777778</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>46365.39027777778</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46365.45277777778</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>46366.76527777778</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46366.82777777778</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE SPICA</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>46368.72361111111</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46368.78611111111</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -551,20 +551,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>CNSHK -&gt; TWKEL</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v/>
+          <t>TWKEL (KEL02)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2614N</t>
+        </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T23:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-10-04T18:00:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -739,22 +741,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUS05)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9002N</t>
-        </is>
+          <t>KRPUS -&gt; RUVVO</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v/>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to RUVVO ~2026-10-03T21:00:00</t>
+          <t>In transit, ETA 2026-10-05T20:00:00</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -865,22 +865,20 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>HKHKG (HKG03)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
+          <t>HKHKG -&gt; CNSHK</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v/>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNSHK ~2026-10-04T00:00:00</t>
+          <t>In transit, ETA 2026-10-04T05:30:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -919,20 +917,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>THBKK -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH04)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T22:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-10-04T09:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>46298.91666666666</v>
+        <v>46317.41666666666</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612S</t>
         </is>
       </c>
     </row>
@@ -1359,20 +1359,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>KRKAN -&gt; CNNGB</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v/>
+          <t>CNNGB (NGB01)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2607W</t>
+        </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T23:00:00</t>
+          <t>Alongside, departs to CNSHK ~2026-10-05T13:00:00</t>
         </is>
       </c>
       <c r="I15" s="3" t="n"/>
@@ -1529,22 +1531,20 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>KRPTK (PTK02)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
+          <t>KRPTK -&gt; KRKAN</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v/>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T21:00:00</t>
+          <t>In transit, ETA 2026-10-04T18:00:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -1659,20 +1659,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>HKHKG -&gt; VNSGN</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v/>
+          <t>VNSGN (SGN03)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T21:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-10-04T14:00:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
@@ -1723,20 +1725,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>KRPTK -&gt; KRKAN</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v/>
+          <t>KRKAN (KAN04)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2616S</t>
+        </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T23:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-10-04T18:00:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
@@ -1851,22 +1855,20 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUS05)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
+          <t>KRPUS -&gt; KRKAN</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v/>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRKAN ~2026-10-03T21:00:00</t>
+          <t>In transit, ETA 2026-10-04T08:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
@@ -2289,20 +2291,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>VNSGN -&gt; HKHKG</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v/>
+          <t>HKHKG (HKG03)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-03T21:00:00</t>
+          <t>Alongside, departs to CNSHK ~2026-10-04T10:30:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
@@ -47835,14 +47839,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47876,7 +47880,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261003-1227-SKED.xlsx)</t>
+          <t>New ETA (auto-20261003-1712-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47887,1444 +47891,6 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>HEUNG-A HOCHIMINH</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RUVVO</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>9002S</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>46300.91666666666</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>46300.83333333334</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HEUNG-A HOCHIMINH</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>9002S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>46304.95833333334</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>46304.875</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Early</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>46299.25</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>46299.33333333334</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>KRUSN</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>46299.95833333334</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>46300.04166666666</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>46306.29166666666</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>46306.375</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>46308.75</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>46308.83333333334</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>46309.125</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>46309.20833333334</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>46310.95833333334</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>46311.04166666666</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE INCHEON</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>46313.04166666666</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>46313.125</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>46300.1875</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>46300.25</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>46300.8125</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>46300.875</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>46302.1875</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>46302.25</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>46304.14583333334</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>46304.20833333334</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>46309.83333333334</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>46309.89583333334</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>46311.08333333334</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>46311.14583333334</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>46311.89583333334</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>46311.95833333334</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>46313.64583333334</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>46313.70833333334</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>46319.02083333334</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>46319.08333333334</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>46321.22916666666</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>46321.29166666666</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>46321.85416666666</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>46321.91666666666</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>46323.22916666666</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>46323.29166666666</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>46325.1875</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>46325.25</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>46332.375</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>46332.4375</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>46333.625</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>46333.6875</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>46334.4375</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>46334.5</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>46336.18472222222</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>46336.24722222222</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>46341.55972222222</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>46341.62222222222</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>46343.76805555556</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>46343.83055555556</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>46344.39305555556</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>46344.45555555556</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>46345.76805555556</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>46345.83055555556</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>46347.72638888889</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>46347.78888888889</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>46353.37222222222</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>46353.43472222222</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>KRKAN</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>46354.62222222222</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>46354.68472222222</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>46355.43472222222</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>46355.49722222222</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>46357.18194444444</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>46357.24444444444</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>46362.55694444444</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>46362.61944444444</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>46364.76527777778</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>46364.82777777778</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>THBKK</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>46365.39027777778</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>46365.45277777778</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>46366.76527777778</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>46366.82777777778</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>SAWASDEE SPICA</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>46368.72361111111</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>46368.78611111111</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Delay</t>
         </is>
       </c>
     </row>

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -983,20 +983,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>THLCH -&gt; HKHKG</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v/>
+          <t>HKHKG (HKG03)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-04T02:00:00</t>
+          <t>Alongside, departs to CNXMN ~2026-10-04T18:30:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
@@ -1171,22 +1173,20 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>KRKAN (KAN06)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2612S</t>
-        </is>
+          <t>KRKAN -&gt; HKHKG</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v/>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to HKHKG ~2026-10-04T03:30:00</t>
+          <t>In transit, ETA 2026-10-07T00:00:00</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -2227,20 +2227,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>HKHKG -&gt; CNXMN</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v/>
+          <t>CNXMN (XMN01)</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-04T02:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-10-04T18:30:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
@@ -47880,7 +47882,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261003-1712-SKED.xlsx)</t>
+          <t>New ETA (auto-20261003-2108-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -805,22 +805,20 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>KRKAN (KAN04)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
+          <t>KRKAN -&gt; CNSHA</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v/>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNSHA ~2026-10-04T05:30:00</t>
+          <t>In transit, ETA 2026-10-05T07:00:00</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
@@ -865,20 +863,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>HKHKG -&gt; CNSHK</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v/>
+          <t>CNSHK (SHE04)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-04T05:30:00</t>
+          <t>Alongside, departs to KRINC ~2026-10-04T18:30:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -1049,22 +1049,20 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>TWKEL (KEL02)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>TWKEL -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v/>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-10-04T06:00:00</t>
+          <t>In transit, ETA 2026-10-06T03:00:00</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -47882,7 +47880,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261003-2108-SKED.xlsx)</t>
+          <t>New ETA (auto-20261003-2345-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -917,22 +917,20 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH04)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>THLCH -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v/>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-10-04T09:00:00</t>
+          <t>In transit, ETA 2026-10-06T00:00:00</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
@@ -1463,22 +1461,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>KRPUS (PUS05)</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
+          <t>KRPUS -&gt; VNSGN</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v/>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to VNSGN ~2026-10-04T11:00:00</t>
+          <t>In transit, ETA 2026-10-09T16:00:00</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
@@ -1789,20 +1785,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CNSHA -&gt; THLCH</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v/>
+          <t>THLCH (LCH05)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-04T11:00:00</t>
+          <t>Alongside, departs to THBKK ~2026-10-04T19:00:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -1819,7 +1817,7 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46299.45833333334</v>
+        <v>46302.70833333334</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1828,7 +1826,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2610S</t>
+          <t>2610N</t>
         </is>
       </c>
     </row>
@@ -1853,20 +1851,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>KRPUS -&gt; KRKAN</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v/>
+          <t>KRKAN (KAN06)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2611S</t>
+        </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-04T08:00:00</t>
+          <t>Alongside, departs to KRUSN ~2026-10-04T16:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
@@ -1917,20 +1917,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>nodata</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v/>
+          <t>KRPTK (PTK02)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>No data in window</t>
+          <t>Alongside, departs to KRKAN ~2026-10-05T04:00:00</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
@@ -2291,22 +2293,20 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>HKHKG (HKG03)</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
+          <t>HKHKG -&gt; CNSHK</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v/>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNSHK ~2026-10-04T10:30:00</t>
+          <t>In transit, ETA 2026-10-04T13:30:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261003-2345-SKED.xlsx)</t>
+          <t>New ETA (auto-20261004-0543-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/Vessel Schedule.xlsx
+++ b/Vessel Schedule.xlsx
@@ -551,22 +551,20 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>TWKEL (KEL02)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
+          <t>TWKEL -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v/>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-10-04T18:00:00</t>
+          <t>In transit, ETA 2026-10-07T03:00:00</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -878,7 +876,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRINC ~2026-10-04T18:30:00</t>
+          <t>Alongside, departs to KRINC ~2026-10-06T18:00:00</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
@@ -981,22 +979,20 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>HKHKG (HKG03)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
+          <t>HKHKG -&gt; CNXMN</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v/>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to CNXMN ~2026-10-04T18:30:00</t>
+          <t>In transit, ETA 2026-10-05T15:00:00</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
@@ -1233,20 +1229,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>KRINC -&gt; KRPUS</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v/>
+          <t>KRPUS (PUS05)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2616S</t>
+        </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-04T17:00:00</t>
+          <t>Alongside, departs to VNSGN ~2026-10-05T14:00:00</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -1525,20 +1523,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>KRPTK -&gt; KRKAN</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v/>
+          <t>KRKAN (KAN04)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2612S</t>
+        </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-04T18:00:00</t>
+          <t>Alongside, departs to KRPUS ~2026-10-05T05:30:00</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
@@ -1668,11 +1668,11 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THLCH ~2026-10-04T14:00:00</t>
+          <t>Alongside, departs to THLCH ~2026-10-05T16:00:00</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46302.08333333334</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46301.375</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1719,22 +1719,20 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>KRKAN (KAN04)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2616S</t>
-        </is>
+          <t>KRKAN -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v/>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-10-04T18:00:00</t>
+          <t>In transit, ETA 2026-10-05T03:00:00</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
@@ -1785,22 +1783,20 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>THLCH (LCH05)</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2610S</t>
-        </is>
+          <t>THLCH -&gt; THBKK</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v/>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to THBKK ~2026-10-04T19:00:00</t>
+          <t>In transit, ETA 2026-10-04T21:00:00</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
@@ -1851,22 +1847,20 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>KRKAN (KAN06)</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2611S</t>
-        </is>
+          <t>KRKAN -&gt; KRUSN</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v/>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRUSN ~2026-10-04T16:00:00</t>
+          <t>In transit, ETA 2026-10-05T01:00:00</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
@@ -2227,22 +2221,20 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>docked</t>
+          <t>transit</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>CNXMN (XMN01)</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
+          <t>CNXMN -&gt; KRPUS</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v/>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Alongside, departs to KRPUS ~2026-10-04T18:30:00</t>
+          <t>In transit, ETA 2026-10-07T03:00:00</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
@@ -2293,20 +2285,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>transit</t>
+          <t>docked</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>HKHKG -&gt; CNSHK</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v/>
+          <t>HKHKG (HKG03)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>In transit, ETA 2026-10-04T13:30:00</t>
+          <t>Alongside, departs to CNSHK ~2026-10-05T05:00:00</t>
         </is>
       </c>
       <c r="I30" s="3" t="n"/>
@@ -2317,7 +2311,7 @@
         <v/>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46315.08333333334</v>
+        <v>46317.83333333334</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -10439,7 +10433,7 @@
         <v>46298.16666666666</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>46298.22916666666</v>
+        <v>46298.2375</v>
       </c>
       <c r="I196" s="3" t="n">
         <v>46299</v>
@@ -10477,13 +10471,13 @@
         </is>
       </c>
       <c r="G197" s="3" t="n">
-        <v>46299.22916666666</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>46299.27083333334</v>
+        <v>46301.25</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>46299.77083333334</v>
+        <v>46301.75</v>
       </c>
     </row>
     <row r="198">
@@ -10518,13 +10512,13 @@
         </is>
       </c>
       <c r="G198" s="3" t="n">
-        <v>46303.0625</v>
+        <v>46305.04166666666</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>46303.10416666666</v>
+        <v>46305.08333333334</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>46303.77083333334</v>
+        <v>46305.75</v>
       </c>
     </row>
     <row r="199">
@@ -10559,13 +10553,13 @@
         </is>
       </c>
       <c r="G199" s="3" t="n">
-        <v>46304.85416666666</v>
+        <v>46306.83333333334</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>46304.89583333334</v>
+        <v>46306.875</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>46305.47916666666</v>
+        <v>46307.45833333334</v>
       </c>
     </row>
     <row r="200">
@@ -29355,10 +29349,10 @@
         <v>46298.875</v>
       </c>
       <c r="H658" s="3" t="n">
-        <v>46299.04166666666</v>
+        <v>46300.41666666666</v>
       </c>
       <c r="I658" s="3" t="n">
-        <v>46299.58333333334</v>
+        <v>46300.66666666666</v>
       </c>
     </row>
     <row r="659">
@@ -29393,13 +29387,13 @@
         </is>
       </c>
       <c r="G659" s="3" t="n">
-        <v>46301.375</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="H659" s="3" t="n">
-        <v>46301.41666666666</v>
+        <v>46302.5</v>
       </c>
       <c r="I659" s="3" t="n">
-        <v>46301.66666666666</v>
+        <v>46302.75</v>
       </c>
     </row>
     <row r="660">
@@ -29434,13 +29428,13 @@
         </is>
       </c>
       <c r="G660" s="3" t="n">
-        <v>46302.08333333334</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="H660" s="3" t="n">
-        <v>46302.20833333334</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="I660" s="3" t="n">
-        <v>46303.33333333334</v>
+        <v>46304.41666666666</v>
       </c>
     </row>
     <row r="661">
@@ -29475,13 +29469,13 @@
         </is>
       </c>
       <c r="G661" s="3" t="n">
-        <v>46303.66666666666</v>
+        <v>46304.75</v>
       </c>
       <c r="H661" s="3" t="n">
-        <v>46303.70833333334</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="I661" s="3" t="n">
-        <v>46304.04166666666</v>
+        <v>46305.125</v>
       </c>
     </row>
     <row r="662">
@@ -29516,13 +29510,13 @@
         </is>
       </c>
       <c r="G662" s="3" t="n">
-        <v>46307.91666666666</v>
+        <v>46309</v>
       </c>
       <c r="H662" s="3" t="n">
-        <v>46307.95833333334</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="I662" s="3" t="n">
-        <v>46308.375</v>
+        <v>46309.45833333334</v>
       </c>
     </row>
     <row r="663">
@@ -29557,13 +29551,13 @@
         </is>
       </c>
       <c r="G663" s="3" t="n">
-        <v>46308.625</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="H663" s="3" t="n">
-        <v>46308.625</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="I663" s="3" t="n">
-        <v>46309</v>
+        <v>46310.08333333334</v>
       </c>
     </row>
     <row r="664">
@@ -29598,13 +29592,13 @@
         </is>
       </c>
       <c r="G664" s="3" t="n">
-        <v>46310.33333333334</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="H664" s="3" t="n">
-        <v>46310.33333333334</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="I664" s="3" t="n">
-        <v>46310.58333333334</v>
+        <v>46311.66666666666</v>
       </c>
     </row>
     <row r="665">
@@ -29639,13 +29633,13 @@
         </is>
       </c>
       <c r="G665" s="3" t="n">
-        <v>46312.41666666666</v>
+        <v>46313.66666666666</v>
       </c>
       <c r="H665" s="3" t="n">
-        <v>46312.45833333334</v>
+        <v>46313.70833333334</v>
       </c>
       <c r="I665" s="3" t="n">
-        <v>46313.16666666666</v>
+        <v>46314.41666666666</v>
       </c>
     </row>
     <row r="666">
@@ -29680,13 +29674,13 @@
         </is>
       </c>
       <c r="G666" s="3" t="n">
-        <v>46313.375</v>
+        <v>46314.625</v>
       </c>
       <c r="H666" s="3" t="n">
-        <v>46313.41666666666</v>
+        <v>46314.66666666666</v>
       </c>
       <c r="I666" s="3" t="n">
-        <v>46313.75</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="667">
@@ -29721,13 +29715,13 @@
         </is>
       </c>
       <c r="G667" s="3" t="n">
-        <v>46317</v>
+        <v>46318.25</v>
       </c>
       <c r="H667" s="3" t="n">
-        <v>46317.04166666666</v>
+        <v>46318.29166666666</v>
       </c>
       <c r="I667" s="3" t="n">
-        <v>46317.41666666666</v>
+        <v>46318.66666666666</v>
       </c>
     </row>
     <row r="668">
@@ -29762,13 +29756,13 @@
         </is>
       </c>
       <c r="G668" s="3" t="n">
-        <v>46319.875</v>
+        <v>46321.125</v>
       </c>
       <c r="H668" s="3" t="n">
-        <v>46320.04166666666</v>
+        <v>46321.29166666666</v>
       </c>
       <c r="I668" s="3" t="n">
-        <v>46320.58333333334</v>
+        <v>46321.83333333334</v>
       </c>
     </row>
     <row r="669">
@@ -29803,13 +29797,13 @@
         </is>
       </c>
       <c r="G669" s="3" t="n">
-        <v>46322.375</v>
+        <v>46323.625</v>
       </c>
       <c r="H669" s="3" t="n">
-        <v>46322.41666666666</v>
+        <v>46323.66666666666</v>
       </c>
       <c r="I669" s="3" t="n">
-        <v>46322.66666666666</v>
+        <v>46323.91666666666</v>
       </c>
     </row>
     <row r="670">
@@ -29844,13 +29838,13 @@
         </is>
       </c>
       <c r="G670" s="3" t="n">
-        <v>46323.08333333334</v>
+        <v>46324.33333333334</v>
       </c>
       <c r="H670" s="3" t="n">
-        <v>46323.20833333334</v>
+        <v>46324.45833333334</v>
       </c>
       <c r="I670" s="3" t="n">
-        <v>46324.33333333334</v>
+        <v>46325.58333333334</v>
       </c>
     </row>
     <row r="671">
@@ -29885,13 +29879,13 @@
         </is>
       </c>
       <c r="G671" s="3" t="n">
-        <v>46324.66666666666</v>
+        <v>46325.91666666666</v>
       </c>
       <c r="H671" s="3" t="n">
-        <v>46324.70833333334</v>
+        <v>46325.95833333334</v>
       </c>
       <c r="I671" s="3" t="n">
-        <v>46325.04166666666</v>
+        <v>46326.29166666666</v>
       </c>
     </row>
     <row r="672">
@@ -29926,13 +29920,13 @@
         </is>
       </c>
       <c r="G672" s="3" t="n">
-        <v>46328.91666666666</v>
+        <v>46330.16666666666</v>
       </c>
       <c r="H672" s="3" t="n">
-        <v>46328.95833333334</v>
+        <v>46330.20833333334</v>
       </c>
       <c r="I672" s="3" t="n">
-        <v>46329.375</v>
+        <v>46330.625</v>
       </c>
     </row>
     <row r="673">
@@ -29967,13 +29961,13 @@
         </is>
       </c>
       <c r="G673" s="3" t="n">
-        <v>46329.625</v>
+        <v>46330.875</v>
       </c>
       <c r="H673" s="3" t="n">
-        <v>46329.625</v>
+        <v>46330.875</v>
       </c>
       <c r="I673" s="3" t="n">
-        <v>46330</v>
+        <v>46331.25</v>
       </c>
     </row>
     <row r="674">
@@ -30008,13 +30002,13 @@
         </is>
       </c>
       <c r="G674" s="3" t="n">
-        <v>46331.25</v>
+        <v>46332.5</v>
       </c>
       <c r="H674" s="3" t="n">
-        <v>46331.25</v>
+        <v>46332.5</v>
       </c>
       <c r="I674" s="3" t="n">
-        <v>46331.5</v>
+        <v>46332.75</v>
       </c>
     </row>
     <row r="675">
@@ -30049,13 +30043,13 @@
         </is>
       </c>
       <c r="G675" s="3" t="n">
-        <v>46334.04097222222</v>
+        <v>46335.29097222222</v>
       </c>
       <c r="H675" s="3" t="n">
-        <v>46334.08263888889</v>
+        <v>46335.33263888889</v>
       </c>
       <c r="I675" s="3" t="n">
-        <v>46334.79097222222</v>
+        <v>46336.04097222222</v>
       </c>
     </row>
     <row r="676">
@@ -30090,13 +30084,13 @@
         </is>
       </c>
       <c r="G676" s="3" t="n">
-        <v>46334.99930555555</v>
+        <v>46336.24930555555</v>
       </c>
       <c r="H676" s="3" t="n">
-        <v>46335.04097222222</v>
+        <v>46336.29097222222</v>
       </c>
       <c r="I676" s="3" t="n">
-        <v>46335.37430555555</v>
+        <v>46336.62430555555</v>
       </c>
     </row>
     <row r="677">
@@ -30131,13 +30125,13 @@
         </is>
       </c>
       <c r="G677" s="3" t="n">
-        <v>46338.20763888889</v>
+        <v>46339.45763888889</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>46338.24930555555</v>
+        <v>46339.49930555555</v>
       </c>
       <c r="I677" s="3" t="n">
-        <v>46338.62430555555</v>
+        <v>46339.87430555555</v>
       </c>
     </row>
     <row r="678">
@@ -30172,13 +30166,13 @@
         </is>
       </c>
       <c r="G678" s="3" t="n">
-        <v>46341.08263888889</v>
+        <v>46342.33263888889</v>
       </c>
       <c r="H678" s="3" t="n">
-        <v>46341.24930555555</v>
+        <v>46342.49930555555</v>
       </c>
       <c r="I678" s="3" t="n">
-        <v>46341.79097222222</v>
+        <v>46343.04097222222</v>
       </c>
     </row>
     <row r="679">
@@ -30213,13 +30207,13 @@
         </is>
       </c>
       <c r="G679" s="3" t="n">
-        <v>46343.58263888889</v>
+        <v>46344.83263888889</v>
       </c>
       <c r="H679" s="3" t="n">
-        <v>46343.62430555555</v>
+        <v>46344.87430555555</v>
       </c>
       <c r="I679" s="3" t="n">
-        <v>46343.87430555555</v>
+        <v>46345.12430555555</v>
       </c>
     </row>
     <row r="680">
@@ -30254,13 +30248,13 @@
         </is>
       </c>
       <c r="G680" s="3" t="n">
-        <v>46344.29097222222</v>
+        <v>46345.54097222222</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>46344.41597222222</v>
+        <v>46345.66597222222</v>
       </c>
       <c r="I680" s="3" t="n">
-        <v>46345.54097222222</v>
+        <v>46346.79097222222</v>
       </c>
     </row>
     <row r="681">
@@ -30295,13 +30289,13 @@
         </is>
       </c>
       <c r="G681" s="3" t="n">
-        <v>46345.87430555555</v>
+        <v>46347.12430555555</v>
       </c>
       <c r="H681" s="3" t="n">
-        <v>46345.91597222222</v>
+        <v>46347.16597222222</v>
       </c>
       <c r="I681" s="3" t="n">
-        <v>46346.24930555555</v>
+        <v>46347.49930555555</v>
       </c>
     </row>
     <row r="682">
@@ -30336,13 +30330,13 @@
         </is>
       </c>
       <c r="G682" s="3" t="n">
-        <v>46350.12430555555</v>
+        <v>46351.37430555555</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>46350.16597222222</v>
+        <v>46351.41597222222</v>
       </c>
       <c r="I682" s="3" t="n">
-        <v>46350.58263888889</v>
+        <v>46351.83263888889</v>
       </c>
     </row>
     <row r="683">
@@ -30377,13 +30371,13 @@
         </is>
       </c>
       <c r="G683" s="3" t="n">
-        <v>46350.83263888889</v>
+        <v>46352.08263888889</v>
       </c>
       <c r="H683" s="3" t="n">
-        <v>46350.83263888889</v>
+        <v>46352.08263888889</v>
       </c>
       <c r="I683" s="3" t="n">
-        <v>46351.20763888889</v>
+        <v>46352.45763888889</v>
       </c>
     </row>
     <row r="684">
@@ -30418,13 +30412,13 @@
         </is>
       </c>
       <c r="G684" s="3" t="n">
-        <v>46352.45763888889</v>
+        <v>46353.70763888889</v>
       </c>
       <c r="H684" s="3" t="n">
-        <v>46352.45763888889</v>
+        <v>46353.70763888889</v>
       </c>
       <c r="I684" s="3" t="n">
-        <v>46352.70763888889</v>
+        <v>46353.95763888889</v>
       </c>
     </row>
     <row r="685">
@@ -30459,13 +30453,13 @@
         </is>
       </c>
       <c r="G685" s="3" t="n">
-        <v>46355.04097222222</v>
+        <v>46356.29097222222</v>
       </c>
       <c r="H685" s="3" t="n">
-        <v>46355.08263888889</v>
+        <v>46356.33263888889</v>
       </c>
       <c r="I685" s="3" t="n">
-        <v>46355.79097222222</v>
+        <v>46357.04097222222</v>
       </c>
     </row>
     <row r="686">
@@ -30500,13 +30494,13 @@
         </is>
       </c>
       <c r="G686" s="3" t="n">
-        <v>46355.99930555555</v>
+        <v>46357.24930555555</v>
       </c>
       <c r="H686" s="3" t="n">
-        <v>46356.04097222222</v>
+        <v>46357.29097222222</v>
       </c>
       <c r="I686" s="3" t="n">
-        <v>46356.37430555555</v>
+        <v>46357.62430555555</v>
       </c>
     </row>
     <row r="687">
@@ -30541,13 +30535,13 @@
         </is>
       </c>
       <c r="G687" s="3" t="n">
-        <v>46359.20763888889</v>
+        <v>46360.45763888889</v>
       </c>
       <c r="H687" s="3" t="n">
-        <v>46359.24930555555</v>
+        <v>46360.49930555555</v>
       </c>
       <c r="I687" s="3" t="n">
-        <v>46359.62430555555</v>
+        <v>46360.87430555555</v>
       </c>
     </row>
     <row r="688">
@@ -30582,13 +30576,13 @@
         </is>
       </c>
       <c r="G688" s="3" t="n">
-        <v>46362.08263888889</v>
+        <v>46363.33263888889</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>46362.24930555555</v>
+        <v>46363.49930555555</v>
       </c>
       <c r="I688" s="3" t="n">
-        <v>46362.79097222222</v>
+        <v>46364.04097222222</v>
       </c>
     </row>
     <row r="689">
@@ -30623,13 +30617,13 @@
         </is>
       </c>
       <c r="G689" s="3" t="n">
-        <v>46364.58263888889</v>
+        <v>46365.83263888889</v>
       </c>
       <c r="H689" s="3" t="n">
-        <v>46364.62430555555</v>
+        <v>46365.87430555555</v>
       </c>
       <c r="I689" s="3" t="n">
-        <v>46364.87430555555</v>
+        <v>46366.12430555555</v>
       </c>
     </row>
     <row r="690">
@@ -30664,13 +30658,13 @@
         </is>
       </c>
       <c r="G690" s="3" t="n">
-        <v>46365.29097222222</v>
+        <v>46366.54097222222</v>
       </c>
       <c r="H690" s="3" t="n">
-        <v>46365.41597222222</v>
+        <v>46366.66597222222</v>
       </c>
       <c r="I690" s="3" t="n">
-        <v>46366.54097222222</v>
+        <v>46367.79097222222</v>
       </c>
     </row>
     <row r="691">
@@ -30705,13 +30699,13 @@
         </is>
       </c>
       <c r="G691" s="3" t="n">
-        <v>46366.87430555555</v>
+        <v>46368.12430555555</v>
       </c>
       <c r="H691" s="3" t="n">
-        <v>46366.91597222222</v>
+        <v>46368.16597222222</v>
       </c>
       <c r="I691" s="3" t="n">
-        <v>46367.24930555555</v>
+        <v>46368.49930555555</v>
       </c>
     </row>
     <row r="692">
@@ -30746,13 +30740,13 @@
         </is>
       </c>
       <c r="G692" s="3" t="n">
-        <v>46371.12430555555</v>
+        <v>46372.37430555555</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>46371.16597222222</v>
+        <v>46372.41597222222</v>
       </c>
       <c r="I692" s="3" t="n">
-        <v>46371.58263888889</v>
+        <v>46372.83263888889</v>
       </c>
     </row>
     <row r="693">
@@ -30787,13 +30781,13 @@
         </is>
       </c>
       <c r="G693" s="3" t="n">
-        <v>46371.83263888889</v>
+        <v>46373.08263888889</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>46371.83263888889</v>
+        <v>46373.08263888889</v>
       </c>
       <c r="I693" s="3" t="n">
-        <v>46372.20763888889</v>
+        <v>46373.45763888889</v>
       </c>
     </row>
     <row r="694">
@@ -30828,13 +30822,13 @@
         </is>
       </c>
       <c r="G694" s="3" t="n">
-        <v>46373.45763888889</v>
+        <v>46374.70763888889</v>
       </c>
       <c r="H694" s="3" t="n">
-        <v>46373.45763888889</v>
+        <v>46374.70763888889</v>
       </c>
       <c r="I694" s="3" t="n">
-        <v>46373.70763888889</v>
+        <v>46374.95763888889</v>
       </c>
     </row>
     <row r="695">
@@ -30869,13 +30863,13 @@
         </is>
       </c>
       <c r="G695" s="3" t="n">
-        <v>46376.04097222222</v>
+        <v>46377.29097222222</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>46376.08263888889</v>
+        <v>46377.33263888889</v>
       </c>
       <c r="I695" s="3" t="n">
-        <v>46376.79097222222</v>
+        <v>46378.04097222222</v>
       </c>
     </row>
     <row r="696">
@@ -30910,13 +30904,13 @@
         </is>
       </c>
       <c r="G696" s="3" t="n">
-        <v>46376.99930555555</v>
+        <v>46378.24930555555</v>
       </c>
       <c r="H696" s="3" t="n">
-        <v>46377.04097222222</v>
+        <v>46378.29097222222</v>
       </c>
       <c r="I696" s="3" t="n">
-        <v>46377.37430555555</v>
+        <v>46378.62430555555</v>
       </c>
     </row>
     <row r="697">
@@ -30951,13 +30945,13 @@
         </is>
       </c>
       <c r="G697" s="3" t="n">
-        <v>46380.20763888889</v>
+        <v>46381.45763888889</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>46380.24930555555</v>
+        <v>46381.49930555555</v>
       </c>
       <c r="I697" s="3" t="n">
-        <v>46380.62430555555</v>
+        <v>46381.87430555555</v>
       </c>
     </row>
     <row r="698">
@@ -30992,13 +30986,13 @@
         </is>
       </c>
       <c r="G698" s="3" t="n">
-        <v>46383.08263888889</v>
+        <v>46384.33263888889</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>46383.24930555555</v>
+        <v>46384.49930555555</v>
       </c>
       <c r="I698" s="3" t="n">
-        <v>46383.79097222222</v>
+        <v>46385.04097222222</v>
       </c>
     </row>
     <row r="699">
@@ -31033,13 +31027,13 @@
         </is>
       </c>
       <c r="G699" s="3" t="n">
-        <v>46385.58263888889</v>
+        <v>46386.83263888889</v>
       </c>
       <c r="H699" s="3" t="n">
-        <v>46385.62430555555</v>
+        <v>46386.87430555555</v>
       </c>
       <c r="I699" s="3" t="n">
-        <v>46385.87430555555</v>
+        <v>46387.12430555555</v>
       </c>
     </row>
     <row r="700">
@@ -31074,13 +31068,13 @@
         </is>
       </c>
       <c r="G700" s="3" t="n">
-        <v>46386.29097222222</v>
+        <v>46387.54097222222</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>46386.41597222222</v>
+        <v>46387.66597222222</v>
       </c>
       <c r="I700" s="3" t="n">
-        <v>46387.54097222222</v>
+        <v>46388.79097222222</v>
       </c>
     </row>
     <row r="701">
@@ -31115,13 +31109,13 @@
         </is>
       </c>
       <c r="G701" s="3" t="n">
-        <v>46387.87430555555</v>
+        <v>46389.12430555555</v>
       </c>
       <c r="H701" s="3" t="n">
-        <v>46387.91597222222</v>
+        <v>46389.16597222222</v>
       </c>
       <c r="I701" s="3" t="n">
-        <v>46388.24930555555</v>
+        <v>46389.49930555555</v>
       </c>
     </row>
     <row r="702">
@@ -31156,13 +31150,13 @@
         </is>
       </c>
       <c r="G702" s="3" t="n">
-        <v>46392.12430555555</v>
+        <v>46393.37430555555</v>
       </c>
       <c r="H702" s="3" t="n">
-        <v>46392.16597222222</v>
+        <v>46393.41597222222</v>
       </c>
       <c r="I702" s="3" t="n">
-        <v>46392.58263888889</v>
+        <v>46393.83263888889</v>
       </c>
     </row>
     <row r="703">
@@ -31197,13 +31191,13 @@
         </is>
       </c>
       <c r="G703" s="3" t="n">
-        <v>46392.83263888889</v>
+        <v>46394.08263888889</v>
       </c>
       <c r="H703" s="3" t="n">
-        <v>46392.83263888889</v>
+        <v>46394.08263888889</v>
       </c>
       <c r="I703" s="3" t="n">
-        <v>46393.20763888889</v>
+        <v>46394.45763888889</v>
       </c>
     </row>
     <row r="704">
@@ -31236,13 +31230,13 @@
         <v/>
       </c>
       <c r="G704" s="3" t="n">
-        <v>46394.45763888889</v>
+        <v>46395.70763888889</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>46394.45763888889</v>
+        <v>46395.70763888889</v>
       </c>
       <c r="I704" s="3" t="n">
-        <v>46394.70763888889</v>
+        <v>46395.95763888889</v>
       </c>
     </row>
     <row r="705">
@@ -44915,10 +44909,10 @@
         <v>46298.875</v>
       </c>
       <c r="H1038" s="3" t="n">
-        <v>46298.9375</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="I1038" s="3" t="n">
-        <v>46299.4375</v>
+        <v>46300.20833333334</v>
       </c>
     </row>
     <row r="1039">
@@ -44953,13 +44947,13 @@
         </is>
       </c>
       <c r="G1039" s="3" t="n">
-        <v>46299.5625</v>
+        <v>46300.33333333334</v>
       </c>
       <c r="H1039" s="3" t="n">
-        <v>46299.6875</v>
+        <v>46302.45833333334</v>
       </c>
       <c r="I1039" s="3" t="n">
-        <v>46300.14583333334</v>
+        <v>46302.91666666666</v>
       </c>
     </row>
     <row r="1040">
@@ -44994,13 +44988,13 @@
         </is>
       </c>
       <c r="G1040" s="3" t="n">
-        <v>46303.25</v>
+        <v>46306</v>
       </c>
       <c r="H1040" s="3" t="n">
-        <v>46303.29166666666</v>
+        <v>46306.04166666666</v>
       </c>
       <c r="I1040" s="3" t="n">
-        <v>46303.95833333334</v>
+        <v>46306.70833333334</v>
       </c>
     </row>
     <row r="1041">
@@ -45035,13 +45029,13 @@
         </is>
       </c>
       <c r="G1041" s="3" t="n">
-        <v>46305.04166666666</v>
+        <v>46307.79166666666</v>
       </c>
       <c r="H1041" s="3" t="n">
-        <v>46305.08333333334</v>
+        <v>46307.83333333334</v>
       </c>
       <c r="I1041" s="3" t="n">
-        <v>46305.66666666666</v>
+        <v>46308.41666666666</v>
       </c>
     </row>
     <row r="1042">
@@ -45076,13 +45070,13 @@
         </is>
       </c>
       <c r="G1042" s="3" t="n">
-        <v>46305.875</v>
+        <v>46308.625</v>
       </c>
       <c r="H1042" s="3" t="n">
-        <v>46305.91666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="I1042" s="3" t="n">
-        <v>46306.25</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="1043">
@@ -45117,13 +45111,13 @@
         </is>
       </c>
       <c r="G1043" s="3" t="n">
-        <v>46307.54166666666</v>
+        <v>46310.29166666666</v>
       </c>
       <c r="H1043" s="3" t="n">
-        <v>46307.70833333334</v>
+        <v>46310.45833333334</v>
       </c>
       <c r="I1043" s="3" t="n">
-        <v>46308.20833333334</v>
+        <v>46310.95833333334</v>
       </c>
     </row>
     <row r="1044">
@@ -45158,13 +45152,13 @@
         </is>
       </c>
       <c r="G1044" s="3" t="n">
-        <v>46312.375</v>
+        <v>46315.125</v>
       </c>
       <c r="H1044" s="3" t="n">
-        <v>46312.54166666666</v>
+        <v>46315.29166666666</v>
       </c>
       <c r="I1044" s="3" t="n">
-        <v>46313.375</v>
+        <v>46316.125</v>
       </c>
     </row>
     <row r="1045">
@@ -45199,13 +45193,13 @@
         </is>
       </c>
       <c r="G1045" s="3" t="n">
-        <v>46315.08333333334</v>
+        <v>46317.83333333334</v>
       </c>
       <c r="H1045" s="3" t="n">
-        <v>46315.125</v>
+        <v>46317.875</v>
       </c>
       <c r="I1045" s="3" t="n">
-        <v>46315.95833333334</v>
+        <v>46318.70833333334</v>
       </c>
     </row>
     <row r="1046">
@@ -45240,13 +45234,13 @@
         </is>
       </c>
       <c r="G1046" s="3" t="n">
-        <v>46319.125</v>
+        <v>46321.875</v>
       </c>
       <c r="H1046" s="3" t="n">
-        <v>46319.16666666666</v>
+        <v>46321.91666666666</v>
       </c>
       <c r="I1046" s="3" t="n">
-        <v>46320.85416666666</v>
+        <v>46323.60416666666</v>
       </c>
     </row>
     <row r="1047">
@@ -45281,13 +45275,13 @@
         </is>
       </c>
       <c r="G1047" s="3" t="n">
-        <v>46322.97916666666</v>
+        <v>46325.72916666666</v>
       </c>
       <c r="H1047" s="3" t="n">
-        <v>46323.14583333334</v>
+        <v>46325.89583333334</v>
       </c>
       <c r="I1047" s="3" t="n">
-        <v>46323.97916666666</v>
+        <v>46326.72916666666</v>
       </c>
     </row>
     <row r="1048">
@@ -45322,13 +45316,13 @@
         </is>
       </c>
       <c r="G1048" s="3" t="n">
-        <v>46326.5</v>
+        <v>46329.25</v>
       </c>
       <c r="H1048" s="3" t="n">
-        <v>46326.5625</v>
+        <v>46329.3125</v>
       </c>
       <c r="I1048" s="3" t="n">
-        <v>46327.0625</v>
+        <v>46329.8125</v>
       </c>
     </row>
     <row r="1049">
@@ -45363,13 +45357,13 @@
         </is>
       </c>
       <c r="G1049" s="3" t="n">
-        <v>46327.29166666666</v>
+        <v>46330.04166666666</v>
       </c>
       <c r="H1049" s="3" t="n">
-        <v>46327.33333333334</v>
+        <v>46330.08333333334</v>
       </c>
       <c r="I1049" s="3" t="n">
-        <v>46327.83333333334</v>
+        <v>46330.58333333334</v>
       </c>
     </row>
     <row r="1050">
@@ -45404,13 +45398,13 @@
         </is>
       </c>
       <c r="G1050" s="3" t="n">
-        <v>46331.02083333334</v>
+        <v>46333.77083333334</v>
       </c>
       <c r="H1050" s="3" t="n">
-        <v>46331.0625</v>
+        <v>46333.8125</v>
       </c>
       <c r="I1050" s="3" t="n">
-        <v>46331.72916666666</v>
+        <v>46334.47916666666</v>
       </c>
     </row>
     <row r="1051">
@@ -45445,13 +45439,13 @@
         </is>
       </c>
       <c r="G1051" s="3" t="n">
-        <v>46332.8125</v>
+        <v>46335.5625</v>
       </c>
       <c r="H1051" s="3" t="n">
-        <v>46332.85416666666</v>
+        <v>46335.60416666666</v>
       </c>
       <c r="I1051" s="3" t="n">
-        <v>46333.4375</v>
+        <v>46336.1875</v>
       </c>
     </row>
     <row r="1052">
@@ -45486,13 +45480,13 @@
         </is>
       </c>
       <c r="G1052" s="3" t="n">
-        <v>46333.625</v>
+        <v>46336.375</v>
       </c>
       <c r="H1052" s="3" t="n">
-        <v>46333.6875</v>
+        <v>46336.4375</v>
       </c>
       <c r="I1052" s="3" t="n">
-        <v>46334.02083333334</v>
+        <v>46336.77083333334</v>
       </c>
     </row>
     <row r="1053">
@@ -45527,13 +45521,13 @@
         </is>
       </c>
       <c r="G1053" s="3" t="n">
-        <v>46335.3125</v>
+        <v>46338.0625</v>
       </c>
       <c r="H1053" s="3" t="n">
-        <v>46335.47916666666</v>
+        <v>46338.22916666666</v>
       </c>
       <c r="I1053" s="3" t="n">
-        <v>46335.97916666666</v>
+        <v>46338.72916666666</v>
       </c>
     </row>
     <row r="1054">
@@ -45568,13 +45562,13 @@
         </is>
       </c>
       <c r="G1054" s="3" t="n">
-        <v>46340.14583333334</v>
+        <v>46342.89583333334</v>
       </c>
       <c r="H1054" s="3" t="n">
-        <v>46340.3125</v>
+        <v>46343.0625</v>
       </c>
       <c r="I1054" s="3" t="n">
-        <v>46341.14583333334</v>
+        <v>46343.89583333334</v>
       </c>
     </row>
     <row r="1055">
@@ -45609,13 +45603,13 @@
         </is>
       </c>
       <c r="G1055" s="3" t="n">
-        <v>46342.8125</v>
+        <v>46345.5625</v>
       </c>
       <c r="H1055" s="3" t="n">
-        <v>46342.85416666666</v>
+        <v>46345.60416666666</v>
       </c>
       <c r="I1055" s="3" t="n">
-        <v>46343.6875</v>
+        <v>46346.4375</v>
       </c>
     </row>
     <row r="1056">
@@ -45650,13 +45644,13 @@
         </is>
       </c>
       <c r="G1056" s="3" t="n">
-        <v>46346.85416666666</v>
+        <v>46349.60416666666</v>
       </c>
       <c r="H1056" s="3" t="n">
-        <v>46346.9375</v>
+        <v>46349.6875</v>
       </c>
       <c r="I1056" s="3" t="n">
-        <v>46348.60416666666</v>
+        <v>46351.35416666666</v>
       </c>
     </row>
     <row r="1057">
@@ -45691,13 +45685,13 @@
         </is>
       </c>
       <c r="G1057" s="3" t="n">
-        <v>46351.0625</v>
+        <v>46353.8125</v>
       </c>
       <c r="H1057" s="3" t="n">
-        <v>46351.22916666666</v>
+        <v>46353.97916666666</v>
       </c>
       <c r="I1057" s="3" t="n">
-        <v>46352.0625</v>
+        <v>46354.8125</v>
       </c>
     </row>
     <row r="1058">
@@ -45732,13 +45726,13 @@
         </is>
       </c>
       <c r="G1058" s="3" t="n">
-        <v>46354.60416666666</v>
+        <v>46357.35416666666</v>
       </c>
       <c r="H1058" s="3" t="n">
-        <v>46354.66666666666</v>
+        <v>46357.41666666666</v>
       </c>
       <c r="I1058" s="3" t="n">
-        <v>46355.16666666666</v>
+        <v>46357.91666666666</v>
       </c>
     </row>
     <row r="1059">
@@ -45773,13 +45767,13 @@
         </is>
       </c>
       <c r="G1059" s="3" t="n">
-        <v>46355.39583333334</v>
+        <v>46358.14583333334</v>
       </c>
       <c r="H1059" s="3" t="n">
-        <v>46355.4375</v>
+        <v>46358.1875</v>
       </c>
       <c r="I1059" s="3" t="n">
-        <v>46355.9375</v>
+        <v>46358.6875</v>
       </c>
     </row>
     <row r="1060">
@@ -45814,13 +45808,13 @@
         </is>
       </c>
       <c r="G1060" s="3" t="n">
-        <v>46359.02083333334</v>
+        <v>46361.77083333334</v>
       </c>
       <c r="H1060" s="3" t="n">
-        <v>46359.0625</v>
+        <v>46361.8125</v>
       </c>
       <c r="I1060" s="3" t="n">
-        <v>46359.72916666666</v>
+        <v>46362.47916666666</v>
       </c>
     </row>
     <row r="1061">
@@ -45855,13 +45849,13 @@
         </is>
       </c>
       <c r="G1061" s="3" t="n">
-        <v>46360.8125</v>
+        <v>46363.5625</v>
       </c>
       <c r="H1061" s="3" t="n">
-        <v>46360.85416666666</v>
+        <v>46363.60416666666</v>
       </c>
       <c r="I1061" s="3" t="n">
-        <v>46361.4375</v>
+        <v>46364.1875</v>
       </c>
     </row>
     <row r="1062">
@@ -45896,13 +45890,13 @@
         </is>
       </c>
       <c r="G1062" s="3" t="n">
-        <v>46361.625</v>
+        <v>46364.375</v>
       </c>
       <c r="H1062" s="3" t="n">
-        <v>46361.6875</v>
+        <v>46364.4375</v>
       </c>
       <c r="I1062" s="3" t="n">
-        <v>46362.02083333334</v>
+        <v>46364.77083333334</v>
       </c>
     </row>
     <row r="1063">
@@ -45937,13 +45931,13 @@
         </is>
       </c>
       <c r="G1063" s="3" t="n">
-        <v>46363.3125</v>
+        <v>46366.0625</v>
       </c>
       <c r="H1063" s="3" t="n">
-        <v>46363.47916666666</v>
+        <v>46366.22916666666</v>
       </c>
       <c r="I1063" s="3" t="n">
-        <v>46363.97916666666</v>
+        <v>46366.72916666666</v>
       </c>
     </row>
     <row r="1064">
@@ -45978,13 +45972,13 @@
         </is>
       </c>
       <c r="G1064" s="3" t="n">
-        <v>46368.14583333334</v>
+        <v>46370.89583333334</v>
       </c>
       <c r="H1064" s="3" t="n">
-        <v>46368.3125</v>
+        <v>46371.0625</v>
       </c>
       <c r="I1064" s="3" t="n">
-        <v>46369.14583333334</v>
+        <v>46371.89583333334</v>
       </c>
     </row>
     <row r="1065">
@@ -46019,13 +46013,13 @@
         </is>
       </c>
       <c r="G1065" s="3" t="n">
-        <v>46370.8125</v>
+        <v>46373.5625</v>
       </c>
       <c r="H1065" s="3" t="n">
-        <v>46370.85416666666</v>
+        <v>46373.60416666666</v>
       </c>
       <c r="I1065" s="3" t="n">
-        <v>46371.6875</v>
+        <v>46374.4375</v>
       </c>
     </row>
     <row r="1066">
@@ -46060,13 +46054,13 @@
         </is>
       </c>
       <c r="G1066" s="3" t="n">
-        <v>46374.85416666666</v>
+        <v>46377.60416666666</v>
       </c>
       <c r="H1066" s="3" t="n">
-        <v>46374.9375</v>
+        <v>46377.6875</v>
       </c>
       <c r="I1066" s="3" t="n">
-        <v>46376.60416666666</v>
+        <v>46379.35416666666</v>
       </c>
     </row>
     <row r="1067">
@@ -46101,13 +46095,13 @@
         </is>
       </c>
       <c r="G1067" s="3" t="n">
-        <v>46379.0625</v>
+        <v>46381.8125</v>
       </c>
       <c r="H1067" s="3" t="n">
-        <v>46379.22916666666</v>
+        <v>46381.97916666666</v>
       </c>
       <c r="I1067" s="3" t="n">
-        <v>46380.0625</v>
+        <v>46382.8125</v>
       </c>
     </row>
     <row r="1068">
@@ -46142,13 +46136,13 @@
         </is>
       </c>
       <c r="G1068" s="3" t="n">
-        <v>46382.60416666666</v>
+        <v>46385.35416666666</v>
       </c>
       <c r="H1068" s="3" t="n">
-        <v>46382.66666666666</v>
+        <v>46385.41666666666</v>
       </c>
       <c r="I1068" s="3" t="n">
-        <v>46383.16666666666</v>
+        <v>46385.91666666666</v>
       </c>
     </row>
     <row r="1069">
@@ -46181,13 +46175,13 @@
         <v/>
       </c>
       <c r="G1069" s="3" t="n">
-        <v>46383.39583333334</v>
+        <v>46386.14583333334</v>
       </c>
       <c r="H1069" s="3" t="n">
-        <v>46383.4375</v>
+        <v>46386.1875</v>
       </c>
       <c r="I1069" s="3" t="n">
-        <v>46383.9375</v>
+        <v>46386.6875</v>
       </c>
     </row>
     <row r="1070">
@@ -47839,14 +47833,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -47880,7 +47874,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>New ETA (auto-20261004-0543-SKED.xlsx)</t>
+          <t>New ETA (auto-20261004-1215-SKED.xlsx)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -47891,6 +47885,2882 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46299.22916666666</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>KRINC</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>46303.0625</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46305.04166666666</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>INCHEON VOYAGER</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2607N</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46304.85416666666</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46306.83333333334</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2610S</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46301.375</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>THBKK</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46303.16666666666</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>46303.66666666666</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46304.75</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>46307.91666666666</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>46308.625</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>46309.70833333334</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SAWASDEE ATLANTIC</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inli